--- a/outputs/transaction_anchor_comparison.xlsx
+++ b/outputs/transaction_anchor_comparison.xlsx
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L14"/>
+  <dimension ref="A1:L15"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="8" customWidth="1" min="1" max="1"/>
@@ -517,10 +517,10 @@
         <v>0</v>
       </c>
       <c r="F2" t="n">
-        <v>20.8</v>
+        <v>35.3</v>
       </c>
       <c r="G2" t="n">
-        <v>20.8</v>
+        <v>35.3</v>
       </c>
       <c r="H2" t="n">
         <v>0</v>
@@ -536,10 +536,10 @@
         </is>
       </c>
       <c r="K2" t="n">
-        <v>26.45</v>
+        <v>29.63</v>
       </c>
       <c r="L2" t="n">
-        <v>26.45</v>
+        <v>29.63</v>
       </c>
     </row>
     <row r="3">
@@ -557,19 +557,19 @@
         <v>88.56</v>
       </c>
       <c r="D3" t="n">
-        <v>85.29000000000001</v>
+        <v>80.78</v>
       </c>
       <c r="E3" t="n">
-        <v>-3.69</v>
+        <v>-8.779999999999999</v>
       </c>
       <c r="F3" t="n">
-        <v>12.2</v>
+        <v>42.7</v>
       </c>
       <c r="G3" t="n">
-        <v>8.1</v>
+        <v>30.9</v>
       </c>
       <c r="H3" t="n">
-        <v>-4.1</v>
+        <v>-11.8</v>
       </c>
       <c r="I3" t="inlineStr">
         <is>
@@ -582,16 +582,16 @@
         </is>
       </c>
       <c r="K3" t="n">
-        <v>49.37</v>
+        <v>62.79</v>
       </c>
       <c r="L3" t="n">
-        <v>47.58</v>
+        <v>57.61</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>ASC</t>
+          <t>TNK</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -600,26 +600,26 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>15.96</v>
+        <v>83.31999999999999</v>
       </c>
       <c r="D4" t="n">
-        <v>17.32</v>
+        <v>77.48999999999999</v>
       </c>
       <c r="E4" t="n">
-        <v>8.539999999999999</v>
+        <v>-6.99</v>
       </c>
       <c r="F4" t="n">
-        <v>-9.4</v>
+        <v>11.4</v>
       </c>
       <c r="G4" t="n">
-        <v>-1.9</v>
+        <v>4.1</v>
       </c>
       <c r="H4" t="n">
-        <v>7.4</v>
+        <v>-7.3</v>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>TRIM/SHORT (overvalued)</t>
+          <t>BUY (undervalued)</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
@@ -628,16 +628,16 @@
         </is>
       </c>
       <c r="K4" t="n">
-        <v>14.5</v>
+        <v>78.90000000000001</v>
       </c>
       <c r="L4" t="n">
-        <v>15.69</v>
+        <v>73.73999999999999</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>STNG</t>
+          <t>FLNG</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -646,22 +646,22 @@
         </is>
       </c>
       <c r="C5" t="n">
-        <v>83.87</v>
+        <v>28.45</v>
       </c>
       <c r="D5" t="n">
-        <v>83.03</v>
+        <v>28.45</v>
       </c>
       <c r="E5" t="n">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="F5" t="n">
-        <v>-2.9</v>
+        <v>0.1</v>
       </c>
       <c r="G5" t="n">
-        <v>-3.9</v>
+        <v>0.1</v>
       </c>
       <c r="H5" t="n">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="I5" t="inlineStr">
         <is>
@@ -674,16 +674,16 @@
         </is>
       </c>
       <c r="K5" t="n">
-        <v>73.40000000000001</v>
+        <v>29.73</v>
       </c>
       <c r="L5" t="n">
-        <v>72.66</v>
+        <v>29.73</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>TNK</t>
+          <t>STNG</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -692,22 +692,22 @@
         </is>
       </c>
       <c r="C6" t="n">
-        <v>83.31999999999999</v>
+        <v>83.87</v>
       </c>
       <c r="D6" t="n">
-        <v>80.83</v>
+        <v>80.34999999999999</v>
       </c>
       <c r="E6" t="n">
-        <v>-2.99</v>
+        <v>-4.19</v>
       </c>
       <c r="F6" t="n">
-        <v>-2.1</v>
+        <v>1</v>
       </c>
       <c r="G6" t="n">
-        <v>-4.1</v>
+        <v>-3.3</v>
       </c>
       <c r="H6" t="n">
-        <v>-2</v>
+        <v>-4.3</v>
       </c>
       <c r="I6" t="inlineStr">
         <is>
@@ -720,16 +720,16 @@
         </is>
       </c>
       <c r="K6" t="n">
-        <v>69.31</v>
+        <v>76.37</v>
       </c>
       <c r="L6" t="n">
-        <v>67.90000000000001</v>
+        <v>73.13</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>FLNG</t>
+          <t>TRMD</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -738,26 +738,26 @@
         </is>
       </c>
       <c r="C7" t="n">
-        <v>28.45</v>
+        <v>26.74</v>
       </c>
       <c r="D7" t="n">
-        <v>28.45</v>
+        <v>25.43</v>
       </c>
       <c r="E7" t="n">
-        <v>0</v>
+        <v>-4.86</v>
       </c>
       <c r="F7" t="n">
-        <v>-5.6</v>
+        <v>-1.3</v>
       </c>
       <c r="G7" t="n">
-        <v>-5.6</v>
+        <v>-5.4</v>
       </c>
       <c r="H7" t="n">
-        <v>0</v>
+        <v>-4.1</v>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>TRIM/SHORT (overvalued)</t>
+          <t>HOLD (fairly valued)</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
@@ -766,16 +766,16 @@
         </is>
       </c>
       <c r="K7" t="n">
-        <v>28.04</v>
+        <v>27.83</v>
       </c>
       <c r="L7" t="n">
-        <v>28.04</v>
+        <v>26.68</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>TRMD</t>
+          <t>SBLK</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -784,22 +784,22 @@
         </is>
       </c>
       <c r="C8" t="n">
-        <v>26.74</v>
+        <v>25.98</v>
       </c>
       <c r="D8" t="n">
-        <v>27.45</v>
+        <v>26.19</v>
       </c>
       <c r="E8" t="n">
-        <v>2.68</v>
+        <v>0.8</v>
       </c>
       <c r="F8" t="n">
-        <v>-9.300000000000001</v>
+        <v>-6.3</v>
       </c>
       <c r="G8" t="n">
-        <v>-7</v>
+        <v>-5.7</v>
       </c>
       <c r="H8" t="n">
-        <v>2.3</v>
+        <v>0.5</v>
       </c>
       <c r="I8" t="inlineStr">
         <is>
@@ -812,16 +812,16 @@
         </is>
       </c>
       <c r="K8" t="n">
-        <v>25.59</v>
+        <v>25.49</v>
       </c>
       <c r="L8" t="n">
-        <v>26.24</v>
+        <v>25.64</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>DHT</t>
+          <t>ASC</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -830,22 +830,22 @@
         </is>
       </c>
       <c r="C9" t="n">
-        <v>15.29</v>
+        <v>15.96</v>
       </c>
       <c r="D9" t="n">
-        <v>13.53</v>
+        <v>15.93</v>
       </c>
       <c r="E9" t="n">
-        <v>-11.51</v>
+        <v>-0.16</v>
       </c>
       <c r="F9" t="n">
-        <v>-18.7</v>
+        <v>-5.8</v>
       </c>
       <c r="G9" t="n">
-        <v>-26.9</v>
+        <v>-5.9</v>
       </c>
       <c r="H9" t="n">
-        <v>-8.199999999999999</v>
+        <v>-0.1</v>
       </c>
       <c r="I9" t="inlineStr">
         <is>
@@ -858,16 +858,16 @@
         </is>
       </c>
       <c r="K9" t="n">
-        <v>13.34</v>
+        <v>15.07</v>
       </c>
       <c r="L9" t="n">
-        <v>12</v>
+        <v>15.05</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>HAFN</t>
+          <t>DHT</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -876,26 +876,26 @@
         </is>
       </c>
       <c r="C10" t="n">
-        <v>5.34</v>
+        <v>15.29</v>
       </c>
       <c r="D10" t="n">
-        <v>5.52</v>
+        <v>12.93</v>
       </c>
       <c r="E10" t="n">
-        <v>3.46</v>
+        <v>-15.41</v>
       </c>
       <c r="F10" t="n">
-        <v>-29.7</v>
+        <v>5.6</v>
       </c>
       <c r="G10" t="n">
-        <v>-27.5</v>
+        <v>-8.1</v>
       </c>
       <c r="H10" t="n">
-        <v>2.2</v>
+        <v>-13.7</v>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>TRIM/SHORT (overvalued)</t>
+          <t>BUY (undervalued)</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
@@ -904,44 +904,44 @@
         </is>
       </c>
       <c r="K10" t="n">
-        <v>5.41</v>
+        <v>17.32</v>
       </c>
       <c r="L10" t="n">
-        <v>5.58</v>
+        <v>15.08</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>INSW</t>
+          <t>FRO</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>WHOLE-COMPANY (hybrid aggregation)</t>
+          <t>whole-company</t>
         </is>
       </c>
       <c r="C11" t="n">
-        <v>57.91</v>
+        <v>28.79</v>
       </c>
       <c r="D11" t="n">
-        <v>56.74</v>
+        <v>24.39</v>
       </c>
       <c r="E11" t="n">
-        <v>-2.01</v>
+        <v>-15.27</v>
       </c>
       <c r="F11" t="n">
-        <v>-33.2</v>
+        <v>-2.1</v>
       </c>
       <c r="G11" t="n">
-        <v>-34.3</v>
+        <v>-14.9</v>
       </c>
       <c r="H11" t="n">
-        <v>-1</v>
+        <v>-12.8</v>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>TRIM/SHORT (overvalued)</t>
+          <t>HOLD (fairly valued)</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
@@ -950,16 +950,16 @@
         </is>
       </c>
       <c r="K11" t="n">
-        <v>52.08</v>
+        <v>33.77</v>
       </c>
       <c r="L11" t="n">
-        <v>51.28</v>
+        <v>29.36</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>FRO</t>
+          <t>ECO</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -968,26 +968,26 @@
         </is>
       </c>
       <c r="C12" t="n">
-        <v>28.79</v>
+        <v>39.93</v>
       </c>
       <c r="D12" t="n">
-        <v>26.21</v>
+        <v>33.7</v>
       </c>
       <c r="E12" t="n">
-        <v>-8.94</v>
+        <v>-15.61</v>
       </c>
       <c r="F12" t="n">
-        <v>-30.8</v>
+        <v>-4.8</v>
       </c>
       <c r="G12" t="n">
-        <v>-37</v>
+        <v>-17.6</v>
       </c>
       <c r="H12" t="n">
-        <v>-6.2</v>
+        <v>-12.8</v>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>TRIM/SHORT (overvalued)</t>
+          <t>HOLD (fairly valued)</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
@@ -996,40 +996,40 @@
         </is>
       </c>
       <c r="K12" t="n">
-        <v>23.87</v>
+        <v>45.41</v>
       </c>
       <c r="L12" t="n">
-        <v>21.74</v>
+        <v>39.32</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>ECO</t>
+          <t>INSW</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>whole-company</t>
+          <t>WHOLE-COMPANY (hybrid aggregation)</t>
         </is>
       </c>
       <c r="C13" t="n">
-        <v>39.93</v>
+        <v>57.91</v>
       </c>
       <c r="D13" t="n">
-        <v>36.5</v>
+        <v>52.43</v>
       </c>
       <c r="E13" t="n">
-        <v>-8.609999999999999</v>
+        <v>-9.470000000000001</v>
       </c>
       <c r="F13" t="n">
-        <v>-31.8</v>
+        <v>-17.2</v>
       </c>
       <c r="G13" t="n">
-        <v>-37.2</v>
+        <v>-23.7</v>
       </c>
       <c r="H13" t="n">
-        <v>-5.4</v>
+        <v>-6.5</v>
       </c>
       <c r="I13" t="inlineStr">
         <is>
@@ -1042,56 +1042,102 @@
         </is>
       </c>
       <c r="K13" t="n">
-        <v>32.53</v>
+        <v>64.59</v>
       </c>
       <c r="L13" t="n">
-        <v>29.96</v>
+        <v>59.5</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
+          <t>HAFN</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>whole-company</t>
+        </is>
+      </c>
+      <c r="C14" t="n">
+        <v>5.34</v>
+      </c>
+      <c r="D14" t="n">
+        <v>5.22</v>
+      </c>
+      <c r="E14" t="n">
+        <v>-2.24</v>
+      </c>
+      <c r="F14" t="n">
+        <v>-23.8</v>
+      </c>
+      <c r="G14" t="n">
+        <v>-25.1</v>
+      </c>
+      <c r="H14" t="n">
+        <v>-1.4</v>
+      </c>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>TRIM/SHORT (overvalued)</t>
+        </is>
+      </c>
+      <c r="J14" t="inlineStr">
+        <is>
+          <t>TRIM/SHORT (overvalued)</t>
+        </is>
+      </c>
+      <c r="K14" t="n">
+        <v>5.87</v>
+      </c>
+      <c r="L14" t="n">
+        <v>5.77</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
           <t>NAT</t>
         </is>
       </c>
-      <c r="B14" t="inlineStr">
-        <is>
-          <t>whole-company</t>
-        </is>
-      </c>
-      <c r="C14" t="n">
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>whole-company</t>
+        </is>
+      </c>
+      <c r="C15" t="n">
         <v>2.63</v>
       </c>
-      <c r="D14" t="n">
-        <v>2.64</v>
-      </c>
-      <c r="E14" t="n">
-        <v>0.17</v>
-      </c>
-      <c r="F14" t="n">
-        <v>-56.1</v>
-      </c>
-      <c r="G14" t="n">
-        <v>-56.1</v>
-      </c>
-      <c r="H14" t="n">
-        <v>0.1</v>
-      </c>
-      <c r="I14" t="inlineStr">
-        <is>
-          <t>TRIM/SHORT (overvalued)</t>
-        </is>
-      </c>
-      <c r="J14" t="inlineStr">
-        <is>
-          <t>TRIM/SHORT (overvalued)</t>
-        </is>
-      </c>
-      <c r="K14" t="n">
-        <v>2.28</v>
-      </c>
-      <c r="L14" t="n">
-        <v>2.28</v>
+      <c r="D15" t="n">
+        <v>2.08</v>
+      </c>
+      <c r="E15" t="n">
+        <v>-20.95</v>
+      </c>
+      <c r="F15" t="n">
+        <v>-35.2</v>
+      </c>
+      <c r="G15" t="n">
+        <v>-44.8</v>
+      </c>
+      <c r="H15" t="n">
+        <v>-9.699999999999999</v>
+      </c>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>TRIM/SHORT (overvalued)</t>
+        </is>
+      </c>
+      <c r="J15" t="inlineStr">
+        <is>
+          <t>TRIM/SHORT (overvalued)</t>
+        </is>
+      </c>
+      <c r="K15" t="n">
+        <v>3.37</v>
+      </c>
+      <c r="L15" t="n">
+        <v>2.87</v>
       </c>
     </row>
   </sheetData>

--- a/outputs/transaction_anchor_comparison.xlsx
+++ b/outputs/transaction_anchor_comparison.xlsx
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L15"/>
+  <dimension ref="A1:L16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="8" customWidth="1" min="1" max="1"/>
@@ -591,7 +591,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>TNK</t>
+          <t>GNK</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -600,44 +600,44 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>83.31999999999999</v>
+        <v>25.4</v>
       </c>
       <c r="D4" t="n">
-        <v>77.48999999999999</v>
+        <v>26.16</v>
       </c>
       <c r="E4" t="n">
-        <v>-6.99</v>
+        <v>2.98</v>
       </c>
       <c r="F4" t="n">
-        <v>11.4</v>
+        <v>4.3</v>
       </c>
       <c r="G4" t="n">
-        <v>4.1</v>
+        <v>6.9</v>
       </c>
       <c r="H4" t="n">
-        <v>-7.3</v>
+        <v>2.6</v>
       </c>
       <c r="I4" t="inlineStr">
         <is>
+          <t>HOLD (fairly valued)</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
           <t>BUY (undervalued)</t>
         </is>
       </c>
-      <c r="J4" t="inlineStr">
-        <is>
-          <t>HOLD (fairly valued)</t>
-        </is>
-      </c>
       <c r="K4" t="n">
-        <v>78.90000000000001</v>
+        <v>25.02</v>
       </c>
       <c r="L4" t="n">
-        <v>73.73999999999999</v>
+        <v>25.65</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>FLNG</t>
+          <t>TNK</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -646,44 +646,44 @@
         </is>
       </c>
       <c r="C5" t="n">
-        <v>28.45</v>
+        <v>83.31999999999999</v>
       </c>
       <c r="D5" t="n">
-        <v>28.45</v>
+        <v>77.48999999999999</v>
       </c>
       <c r="E5" t="n">
-        <v>0</v>
+        <v>-6.99</v>
       </c>
       <c r="F5" t="n">
-        <v>0.1</v>
+        <v>11.4</v>
       </c>
       <c r="G5" t="n">
-        <v>0.1</v>
+        <v>4.1</v>
       </c>
       <c r="H5" t="n">
-        <v>0</v>
+        <v>-7.3</v>
       </c>
       <c r="I5" t="inlineStr">
         <is>
+          <t>BUY (undervalued)</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
           <t>HOLD (fairly valued)</t>
         </is>
       </c>
-      <c r="J5" t="inlineStr">
-        <is>
-          <t>HOLD (fairly valued)</t>
-        </is>
-      </c>
       <c r="K5" t="n">
-        <v>29.73</v>
+        <v>78.90000000000001</v>
       </c>
       <c r="L5" t="n">
-        <v>29.73</v>
+        <v>73.73999999999999</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>STNG</t>
+          <t>FLNG</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -692,22 +692,22 @@
         </is>
       </c>
       <c r="C6" t="n">
-        <v>83.87</v>
+        <v>28.45</v>
       </c>
       <c r="D6" t="n">
-        <v>80.34999999999999</v>
+        <v>28.45</v>
       </c>
       <c r="E6" t="n">
-        <v>-4.19</v>
+        <v>0</v>
       </c>
       <c r="F6" t="n">
-        <v>1</v>
+        <v>0.1</v>
       </c>
       <c r="G6" t="n">
-        <v>-3.3</v>
+        <v>0.1</v>
       </c>
       <c r="H6" t="n">
-        <v>-4.3</v>
+        <v>0</v>
       </c>
       <c r="I6" t="inlineStr">
         <is>
@@ -720,16 +720,16 @@
         </is>
       </c>
       <c r="K6" t="n">
-        <v>76.37</v>
+        <v>29.73</v>
       </c>
       <c r="L6" t="n">
-        <v>73.13</v>
+        <v>29.73</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>TRMD</t>
+          <t>STNG</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -738,22 +738,22 @@
         </is>
       </c>
       <c r="C7" t="n">
-        <v>26.74</v>
+        <v>83.87</v>
       </c>
       <c r="D7" t="n">
-        <v>25.43</v>
+        <v>80.34999999999999</v>
       </c>
       <c r="E7" t="n">
-        <v>-4.86</v>
+        <v>-4.19</v>
       </c>
       <c r="F7" t="n">
-        <v>-1.3</v>
+        <v>1</v>
       </c>
       <c r="G7" t="n">
-        <v>-5.4</v>
+        <v>-3.3</v>
       </c>
       <c r="H7" t="n">
-        <v>-4.1</v>
+        <v>-4.3</v>
       </c>
       <c r="I7" t="inlineStr">
         <is>
@@ -762,20 +762,20 @@
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>TRIM/SHORT (overvalued)</t>
+          <t>HOLD (fairly valued)</t>
         </is>
       </c>
       <c r="K7" t="n">
-        <v>27.83</v>
+        <v>76.37</v>
       </c>
       <c r="L7" t="n">
-        <v>26.68</v>
+        <v>73.13</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>SBLK</t>
+          <t>TRMD</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -784,26 +784,26 @@
         </is>
       </c>
       <c r="C8" t="n">
-        <v>25.98</v>
+        <v>26.74</v>
       </c>
       <c r="D8" t="n">
-        <v>26.19</v>
+        <v>25.43</v>
       </c>
       <c r="E8" t="n">
-        <v>0.8</v>
+        <v>-4.86</v>
       </c>
       <c r="F8" t="n">
-        <v>-6.3</v>
+        <v>-1.3</v>
       </c>
       <c r="G8" t="n">
-        <v>-5.7</v>
+        <v>-5.4</v>
       </c>
       <c r="H8" t="n">
-        <v>0.5</v>
+        <v>-4.1</v>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>TRIM/SHORT (overvalued)</t>
+          <t>HOLD (fairly valued)</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
@@ -812,16 +812,16 @@
         </is>
       </c>
       <c r="K8" t="n">
-        <v>25.49</v>
+        <v>27.83</v>
       </c>
       <c r="L8" t="n">
-        <v>25.64</v>
+        <v>26.68</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>ASC</t>
+          <t>SBLK</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -830,22 +830,22 @@
         </is>
       </c>
       <c r="C9" t="n">
-        <v>15.96</v>
+        <v>25.98</v>
       </c>
       <c r="D9" t="n">
-        <v>15.93</v>
+        <v>26.17</v>
       </c>
       <c r="E9" t="n">
-        <v>-0.16</v>
+        <v>0.74</v>
       </c>
       <c r="F9" t="n">
-        <v>-5.8</v>
+        <v>-6.3</v>
       </c>
       <c r="G9" t="n">
-        <v>-5.9</v>
+        <v>-5.7</v>
       </c>
       <c r="H9" t="n">
-        <v>-0.1</v>
+        <v>0.5</v>
       </c>
       <c r="I9" t="inlineStr">
         <is>
@@ -858,16 +858,16 @@
         </is>
       </c>
       <c r="K9" t="n">
-        <v>15.07</v>
+        <v>25.49</v>
       </c>
       <c r="L9" t="n">
-        <v>15.05</v>
+        <v>25.64</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>DHT</t>
+          <t>ASC</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -876,26 +876,26 @@
         </is>
       </c>
       <c r="C10" t="n">
-        <v>15.29</v>
+        <v>15.96</v>
       </c>
       <c r="D10" t="n">
-        <v>12.93</v>
+        <v>15.93</v>
       </c>
       <c r="E10" t="n">
-        <v>-15.41</v>
+        <v>-0.16</v>
       </c>
       <c r="F10" t="n">
-        <v>5.6</v>
+        <v>-5.8</v>
       </c>
       <c r="G10" t="n">
-        <v>-8.1</v>
+        <v>-5.9</v>
       </c>
       <c r="H10" t="n">
-        <v>-13.7</v>
+        <v>-0.1</v>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>BUY (undervalued)</t>
+          <t>TRIM/SHORT (overvalued)</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
@@ -904,16 +904,16 @@
         </is>
       </c>
       <c r="K10" t="n">
-        <v>17.32</v>
+        <v>15.07</v>
       </c>
       <c r="L10" t="n">
-        <v>15.08</v>
+        <v>15.05</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>FRO</t>
+          <t>DHT</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -922,26 +922,26 @@
         </is>
       </c>
       <c r="C11" t="n">
-        <v>28.79</v>
+        <v>15.29</v>
       </c>
       <c r="D11" t="n">
-        <v>24.39</v>
+        <v>12.93</v>
       </c>
       <c r="E11" t="n">
-        <v>-15.27</v>
+        <v>-15.41</v>
       </c>
       <c r="F11" t="n">
-        <v>-2.1</v>
+        <v>5.6</v>
       </c>
       <c r="G11" t="n">
-        <v>-14.9</v>
+        <v>-8.1</v>
       </c>
       <c r="H11" t="n">
-        <v>-12.8</v>
+        <v>-13.7</v>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>HOLD (fairly valued)</t>
+          <t>BUY (undervalued)</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
@@ -950,16 +950,16 @@
         </is>
       </c>
       <c r="K11" t="n">
-        <v>33.77</v>
+        <v>17.32</v>
       </c>
       <c r="L11" t="n">
-        <v>29.36</v>
+        <v>15.08</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>ECO</t>
+          <t>FRO</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -968,19 +968,19 @@
         </is>
       </c>
       <c r="C12" t="n">
-        <v>39.93</v>
+        <v>28.79</v>
       </c>
       <c r="D12" t="n">
-        <v>33.7</v>
+        <v>24.39</v>
       </c>
       <c r="E12" t="n">
-        <v>-15.61</v>
+        <v>-15.27</v>
       </c>
       <c r="F12" t="n">
-        <v>-4.8</v>
+        <v>-2.1</v>
       </c>
       <c r="G12" t="n">
-        <v>-17.6</v>
+        <v>-14.9</v>
       </c>
       <c r="H12" t="n">
         <v>-12.8</v>
@@ -996,44 +996,44 @@
         </is>
       </c>
       <c r="K12" t="n">
-        <v>45.41</v>
+        <v>33.77</v>
       </c>
       <c r="L12" t="n">
-        <v>39.32</v>
+        <v>29.36</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>INSW</t>
+          <t>ECO</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>WHOLE-COMPANY (hybrid aggregation)</t>
+          <t>whole-company</t>
         </is>
       </c>
       <c r="C13" t="n">
-        <v>57.91</v>
+        <v>39.93</v>
       </c>
       <c r="D13" t="n">
-        <v>52.43</v>
+        <v>33.7</v>
       </c>
       <c r="E13" t="n">
-        <v>-9.470000000000001</v>
+        <v>-15.61</v>
       </c>
       <c r="F13" t="n">
-        <v>-17.2</v>
+        <v>-4.8</v>
       </c>
       <c r="G13" t="n">
-        <v>-23.7</v>
+        <v>-17.6</v>
       </c>
       <c r="H13" t="n">
-        <v>-6.5</v>
+        <v>-12.8</v>
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>TRIM/SHORT (overvalued)</t>
+          <t>HOLD (fairly valued)</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
@@ -1042,40 +1042,40 @@
         </is>
       </c>
       <c r="K13" t="n">
-        <v>64.59</v>
+        <v>45.41</v>
       </c>
       <c r="L13" t="n">
-        <v>59.5</v>
+        <v>39.32</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>HAFN</t>
+          <t>INSW</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>whole-company</t>
+          <t>WHOLE-COMPANY (hybrid aggregation)</t>
         </is>
       </c>
       <c r="C14" t="n">
-        <v>5.34</v>
+        <v>57.91</v>
       </c>
       <c r="D14" t="n">
-        <v>5.22</v>
+        <v>52.43</v>
       </c>
       <c r="E14" t="n">
-        <v>-2.24</v>
+        <v>-9.470000000000001</v>
       </c>
       <c r="F14" t="n">
-        <v>-23.8</v>
+        <v>-17.2</v>
       </c>
       <c r="G14" t="n">
-        <v>-25.1</v>
+        <v>-23.7</v>
       </c>
       <c r="H14" t="n">
-        <v>-1.4</v>
+        <v>-6.5</v>
       </c>
       <c r="I14" t="inlineStr">
         <is>
@@ -1088,55 +1088,101 @@
         </is>
       </c>
       <c r="K14" t="n">
-        <v>5.87</v>
+        <v>64.59</v>
       </c>
       <c r="L14" t="n">
-        <v>5.77</v>
+        <v>59.5</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
+          <t>HAFN</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>whole-company</t>
+        </is>
+      </c>
+      <c r="C15" t="n">
+        <v>5.34</v>
+      </c>
+      <c r="D15" t="n">
+        <v>5.22</v>
+      </c>
+      <c r="E15" t="n">
+        <v>-2.24</v>
+      </c>
+      <c r="F15" t="n">
+        <v>-23.8</v>
+      </c>
+      <c r="G15" t="n">
+        <v>-25.1</v>
+      </c>
+      <c r="H15" t="n">
+        <v>-1.4</v>
+      </c>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>TRIM/SHORT (overvalued)</t>
+        </is>
+      </c>
+      <c r="J15" t="inlineStr">
+        <is>
+          <t>TRIM/SHORT (overvalued)</t>
+        </is>
+      </c>
+      <c r="K15" t="n">
+        <v>5.87</v>
+      </c>
+      <c r="L15" t="n">
+        <v>5.77</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
           <t>NAT</t>
         </is>
       </c>
-      <c r="B15" t="inlineStr">
-        <is>
-          <t>whole-company</t>
-        </is>
-      </c>
-      <c r="C15" t="n">
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>whole-company</t>
+        </is>
+      </c>
+      <c r="C16" t="n">
         <v>2.63</v>
       </c>
-      <c r="D15" t="n">
+      <c r="D16" t="n">
         <v>2.08</v>
       </c>
-      <c r="E15" t="n">
+      <c r="E16" t="n">
         <v>-20.95</v>
       </c>
-      <c r="F15" t="n">
+      <c r="F16" t="n">
         <v>-35.2</v>
       </c>
-      <c r="G15" t="n">
+      <c r="G16" t="n">
         <v>-44.8</v>
       </c>
-      <c r="H15" t="n">
+      <c r="H16" t="n">
         <v>-9.699999999999999</v>
       </c>
-      <c r="I15" t="inlineStr">
-        <is>
-          <t>TRIM/SHORT (overvalued)</t>
-        </is>
-      </c>
-      <c r="J15" t="inlineStr">
-        <is>
-          <t>TRIM/SHORT (overvalued)</t>
-        </is>
-      </c>
-      <c r="K15" t="n">
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>TRIM/SHORT (overvalued)</t>
+        </is>
+      </c>
+      <c r="J16" t="inlineStr">
+        <is>
+          <t>TRIM/SHORT (overvalued)</t>
+        </is>
+      </c>
+      <c r="K16" t="n">
         <v>3.37</v>
       </c>
-      <c r="L15" t="n">
+      <c r="L16" t="n">
         <v>2.87</v>
       </c>
     </row>

--- a/outputs/transaction_anchor_comparison.xlsx
+++ b/outputs/transaction_anchor_comparison.xlsx
@@ -557,10 +557,10 @@
         <v>88.56</v>
       </c>
       <c r="D3" t="n">
-        <v>80.78</v>
+        <v>80.79000000000001</v>
       </c>
       <c r="E3" t="n">
-        <v>-8.779999999999999</v>
+        <v>-8.77</v>
       </c>
       <c r="F3" t="n">
         <v>42.7</v>
@@ -649,10 +649,10 @@
         <v>83.31999999999999</v>
       </c>
       <c r="D5" t="n">
-        <v>77.48999999999999</v>
+        <v>77.45</v>
       </c>
       <c r="E5" t="n">
-        <v>-6.99</v>
+        <v>-7.04</v>
       </c>
       <c r="F5" t="n">
         <v>11.4</v>
@@ -677,7 +677,7 @@
         <v>78.90000000000001</v>
       </c>
       <c r="L5" t="n">
-        <v>73.73999999999999</v>
+        <v>73.7</v>
       </c>
     </row>
     <row r="6">
@@ -971,10 +971,10 @@
         <v>28.79</v>
       </c>
       <c r="D12" t="n">
-        <v>24.39</v>
+        <v>24.4</v>
       </c>
       <c r="E12" t="n">
-        <v>-15.27</v>
+        <v>-15.25</v>
       </c>
       <c r="F12" t="n">
         <v>-2.1</v>
@@ -1017,19 +1017,19 @@
         <v>39.93</v>
       </c>
       <c r="D13" t="n">
-        <v>33.7</v>
+        <v>33.71</v>
       </c>
       <c r="E13" t="n">
-        <v>-15.61</v>
+        <v>-15.58</v>
       </c>
       <c r="F13" t="n">
         <v>-4.8</v>
       </c>
       <c r="G13" t="n">
-        <v>-17.6</v>
+        <v>-17.5</v>
       </c>
       <c r="H13" t="n">
-        <v>-12.8</v>
+        <v>-12.7</v>
       </c>
       <c r="I13" t="inlineStr">
         <is>
@@ -1045,7 +1045,7 @@
         <v>45.41</v>
       </c>
       <c r="L13" t="n">
-        <v>39.32</v>
+        <v>39.33</v>
       </c>
     </row>
     <row r="14">
@@ -1063,19 +1063,19 @@
         <v>57.91</v>
       </c>
       <c r="D14" t="n">
-        <v>52.43</v>
+        <v>52.4</v>
       </c>
       <c r="E14" t="n">
-        <v>-9.470000000000001</v>
+        <v>-9.51</v>
       </c>
       <c r="F14" t="n">
         <v>-17.2</v>
       </c>
       <c r="G14" t="n">
-        <v>-23.7</v>
+        <v>-23.8</v>
       </c>
       <c r="H14" t="n">
-        <v>-6.5</v>
+        <v>-6.6</v>
       </c>
       <c r="I14" t="inlineStr">
         <is>
@@ -1091,7 +1091,7 @@
         <v>64.59</v>
       </c>
       <c r="L14" t="n">
-        <v>59.5</v>
+        <v>59.47</v>
       </c>
     </row>
     <row r="15">
@@ -1155,19 +1155,19 @@
         <v>2.63</v>
       </c>
       <c r="D16" t="n">
-        <v>2.08</v>
+        <v>2.07</v>
       </c>
       <c r="E16" t="n">
-        <v>-20.95</v>
+        <v>-21.23</v>
       </c>
       <c r="F16" t="n">
         <v>-35.2</v>
       </c>
       <c r="G16" t="n">
-        <v>-44.8</v>
+        <v>-44.9</v>
       </c>
       <c r="H16" t="n">
-        <v>-9.699999999999999</v>
+        <v>-9.800000000000001</v>
       </c>
       <c r="I16" t="inlineStr">
         <is>
@@ -1183,7 +1183,7 @@
         <v>3.37</v>
       </c>
       <c r="L16" t="n">
-        <v>2.87</v>
+        <v>2.86</v>
       </c>
     </row>
   </sheetData>

--- a/outputs/transaction_anchor_comparison.xlsx
+++ b/outputs/transaction_anchor_comparison.xlsx
@@ -603,19 +603,19 @@
         <v>25.4</v>
       </c>
       <c r="D4" t="n">
-        <v>26.16</v>
+        <v>26.24</v>
       </c>
       <c r="E4" t="n">
-        <v>2.98</v>
+        <v>3.33</v>
       </c>
       <c r="F4" t="n">
         <v>4.3</v>
       </c>
       <c r="G4" t="n">
-        <v>6.9</v>
+        <v>7.2</v>
       </c>
       <c r="H4" t="n">
-        <v>2.6</v>
+        <v>3</v>
       </c>
       <c r="I4" t="inlineStr">
         <is>
@@ -631,7 +631,7 @@
         <v>25.02</v>
       </c>
       <c r="L4" t="n">
-        <v>25.65</v>
+        <v>25.73</v>
       </c>
     </row>
     <row r="5">
@@ -833,19 +833,19 @@
         <v>25.98</v>
       </c>
       <c r="D9" t="n">
-        <v>26.17</v>
+        <v>26.27</v>
       </c>
       <c r="E9" t="n">
-        <v>0.74</v>
+        <v>1.1</v>
       </c>
       <c r="F9" t="n">
         <v>-6.3</v>
       </c>
       <c r="G9" t="n">
-        <v>-5.7</v>
+        <v>-5.4</v>
       </c>
       <c r="H9" t="n">
-        <v>0.5</v>
+        <v>0.8</v>
       </c>
       <c r="I9" t="inlineStr">
         <is>
@@ -861,7 +861,7 @@
         <v>25.49</v>
       </c>
       <c r="L9" t="n">
-        <v>25.64</v>
+        <v>25.72</v>
       </c>
     </row>
     <row r="10">

--- a/outputs/transaction_anchor_comparison.xlsx
+++ b/outputs/transaction_anchor_comparison.xlsx
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L16"/>
+  <dimension ref="A1:L17"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="8" customWidth="1" min="1" max="1"/>
@@ -499,7 +499,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>CCEC</t>
+          <t>CMDB</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -508,22 +508,22 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>28.1</v>
+        <v>32.62</v>
       </c>
       <c r="D2" t="n">
-        <v>28.1</v>
+        <v>32.23</v>
       </c>
       <c r="E2" t="n">
-        <v>0</v>
+        <v>-1.22</v>
       </c>
       <c r="F2" t="n">
-        <v>35.3</v>
+        <v>66.2</v>
       </c>
       <c r="G2" t="n">
-        <v>35.3</v>
+        <v>64.2</v>
       </c>
       <c r="H2" t="n">
-        <v>0</v>
+        <v>-2</v>
       </c>
       <c r="I2" t="inlineStr">
         <is>
@@ -536,16 +536,16 @@
         </is>
       </c>
       <c r="K2" t="n">
-        <v>29.63</v>
+        <v>28.66</v>
       </c>
       <c r="L2" t="n">
-        <v>29.63</v>
+        <v>28.32</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>TEN</t>
+          <t>CCEC</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -554,22 +554,22 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>88.56</v>
+        <v>28.1</v>
       </c>
       <c r="D3" t="n">
-        <v>80.79000000000001</v>
+        <v>28.1</v>
       </c>
       <c r="E3" t="n">
-        <v>-8.77</v>
+        <v>0</v>
       </c>
       <c r="F3" t="n">
-        <v>42.7</v>
+        <v>35.3</v>
       </c>
       <c r="G3" t="n">
-        <v>30.9</v>
+        <v>35.3</v>
       </c>
       <c r="H3" t="n">
-        <v>-11.8</v>
+        <v>0</v>
       </c>
       <c r="I3" t="inlineStr">
         <is>
@@ -582,16 +582,16 @@
         </is>
       </c>
       <c r="K3" t="n">
-        <v>62.79</v>
+        <v>29.63</v>
       </c>
       <c r="L3" t="n">
-        <v>57.61</v>
+        <v>29.63</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>GNK</t>
+          <t>TEN</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -600,26 +600,26 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>25.4</v>
+        <v>88.56</v>
       </c>
       <c r="D4" t="n">
-        <v>26.24</v>
+        <v>80.79000000000001</v>
       </c>
       <c r="E4" t="n">
-        <v>3.33</v>
+        <v>-8.77</v>
       </c>
       <c r="F4" t="n">
-        <v>4.3</v>
+        <v>42.7</v>
       </c>
       <c r="G4" t="n">
-        <v>7.2</v>
+        <v>30.9</v>
       </c>
       <c r="H4" t="n">
-        <v>3</v>
+        <v>-11.8</v>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>HOLD (fairly valued)</t>
+          <t>BUY (undervalued)</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
@@ -628,16 +628,16 @@
         </is>
       </c>
       <c r="K4" t="n">
-        <v>25.02</v>
+        <v>62.79</v>
       </c>
       <c r="L4" t="n">
-        <v>25.73</v>
+        <v>57.61</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>TNK</t>
+          <t>GNK</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -646,44 +646,44 @@
         </is>
       </c>
       <c r="C5" t="n">
-        <v>83.31999999999999</v>
+        <v>25.4</v>
       </c>
       <c r="D5" t="n">
-        <v>77.45</v>
+        <v>26.24</v>
       </c>
       <c r="E5" t="n">
-        <v>-7.04</v>
+        <v>3.33</v>
       </c>
       <c r="F5" t="n">
-        <v>11.4</v>
+        <v>4.3</v>
       </c>
       <c r="G5" t="n">
-        <v>4.1</v>
+        <v>7.2</v>
       </c>
       <c r="H5" t="n">
-        <v>-7.3</v>
+        <v>3</v>
       </c>
       <c r="I5" t="inlineStr">
         <is>
+          <t>HOLD (fairly valued)</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
           <t>BUY (undervalued)</t>
         </is>
       </c>
-      <c r="J5" t="inlineStr">
-        <is>
-          <t>HOLD (fairly valued)</t>
-        </is>
-      </c>
       <c r="K5" t="n">
-        <v>78.90000000000001</v>
+        <v>25.02</v>
       </c>
       <c r="L5" t="n">
-        <v>73.7</v>
+        <v>25.73</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>FLNG</t>
+          <t>TNK</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -692,44 +692,44 @@
         </is>
       </c>
       <c r="C6" t="n">
-        <v>28.45</v>
+        <v>83.31999999999999</v>
       </c>
       <c r="D6" t="n">
-        <v>28.45</v>
+        <v>77.45</v>
       </c>
       <c r="E6" t="n">
-        <v>0</v>
+        <v>-7.04</v>
       </c>
       <c r="F6" t="n">
-        <v>0.1</v>
+        <v>11.4</v>
       </c>
       <c r="G6" t="n">
-        <v>0.1</v>
+        <v>4.1</v>
       </c>
       <c r="H6" t="n">
-        <v>0</v>
+        <v>-7.3</v>
       </c>
       <c r="I6" t="inlineStr">
         <is>
+          <t>BUY (undervalued)</t>
+        </is>
+      </c>
+      <c r="J6" t="inlineStr">
+        <is>
           <t>HOLD (fairly valued)</t>
         </is>
       </c>
-      <c r="J6" t="inlineStr">
-        <is>
-          <t>HOLD (fairly valued)</t>
-        </is>
-      </c>
       <c r="K6" t="n">
-        <v>29.73</v>
+        <v>78.90000000000001</v>
       </c>
       <c r="L6" t="n">
-        <v>29.73</v>
+        <v>73.7</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>STNG</t>
+          <t>FLNG</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -738,22 +738,22 @@
         </is>
       </c>
       <c r="C7" t="n">
-        <v>83.87</v>
+        <v>28.45</v>
       </c>
       <c r="D7" t="n">
-        <v>80.34999999999999</v>
+        <v>28.45</v>
       </c>
       <c r="E7" t="n">
-        <v>-4.19</v>
+        <v>0</v>
       </c>
       <c r="F7" t="n">
-        <v>1</v>
+        <v>0.1</v>
       </c>
       <c r="G7" t="n">
-        <v>-3.3</v>
+        <v>0.1</v>
       </c>
       <c r="H7" t="n">
-        <v>-4.3</v>
+        <v>0</v>
       </c>
       <c r="I7" t="inlineStr">
         <is>
@@ -766,16 +766,16 @@
         </is>
       </c>
       <c r="K7" t="n">
-        <v>76.37</v>
+        <v>29.73</v>
       </c>
       <c r="L7" t="n">
-        <v>73.13</v>
+        <v>29.73</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>TRMD</t>
+          <t>STNG</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -784,22 +784,22 @@
         </is>
       </c>
       <c r="C8" t="n">
-        <v>26.74</v>
+        <v>83.87</v>
       </c>
       <c r="D8" t="n">
-        <v>25.43</v>
+        <v>80.34999999999999</v>
       </c>
       <c r="E8" t="n">
-        <v>-4.86</v>
+        <v>-4.19</v>
       </c>
       <c r="F8" t="n">
-        <v>-1.3</v>
+        <v>1</v>
       </c>
       <c r="G8" t="n">
-        <v>-5.4</v>
+        <v>-3.3</v>
       </c>
       <c r="H8" t="n">
-        <v>-4.1</v>
+        <v>-4.3</v>
       </c>
       <c r="I8" t="inlineStr">
         <is>
@@ -808,20 +808,20 @@
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>TRIM/SHORT (overvalued)</t>
+          <t>HOLD (fairly valued)</t>
         </is>
       </c>
       <c r="K8" t="n">
-        <v>27.83</v>
+        <v>76.37</v>
       </c>
       <c r="L8" t="n">
-        <v>26.68</v>
+        <v>73.13</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>SBLK</t>
+          <t>TRMD</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -830,26 +830,26 @@
         </is>
       </c>
       <c r="C9" t="n">
-        <v>25.98</v>
+        <v>26.74</v>
       </c>
       <c r="D9" t="n">
-        <v>26.27</v>
+        <v>25.43</v>
       </c>
       <c r="E9" t="n">
-        <v>1.1</v>
+        <v>-4.86</v>
       </c>
       <c r="F9" t="n">
-        <v>-6.3</v>
+        <v>-1.3</v>
       </c>
       <c r="G9" t="n">
         <v>-5.4</v>
       </c>
       <c r="H9" t="n">
-        <v>0.8</v>
+        <v>-4.1</v>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>TRIM/SHORT (overvalued)</t>
+          <t>HOLD (fairly valued)</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
@@ -858,16 +858,16 @@
         </is>
       </c>
       <c r="K9" t="n">
-        <v>25.49</v>
+        <v>27.83</v>
       </c>
       <c r="L9" t="n">
-        <v>25.72</v>
+        <v>26.68</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>ASC</t>
+          <t>SBLK</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -876,22 +876,22 @@
         </is>
       </c>
       <c r="C10" t="n">
-        <v>15.96</v>
+        <v>25.98</v>
       </c>
       <c r="D10" t="n">
-        <v>15.93</v>
+        <v>26.27</v>
       </c>
       <c r="E10" t="n">
-        <v>-0.16</v>
+        <v>1.1</v>
       </c>
       <c r="F10" t="n">
-        <v>-5.8</v>
+        <v>-6.3</v>
       </c>
       <c r="G10" t="n">
-        <v>-5.9</v>
+        <v>-5.4</v>
       </c>
       <c r="H10" t="n">
-        <v>-0.1</v>
+        <v>0.8</v>
       </c>
       <c r="I10" t="inlineStr">
         <is>
@@ -904,16 +904,16 @@
         </is>
       </c>
       <c r="K10" t="n">
-        <v>15.07</v>
+        <v>25.49</v>
       </c>
       <c r="L10" t="n">
-        <v>15.05</v>
+        <v>25.72</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>DHT</t>
+          <t>ASC</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -922,26 +922,26 @@
         </is>
       </c>
       <c r="C11" t="n">
-        <v>15.29</v>
+        <v>15.96</v>
       </c>
       <c r="D11" t="n">
-        <v>12.93</v>
+        <v>15.93</v>
       </c>
       <c r="E11" t="n">
-        <v>-15.41</v>
+        <v>-0.16</v>
       </c>
       <c r="F11" t="n">
-        <v>5.6</v>
+        <v>-5.8</v>
       </c>
       <c r="G11" t="n">
-        <v>-8.1</v>
+        <v>-5.9</v>
       </c>
       <c r="H11" t="n">
-        <v>-13.7</v>
+        <v>-0.1</v>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>BUY (undervalued)</t>
+          <t>TRIM/SHORT (overvalued)</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
@@ -950,16 +950,16 @@
         </is>
       </c>
       <c r="K11" t="n">
-        <v>17.32</v>
+        <v>15.07</v>
       </c>
       <c r="L11" t="n">
-        <v>15.08</v>
+        <v>15.05</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>FRO</t>
+          <t>DHT</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -968,26 +968,26 @@
         </is>
       </c>
       <c r="C12" t="n">
-        <v>28.79</v>
+        <v>15.29</v>
       </c>
       <c r="D12" t="n">
-        <v>24.4</v>
+        <v>12.93</v>
       </c>
       <c r="E12" t="n">
-        <v>-15.25</v>
+        <v>-15.41</v>
       </c>
       <c r="F12" t="n">
-        <v>-2.1</v>
+        <v>5.6</v>
       </c>
       <c r="G12" t="n">
-        <v>-14.9</v>
+        <v>-8.1</v>
       </c>
       <c r="H12" t="n">
-        <v>-12.8</v>
+        <v>-13.7</v>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>HOLD (fairly valued)</t>
+          <t>BUY (undervalued)</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
@@ -996,16 +996,16 @@
         </is>
       </c>
       <c r="K12" t="n">
-        <v>33.77</v>
+        <v>17.32</v>
       </c>
       <c r="L12" t="n">
-        <v>29.36</v>
+        <v>15.08</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>ECO</t>
+          <t>FRO</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -1014,22 +1014,22 @@
         </is>
       </c>
       <c r="C13" t="n">
-        <v>39.93</v>
+        <v>28.79</v>
       </c>
       <c r="D13" t="n">
-        <v>33.71</v>
+        <v>24.4</v>
       </c>
       <c r="E13" t="n">
-        <v>-15.58</v>
+        <v>-15.25</v>
       </c>
       <c r="F13" t="n">
-        <v>-4.8</v>
+        <v>-2.1</v>
       </c>
       <c r="G13" t="n">
-        <v>-17.5</v>
+        <v>-14.9</v>
       </c>
       <c r="H13" t="n">
-        <v>-12.7</v>
+        <v>-12.8</v>
       </c>
       <c r="I13" t="inlineStr">
         <is>
@@ -1042,44 +1042,44 @@
         </is>
       </c>
       <c r="K13" t="n">
-        <v>45.41</v>
+        <v>33.77</v>
       </c>
       <c r="L13" t="n">
-        <v>39.33</v>
+        <v>29.36</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>INSW</t>
+          <t>ECO</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>WHOLE-COMPANY (hybrid aggregation)</t>
+          <t>whole-company</t>
         </is>
       </c>
       <c r="C14" t="n">
-        <v>57.91</v>
+        <v>39.93</v>
       </c>
       <c r="D14" t="n">
-        <v>52.4</v>
+        <v>33.71</v>
       </c>
       <c r="E14" t="n">
-        <v>-9.51</v>
+        <v>-15.58</v>
       </c>
       <c r="F14" t="n">
-        <v>-17.2</v>
+        <v>-4.8</v>
       </c>
       <c r="G14" t="n">
-        <v>-23.8</v>
+        <v>-17.5</v>
       </c>
       <c r="H14" t="n">
-        <v>-6.6</v>
+        <v>-12.7</v>
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>TRIM/SHORT (overvalued)</t>
+          <t>HOLD (fairly valued)</t>
         </is>
       </c>
       <c r="J14" t="inlineStr">
@@ -1088,40 +1088,40 @@
         </is>
       </c>
       <c r="K14" t="n">
-        <v>64.59</v>
+        <v>45.41</v>
       </c>
       <c r="L14" t="n">
-        <v>59.47</v>
+        <v>39.33</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>HAFN</t>
+          <t>INSW</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>whole-company</t>
+          <t>WHOLE-COMPANY (hybrid aggregation)</t>
         </is>
       </c>
       <c r="C15" t="n">
-        <v>5.34</v>
+        <v>57.91</v>
       </c>
       <c r="D15" t="n">
-        <v>5.22</v>
+        <v>52.4</v>
       </c>
       <c r="E15" t="n">
-        <v>-2.24</v>
+        <v>-9.51</v>
       </c>
       <c r="F15" t="n">
+        <v>-17.2</v>
+      </c>
+      <c r="G15" t="n">
         <v>-23.8</v>
       </c>
-      <c r="G15" t="n">
-        <v>-25.1</v>
-      </c>
       <c r="H15" t="n">
-        <v>-1.4</v>
+        <v>-6.6</v>
       </c>
       <c r="I15" t="inlineStr">
         <is>
@@ -1134,55 +1134,101 @@
         </is>
       </c>
       <c r="K15" t="n">
-        <v>5.87</v>
+        <v>64.59</v>
       </c>
       <c r="L15" t="n">
-        <v>5.77</v>
+        <v>59.47</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
+          <t>HAFN</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>whole-company</t>
+        </is>
+      </c>
+      <c r="C16" t="n">
+        <v>5.34</v>
+      </c>
+      <c r="D16" t="n">
+        <v>5.22</v>
+      </c>
+      <c r="E16" t="n">
+        <v>-2.24</v>
+      </c>
+      <c r="F16" t="n">
+        <v>-23.8</v>
+      </c>
+      <c r="G16" t="n">
+        <v>-25.1</v>
+      </c>
+      <c r="H16" t="n">
+        <v>-1.4</v>
+      </c>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>TRIM/SHORT (overvalued)</t>
+        </is>
+      </c>
+      <c r="J16" t="inlineStr">
+        <is>
+          <t>TRIM/SHORT (overvalued)</t>
+        </is>
+      </c>
+      <c r="K16" t="n">
+        <v>5.87</v>
+      </c>
+      <c r="L16" t="n">
+        <v>5.77</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
           <t>NAT</t>
         </is>
       </c>
-      <c r="B16" t="inlineStr">
-        <is>
-          <t>whole-company</t>
-        </is>
-      </c>
-      <c r="C16" t="n">
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>whole-company</t>
+        </is>
+      </c>
+      <c r="C17" t="n">
         <v>2.63</v>
       </c>
-      <c r="D16" t="n">
+      <c r="D17" t="n">
         <v>2.07</v>
       </c>
-      <c r="E16" t="n">
+      <c r="E17" t="n">
         <v>-21.23</v>
       </c>
-      <c r="F16" t="n">
+      <c r="F17" t="n">
         <v>-35.2</v>
       </c>
-      <c r="G16" t="n">
+      <c r="G17" t="n">
         <v>-44.9</v>
       </c>
-      <c r="H16" t="n">
+      <c r="H17" t="n">
         <v>-9.800000000000001</v>
       </c>
-      <c r="I16" t="inlineStr">
-        <is>
-          <t>TRIM/SHORT (overvalued)</t>
-        </is>
-      </c>
-      <c r="J16" t="inlineStr">
-        <is>
-          <t>TRIM/SHORT (overvalued)</t>
-        </is>
-      </c>
-      <c r="K16" t="n">
+      <c r="I17" t="inlineStr">
+        <is>
+          <t>TRIM/SHORT (overvalued)</t>
+        </is>
+      </c>
+      <c r="J17" t="inlineStr">
+        <is>
+          <t>TRIM/SHORT (overvalued)</t>
+        </is>
+      </c>
+      <c r="K17" t="n">
         <v>3.37</v>
       </c>
-      <c r="L16" t="n">
+      <c r="L17" t="n">
         <v>2.86</v>
       </c>
     </row>

--- a/outputs/transaction_anchor_comparison.xlsx
+++ b/outputs/transaction_anchor_comparison.xlsx
@@ -499,7 +499,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>CMDB</t>
+          <t>CCEC</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -508,22 +508,22 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>32.62</v>
+        <v>28.1</v>
       </c>
       <c r="D2" t="n">
-        <v>32.23</v>
+        <v>28.1</v>
       </c>
       <c r="E2" t="n">
-        <v>-1.22</v>
+        <v>0</v>
       </c>
       <c r="F2" t="n">
-        <v>66.2</v>
+        <v>35.3</v>
       </c>
       <c r="G2" t="n">
-        <v>64.2</v>
+        <v>35.3</v>
       </c>
       <c r="H2" t="n">
-        <v>-2</v>
+        <v>0</v>
       </c>
       <c r="I2" t="inlineStr">
         <is>
@@ -536,16 +536,16 @@
         </is>
       </c>
       <c r="K2" t="n">
-        <v>28.66</v>
+        <v>29.63</v>
       </c>
       <c r="L2" t="n">
-        <v>28.32</v>
+        <v>29.63</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>CCEC</t>
+          <t>TEN</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -554,22 +554,22 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>28.1</v>
+        <v>88.56</v>
       </c>
       <c r="D3" t="n">
-        <v>28.1</v>
+        <v>80.79000000000001</v>
       </c>
       <c r="E3" t="n">
-        <v>0</v>
+        <v>-8.77</v>
       </c>
       <c r="F3" t="n">
-        <v>35.3</v>
+        <v>42.7</v>
       </c>
       <c r="G3" t="n">
-        <v>35.3</v>
+        <v>30.9</v>
       </c>
       <c r="H3" t="n">
-        <v>0</v>
+        <v>-11.8</v>
       </c>
       <c r="I3" t="inlineStr">
         <is>
@@ -582,16 +582,16 @@
         </is>
       </c>
       <c r="K3" t="n">
-        <v>29.63</v>
+        <v>62.79</v>
       </c>
       <c r="L3" t="n">
-        <v>29.63</v>
+        <v>57.61</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>TEN</t>
+          <t>CMDB</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -600,22 +600,22 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>88.56</v>
+        <v>32.62</v>
       </c>
       <c r="D4" t="n">
-        <v>80.79000000000001</v>
+        <v>32.23</v>
       </c>
       <c r="E4" t="n">
-        <v>-8.77</v>
+        <v>-1.22</v>
       </c>
       <c r="F4" t="n">
-        <v>42.7</v>
+        <v>16.3</v>
       </c>
       <c r="G4" t="n">
-        <v>30.9</v>
+        <v>14.9</v>
       </c>
       <c r="H4" t="n">
-        <v>-11.8</v>
+        <v>-1.4</v>
       </c>
       <c r="I4" t="inlineStr">
         <is>
@@ -628,10 +628,10 @@
         </is>
       </c>
       <c r="K4" t="n">
-        <v>62.79</v>
+        <v>20.06</v>
       </c>
       <c r="L4" t="n">
-        <v>57.61</v>
+        <v>19.82</v>
       </c>
     </row>
     <row r="5">

--- a/outputs/transaction_anchor_comparison.xlsx
+++ b/outputs/transaction_anchor_comparison.xlsx
@@ -499,7 +499,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>CCEC</t>
+          <t>TEN</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -508,22 +508,22 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>28.1</v>
+        <v>88.56</v>
       </c>
       <c r="D2" t="n">
-        <v>28.1</v>
+        <v>80.79000000000001</v>
       </c>
       <c r="E2" t="n">
-        <v>0</v>
+        <v>-8.77</v>
       </c>
       <c r="F2" t="n">
-        <v>35.3</v>
+        <v>69.09999999999999</v>
       </c>
       <c r="G2" t="n">
-        <v>35.3</v>
+        <v>55.1</v>
       </c>
       <c r="H2" t="n">
-        <v>0</v>
+        <v>-13.9</v>
       </c>
       <c r="I2" t="inlineStr">
         <is>
@@ -536,16 +536,16 @@
         </is>
       </c>
       <c r="K2" t="n">
-        <v>29.63</v>
+        <v>62.79</v>
       </c>
       <c r="L2" t="n">
-        <v>29.63</v>
+        <v>57.61</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>TEN</t>
+          <t>CCEC</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -554,22 +554,22 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>88.56</v>
+        <v>28.1</v>
       </c>
       <c r="D3" t="n">
-        <v>80.79000000000001</v>
+        <v>28.1</v>
       </c>
       <c r="E3" t="n">
-        <v>-8.77</v>
+        <v>0</v>
       </c>
       <c r="F3" t="n">
-        <v>42.7</v>
+        <v>38.1</v>
       </c>
       <c r="G3" t="n">
-        <v>30.9</v>
+        <v>38.1</v>
       </c>
       <c r="H3" t="n">
-        <v>-11.8</v>
+        <v>0</v>
       </c>
       <c r="I3" t="inlineStr">
         <is>
@@ -582,10 +582,10 @@
         </is>
       </c>
       <c r="K3" t="n">
-        <v>62.79</v>
+        <v>29.63</v>
       </c>
       <c r="L3" t="n">
-        <v>57.61</v>
+        <v>29.63</v>
       </c>
     </row>
     <row r="4">
@@ -609,10 +609,10 @@
         <v>-1.22</v>
       </c>
       <c r="F4" t="n">
-        <v>16.3</v>
+        <v>16.4</v>
       </c>
       <c r="G4" t="n">
-        <v>14.9</v>
+        <v>15</v>
       </c>
       <c r="H4" t="n">
         <v>-1.4</v>
@@ -655,17 +655,17 @@
         <v>3.33</v>
       </c>
       <c r="F5" t="n">
-        <v>4.3</v>
+        <v>6.5</v>
       </c>
       <c r="G5" t="n">
-        <v>7.2</v>
+        <v>9.5</v>
       </c>
       <c r="H5" t="n">
         <v>3</v>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>HOLD (fairly valued)</t>
+          <t>BUY (undervalued)</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
@@ -701,13 +701,13 @@
         <v>-7.04</v>
       </c>
       <c r="F6" t="n">
-        <v>11.4</v>
+        <v>8.4</v>
       </c>
       <c r="G6" t="n">
-        <v>4.1</v>
+        <v>1.3</v>
       </c>
       <c r="H6" t="n">
-        <v>-7.3</v>
+        <v>-7.1</v>
       </c>
       <c r="I6" t="inlineStr">
         <is>
@@ -747,10 +747,10 @@
         <v>0</v>
       </c>
       <c r="F7" t="n">
-        <v>0.1</v>
+        <v>-2</v>
       </c>
       <c r="G7" t="n">
-        <v>0.1</v>
+        <v>-2</v>
       </c>
       <c r="H7" t="n">
         <v>0</v>
@@ -775,7 +775,7 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>STNG</t>
+          <t>SBLK</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -784,22 +784,22 @@
         </is>
       </c>
       <c r="C8" t="n">
-        <v>83.87</v>
+        <v>25.98</v>
       </c>
       <c r="D8" t="n">
-        <v>80.34999999999999</v>
+        <v>26.27</v>
       </c>
       <c r="E8" t="n">
-        <v>-4.19</v>
+        <v>1.1</v>
       </c>
       <c r="F8" t="n">
-        <v>1</v>
+        <v>-4.1</v>
       </c>
       <c r="G8" t="n">
-        <v>-3.3</v>
+        <v>-3.2</v>
       </c>
       <c r="H8" t="n">
-        <v>-4.3</v>
+        <v>0.9</v>
       </c>
       <c r="I8" t="inlineStr">
         <is>
@@ -812,16 +812,16 @@
         </is>
       </c>
       <c r="K8" t="n">
-        <v>76.37</v>
+        <v>25.49</v>
       </c>
       <c r="L8" t="n">
-        <v>73.13</v>
+        <v>25.72</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>TRMD</t>
+          <t>STNG</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -830,22 +830,22 @@
         </is>
       </c>
       <c r="C9" t="n">
-        <v>26.74</v>
+        <v>83.87</v>
       </c>
       <c r="D9" t="n">
-        <v>25.43</v>
+        <v>80.34999999999999</v>
       </c>
       <c r="E9" t="n">
-        <v>-4.86</v>
+        <v>-4.19</v>
       </c>
       <c r="F9" t="n">
-        <v>-1.3</v>
+        <v>-0.1</v>
       </c>
       <c r="G9" t="n">
-        <v>-5.4</v>
+        <v>-4.4</v>
       </c>
       <c r="H9" t="n">
-        <v>-4.1</v>
+        <v>-4.2</v>
       </c>
       <c r="I9" t="inlineStr">
         <is>
@@ -854,20 +854,20 @@
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>TRIM/SHORT (overvalued)</t>
+          <t>HOLD (fairly valued)</t>
         </is>
       </c>
       <c r="K9" t="n">
-        <v>27.83</v>
+        <v>76.37</v>
       </c>
       <c r="L9" t="n">
-        <v>26.68</v>
+        <v>73.13</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>SBLK</t>
+          <t>ASC</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -876,22 +876,22 @@
         </is>
       </c>
       <c r="C10" t="n">
-        <v>25.98</v>
+        <v>15.96</v>
       </c>
       <c r="D10" t="n">
-        <v>26.27</v>
+        <v>15.93</v>
       </c>
       <c r="E10" t="n">
-        <v>1.1</v>
+        <v>-0.16</v>
       </c>
       <c r="F10" t="n">
-        <v>-6.3</v>
+        <v>-8.300000000000001</v>
       </c>
       <c r="G10" t="n">
-        <v>-5.4</v>
+        <v>-8.4</v>
       </c>
       <c r="H10" t="n">
-        <v>0.8</v>
+        <v>-0.1</v>
       </c>
       <c r="I10" t="inlineStr">
         <is>
@@ -904,16 +904,16 @@
         </is>
       </c>
       <c r="K10" t="n">
-        <v>25.49</v>
+        <v>15.07</v>
       </c>
       <c r="L10" t="n">
-        <v>25.72</v>
+        <v>15.05</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>ASC</t>
+          <t>TRMD</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -922,26 +922,26 @@
         </is>
       </c>
       <c r="C11" t="n">
-        <v>15.96</v>
+        <v>26.74</v>
       </c>
       <c r="D11" t="n">
-        <v>15.93</v>
+        <v>25.43</v>
       </c>
       <c r="E11" t="n">
-        <v>-0.16</v>
+        <v>-4.86</v>
       </c>
       <c r="F11" t="n">
-        <v>-5.8</v>
+        <v>-4.6</v>
       </c>
       <c r="G11" t="n">
-        <v>-5.9</v>
+        <v>-8.6</v>
       </c>
       <c r="H11" t="n">
-        <v>-0.1</v>
+        <v>-4</v>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>TRIM/SHORT (overvalued)</t>
+          <t>HOLD (fairly valued)</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
@@ -950,10 +950,10 @@
         </is>
       </c>
       <c r="K11" t="n">
-        <v>15.07</v>
+        <v>27.83</v>
       </c>
       <c r="L11" t="n">
-        <v>15.05</v>
+        <v>26.68</v>
       </c>
     </row>
     <row r="12">
@@ -977,17 +977,17 @@
         <v>-15.41</v>
       </c>
       <c r="F12" t="n">
-        <v>5.6</v>
+        <v>4.4</v>
       </c>
       <c r="G12" t="n">
-        <v>-8.1</v>
+        <v>-9.199999999999999</v>
       </c>
       <c r="H12" t="n">
-        <v>-13.7</v>
+        <v>-13.5</v>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>BUY (undervalued)</t>
+          <t>HOLD (fairly valued)</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
@@ -1023,17 +1023,17 @@
         <v>-15.25</v>
       </c>
       <c r="F13" t="n">
-        <v>-2.1</v>
+        <v>-6.9</v>
       </c>
       <c r="G13" t="n">
-        <v>-14.9</v>
+        <v>-19.1</v>
       </c>
       <c r="H13" t="n">
-        <v>-12.8</v>
+        <v>-12.2</v>
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>HOLD (fairly valued)</t>
+          <t>TRIM/SHORT (overvalued)</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
@@ -1069,17 +1069,17 @@
         <v>-15.58</v>
       </c>
       <c r="F14" t="n">
-        <v>-4.8</v>
+        <v>-7.7</v>
       </c>
       <c r="G14" t="n">
-        <v>-17.5</v>
+        <v>-20.1</v>
       </c>
       <c r="H14" t="n">
-        <v>-12.7</v>
+        <v>-12.3</v>
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>HOLD (fairly valued)</t>
+          <t>TRIM/SHORT (overvalued)</t>
         </is>
       </c>
       <c r="J14" t="inlineStr">
@@ -1097,31 +1097,31 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>INSW</t>
+          <t>HAFN</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>WHOLE-COMPANY (hybrid aggregation)</t>
+          <t>whole-company</t>
         </is>
       </c>
       <c r="C15" t="n">
-        <v>57.91</v>
+        <v>5.34</v>
       </c>
       <c r="D15" t="n">
-        <v>52.4</v>
+        <v>5.22</v>
       </c>
       <c r="E15" t="n">
-        <v>-9.51</v>
+        <v>-2.24</v>
       </c>
       <c r="F15" t="n">
-        <v>-17.2</v>
+        <v>-20.2</v>
       </c>
       <c r="G15" t="n">
-        <v>-23.8</v>
+        <v>-21.7</v>
       </c>
       <c r="H15" t="n">
-        <v>-6.6</v>
+        <v>-1.4</v>
       </c>
       <c r="I15" t="inlineStr">
         <is>
@@ -1134,40 +1134,40 @@
         </is>
       </c>
       <c r="K15" t="n">
-        <v>64.59</v>
+        <v>5.87</v>
       </c>
       <c r="L15" t="n">
-        <v>59.47</v>
+        <v>5.77</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>HAFN</t>
+          <t>INSW</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>whole-company</t>
+          <t>WHOLE-COMPANY (hybrid aggregation)</t>
         </is>
       </c>
       <c r="C16" t="n">
-        <v>5.34</v>
+        <v>57.91</v>
       </c>
       <c r="D16" t="n">
-        <v>5.22</v>
+        <v>52.4</v>
       </c>
       <c r="E16" t="n">
-        <v>-2.24</v>
+        <v>-9.51</v>
       </c>
       <c r="F16" t="n">
-        <v>-23.8</v>
+        <v>-21.8</v>
       </c>
       <c r="G16" t="n">
-        <v>-25.1</v>
+        <v>-28</v>
       </c>
       <c r="H16" t="n">
-        <v>-1.4</v>
+        <v>-6.2</v>
       </c>
       <c r="I16" t="inlineStr">
         <is>
@@ -1180,10 +1180,10 @@
         </is>
       </c>
       <c r="K16" t="n">
-        <v>5.87</v>
+        <v>64.59</v>
       </c>
       <c r="L16" t="n">
-        <v>5.77</v>
+        <v>59.47</v>
       </c>
     </row>
     <row r="17">
@@ -1207,10 +1207,10 @@
         <v>-21.23</v>
       </c>
       <c r="F17" t="n">
-        <v>-35.2</v>
+        <v>-34.9</v>
       </c>
       <c r="G17" t="n">
-        <v>-44.9</v>
+        <v>-44.7</v>
       </c>
       <c r="H17" t="n">
         <v>-9.800000000000001</v>

--- a/outputs/transaction_anchor_comparison.xlsx
+++ b/outputs/transaction_anchor_comparison.xlsx
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L17"/>
+  <dimension ref="A1:L18"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="8" customWidth="1" min="1" max="1"/>
@@ -517,13 +517,13 @@
         <v>-8.77</v>
       </c>
       <c r="F2" t="n">
-        <v>69.09999999999999</v>
+        <v>65.3</v>
       </c>
       <c r="G2" t="n">
-        <v>55.1</v>
+        <v>51.7</v>
       </c>
       <c r="H2" t="n">
-        <v>-13.9</v>
+        <v>-13.6</v>
       </c>
       <c r="I2" t="inlineStr">
         <is>
@@ -545,7 +545,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>CCEC</t>
+          <t>CAPT</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -554,22 +554,22 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>28.1</v>
+        <v>17.91</v>
       </c>
       <c r="D3" t="n">
-        <v>28.1</v>
+        <v>17.74</v>
       </c>
       <c r="E3" t="n">
-        <v>0</v>
+        <v>-0.96</v>
       </c>
       <c r="F3" t="n">
-        <v>38.1</v>
+        <v>42.5</v>
       </c>
       <c r="G3" t="n">
-        <v>38.1</v>
+        <v>38.8</v>
       </c>
       <c r="H3" t="n">
-        <v>0</v>
+        <v>-3.7</v>
       </c>
       <c r="I3" t="inlineStr">
         <is>
@@ -582,16 +582,16 @@
         </is>
       </c>
       <c r="K3" t="n">
-        <v>29.63</v>
+        <v>18.15</v>
       </c>
       <c r="L3" t="n">
-        <v>29.63</v>
+        <v>17.68</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>CMDB</t>
+          <t>CCEC</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -600,22 +600,22 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>32.62</v>
+        <v>28.1</v>
       </c>
       <c r="D4" t="n">
-        <v>32.23</v>
+        <v>28.1</v>
       </c>
       <c r="E4" t="n">
-        <v>-1.22</v>
+        <v>0</v>
       </c>
       <c r="F4" t="n">
-        <v>16.4</v>
+        <v>33.5</v>
       </c>
       <c r="G4" t="n">
-        <v>15</v>
+        <v>33.5</v>
       </c>
       <c r="H4" t="n">
-        <v>-1.4</v>
+        <v>0</v>
       </c>
       <c r="I4" t="inlineStr">
         <is>
@@ -628,16 +628,16 @@
         </is>
       </c>
       <c r="K4" t="n">
-        <v>20.06</v>
+        <v>29.63</v>
       </c>
       <c r="L4" t="n">
-        <v>19.82</v>
+        <v>29.63</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>GNK</t>
+          <t>CMDB</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -646,22 +646,22 @@
         </is>
       </c>
       <c r="C5" t="n">
-        <v>25.4</v>
+        <v>32.62</v>
       </c>
       <c r="D5" t="n">
-        <v>26.24</v>
+        <v>32.23</v>
       </c>
       <c r="E5" t="n">
-        <v>3.33</v>
+        <v>-1.22</v>
       </c>
       <c r="F5" t="n">
-        <v>6.5</v>
+        <v>15.4</v>
       </c>
       <c r="G5" t="n">
-        <v>9.5</v>
+        <v>14</v>
       </c>
       <c r="H5" t="n">
-        <v>3</v>
+        <v>-1.4</v>
       </c>
       <c r="I5" t="inlineStr">
         <is>
@@ -674,16 +674,16 @@
         </is>
       </c>
       <c r="K5" t="n">
-        <v>25.02</v>
+        <v>20.06</v>
       </c>
       <c r="L5" t="n">
-        <v>25.73</v>
+        <v>19.82</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>TNK</t>
+          <t>GNK</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -692,22 +692,22 @@
         </is>
       </c>
       <c r="C6" t="n">
-        <v>83.31999999999999</v>
+        <v>25.4</v>
       </c>
       <c r="D6" t="n">
-        <v>77.45</v>
+        <v>26.24</v>
       </c>
       <c r="E6" t="n">
-        <v>-7.04</v>
+        <v>3.33</v>
       </c>
       <c r="F6" t="n">
-        <v>8.4</v>
+        <v>5.1</v>
       </c>
       <c r="G6" t="n">
-        <v>1.3</v>
+        <v>8.1</v>
       </c>
       <c r="H6" t="n">
-        <v>-7.1</v>
+        <v>3</v>
       </c>
       <c r="I6" t="inlineStr">
         <is>
@@ -716,20 +716,20 @@
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>HOLD (fairly valued)</t>
+          <t>BUY (undervalued)</t>
         </is>
       </c>
       <c r="K6" t="n">
-        <v>78.90000000000001</v>
+        <v>25.02</v>
       </c>
       <c r="L6" t="n">
-        <v>73.7</v>
+        <v>25.73</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>FLNG</t>
+          <t>TNK</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -738,44 +738,44 @@
         </is>
       </c>
       <c r="C7" t="n">
-        <v>28.45</v>
+        <v>83.31999999999999</v>
       </c>
       <c r="D7" t="n">
-        <v>28.45</v>
+        <v>77.45</v>
       </c>
       <c r="E7" t="n">
-        <v>0</v>
+        <v>-7.04</v>
       </c>
       <c r="F7" t="n">
-        <v>-2</v>
+        <v>6.5</v>
       </c>
       <c r="G7" t="n">
-        <v>-2</v>
+        <v>-0.5</v>
       </c>
       <c r="H7" t="n">
-        <v>0</v>
+        <v>-7</v>
       </c>
       <c r="I7" t="inlineStr">
         <is>
+          <t>BUY (undervalued)</t>
+        </is>
+      </c>
+      <c r="J7" t="inlineStr">
+        <is>
           <t>HOLD (fairly valued)</t>
         </is>
       </c>
-      <c r="J7" t="inlineStr">
-        <is>
-          <t>HOLD (fairly valued)</t>
-        </is>
-      </c>
       <c r="K7" t="n">
-        <v>29.73</v>
+        <v>78.90000000000001</v>
       </c>
       <c r="L7" t="n">
-        <v>29.73</v>
+        <v>73.7</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>SBLK</t>
+          <t>FLNG</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -784,22 +784,22 @@
         </is>
       </c>
       <c r="C8" t="n">
-        <v>25.98</v>
+        <v>28.45</v>
       </c>
       <c r="D8" t="n">
-        <v>26.27</v>
+        <v>28.45</v>
       </c>
       <c r="E8" t="n">
-        <v>1.1</v>
+        <v>0</v>
       </c>
       <c r="F8" t="n">
-        <v>-4.1</v>
+        <v>-4.4</v>
       </c>
       <c r="G8" t="n">
-        <v>-3.2</v>
+        <v>-4.4</v>
       </c>
       <c r="H8" t="n">
-        <v>0.9</v>
+        <v>0</v>
       </c>
       <c r="I8" t="inlineStr">
         <is>
@@ -812,16 +812,16 @@
         </is>
       </c>
       <c r="K8" t="n">
-        <v>25.49</v>
+        <v>29.73</v>
       </c>
       <c r="L8" t="n">
-        <v>25.72</v>
+        <v>29.73</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>STNG</t>
+          <t>SBLK</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -830,44 +830,44 @@
         </is>
       </c>
       <c r="C9" t="n">
-        <v>83.87</v>
+        <v>25.98</v>
       </c>
       <c r="D9" t="n">
-        <v>80.34999999999999</v>
+        <v>26.27</v>
       </c>
       <c r="E9" t="n">
-        <v>-4.19</v>
+        <v>1.1</v>
       </c>
       <c r="F9" t="n">
-        <v>-0.1</v>
+        <v>-5.8</v>
       </c>
       <c r="G9" t="n">
-        <v>-4.4</v>
+        <v>-5</v>
       </c>
       <c r="H9" t="n">
-        <v>-4.2</v>
+        <v>0.8</v>
       </c>
       <c r="I9" t="inlineStr">
         <is>
+          <t>TRIM/SHORT (overvalued)</t>
+        </is>
+      </c>
+      <c r="J9" t="inlineStr">
+        <is>
           <t>HOLD (fairly valued)</t>
         </is>
       </c>
-      <c r="J9" t="inlineStr">
-        <is>
-          <t>HOLD (fairly valued)</t>
-        </is>
-      </c>
       <c r="K9" t="n">
-        <v>76.37</v>
+        <v>25.49</v>
       </c>
       <c r="L9" t="n">
-        <v>73.13</v>
+        <v>25.72</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>ASC</t>
+          <t>STNG</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -876,26 +876,26 @@
         </is>
       </c>
       <c r="C10" t="n">
-        <v>15.96</v>
+        <v>83.87</v>
       </c>
       <c r="D10" t="n">
-        <v>15.93</v>
+        <v>80.34999999999999</v>
       </c>
       <c r="E10" t="n">
-        <v>-0.16</v>
+        <v>-4.19</v>
       </c>
       <c r="F10" t="n">
-        <v>-8.300000000000001</v>
+        <v>-2</v>
       </c>
       <c r="G10" t="n">
-        <v>-8.4</v>
+        <v>-6.2</v>
       </c>
       <c r="H10" t="n">
-        <v>-0.1</v>
+        <v>-4.2</v>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>TRIM/SHORT (overvalued)</t>
+          <t>HOLD (fairly valued)</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
@@ -904,16 +904,16 @@
         </is>
       </c>
       <c r="K10" t="n">
-        <v>15.07</v>
+        <v>76.37</v>
       </c>
       <c r="L10" t="n">
-        <v>15.05</v>
+        <v>73.13</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>TRMD</t>
+          <t>ASC</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -922,26 +922,26 @@
         </is>
       </c>
       <c r="C11" t="n">
-        <v>26.74</v>
+        <v>15.96</v>
       </c>
       <c r="D11" t="n">
-        <v>25.43</v>
+        <v>15.93</v>
       </c>
       <c r="E11" t="n">
-        <v>-4.86</v>
+        <v>-0.16</v>
       </c>
       <c r="F11" t="n">
-        <v>-4.6</v>
+        <v>-10.8</v>
       </c>
       <c r="G11" t="n">
-        <v>-8.6</v>
+        <v>-10.9</v>
       </c>
       <c r="H11" t="n">
-        <v>-4</v>
+        <v>-0.1</v>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>HOLD (fairly valued)</t>
+          <t>TRIM/SHORT (overvalued)</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
@@ -950,10 +950,10 @@
         </is>
       </c>
       <c r="K11" t="n">
-        <v>27.83</v>
+        <v>15.07</v>
       </c>
       <c r="L11" t="n">
-        <v>26.68</v>
+        <v>15.05</v>
       </c>
     </row>
     <row r="12">
@@ -977,13 +977,13 @@
         <v>-15.41</v>
       </c>
       <c r="F12" t="n">
-        <v>4.4</v>
+        <v>2.3</v>
       </c>
       <c r="G12" t="n">
-        <v>-9.199999999999999</v>
+        <v>-10.9</v>
       </c>
       <c r="H12" t="n">
-        <v>-13.5</v>
+        <v>-13.3</v>
       </c>
       <c r="I12" t="inlineStr">
         <is>
@@ -1005,7 +1005,7 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>FRO</t>
+          <t>TRMD</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -1014,22 +1014,22 @@
         </is>
       </c>
       <c r="C13" t="n">
-        <v>28.79</v>
+        <v>26.74</v>
       </c>
       <c r="D13" t="n">
-        <v>24.4</v>
+        <v>25.43</v>
       </c>
       <c r="E13" t="n">
-        <v>-15.25</v>
+        <v>-4.86</v>
       </c>
       <c r="F13" t="n">
-        <v>-6.9</v>
+        <v>-7.2</v>
       </c>
       <c r="G13" t="n">
-        <v>-19.1</v>
+        <v>-11</v>
       </c>
       <c r="H13" t="n">
-        <v>-12.2</v>
+        <v>-3.8</v>
       </c>
       <c r="I13" t="inlineStr">
         <is>
@@ -1042,10 +1042,10 @@
         </is>
       </c>
       <c r="K13" t="n">
-        <v>33.77</v>
+        <v>27.83</v>
       </c>
       <c r="L13" t="n">
-        <v>29.36</v>
+        <v>26.68</v>
       </c>
     </row>
     <row r="14">
@@ -1069,13 +1069,13 @@
         <v>-15.58</v>
       </c>
       <c r="F14" t="n">
-        <v>-7.7</v>
+        <v>-10.2</v>
       </c>
       <c r="G14" t="n">
-        <v>-20.1</v>
+        <v>-22.2</v>
       </c>
       <c r="H14" t="n">
-        <v>-12.3</v>
+        <v>-12</v>
       </c>
       <c r="I14" t="inlineStr">
         <is>
@@ -1115,10 +1115,10 @@
         <v>-2.24</v>
       </c>
       <c r="F15" t="n">
-        <v>-20.2</v>
+        <v>-21.1</v>
       </c>
       <c r="G15" t="n">
-        <v>-21.7</v>
+        <v>-22.5</v>
       </c>
       <c r="H15" t="n">
         <v>-1.4</v>
@@ -1143,31 +1143,31 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>INSW</t>
+          <t>FRO</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>WHOLE-COMPANY (hybrid aggregation)</t>
+          <t>whole-company</t>
         </is>
       </c>
       <c r="C16" t="n">
-        <v>57.91</v>
+        <v>28.79</v>
       </c>
       <c r="D16" t="n">
-        <v>52.4</v>
+        <v>24.4</v>
       </c>
       <c r="E16" t="n">
-        <v>-9.51</v>
+        <v>-15.25</v>
       </c>
       <c r="F16" t="n">
-        <v>-21.8</v>
+        <v>-11.3</v>
       </c>
       <c r="G16" t="n">
-        <v>-28</v>
+        <v>-22.9</v>
       </c>
       <c r="H16" t="n">
-        <v>-6.2</v>
+        <v>-11.6</v>
       </c>
       <c r="I16" t="inlineStr">
         <is>
@@ -1180,55 +1180,101 @@
         </is>
       </c>
       <c r="K16" t="n">
-        <v>64.59</v>
+        <v>33.77</v>
       </c>
       <c r="L16" t="n">
-        <v>59.47</v>
+        <v>29.36</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
+          <t>INSW</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>WHOLE-COMPANY (hybrid aggregation)</t>
+        </is>
+      </c>
+      <c r="C17" t="n">
+        <v>57.91</v>
+      </c>
+      <c r="D17" t="n">
+        <v>52.4</v>
+      </c>
+      <c r="E17" t="n">
+        <v>-9.51</v>
+      </c>
+      <c r="F17" t="n">
+        <v>-23.4</v>
+      </c>
+      <c r="G17" t="n">
+        <v>-29.4</v>
+      </c>
+      <c r="H17" t="n">
+        <v>-6.1</v>
+      </c>
+      <c r="I17" t="inlineStr">
+        <is>
+          <t>TRIM/SHORT (overvalued)</t>
+        </is>
+      </c>
+      <c r="J17" t="inlineStr">
+        <is>
+          <t>TRIM/SHORT (overvalued)</t>
+        </is>
+      </c>
+      <c r="K17" t="n">
+        <v>64.59</v>
+      </c>
+      <c r="L17" t="n">
+        <v>59.47</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
           <t>NAT</t>
         </is>
       </c>
-      <c r="B17" t="inlineStr">
-        <is>
-          <t>whole-company</t>
-        </is>
-      </c>
-      <c r="C17" t="n">
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>whole-company</t>
+        </is>
+      </c>
+      <c r="C18" t="n">
         <v>2.63</v>
       </c>
-      <c r="D17" t="n">
+      <c r="D18" t="n">
         <v>2.07</v>
       </c>
-      <c r="E17" t="n">
+      <c r="E18" t="n">
         <v>-21.23</v>
       </c>
-      <c r="F17" t="n">
-        <v>-34.9</v>
-      </c>
-      <c r="G17" t="n">
-        <v>-44.7</v>
-      </c>
-      <c r="H17" t="n">
-        <v>-9.800000000000001</v>
-      </c>
-      <c r="I17" t="inlineStr">
-        <is>
-          <t>TRIM/SHORT (overvalued)</t>
-        </is>
-      </c>
-      <c r="J17" t="inlineStr">
-        <is>
-          <t>TRIM/SHORT (overvalued)</t>
-        </is>
-      </c>
-      <c r="K17" t="n">
+      <c r="F18" t="n">
+        <v>-35.9</v>
+      </c>
+      <c r="G18" t="n">
+        <v>-45.6</v>
+      </c>
+      <c r="H18" t="n">
+        <v>-9.699999999999999</v>
+      </c>
+      <c r="I18" t="inlineStr">
+        <is>
+          <t>TRIM/SHORT (overvalued)</t>
+        </is>
+      </c>
+      <c r="J18" t="inlineStr">
+        <is>
+          <t>TRIM/SHORT (overvalued)</t>
+        </is>
+      </c>
+      <c r="K18" t="n">
         <v>3.37</v>
       </c>
-      <c r="L17" t="n">
+      <c r="L18" t="n">
         <v>2.86</v>
       </c>
     </row>

--- a/outputs/transaction_anchor_comparison.xlsx
+++ b/outputs/transaction_anchor_comparison.xlsx
@@ -508,22 +508,22 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>88.56</v>
+        <v>95.95</v>
       </c>
       <c r="D2" t="n">
-        <v>80.79000000000001</v>
+        <v>88.13</v>
       </c>
       <c r="E2" t="n">
-        <v>-8.77</v>
+        <v>-8.15</v>
       </c>
       <c r="F2" t="n">
-        <v>65.3</v>
+        <v>78.5</v>
       </c>
       <c r="G2" t="n">
-        <v>51.7</v>
+        <v>64.7</v>
       </c>
       <c r="H2" t="n">
-        <v>-13.6</v>
+        <v>-13.8</v>
       </c>
       <c r="I2" t="inlineStr">
         <is>
@@ -536,10 +536,10 @@
         </is>
       </c>
       <c r="K2" t="n">
-        <v>62.79</v>
+        <v>67.81</v>
       </c>
       <c r="L2" t="n">
-        <v>57.61</v>
+        <v>62.56</v>
       </c>
     </row>
     <row r="3">

--- a/outputs/transaction_anchor_comparison.xlsx
+++ b/outputs/transaction_anchor_comparison.xlsx
@@ -517,13 +517,13 @@
         <v>-8.15</v>
       </c>
       <c r="F2" t="n">
-        <v>78.5</v>
+        <v>82.7</v>
       </c>
       <c r="G2" t="n">
-        <v>64.7</v>
+        <v>68.59999999999999</v>
       </c>
       <c r="H2" t="n">
-        <v>-13.8</v>
+        <v>-14.1</v>
       </c>
       <c r="I2" t="inlineStr">
         <is>
@@ -563,10 +563,10 @@
         <v>-0.96</v>
       </c>
       <c r="F3" t="n">
-        <v>42.5</v>
+        <v>41.9</v>
       </c>
       <c r="G3" t="n">
-        <v>38.8</v>
+        <v>38.2</v>
       </c>
       <c r="H3" t="n">
         <v>-3.7</v>
@@ -609,10 +609,10 @@
         <v>0</v>
       </c>
       <c r="F4" t="n">
-        <v>33.5</v>
+        <v>37.7</v>
       </c>
       <c r="G4" t="n">
-        <v>33.5</v>
+        <v>37.7</v>
       </c>
       <c r="H4" t="n">
         <v>0</v>
@@ -655,10 +655,10 @@
         <v>-1.22</v>
       </c>
       <c r="F5" t="n">
-        <v>15.4</v>
+        <v>14</v>
       </c>
       <c r="G5" t="n">
-        <v>14</v>
+        <v>12.6</v>
       </c>
       <c r="H5" t="n">
         <v>-1.4</v>
@@ -701,10 +701,10 @@
         <v>3.33</v>
       </c>
       <c r="F6" t="n">
-        <v>5.1</v>
+        <v>5.6</v>
       </c>
       <c r="G6" t="n">
-        <v>8.1</v>
+        <v>8.6</v>
       </c>
       <c r="H6" t="n">
         <v>3</v>
@@ -747,13 +747,13 @@
         <v>-7.04</v>
       </c>
       <c r="F7" t="n">
-        <v>6.5</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="G7" t="n">
-        <v>-0.5</v>
+        <v>1.7</v>
       </c>
       <c r="H7" t="n">
-        <v>-7</v>
+        <v>-7.2</v>
       </c>
       <c r="I7" t="inlineStr">
         <is>
@@ -793,10 +793,10 @@
         <v>0</v>
       </c>
       <c r="F8" t="n">
-        <v>-4.4</v>
+        <v>-2.5</v>
       </c>
       <c r="G8" t="n">
-        <v>-4.4</v>
+        <v>-2.5</v>
       </c>
       <c r="H8" t="n">
         <v>0</v>
@@ -821,7 +821,7 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>SBLK</t>
+          <t>STNG</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -830,26 +830,26 @@
         </is>
       </c>
       <c r="C9" t="n">
-        <v>25.98</v>
+        <v>83.87</v>
       </c>
       <c r="D9" t="n">
-        <v>26.27</v>
+        <v>80.34999999999999</v>
       </c>
       <c r="E9" t="n">
-        <v>1.1</v>
+        <v>-4.19</v>
       </c>
       <c r="F9" t="n">
-        <v>-5.8</v>
+        <v>0.3</v>
       </c>
       <c r="G9" t="n">
-        <v>-5</v>
+        <v>-4</v>
       </c>
       <c r="H9" t="n">
-        <v>0.8</v>
+        <v>-4.3</v>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>TRIM/SHORT (overvalued)</t>
+          <t>HOLD (fairly valued)</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
@@ -858,16 +858,16 @@
         </is>
       </c>
       <c r="K9" t="n">
-        <v>25.49</v>
+        <v>76.37</v>
       </c>
       <c r="L9" t="n">
-        <v>25.72</v>
+        <v>73.13</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>STNG</t>
+          <t>SBLK</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -876,26 +876,26 @@
         </is>
       </c>
       <c r="C10" t="n">
-        <v>83.87</v>
+        <v>25.98</v>
       </c>
       <c r="D10" t="n">
-        <v>80.34999999999999</v>
+        <v>26.27</v>
       </c>
       <c r="E10" t="n">
-        <v>-4.19</v>
+        <v>1.1</v>
       </c>
       <c r="F10" t="n">
-        <v>-2</v>
+        <v>-6.1</v>
       </c>
       <c r="G10" t="n">
-        <v>-6.2</v>
+        <v>-5.3</v>
       </c>
       <c r="H10" t="n">
-        <v>-4.2</v>
+        <v>0.8</v>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>HOLD (fairly valued)</t>
+          <t>TRIM/SHORT (overvalued)</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
@@ -904,16 +904,16 @@
         </is>
       </c>
       <c r="K10" t="n">
-        <v>76.37</v>
+        <v>25.49</v>
       </c>
       <c r="L10" t="n">
-        <v>73.13</v>
+        <v>25.72</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>ASC</t>
+          <t>TRMD</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -922,26 +922,26 @@
         </is>
       </c>
       <c r="C11" t="n">
-        <v>15.96</v>
+        <v>26.74</v>
       </c>
       <c r="D11" t="n">
-        <v>15.93</v>
+        <v>25.43</v>
       </c>
       <c r="E11" t="n">
-        <v>-0.16</v>
+        <v>-4.86</v>
       </c>
       <c r="F11" t="n">
-        <v>-10.8</v>
+        <v>-3.9</v>
       </c>
       <c r="G11" t="n">
-        <v>-10.9</v>
+        <v>-7.9</v>
       </c>
       <c r="H11" t="n">
-        <v>-0.1</v>
+        <v>-4</v>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>TRIM/SHORT (overvalued)</t>
+          <t>HOLD (fairly valued)</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
@@ -950,16 +950,16 @@
         </is>
       </c>
       <c r="K11" t="n">
-        <v>15.07</v>
+        <v>27.83</v>
       </c>
       <c r="L11" t="n">
-        <v>15.05</v>
+        <v>26.68</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>DHT</t>
+          <t>ASC</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -968,26 +968,26 @@
         </is>
       </c>
       <c r="C12" t="n">
-        <v>15.29</v>
+        <v>15.96</v>
       </c>
       <c r="D12" t="n">
-        <v>12.93</v>
+        <v>15.93</v>
       </c>
       <c r="E12" t="n">
-        <v>-15.41</v>
+        <v>-0.16</v>
       </c>
       <c r="F12" t="n">
-        <v>2.3</v>
+        <v>-8</v>
       </c>
       <c r="G12" t="n">
-        <v>-10.9</v>
+        <v>-8.1</v>
       </c>
       <c r="H12" t="n">
-        <v>-13.3</v>
+        <v>-0.1</v>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>HOLD (fairly valued)</t>
+          <t>TRIM/SHORT (overvalued)</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
@@ -996,16 +996,16 @@
         </is>
       </c>
       <c r="K12" t="n">
-        <v>17.32</v>
+        <v>15.07</v>
       </c>
       <c r="L12" t="n">
-        <v>15.08</v>
+        <v>15.05</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>TRMD</t>
+          <t>DHT</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -1014,26 +1014,26 @@
         </is>
       </c>
       <c r="C13" t="n">
-        <v>26.74</v>
+        <v>15.29</v>
       </c>
       <c r="D13" t="n">
-        <v>25.43</v>
+        <v>12.93</v>
       </c>
       <c r="E13" t="n">
-        <v>-4.86</v>
+        <v>-15.41</v>
       </c>
       <c r="F13" t="n">
-        <v>-7.2</v>
+        <v>4</v>
       </c>
       <c r="G13" t="n">
-        <v>-11</v>
+        <v>-9.4</v>
       </c>
       <c r="H13" t="n">
-        <v>-3.8</v>
+        <v>-13.5</v>
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>TRIM/SHORT (overvalued)</t>
+          <t>HOLD (fairly valued)</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
@@ -1042,16 +1042,16 @@
         </is>
       </c>
       <c r="K13" t="n">
-        <v>27.83</v>
+        <v>17.32</v>
       </c>
       <c r="L13" t="n">
-        <v>26.68</v>
+        <v>15.08</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>ECO</t>
+          <t>HAFN</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1060,22 +1060,22 @@
         </is>
       </c>
       <c r="C14" t="n">
-        <v>39.93</v>
+        <v>5.34</v>
       </c>
       <c r="D14" t="n">
-        <v>33.71</v>
+        <v>5.22</v>
       </c>
       <c r="E14" t="n">
-        <v>-15.58</v>
+        <v>-2.24</v>
       </c>
       <c r="F14" t="n">
-        <v>-10.2</v>
+        <v>-19.4</v>
       </c>
       <c r="G14" t="n">
-        <v>-22.2</v>
+        <v>-20.8</v>
       </c>
       <c r="H14" t="n">
-        <v>-12</v>
+        <v>-1.4</v>
       </c>
       <c r="I14" t="inlineStr">
         <is>
@@ -1088,16 +1088,16 @@
         </is>
       </c>
       <c r="K14" t="n">
-        <v>45.41</v>
+        <v>5.87</v>
       </c>
       <c r="L14" t="n">
-        <v>39.33</v>
+        <v>5.77</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>HAFN</t>
+          <t>FRO</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1106,22 +1106,22 @@
         </is>
       </c>
       <c r="C15" t="n">
-        <v>5.34</v>
+        <v>28.79</v>
       </c>
       <c r="D15" t="n">
-        <v>5.22</v>
+        <v>24.4</v>
       </c>
       <c r="E15" t="n">
-        <v>-2.24</v>
+        <v>-15.25</v>
       </c>
       <c r="F15" t="n">
-        <v>-21.1</v>
+        <v>-9.1</v>
       </c>
       <c r="G15" t="n">
-        <v>-22.5</v>
+        <v>-20.9</v>
       </c>
       <c r="H15" t="n">
-        <v>-1.4</v>
+        <v>-11.9</v>
       </c>
       <c r="I15" t="inlineStr">
         <is>
@@ -1134,16 +1134,16 @@
         </is>
       </c>
       <c r="K15" t="n">
-        <v>5.87</v>
+        <v>33.77</v>
       </c>
       <c r="L15" t="n">
-        <v>5.77</v>
+        <v>29.36</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>FRO</t>
+          <t>ECO</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1152,22 +1152,22 @@
         </is>
       </c>
       <c r="C16" t="n">
-        <v>28.79</v>
+        <v>39.93</v>
       </c>
       <c r="D16" t="n">
-        <v>24.4</v>
+        <v>33.71</v>
       </c>
       <c r="E16" t="n">
-        <v>-15.25</v>
+        <v>-15.58</v>
       </c>
       <c r="F16" t="n">
-        <v>-11.3</v>
+        <v>-8.699999999999999</v>
       </c>
       <c r="G16" t="n">
-        <v>-22.9</v>
+        <v>-21</v>
       </c>
       <c r="H16" t="n">
-        <v>-11.6</v>
+        <v>-12.2</v>
       </c>
       <c r="I16" t="inlineStr">
         <is>
@@ -1180,10 +1180,10 @@
         </is>
       </c>
       <c r="K16" t="n">
-        <v>33.77</v>
+        <v>45.41</v>
       </c>
       <c r="L16" t="n">
-        <v>29.36</v>
+        <v>39.33</v>
       </c>
     </row>
     <row r="17">
@@ -1207,13 +1207,13 @@
         <v>-9.51</v>
       </c>
       <c r="F17" t="n">
-        <v>-23.4</v>
+        <v>-21.8</v>
       </c>
       <c r="G17" t="n">
-        <v>-29.4</v>
+        <v>-28</v>
       </c>
       <c r="H17" t="n">
-        <v>-6.1</v>
+        <v>-6.2</v>
       </c>
       <c r="I17" t="inlineStr">
         <is>
@@ -1253,13 +1253,13 @@
         <v>-21.23</v>
       </c>
       <c r="F18" t="n">
-        <v>-35.9</v>
+        <v>-34.5</v>
       </c>
       <c r="G18" t="n">
-        <v>-45.6</v>
+        <v>-44.4</v>
       </c>
       <c r="H18" t="n">
-        <v>-9.699999999999999</v>
+        <v>-9.9</v>
       </c>
       <c r="I18" t="inlineStr">
         <is>

--- a/outputs/transaction_anchor_comparison.xlsx
+++ b/outputs/transaction_anchor_comparison.xlsx
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L18"/>
+  <dimension ref="A1:L20"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="8" customWidth="1" min="1" max="1"/>
@@ -1051,7 +1051,7 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>HAFN</t>
+          <t>GSL</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1060,22 +1060,22 @@
         </is>
       </c>
       <c r="C14" t="n">
-        <v>5.34</v>
+        <v>38.59</v>
       </c>
       <c r="D14" t="n">
-        <v>5.22</v>
+        <v>38.59</v>
       </c>
       <c r="E14" t="n">
-        <v>-2.24</v>
+        <v>0</v>
       </c>
       <c r="F14" t="n">
-        <v>-19.4</v>
+        <v>-18.5</v>
       </c>
       <c r="G14" t="n">
-        <v>-20.8</v>
+        <v>-18.5</v>
       </c>
       <c r="H14" t="n">
-        <v>-1.4</v>
+        <v>0</v>
       </c>
       <c r="I14" t="inlineStr">
         <is>
@@ -1088,16 +1088,16 @@
         </is>
       </c>
       <c r="K14" t="n">
-        <v>5.87</v>
+        <v>31.76</v>
       </c>
       <c r="L14" t="n">
-        <v>5.77</v>
+        <v>31.76</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>FRO</t>
+          <t>HAFN</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1106,22 +1106,22 @@
         </is>
       </c>
       <c r="C15" t="n">
-        <v>28.79</v>
+        <v>5.34</v>
       </c>
       <c r="D15" t="n">
-        <v>24.4</v>
+        <v>5.22</v>
       </c>
       <c r="E15" t="n">
-        <v>-15.25</v>
+        <v>-2.24</v>
       </c>
       <c r="F15" t="n">
-        <v>-9.1</v>
+        <v>-19.4</v>
       </c>
       <c r="G15" t="n">
-        <v>-20.9</v>
+        <v>-20.8</v>
       </c>
       <c r="H15" t="n">
-        <v>-11.9</v>
+        <v>-1.4</v>
       </c>
       <c r="I15" t="inlineStr">
         <is>
@@ -1134,16 +1134,16 @@
         </is>
       </c>
       <c r="K15" t="n">
-        <v>33.77</v>
+        <v>5.87</v>
       </c>
       <c r="L15" t="n">
-        <v>29.36</v>
+        <v>5.77</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>ECO</t>
+          <t>FRO</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1152,22 +1152,22 @@
         </is>
       </c>
       <c r="C16" t="n">
-        <v>39.93</v>
+        <v>28.79</v>
       </c>
       <c r="D16" t="n">
-        <v>33.71</v>
+        <v>24.4</v>
       </c>
       <c r="E16" t="n">
-        <v>-15.58</v>
+        <v>-15.25</v>
       </c>
       <c r="F16" t="n">
-        <v>-8.699999999999999</v>
+        <v>-9.1</v>
       </c>
       <c r="G16" t="n">
-        <v>-21</v>
+        <v>-20.9</v>
       </c>
       <c r="H16" t="n">
-        <v>-12.2</v>
+        <v>-11.9</v>
       </c>
       <c r="I16" t="inlineStr">
         <is>
@@ -1180,40 +1180,40 @@
         </is>
       </c>
       <c r="K16" t="n">
-        <v>45.41</v>
+        <v>33.77</v>
       </c>
       <c r="L16" t="n">
-        <v>39.33</v>
+        <v>29.36</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>INSW</t>
+          <t>ECO</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>WHOLE-COMPANY (hybrid aggregation)</t>
+          <t>whole-company</t>
         </is>
       </c>
       <c r="C17" t="n">
-        <v>57.91</v>
+        <v>39.93</v>
       </c>
       <c r="D17" t="n">
-        <v>52.4</v>
+        <v>33.71</v>
       </c>
       <c r="E17" t="n">
-        <v>-9.51</v>
+        <v>-15.58</v>
       </c>
       <c r="F17" t="n">
-        <v>-21.8</v>
+        <v>-8.699999999999999</v>
       </c>
       <c r="G17" t="n">
-        <v>-28</v>
+        <v>-21</v>
       </c>
       <c r="H17" t="n">
-        <v>-6.2</v>
+        <v>-12.2</v>
       </c>
       <c r="I17" t="inlineStr">
         <is>
@@ -1226,55 +1226,147 @@
         </is>
       </c>
       <c r="K17" t="n">
-        <v>64.59</v>
+        <v>45.41</v>
       </c>
       <c r="L17" t="n">
-        <v>59.47</v>
+        <v>39.33</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
+          <t>INSW</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>WHOLE-COMPANY (hybrid aggregation)</t>
+        </is>
+      </c>
+      <c r="C18" t="n">
+        <v>57.91</v>
+      </c>
+      <c r="D18" t="n">
+        <v>52.4</v>
+      </c>
+      <c r="E18" t="n">
+        <v>-9.51</v>
+      </c>
+      <c r="F18" t="n">
+        <v>-21.8</v>
+      </c>
+      <c r="G18" t="n">
+        <v>-28</v>
+      </c>
+      <c r="H18" t="n">
+        <v>-6.2</v>
+      </c>
+      <c r="I18" t="inlineStr">
+        <is>
+          <t>TRIM/SHORT (overvalued)</t>
+        </is>
+      </c>
+      <c r="J18" t="inlineStr">
+        <is>
+          <t>TRIM/SHORT (overvalued)</t>
+        </is>
+      </c>
+      <c r="K18" t="n">
+        <v>64.59</v>
+      </c>
+      <c r="L18" t="n">
+        <v>59.47</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>MPCC</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>whole-company</t>
+        </is>
+      </c>
+      <c r="C19" t="n">
+        <v>2.27</v>
+      </c>
+      <c r="D19" t="n">
+        <v>2.27</v>
+      </c>
+      <c r="E19" t="n">
+        <v>0</v>
+      </c>
+      <c r="F19" t="n">
+        <v>-29.6</v>
+      </c>
+      <c r="G19" t="n">
+        <v>-29.6</v>
+      </c>
+      <c r="H19" t="n">
+        <v>0</v>
+      </c>
+      <c r="I19" t="inlineStr">
+        <is>
+          <t>TRIM/SHORT (overvalued)</t>
+        </is>
+      </c>
+      <c r="J19" t="inlineStr">
+        <is>
+          <t>TRIM/SHORT (overvalued)</t>
+        </is>
+      </c>
+      <c r="K19" t="n">
+        <v>1.96</v>
+      </c>
+      <c r="L19" t="n">
+        <v>1.96</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
           <t>NAT</t>
         </is>
       </c>
-      <c r="B18" t="inlineStr">
-        <is>
-          <t>whole-company</t>
-        </is>
-      </c>
-      <c r="C18" t="n">
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>whole-company</t>
+        </is>
+      </c>
+      <c r="C20" t="n">
         <v>2.63</v>
       </c>
-      <c r="D18" t="n">
+      <c r="D20" t="n">
         <v>2.07</v>
       </c>
-      <c r="E18" t="n">
+      <c r="E20" t="n">
         <v>-21.23</v>
       </c>
-      <c r="F18" t="n">
+      <c r="F20" t="n">
         <v>-34.5</v>
       </c>
-      <c r="G18" t="n">
+      <c r="G20" t="n">
         <v>-44.4</v>
       </c>
-      <c r="H18" t="n">
+      <c r="H20" t="n">
         <v>-9.9</v>
       </c>
-      <c r="I18" t="inlineStr">
-        <is>
-          <t>TRIM/SHORT (overvalued)</t>
-        </is>
-      </c>
-      <c r="J18" t="inlineStr">
-        <is>
-          <t>TRIM/SHORT (overvalued)</t>
-        </is>
-      </c>
-      <c r="K18" t="n">
+      <c r="I20" t="inlineStr">
+        <is>
+          <t>TRIM/SHORT (overvalued)</t>
+        </is>
+      </c>
+      <c r="J20" t="inlineStr">
+        <is>
+          <t>TRIM/SHORT (overvalued)</t>
+        </is>
+      </c>
+      <c r="K20" t="n">
         <v>3.37</v>
       </c>
-      <c r="L18" t="n">
+      <c r="L20" t="n">
         <v>2.86</v>
       </c>
     </row>

--- a/outputs/transaction_anchor_comparison.xlsx
+++ b/outputs/transaction_anchor_comparison.xlsx
@@ -511,19 +511,19 @@
         <v>95.95</v>
       </c>
       <c r="D2" t="n">
-        <v>88.13</v>
+        <v>87.56</v>
       </c>
       <c r="E2" t="n">
-        <v>-8.15</v>
+        <v>-8.74</v>
       </c>
       <c r="F2" t="n">
         <v>82.7</v>
       </c>
       <c r="G2" t="n">
-        <v>68.59999999999999</v>
+        <v>67.7</v>
       </c>
       <c r="H2" t="n">
-        <v>-14.1</v>
+        <v>-15</v>
       </c>
       <c r="I2" t="inlineStr">
         <is>
@@ -539,7 +539,7 @@
         <v>67.81</v>
       </c>
       <c r="L2" t="n">
-        <v>62.56</v>
+        <v>62.23</v>
       </c>
     </row>
     <row r="3">
@@ -560,7 +560,7 @@
         <v>17.74</v>
       </c>
       <c r="E3" t="n">
-        <v>-0.96</v>
+        <v>-0.95</v>
       </c>
       <c r="F3" t="n">
         <v>41.9</v>
@@ -649,19 +649,19 @@
         <v>32.62</v>
       </c>
       <c r="D5" t="n">
-        <v>32.23</v>
+        <v>32.49</v>
       </c>
       <c r="E5" t="n">
-        <v>-1.22</v>
+        <v>-0.42</v>
       </c>
       <c r="F5" t="n">
         <v>14</v>
       </c>
       <c r="G5" t="n">
-        <v>12.6</v>
+        <v>13.5</v>
       </c>
       <c r="H5" t="n">
-        <v>-1.4</v>
+        <v>-0.5</v>
       </c>
       <c r="I5" t="inlineStr">
         <is>
@@ -677,7 +677,7 @@
         <v>20.06</v>
       </c>
       <c r="L5" t="n">
-        <v>19.82</v>
+        <v>19.98</v>
       </c>
     </row>
     <row r="6">
@@ -695,19 +695,19 @@
         <v>25.4</v>
       </c>
       <c r="D6" t="n">
-        <v>26.24</v>
+        <v>26.27</v>
       </c>
       <c r="E6" t="n">
-        <v>3.33</v>
+        <v>3.44</v>
       </c>
       <c r="F6" t="n">
         <v>5.6</v>
       </c>
       <c r="G6" t="n">
-        <v>8.6</v>
+        <v>8.699999999999999</v>
       </c>
       <c r="H6" t="n">
-        <v>3</v>
+        <v>3.1</v>
       </c>
       <c r="I6" t="inlineStr">
         <is>
@@ -723,7 +723,7 @@
         <v>25.02</v>
       </c>
       <c r="L6" t="n">
-        <v>25.73</v>
+        <v>25.76</v>
       </c>
     </row>
     <row r="7">
@@ -741,10 +741,10 @@
         <v>83.31999999999999</v>
       </c>
       <c r="D7" t="n">
-        <v>77.45</v>
+        <v>77.47</v>
       </c>
       <c r="E7" t="n">
-        <v>-7.04</v>
+        <v>-7.01</v>
       </c>
       <c r="F7" t="n">
         <v>8.800000000000001</v>
@@ -753,7 +753,7 @@
         <v>1.7</v>
       </c>
       <c r="H7" t="n">
-        <v>-7.2</v>
+        <v>-7.1</v>
       </c>
       <c r="I7" t="inlineStr">
         <is>
@@ -769,7 +769,7 @@
         <v>78.90000000000001</v>
       </c>
       <c r="L7" t="n">
-        <v>73.7</v>
+        <v>73.72</v>
       </c>
     </row>
     <row r="8">
@@ -879,19 +879,19 @@
         <v>25.98</v>
       </c>
       <c r="D10" t="n">
-        <v>26.27</v>
+        <v>26.57</v>
       </c>
       <c r="E10" t="n">
-        <v>1.1</v>
+        <v>2.28</v>
       </c>
       <c r="F10" t="n">
         <v>-6.1</v>
       </c>
       <c r="G10" t="n">
-        <v>-5.3</v>
+        <v>-4.3</v>
       </c>
       <c r="H10" t="n">
-        <v>0.8</v>
+        <v>1.8</v>
       </c>
       <c r="I10" t="inlineStr">
         <is>
@@ -900,14 +900,14 @@
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>TRIM/SHORT (overvalued)</t>
+          <t>HOLD (fairly valued)</t>
         </is>
       </c>
       <c r="K10" t="n">
         <v>25.49</v>
       </c>
       <c r="L10" t="n">
-        <v>25.72</v>
+        <v>25.98</v>
       </c>
     </row>
     <row r="11">
@@ -1247,10 +1247,10 @@
         <v>57.91</v>
       </c>
       <c r="D18" t="n">
-        <v>52.4</v>
+        <v>52.39</v>
       </c>
       <c r="E18" t="n">
-        <v>-9.51</v>
+        <v>-9.529999999999999</v>
       </c>
       <c r="F18" t="n">
         <v>-21.8</v>

--- a/outputs/transaction_anchor_comparison.xlsx
+++ b/outputs/transaction_anchor_comparison.xlsx
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L20"/>
+  <dimension ref="A1:L21"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="8" customWidth="1" min="1" max="1"/>
@@ -499,7 +499,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>TEN</t>
+          <t>BRUT</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -508,22 +508,22 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>95.95</v>
+        <v>9.4</v>
       </c>
       <c r="D2" t="n">
-        <v>87.56</v>
+        <v>9.4</v>
       </c>
       <c r="E2" t="n">
-        <v>-8.74</v>
+        <v>0</v>
       </c>
       <c r="F2" t="n">
-        <v>82.7</v>
+        <v>100</v>
       </c>
       <c r="G2" t="n">
-        <v>67.7</v>
+        <v>97.3</v>
       </c>
       <c r="H2" t="n">
-        <v>-15</v>
+        <v>-2.7</v>
       </c>
       <c r="I2" t="inlineStr">
         <is>
@@ -536,16 +536,16 @@
         </is>
       </c>
       <c r="K2" t="n">
-        <v>67.81</v>
+        <v>10.8</v>
       </c>
       <c r="L2" t="n">
-        <v>62.23</v>
+        <v>10.65</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>CAPT</t>
+          <t>TEN</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -554,22 +554,22 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>17.91</v>
+        <v>95.95</v>
       </c>
       <c r="D3" t="n">
-        <v>17.74</v>
+        <v>87.56</v>
       </c>
       <c r="E3" t="n">
-        <v>-0.95</v>
+        <v>-8.74</v>
       </c>
       <c r="F3" t="n">
-        <v>41.9</v>
+        <v>77.09999999999999</v>
       </c>
       <c r="G3" t="n">
-        <v>38.2</v>
+        <v>62.5</v>
       </c>
       <c r="H3" t="n">
-        <v>-3.7</v>
+        <v>-14.6</v>
       </c>
       <c r="I3" t="inlineStr">
         <is>
@@ -582,10 +582,10 @@
         </is>
       </c>
       <c r="K3" t="n">
-        <v>18.15</v>
+        <v>67.81</v>
       </c>
       <c r="L3" t="n">
-        <v>17.68</v>
+        <v>62.23</v>
       </c>
     </row>
     <row r="4">
@@ -609,10 +609,10 @@
         <v>0</v>
       </c>
       <c r="F4" t="n">
-        <v>37.7</v>
+        <v>47.9</v>
       </c>
       <c r="G4" t="n">
-        <v>37.7</v>
+        <v>47.9</v>
       </c>
       <c r="H4" t="n">
         <v>0</v>
@@ -637,7 +637,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>CMDB</t>
+          <t>CAPT</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -646,22 +646,22 @@
         </is>
       </c>
       <c r="C5" t="n">
-        <v>32.62</v>
+        <v>15.22</v>
       </c>
       <c r="D5" t="n">
-        <v>32.49</v>
+        <v>15.05</v>
       </c>
       <c r="E5" t="n">
-        <v>-0.42</v>
+        <v>-1.12</v>
       </c>
       <c r="F5" t="n">
-        <v>14</v>
+        <v>24.6</v>
       </c>
       <c r="G5" t="n">
-        <v>13.5</v>
+        <v>22.4</v>
       </c>
       <c r="H5" t="n">
-        <v>-0.5</v>
+        <v>-2.3</v>
       </c>
       <c r="I5" t="inlineStr">
         <is>
@@ -674,16 +674,16 @@
         </is>
       </c>
       <c r="K5" t="n">
-        <v>20.06</v>
+        <v>16.5</v>
       </c>
       <c r="L5" t="n">
-        <v>19.98</v>
+        <v>16.2</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>GNK</t>
+          <t>CMDB</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -692,22 +692,22 @@
         </is>
       </c>
       <c r="C6" t="n">
-        <v>25.4</v>
+        <v>32.62</v>
       </c>
       <c r="D6" t="n">
-        <v>26.27</v>
+        <v>32.49</v>
       </c>
       <c r="E6" t="n">
-        <v>3.44</v>
+        <v>-0.42</v>
       </c>
       <c r="F6" t="n">
-        <v>5.6</v>
+        <v>18.7</v>
       </c>
       <c r="G6" t="n">
-        <v>8.699999999999999</v>
+        <v>18.2</v>
       </c>
       <c r="H6" t="n">
-        <v>3.1</v>
+        <v>-0.5</v>
       </c>
       <c r="I6" t="inlineStr">
         <is>
@@ -720,16 +720,16 @@
         </is>
       </c>
       <c r="K6" t="n">
-        <v>25.02</v>
+        <v>20.06</v>
       </c>
       <c r="L6" t="n">
-        <v>25.76</v>
+        <v>19.98</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>TNK</t>
+          <t>GNK</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -738,22 +738,22 @@
         </is>
       </c>
       <c r="C7" t="n">
-        <v>83.31999999999999</v>
+        <v>25.4</v>
       </c>
       <c r="D7" t="n">
-        <v>77.47</v>
+        <v>26.27</v>
       </c>
       <c r="E7" t="n">
-        <v>-7.01</v>
+        <v>3.44</v>
       </c>
       <c r="F7" t="n">
+        <v>5.7</v>
+      </c>
+      <c r="G7" t="n">
         <v>8.800000000000001</v>
       </c>
-      <c r="G7" t="n">
-        <v>1.7</v>
-      </c>
       <c r="H7" t="n">
-        <v>-7.1</v>
+        <v>3.1</v>
       </c>
       <c r="I7" t="inlineStr">
         <is>
@@ -762,20 +762,20 @@
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>HOLD (fairly valued)</t>
+          <t>BUY (undervalued)</t>
         </is>
       </c>
       <c r="K7" t="n">
-        <v>78.90000000000001</v>
+        <v>25.02</v>
       </c>
       <c r="L7" t="n">
-        <v>73.72</v>
+        <v>25.76</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>FLNG</t>
+          <t>SBLK</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -784,22 +784,22 @@
         </is>
       </c>
       <c r="C8" t="n">
-        <v>28.45</v>
+        <v>25.98</v>
       </c>
       <c r="D8" t="n">
-        <v>28.45</v>
+        <v>26.57</v>
       </c>
       <c r="E8" t="n">
-        <v>0</v>
+        <v>2.28</v>
       </c>
       <c r="F8" t="n">
-        <v>-2.5</v>
+        <v>-1.2</v>
       </c>
       <c r="G8" t="n">
-        <v>-2.5</v>
+        <v>0.6</v>
       </c>
       <c r="H8" t="n">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="I8" t="inlineStr">
         <is>
@@ -812,16 +812,16 @@
         </is>
       </c>
       <c r="K8" t="n">
-        <v>29.73</v>
+        <v>25.49</v>
       </c>
       <c r="L8" t="n">
-        <v>29.73</v>
+        <v>25.98</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>STNG</t>
+          <t>FLNG</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -830,22 +830,22 @@
         </is>
       </c>
       <c r="C9" t="n">
-        <v>83.87</v>
+        <v>28.45</v>
       </c>
       <c r="D9" t="n">
-        <v>80.34999999999999</v>
+        <v>28.45</v>
       </c>
       <c r="E9" t="n">
-        <v>-4.19</v>
+        <v>0</v>
       </c>
       <c r="F9" t="n">
-        <v>0.3</v>
+        <v>-0</v>
       </c>
       <c r="G9" t="n">
-        <v>-4</v>
+        <v>-0</v>
       </c>
       <c r="H9" t="n">
-        <v>-4.3</v>
+        <v>0</v>
       </c>
       <c r="I9" t="inlineStr">
         <is>
@@ -858,16 +858,16 @@
         </is>
       </c>
       <c r="K9" t="n">
-        <v>76.37</v>
+        <v>29.73</v>
       </c>
       <c r="L9" t="n">
-        <v>73.13</v>
+        <v>29.73</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>SBLK</t>
+          <t>TNK</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -876,26 +876,26 @@
         </is>
       </c>
       <c r="C10" t="n">
-        <v>25.98</v>
+        <v>83.31999999999999</v>
       </c>
       <c r="D10" t="n">
-        <v>26.57</v>
+        <v>77.47</v>
       </c>
       <c r="E10" t="n">
-        <v>2.28</v>
+        <v>-7.01</v>
       </c>
       <c r="F10" t="n">
-        <v>-6.1</v>
+        <v>6</v>
       </c>
       <c r="G10" t="n">
-        <v>-4.3</v>
+        <v>-1</v>
       </c>
       <c r="H10" t="n">
-        <v>1.8</v>
+        <v>-7</v>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>TRIM/SHORT (overvalued)</t>
+          <t>BUY (undervalued)</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
@@ -904,16 +904,16 @@
         </is>
       </c>
       <c r="K10" t="n">
-        <v>25.49</v>
+        <v>78.90000000000001</v>
       </c>
       <c r="L10" t="n">
-        <v>25.98</v>
+        <v>73.72</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>TRMD</t>
+          <t>STNG</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -922,26 +922,26 @@
         </is>
       </c>
       <c r="C11" t="n">
-        <v>26.74</v>
+        <v>83.87</v>
       </c>
       <c r="D11" t="n">
-        <v>25.43</v>
+        <v>80.34999999999999</v>
       </c>
       <c r="E11" t="n">
-        <v>-4.86</v>
+        <v>-4.19</v>
       </c>
       <c r="F11" t="n">
-        <v>-3.9</v>
+        <v>-5.2</v>
       </c>
       <c r="G11" t="n">
-        <v>-7.9</v>
+        <v>-9.199999999999999</v>
       </c>
       <c r="H11" t="n">
         <v>-4</v>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>HOLD (fairly valued)</t>
+          <t>TRIM/SHORT (overvalued)</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
@@ -950,16 +950,16 @@
         </is>
       </c>
       <c r="K11" t="n">
-        <v>27.83</v>
+        <v>76.37</v>
       </c>
       <c r="L11" t="n">
-        <v>26.68</v>
+        <v>73.13</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>ASC</t>
+          <t>TRMD</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -968,22 +968,22 @@
         </is>
       </c>
       <c r="C12" t="n">
-        <v>15.96</v>
+        <v>26.74</v>
       </c>
       <c r="D12" t="n">
-        <v>15.93</v>
+        <v>25.43</v>
       </c>
       <c r="E12" t="n">
-        <v>-0.16</v>
+        <v>-4.86</v>
       </c>
       <c r="F12" t="n">
-        <v>-8</v>
+        <v>-5.4</v>
       </c>
       <c r="G12" t="n">
-        <v>-8.1</v>
+        <v>-9.300000000000001</v>
       </c>
       <c r="H12" t="n">
-        <v>-0.1</v>
+        <v>-3.9</v>
       </c>
       <c r="I12" t="inlineStr">
         <is>
@@ -996,16 +996,16 @@
         </is>
       </c>
       <c r="K12" t="n">
-        <v>15.07</v>
+        <v>27.83</v>
       </c>
       <c r="L12" t="n">
-        <v>15.05</v>
+        <v>26.68</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>DHT</t>
+          <t>ASC</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -1014,26 +1014,26 @@
         </is>
       </c>
       <c r="C13" t="n">
-        <v>15.29</v>
+        <v>15.96</v>
       </c>
       <c r="D13" t="n">
-        <v>12.93</v>
+        <v>15.93</v>
       </c>
       <c r="E13" t="n">
-        <v>-15.41</v>
+        <v>-0.16</v>
       </c>
       <c r="F13" t="n">
-        <v>4</v>
+        <v>-11.7</v>
       </c>
       <c r="G13" t="n">
-        <v>-9.4</v>
+        <v>-11.8</v>
       </c>
       <c r="H13" t="n">
-        <v>-13.5</v>
+        <v>-0.1</v>
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>HOLD (fairly valued)</t>
+          <t>TRIM/SHORT (overvalued)</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
@@ -1042,10 +1042,10 @@
         </is>
       </c>
       <c r="K13" t="n">
-        <v>17.32</v>
+        <v>15.07</v>
       </c>
       <c r="L13" t="n">
-        <v>15.08</v>
+        <v>15.05</v>
       </c>
     </row>
     <row r="14">
@@ -1069,10 +1069,10 @@
         <v>0</v>
       </c>
       <c r="F14" t="n">
-        <v>-18.5</v>
+        <v>-16.2</v>
       </c>
       <c r="G14" t="n">
-        <v>-18.5</v>
+        <v>-16.2</v>
       </c>
       <c r="H14" t="n">
         <v>0</v>
@@ -1097,7 +1097,7 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>HAFN</t>
+          <t>DHT</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1106,22 +1106,22 @@
         </is>
       </c>
       <c r="C15" t="n">
-        <v>5.34</v>
+        <v>15.29</v>
       </c>
       <c r="D15" t="n">
-        <v>5.22</v>
+        <v>12.93</v>
       </c>
       <c r="E15" t="n">
-        <v>-2.24</v>
+        <v>-15.41</v>
       </c>
       <c r="F15" t="n">
-        <v>-19.4</v>
+        <v>-8.300000000000001</v>
       </c>
       <c r="G15" t="n">
-        <v>-20.8</v>
+        <v>-20.2</v>
       </c>
       <c r="H15" t="n">
-        <v>-1.4</v>
+        <v>-11.9</v>
       </c>
       <c r="I15" t="inlineStr">
         <is>
@@ -1134,16 +1134,16 @@
         </is>
       </c>
       <c r="K15" t="n">
-        <v>5.87</v>
+        <v>17.32</v>
       </c>
       <c r="L15" t="n">
-        <v>5.77</v>
+        <v>15.08</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>FRO</t>
+          <t>HAFN</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1152,22 +1152,22 @@
         </is>
       </c>
       <c r="C16" t="n">
-        <v>28.79</v>
+        <v>5.34</v>
       </c>
       <c r="D16" t="n">
-        <v>24.4</v>
+        <v>5.22</v>
       </c>
       <c r="E16" t="n">
-        <v>-15.25</v>
+        <v>-2.24</v>
       </c>
       <c r="F16" t="n">
-        <v>-9.1</v>
+        <v>-18.8</v>
       </c>
       <c r="G16" t="n">
-        <v>-20.9</v>
+        <v>-20.3</v>
       </c>
       <c r="H16" t="n">
-        <v>-11.9</v>
+        <v>-1.4</v>
       </c>
       <c r="I16" t="inlineStr">
         <is>
@@ -1180,10 +1180,10 @@
         </is>
       </c>
       <c r="K16" t="n">
-        <v>33.77</v>
+        <v>5.87</v>
       </c>
       <c r="L16" t="n">
-        <v>29.36</v>
+        <v>5.77</v>
       </c>
     </row>
     <row r="17">
@@ -1207,13 +1207,13 @@
         <v>-15.58</v>
       </c>
       <c r="F17" t="n">
-        <v>-8.699999999999999</v>
+        <v>-13.5</v>
       </c>
       <c r="G17" t="n">
-        <v>-21</v>
+        <v>-25.1</v>
       </c>
       <c r="H17" t="n">
-        <v>-12.2</v>
+        <v>-11.6</v>
       </c>
       <c r="I17" t="inlineStr">
         <is>
@@ -1235,31 +1235,31 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>INSW</t>
+          <t>MPCC</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>WHOLE-COMPANY (hybrid aggregation)</t>
+          <t>whole-company</t>
         </is>
       </c>
       <c r="C18" t="n">
-        <v>57.91</v>
+        <v>2.02</v>
       </c>
       <c r="D18" t="n">
-        <v>52.39</v>
+        <v>2.02</v>
       </c>
       <c r="E18" t="n">
-        <v>-9.529999999999999</v>
+        <v>0</v>
       </c>
       <c r="F18" t="n">
-        <v>-21.8</v>
+        <v>-27.3</v>
       </c>
       <c r="G18" t="n">
-        <v>-28</v>
+        <v>-27.3</v>
       </c>
       <c r="H18" t="n">
-        <v>-6.2</v>
+        <v>0</v>
       </c>
       <c r="I18" t="inlineStr">
         <is>
@@ -1272,16 +1272,16 @@
         </is>
       </c>
       <c r="K18" t="n">
-        <v>64.59</v>
+        <v>1.85</v>
       </c>
       <c r="L18" t="n">
-        <v>59.47</v>
+        <v>1.85</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>MPCC</t>
+          <t>FRO</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1290,22 +1290,22 @@
         </is>
       </c>
       <c r="C19" t="n">
-        <v>2.27</v>
+        <v>28.47</v>
       </c>
       <c r="D19" t="n">
-        <v>2.27</v>
+        <v>24.08</v>
       </c>
       <c r="E19" t="n">
-        <v>0</v>
+        <v>-15.42</v>
       </c>
       <c r="F19" t="n">
-        <v>-29.6</v>
+        <v>-18</v>
       </c>
       <c r="G19" t="n">
-        <v>-29.6</v>
+        <v>-28.7</v>
       </c>
       <c r="H19" t="n">
-        <v>0</v>
+        <v>-10.7</v>
       </c>
       <c r="I19" t="inlineStr">
         <is>
@@ -1318,55 +1318,101 @@
         </is>
       </c>
       <c r="K19" t="n">
-        <v>1.96</v>
+        <v>33.57</v>
       </c>
       <c r="L19" t="n">
-        <v>1.96</v>
+        <v>29.18</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
+          <t>INSW</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>WHOLE-COMPANY (hybrid aggregation)</t>
+        </is>
+      </c>
+      <c r="C20" t="n">
+        <v>57.91</v>
+      </c>
+      <c r="D20" t="n">
+        <v>52.39</v>
+      </c>
+      <c r="E20" t="n">
+        <v>-9.529999999999999</v>
+      </c>
+      <c r="F20" t="n">
+        <v>-23.6</v>
+      </c>
+      <c r="G20" t="n">
+        <v>-29.6</v>
+      </c>
+      <c r="H20" t="n">
+        <v>-6.1</v>
+      </c>
+      <c r="I20" t="inlineStr">
+        <is>
+          <t>TRIM/SHORT (overvalued)</t>
+        </is>
+      </c>
+      <c r="J20" t="inlineStr">
+        <is>
+          <t>TRIM/SHORT (overvalued)</t>
+        </is>
+      </c>
+      <c r="K20" t="n">
+        <v>64.59</v>
+      </c>
+      <c r="L20" t="n">
+        <v>59.47</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
           <t>NAT</t>
         </is>
       </c>
-      <c r="B20" t="inlineStr">
-        <is>
-          <t>whole-company</t>
-        </is>
-      </c>
-      <c r="C20" t="n">
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>whole-company</t>
+        </is>
+      </c>
+      <c r="C21" t="n">
         <v>2.63</v>
       </c>
-      <c r="D20" t="n">
+      <c r="D21" t="n">
         <v>2.07</v>
       </c>
-      <c r="E20" t="n">
+      <c r="E21" t="n">
         <v>-21.23</v>
       </c>
-      <c r="F20" t="n">
-        <v>-34.5</v>
-      </c>
-      <c r="G20" t="n">
-        <v>-44.4</v>
-      </c>
-      <c r="H20" t="n">
-        <v>-9.9</v>
-      </c>
-      <c r="I20" t="inlineStr">
-        <is>
-          <t>TRIM/SHORT (overvalued)</t>
-        </is>
-      </c>
-      <c r="J20" t="inlineStr">
-        <is>
-          <t>TRIM/SHORT (overvalued)</t>
-        </is>
-      </c>
-      <c r="K20" t="n">
+      <c r="F21" t="n">
+        <v>-42.4</v>
+      </c>
+      <c r="G21" t="n">
+        <v>-51.1</v>
+      </c>
+      <c r="H21" t="n">
+        <v>-8.699999999999999</v>
+      </c>
+      <c r="I21" t="inlineStr">
+        <is>
+          <t>TRIM/SHORT (overvalued)</t>
+        </is>
+      </c>
+      <c r="J21" t="inlineStr">
+        <is>
+          <t>TRIM/SHORT (overvalued)</t>
+        </is>
+      </c>
+      <c r="K21" t="n">
         <v>3.37</v>
       </c>
-      <c r="L20" t="n">
+      <c r="L21" t="n">
         <v>2.86</v>
       </c>
     </row>

--- a/outputs/transaction_anchor_comparison.xlsx
+++ b/outputs/transaction_anchor_comparison.xlsx
@@ -646,10 +646,10 @@
         </is>
       </c>
       <c r="C5" t="n">
-        <v>15.22</v>
+        <v>15.2</v>
       </c>
       <c r="D5" t="n">
-        <v>15.05</v>
+        <v>15.03</v>
       </c>
       <c r="E5" t="n">
         <v>-1.12</v>
@@ -661,7 +661,7 @@
         <v>22.4</v>
       </c>
       <c r="H5" t="n">
-        <v>-2.3</v>
+        <v>-2.2</v>
       </c>
       <c r="I5" t="inlineStr">
         <is>

--- a/outputs/transaction_anchor_comparison.xlsx
+++ b/outputs/transaction_anchor_comparison.xlsx
@@ -517,13 +517,13 @@
         <v>0</v>
       </c>
       <c r="F2" t="n">
-        <v>100</v>
+        <v>102.5</v>
       </c>
       <c r="G2" t="n">
-        <v>97.3</v>
+        <v>100.1</v>
       </c>
       <c r="H2" t="n">
-        <v>-2.7</v>
+        <v>-2.4</v>
       </c>
       <c r="I2" t="inlineStr">
         <is>
@@ -536,16 +536,16 @@
         </is>
       </c>
       <c r="K2" t="n">
+        <v>10.93</v>
+      </c>
+      <c r="L2" t="n">
         <v>10.8</v>
-      </c>
-      <c r="L2" t="n">
-        <v>10.65</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>TEN</t>
+          <t>CCEC</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -554,22 +554,22 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>95.95</v>
+        <v>28.1</v>
       </c>
       <c r="D3" t="n">
-        <v>87.56</v>
+        <v>28.1</v>
       </c>
       <c r="E3" t="n">
-        <v>-8.74</v>
+        <v>0</v>
       </c>
       <c r="F3" t="n">
-        <v>77.09999999999999</v>
+        <v>79.3</v>
       </c>
       <c r="G3" t="n">
-        <v>62.5</v>
+        <v>79.3</v>
       </c>
       <c r="H3" t="n">
-        <v>-14.6</v>
+        <v>0</v>
       </c>
       <c r="I3" t="inlineStr">
         <is>
@@ -582,16 +582,16 @@
         </is>
       </c>
       <c r="K3" t="n">
-        <v>67.81</v>
+        <v>35.91</v>
       </c>
       <c r="L3" t="n">
-        <v>62.23</v>
+        <v>35.91</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>CCEC</t>
+          <t>TEN</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -600,22 +600,22 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>28.1</v>
+        <v>95.95</v>
       </c>
       <c r="D4" t="n">
-        <v>28.1</v>
+        <v>87.56</v>
       </c>
       <c r="E4" t="n">
-        <v>0</v>
+        <v>-8.74</v>
       </c>
       <c r="F4" t="n">
-        <v>47.9</v>
+        <v>83.59999999999999</v>
       </c>
       <c r="G4" t="n">
-        <v>47.9</v>
+        <v>69.3</v>
       </c>
       <c r="H4" t="n">
-        <v>0</v>
+        <v>-14.2</v>
       </c>
       <c r="I4" t="inlineStr">
         <is>
@@ -628,10 +628,10 @@
         </is>
       </c>
       <c r="K4" t="n">
-        <v>29.63</v>
+        <v>70.29000000000001</v>
       </c>
       <c r="L4" t="n">
-        <v>29.63</v>
+        <v>64.84</v>
       </c>
     </row>
     <row r="5">
@@ -655,13 +655,13 @@
         <v>-1.12</v>
       </c>
       <c r="F5" t="n">
-        <v>24.6</v>
+        <v>28.8</v>
       </c>
       <c r="G5" t="n">
-        <v>22.4</v>
+        <v>26.7</v>
       </c>
       <c r="H5" t="n">
-        <v>-2.2</v>
+        <v>-2.1</v>
       </c>
       <c r="I5" t="inlineStr">
         <is>
@@ -674,10 +674,10 @@
         </is>
       </c>
       <c r="K5" t="n">
-        <v>16.5</v>
+        <v>17.05</v>
       </c>
       <c r="L5" t="n">
-        <v>16.2</v>
+        <v>16.77</v>
       </c>
     </row>
     <row r="6">
@@ -701,10 +701,10 @@
         <v>-0.42</v>
       </c>
       <c r="F6" t="n">
-        <v>18.7</v>
+        <v>25.5</v>
       </c>
       <c r="G6" t="n">
-        <v>18.2</v>
+        <v>25</v>
       </c>
       <c r="H6" t="n">
         <v>-0.5</v>
@@ -720,10 +720,10 @@
         </is>
       </c>
       <c r="K6" t="n">
-        <v>20.06</v>
+        <v>21.22</v>
       </c>
       <c r="L6" t="n">
-        <v>19.98</v>
+        <v>21.13</v>
       </c>
     </row>
     <row r="7">
@@ -747,35 +747,35 @@
         <v>3.44</v>
       </c>
       <c r="F7" t="n">
-        <v>5.7</v>
+        <v>4.2</v>
       </c>
       <c r="G7" t="n">
-        <v>8.800000000000001</v>
+        <v>7.3</v>
       </c>
       <c r="H7" t="n">
         <v>3.1</v>
       </c>
       <c r="I7" t="inlineStr">
         <is>
+          <t>HOLD (fairly valued)</t>
+        </is>
+      </c>
+      <c r="J7" t="inlineStr">
+        <is>
           <t>BUY (undervalued)</t>
         </is>
       </c>
-      <c r="J7" t="inlineStr">
-        <is>
-          <t>BUY (undervalued)</t>
-        </is>
-      </c>
       <c r="K7" t="n">
-        <v>25.02</v>
+        <v>24.69</v>
       </c>
       <c r="L7" t="n">
-        <v>25.76</v>
+        <v>25.41</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>SBLK</t>
+          <t>GSL</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -784,44 +784,44 @@
         </is>
       </c>
       <c r="C8" t="n">
-        <v>25.98</v>
+        <v>38.59</v>
       </c>
       <c r="D8" t="n">
-        <v>26.57</v>
+        <v>38.59</v>
       </c>
       <c r="E8" t="n">
-        <v>2.28</v>
+        <v>0</v>
       </c>
       <c r="F8" t="n">
-        <v>-1.2</v>
+        <v>7.1</v>
       </c>
       <c r="G8" t="n">
-        <v>0.6</v>
+        <v>7.1</v>
       </c>
       <c r="H8" t="n">
-        <v>1.9</v>
+        <v>0</v>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>HOLD (fairly valued)</t>
+          <t>BUY (undervalued)</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>HOLD (fairly valued)</t>
+          <t>BUY (undervalued)</t>
         </is>
       </c>
       <c r="K8" t="n">
-        <v>25.49</v>
+        <v>40.59</v>
       </c>
       <c r="L8" t="n">
-        <v>25.98</v>
+        <v>40.59</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>FLNG</t>
+          <t>TNK</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -830,44 +830,44 @@
         </is>
       </c>
       <c r="C9" t="n">
-        <v>28.45</v>
+        <v>83.31999999999999</v>
       </c>
       <c r="D9" t="n">
-        <v>28.45</v>
+        <v>77.47</v>
       </c>
       <c r="E9" t="n">
-        <v>0</v>
+        <v>-7.01</v>
       </c>
       <c r="F9" t="n">
-        <v>-0</v>
+        <v>13.7</v>
       </c>
       <c r="G9" t="n">
-        <v>-0</v>
+        <v>6.9</v>
       </c>
       <c r="H9" t="n">
-        <v>0</v>
+        <v>-6.8</v>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>HOLD (fairly valued)</t>
+          <t>BUY (undervalued)</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>HOLD (fairly valued)</t>
+          <t>BUY (undervalued)</t>
         </is>
       </c>
       <c r="K9" t="n">
-        <v>29.73</v>
+        <v>84.64</v>
       </c>
       <c r="L9" t="n">
-        <v>29.73</v>
+        <v>79.56</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>TNK</t>
+          <t>FLNG</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -876,26 +876,26 @@
         </is>
       </c>
       <c r="C10" t="n">
-        <v>83.31999999999999</v>
+        <v>28.45</v>
       </c>
       <c r="D10" t="n">
-        <v>77.47</v>
+        <v>28.45</v>
       </c>
       <c r="E10" t="n">
-        <v>-7.01</v>
+        <v>0</v>
       </c>
       <c r="F10" t="n">
-        <v>6</v>
+        <v>3.1</v>
       </c>
       <c r="G10" t="n">
-        <v>-1</v>
+        <v>3.1</v>
       </c>
       <c r="H10" t="n">
-        <v>-7</v>
+        <v>0</v>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>BUY (undervalued)</t>
+          <t>HOLD (fairly valued)</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
@@ -904,16 +904,16 @@
         </is>
       </c>
       <c r="K10" t="n">
-        <v>78.90000000000001</v>
+        <v>30.67</v>
       </c>
       <c r="L10" t="n">
-        <v>73.72</v>
+        <v>30.67</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>STNG</t>
+          <t>SBLK</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -922,44 +922,44 @@
         </is>
       </c>
       <c r="C11" t="n">
-        <v>83.87</v>
+        <v>25.98</v>
       </c>
       <c r="D11" t="n">
-        <v>80.34999999999999</v>
+        <v>26.57</v>
       </c>
       <c r="E11" t="n">
-        <v>-4.19</v>
+        <v>2.28</v>
       </c>
       <c r="F11" t="n">
-        <v>-5.2</v>
+        <v>-2</v>
       </c>
       <c r="G11" t="n">
-        <v>-9.199999999999999</v>
+        <v>-0.2</v>
       </c>
       <c r="H11" t="n">
-        <v>-4</v>
+        <v>1.9</v>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>TRIM/SHORT (overvalued)</t>
+          <t>HOLD (fairly valued)</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>TRIM/SHORT (overvalued)</t>
+          <t>HOLD (fairly valued)</t>
         </is>
       </c>
       <c r="K11" t="n">
-        <v>76.37</v>
+        <v>25.28</v>
       </c>
       <c r="L11" t="n">
-        <v>73.13</v>
+        <v>25.76</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>TRMD</t>
+          <t>STNG</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -968,44 +968,44 @@
         </is>
       </c>
       <c r="C12" t="n">
-        <v>26.74</v>
+        <v>83.87</v>
       </c>
       <c r="D12" t="n">
-        <v>25.43</v>
+        <v>80.34999999999999</v>
       </c>
       <c r="E12" t="n">
-        <v>-4.86</v>
+        <v>-4.19</v>
       </c>
       <c r="F12" t="n">
-        <v>-5.4</v>
+        <v>3.2</v>
       </c>
       <c r="G12" t="n">
-        <v>-9.300000000000001</v>
+        <v>-0.7</v>
       </c>
       <c r="H12" t="n">
         <v>-3.9</v>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>TRIM/SHORT (overvalued)</t>
+          <t>HOLD (fairly valued)</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>TRIM/SHORT (overvalued)</t>
+          <t>HOLD (fairly valued)</t>
         </is>
       </c>
       <c r="K12" t="n">
-        <v>27.83</v>
+        <v>83.16</v>
       </c>
       <c r="L12" t="n">
-        <v>26.68</v>
+        <v>79.98999999999999</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>ASC</t>
+          <t>TRMD</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -1014,26 +1014,26 @@
         </is>
       </c>
       <c r="C13" t="n">
-        <v>15.96</v>
+        <v>26.74</v>
       </c>
       <c r="D13" t="n">
-        <v>15.93</v>
+        <v>25.43</v>
       </c>
       <c r="E13" t="n">
-        <v>-0.16</v>
+        <v>-4.86</v>
       </c>
       <c r="F13" t="n">
-        <v>-11.7</v>
+        <v>-3.3</v>
       </c>
       <c r="G13" t="n">
-        <v>-11.8</v>
+        <v>-7.1</v>
       </c>
       <c r="H13" t="n">
-        <v>-0.1</v>
+        <v>-3.8</v>
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>TRIM/SHORT (overvalued)</t>
+          <t>HOLD (fairly valued)</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
@@ -1042,16 +1042,16 @@
         </is>
       </c>
       <c r="K13" t="n">
-        <v>15.07</v>
+        <v>28.45</v>
       </c>
       <c r="L13" t="n">
-        <v>15.05</v>
+        <v>27.32</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>GSL</t>
+          <t>ASC</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1060,22 +1060,22 @@
         </is>
       </c>
       <c r="C14" t="n">
-        <v>38.59</v>
+        <v>15.96</v>
       </c>
       <c r="D14" t="n">
-        <v>38.59</v>
+        <v>15.93</v>
       </c>
       <c r="E14" t="n">
-        <v>0</v>
+        <v>-0.16</v>
       </c>
       <c r="F14" t="n">
-        <v>-16.2</v>
+        <v>-11.1</v>
       </c>
       <c r="G14" t="n">
-        <v>-16.2</v>
+        <v>-11.3</v>
       </c>
       <c r="H14" t="n">
-        <v>0</v>
+        <v>-0.1</v>
       </c>
       <c r="I14" t="inlineStr">
         <is>
@@ -1088,16 +1088,16 @@
         </is>
       </c>
       <c r="K14" t="n">
-        <v>31.76</v>
+        <v>15.17</v>
       </c>
       <c r="L14" t="n">
-        <v>31.76</v>
+        <v>15.15</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>DHT</t>
+          <t>MPCC</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1106,22 +1106,22 @@
         </is>
       </c>
       <c r="C15" t="n">
-        <v>15.29</v>
+        <v>2.02</v>
       </c>
       <c r="D15" t="n">
-        <v>12.93</v>
+        <v>2.02</v>
       </c>
       <c r="E15" t="n">
-        <v>-15.41</v>
+        <v>0</v>
       </c>
       <c r="F15" t="n">
-        <v>-8.300000000000001</v>
+        <v>-17.1</v>
       </c>
       <c r="G15" t="n">
-        <v>-20.2</v>
+        <v>-17.1</v>
       </c>
       <c r="H15" t="n">
-        <v>-11.9</v>
+        <v>0</v>
       </c>
       <c r="I15" t="inlineStr">
         <is>
@@ -1134,10 +1134,10 @@
         </is>
       </c>
       <c r="K15" t="n">
-        <v>17.32</v>
+        <v>2.11</v>
       </c>
       <c r="L15" t="n">
-        <v>15.08</v>
+        <v>2.11</v>
       </c>
     </row>
     <row r="16">
@@ -1161,10 +1161,10 @@
         <v>-2.24</v>
       </c>
       <c r="F16" t="n">
-        <v>-18.8</v>
+        <v>-16.8</v>
       </c>
       <c r="G16" t="n">
-        <v>-20.3</v>
+        <v>-18.2</v>
       </c>
       <c r="H16" t="n">
         <v>-1.4</v>
@@ -1180,16 +1180,16 @@
         </is>
       </c>
       <c r="K16" t="n">
-        <v>5.87</v>
+        <v>6.01</v>
       </c>
       <c r="L16" t="n">
-        <v>5.77</v>
+        <v>5.91</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>ECO</t>
+          <t>DHT</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1198,19 +1198,19 @@
         </is>
       </c>
       <c r="C17" t="n">
-        <v>39.93</v>
+        <v>15.29</v>
       </c>
       <c r="D17" t="n">
-        <v>33.71</v>
+        <v>12.93</v>
       </c>
       <c r="E17" t="n">
-        <v>-15.58</v>
+        <v>-15.41</v>
       </c>
       <c r="F17" t="n">
-        <v>-13.5</v>
+        <v>-10.2</v>
       </c>
       <c r="G17" t="n">
-        <v>-25.1</v>
+        <v>-21.8</v>
       </c>
       <c r="H17" t="n">
         <v>-11.6</v>
@@ -1226,16 +1226,16 @@
         </is>
       </c>
       <c r="K17" t="n">
-        <v>45.41</v>
+        <v>16.96</v>
       </c>
       <c r="L17" t="n">
-        <v>39.33</v>
+        <v>14.77</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>MPCC</t>
+          <t>ECO</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1244,22 +1244,22 @@
         </is>
       </c>
       <c r="C18" t="n">
-        <v>2.02</v>
+        <v>39.93</v>
       </c>
       <c r="D18" t="n">
-        <v>2.02</v>
+        <v>33.71</v>
       </c>
       <c r="E18" t="n">
-        <v>0</v>
+        <v>-15.58</v>
       </c>
       <c r="F18" t="n">
-        <v>-27.3</v>
+        <v>-13.6</v>
       </c>
       <c r="G18" t="n">
-        <v>-27.3</v>
+        <v>-24.9</v>
       </c>
       <c r="H18" t="n">
-        <v>0</v>
+        <v>-11.3</v>
       </c>
       <c r="I18" t="inlineStr">
         <is>
@@ -1272,40 +1272,40 @@
         </is>
       </c>
       <c r="K18" t="n">
-        <v>1.85</v>
+        <v>45.33</v>
       </c>
       <c r="L18" t="n">
-        <v>1.85</v>
+        <v>39.41</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>FRO</t>
+          <t>INSW</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>whole-company</t>
+          <t>WHOLE-COMPANY (hybrid aggregation)</t>
         </is>
       </c>
       <c r="C19" t="n">
-        <v>28.47</v>
+        <v>57.91</v>
       </c>
       <c r="D19" t="n">
-        <v>24.08</v>
+        <v>52.39</v>
       </c>
       <c r="E19" t="n">
-        <v>-15.42</v>
+        <v>-9.529999999999999</v>
       </c>
       <c r="F19" t="n">
-        <v>-18</v>
+        <v>-21.7</v>
       </c>
       <c r="G19" t="n">
-        <v>-28.7</v>
+        <v>-27.6</v>
       </c>
       <c r="H19" t="n">
-        <v>-10.7</v>
+        <v>-5.9</v>
       </c>
       <c r="I19" t="inlineStr">
         <is>
@@ -1318,40 +1318,40 @@
         </is>
       </c>
       <c r="K19" t="n">
-        <v>33.57</v>
+        <v>66.17</v>
       </c>
       <c r="L19" t="n">
-        <v>29.18</v>
+        <v>61.16</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>INSW</t>
+          <t>FRO</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>WHOLE-COMPANY (hybrid aggregation)</t>
+          <t>whole-company</t>
         </is>
       </c>
       <c r="C20" t="n">
-        <v>57.91</v>
+        <v>28.47</v>
       </c>
       <c r="D20" t="n">
-        <v>52.39</v>
+        <v>24.08</v>
       </c>
       <c r="E20" t="n">
-        <v>-9.529999999999999</v>
+        <v>-15.42</v>
       </c>
       <c r="F20" t="n">
-        <v>-23.6</v>
+        <v>-19.5</v>
       </c>
       <c r="G20" t="n">
-        <v>-29.6</v>
+        <v>-29.9</v>
       </c>
       <c r="H20" t="n">
-        <v>-6.1</v>
+        <v>-10.4</v>
       </c>
       <c r="I20" t="inlineStr">
         <is>
@@ -1364,10 +1364,10 @@
         </is>
       </c>
       <c r="K20" t="n">
-        <v>64.59</v>
+        <v>32.95</v>
       </c>
       <c r="L20" t="n">
-        <v>59.47</v>
+        <v>28.68</v>
       </c>
     </row>
     <row r="21">
@@ -1391,13 +1391,13 @@
         <v>-21.23</v>
       </c>
       <c r="F21" t="n">
-        <v>-42.4</v>
+        <v>-43.9</v>
       </c>
       <c r="G21" t="n">
-        <v>-51.1</v>
+        <v>-52.5</v>
       </c>
       <c r="H21" t="n">
-        <v>-8.699999999999999</v>
+        <v>-8.5</v>
       </c>
       <c r="I21" t="inlineStr">
         <is>
@@ -1410,10 +1410,10 @@
         </is>
       </c>
       <c r="K21" t="n">
-        <v>3.37</v>
+        <v>3.28</v>
       </c>
       <c r="L21" t="n">
-        <v>2.86</v>
+        <v>2.78</v>
       </c>
     </row>
   </sheetData>

--- a/outputs/transaction_anchor_comparison.xlsx
+++ b/outputs/transaction_anchor_comparison.xlsx
@@ -539,7 +539,7 @@
         <v>10.93</v>
       </c>
       <c r="L2" t="n">
-        <v>10.8</v>
+        <v>10.81</v>
       </c>
     </row>
     <row r="3">
@@ -603,19 +603,19 @@
         <v>95.95</v>
       </c>
       <c r="D4" t="n">
-        <v>87.56</v>
+        <v>87.7</v>
       </c>
       <c r="E4" t="n">
-        <v>-8.74</v>
+        <v>-8.6</v>
       </c>
       <c r="F4" t="n">
         <v>83.59999999999999</v>
       </c>
       <c r="G4" t="n">
-        <v>69.3</v>
+        <v>69.59999999999999</v>
       </c>
       <c r="H4" t="n">
-        <v>-14.2</v>
+        <v>-14</v>
       </c>
       <c r="I4" t="inlineStr">
         <is>
@@ -631,7 +631,7 @@
         <v>70.29000000000001</v>
       </c>
       <c r="L4" t="n">
-        <v>64.84</v>
+        <v>64.93000000000001</v>
       </c>
     </row>
     <row r="5">
@@ -833,10 +833,10 @@
         <v>83.31999999999999</v>
       </c>
       <c r="D9" t="n">
-        <v>77.47</v>
+        <v>77.51000000000001</v>
       </c>
       <c r="E9" t="n">
-        <v>-7.01</v>
+        <v>-6.97</v>
       </c>
       <c r="F9" t="n">
         <v>13.7</v>
@@ -861,7 +861,7 @@
         <v>84.64</v>
       </c>
       <c r="L9" t="n">
-        <v>79.56</v>
+        <v>79.59</v>
       </c>
     </row>
     <row r="10">
@@ -1201,19 +1201,19 @@
         <v>15.29</v>
       </c>
       <c r="D17" t="n">
-        <v>12.93</v>
+        <v>13.1</v>
       </c>
       <c r="E17" t="n">
-        <v>-15.41</v>
+        <v>-14.35</v>
       </c>
       <c r="F17" t="n">
         <v>-10.2</v>
       </c>
       <c r="G17" t="n">
-        <v>-21.8</v>
+        <v>-21</v>
       </c>
       <c r="H17" t="n">
-        <v>-11.6</v>
+        <v>-10.8</v>
       </c>
       <c r="I17" t="inlineStr">
         <is>
@@ -1229,7 +1229,7 @@
         <v>16.96</v>
       </c>
       <c r="L17" t="n">
-        <v>14.77</v>
+        <v>14.92</v>
       </c>
     </row>
     <row r="18">
@@ -1247,19 +1247,19 @@
         <v>39.93</v>
       </c>
       <c r="D18" t="n">
-        <v>33.71</v>
+        <v>33.88</v>
       </c>
       <c r="E18" t="n">
-        <v>-15.58</v>
+        <v>-15.16</v>
       </c>
       <c r="F18" t="n">
         <v>-13.6</v>
       </c>
       <c r="G18" t="n">
-        <v>-24.9</v>
+        <v>-24.6</v>
       </c>
       <c r="H18" t="n">
-        <v>-11.3</v>
+        <v>-10.9</v>
       </c>
       <c r="I18" t="inlineStr">
         <is>
@@ -1275,7 +1275,7 @@
         <v>45.33</v>
       </c>
       <c r="L18" t="n">
-        <v>39.41</v>
+        <v>39.59</v>
       </c>
     </row>
     <row r="19">
@@ -1293,19 +1293,19 @@
         <v>57.91</v>
       </c>
       <c r="D19" t="n">
-        <v>52.39</v>
+        <v>52.59</v>
       </c>
       <c r="E19" t="n">
-        <v>-9.529999999999999</v>
+        <v>-9.18</v>
       </c>
       <c r="F19" t="n">
         <v>-21.7</v>
       </c>
       <c r="G19" t="n">
-        <v>-27.6</v>
+        <v>-27.4</v>
       </c>
       <c r="H19" t="n">
-        <v>-5.9</v>
+        <v>-5.7</v>
       </c>
       <c r="I19" t="inlineStr">
         <is>
@@ -1321,7 +1321,7 @@
         <v>66.17</v>
       </c>
       <c r="L19" t="n">
-        <v>61.16</v>
+        <v>61.34</v>
       </c>
     </row>
     <row r="20">
@@ -1339,19 +1339,19 @@
         <v>28.47</v>
       </c>
       <c r="D20" t="n">
-        <v>24.08</v>
+        <v>24.22</v>
       </c>
       <c r="E20" t="n">
-        <v>-15.42</v>
+        <v>-14.93</v>
       </c>
       <c r="F20" t="n">
         <v>-19.5</v>
       </c>
       <c r="G20" t="n">
-        <v>-29.9</v>
+        <v>-29.6</v>
       </c>
       <c r="H20" t="n">
-        <v>-10.4</v>
+        <v>-10.1</v>
       </c>
       <c r="I20" t="inlineStr">
         <is>
@@ -1367,7 +1367,7 @@
         <v>32.95</v>
       </c>
       <c r="L20" t="n">
-        <v>28.68</v>
+        <v>28.82</v>
       </c>
     </row>
     <row r="21">

--- a/outputs/transaction_anchor_comparison.xlsx
+++ b/outputs/transaction_anchor_comparison.xlsx
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L21"/>
+  <dimension ref="A1:L22"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="8" customWidth="1" min="1" max="1"/>
@@ -517,10 +517,10 @@
         <v>0</v>
       </c>
       <c r="F2" t="n">
-        <v>102.5</v>
+        <v>104.8</v>
       </c>
       <c r="G2" t="n">
-        <v>100.1</v>
+        <v>102.4</v>
       </c>
       <c r="H2" t="n">
         <v>-2.4</v>
@@ -545,7 +545,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>CCEC</t>
+          <t>TEN</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -554,22 +554,22 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>28.1</v>
+        <v>95.95</v>
       </c>
       <c r="D3" t="n">
-        <v>28.1</v>
+        <v>87.7</v>
       </c>
       <c r="E3" t="n">
-        <v>0</v>
+        <v>-8.6</v>
       </c>
       <c r="F3" t="n">
-        <v>79.3</v>
+        <v>91.40000000000001</v>
       </c>
       <c r="G3" t="n">
-        <v>79.3</v>
+        <v>76.8</v>
       </c>
       <c r="H3" t="n">
-        <v>0</v>
+        <v>-14.6</v>
       </c>
       <c r="I3" t="inlineStr">
         <is>
@@ -582,16 +582,16 @@
         </is>
       </c>
       <c r="K3" t="n">
-        <v>35.91</v>
+        <v>70.29000000000001</v>
       </c>
       <c r="L3" t="n">
-        <v>35.91</v>
+        <v>64.93000000000001</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>TEN</t>
+          <t>CCEC</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -600,22 +600,22 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>95.95</v>
+        <v>28.1</v>
       </c>
       <c r="D4" t="n">
-        <v>87.7</v>
+        <v>28.1</v>
       </c>
       <c r="E4" t="n">
-        <v>-8.6</v>
+        <v>0</v>
       </c>
       <c r="F4" t="n">
-        <v>83.59999999999999</v>
+        <v>73.40000000000001</v>
       </c>
       <c r="G4" t="n">
-        <v>69.59999999999999</v>
+        <v>73.40000000000001</v>
       </c>
       <c r="H4" t="n">
-        <v>-14</v>
+        <v>0</v>
       </c>
       <c r="I4" t="inlineStr">
         <is>
@@ -628,10 +628,10 @@
         </is>
       </c>
       <c r="K4" t="n">
-        <v>70.29000000000001</v>
+        <v>35.91</v>
       </c>
       <c r="L4" t="n">
-        <v>64.93000000000001</v>
+        <v>35.91</v>
       </c>
     </row>
     <row r="5">
@@ -655,13 +655,13 @@
         <v>-1.12</v>
       </c>
       <c r="F5" t="n">
-        <v>28.8</v>
+        <v>33.3</v>
       </c>
       <c r="G5" t="n">
-        <v>26.7</v>
+        <v>31.1</v>
       </c>
       <c r="H5" t="n">
-        <v>-2.1</v>
+        <v>-2.2</v>
       </c>
       <c r="I5" t="inlineStr">
         <is>
@@ -701,10 +701,10 @@
         <v>-0.42</v>
       </c>
       <c r="F6" t="n">
-        <v>25.5</v>
+        <v>21.4</v>
       </c>
       <c r="G6" t="n">
-        <v>25</v>
+        <v>20.9</v>
       </c>
       <c r="H6" t="n">
         <v>-0.5</v>
@@ -729,7 +729,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>GNK</t>
+          <t>TNK</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -738,26 +738,26 @@
         </is>
       </c>
       <c r="C7" t="n">
-        <v>25.4</v>
+        <v>83.31999999999999</v>
       </c>
       <c r="D7" t="n">
-        <v>26.27</v>
+        <v>77.51000000000001</v>
       </c>
       <c r="E7" t="n">
-        <v>3.44</v>
+        <v>-6.97</v>
       </c>
       <c r="F7" t="n">
-        <v>4.2</v>
+        <v>24.5</v>
       </c>
       <c r="G7" t="n">
-        <v>7.3</v>
+        <v>17.1</v>
       </c>
       <c r="H7" t="n">
-        <v>3.1</v>
+        <v>-7.4</v>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>HOLD (fairly valued)</t>
+          <t>BUY (undervalued)</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
@@ -766,40 +766,40 @@
         </is>
       </c>
       <c r="K7" t="n">
-        <v>24.69</v>
+        <v>84.64</v>
       </c>
       <c r="L7" t="n">
-        <v>25.41</v>
+        <v>79.59</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>GSL</t>
+          <t>CMBT</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>whole-company</t>
+          <t>WHOLE-COMPANY (hybrid aggregation)</t>
         </is>
       </c>
       <c r="C8" t="n">
-        <v>38.59</v>
+        <v>13.97</v>
       </c>
       <c r="D8" t="n">
-        <v>38.59</v>
+        <v>15.26</v>
       </c>
       <c r="E8" t="n">
-        <v>0</v>
+        <v>9.18</v>
       </c>
       <c r="F8" t="n">
-        <v>7.1</v>
+        <v>2.7</v>
       </c>
       <c r="G8" t="n">
-        <v>7.1</v>
+        <v>11</v>
       </c>
       <c r="H8" t="n">
-        <v>0</v>
+        <v>8.4</v>
       </c>
       <c r="I8" t="inlineStr">
         <is>
@@ -812,16 +812,16 @@
         </is>
       </c>
       <c r="K8" t="n">
-        <v>40.59</v>
+        <v>14.48</v>
       </c>
       <c r="L8" t="n">
-        <v>40.59</v>
+        <v>15.66</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>TNK</t>
+          <t>STNG</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -830,22 +830,22 @@
         </is>
       </c>
       <c r="C9" t="n">
-        <v>83.31999999999999</v>
+        <v>83.87</v>
       </c>
       <c r="D9" t="n">
-        <v>77.51000000000001</v>
+        <v>80.34999999999999</v>
       </c>
       <c r="E9" t="n">
-        <v>-6.97</v>
+        <v>-4.19</v>
       </c>
       <c r="F9" t="n">
-        <v>13.7</v>
+        <v>14.6</v>
       </c>
       <c r="G9" t="n">
-        <v>6.9</v>
+        <v>10.2</v>
       </c>
       <c r="H9" t="n">
-        <v>-6.8</v>
+        <v>-4.4</v>
       </c>
       <c r="I9" t="inlineStr">
         <is>
@@ -858,16 +858,16 @@
         </is>
       </c>
       <c r="K9" t="n">
-        <v>84.64</v>
+        <v>83.16</v>
       </c>
       <c r="L9" t="n">
-        <v>79.59</v>
+        <v>79.98999999999999</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>FLNG</t>
+          <t>GNK</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -876,23 +876,23 @@
         </is>
       </c>
       <c r="C10" t="n">
-        <v>28.45</v>
+        <v>25.4</v>
       </c>
       <c r="D10" t="n">
-        <v>28.45</v>
+        <v>26.27</v>
       </c>
       <c r="E10" t="n">
-        <v>0</v>
+        <v>3.44</v>
       </c>
       <c r="F10" t="n">
+        <v>4.7</v>
+      </c>
+      <c r="G10" t="n">
+        <v>7.8</v>
+      </c>
+      <c r="H10" t="n">
         <v>3.1</v>
       </c>
-      <c r="G10" t="n">
-        <v>3.1</v>
-      </c>
-      <c r="H10" t="n">
-        <v>0</v>
-      </c>
       <c r="I10" t="inlineStr">
         <is>
           <t>HOLD (fairly valued)</t>
@@ -900,20 +900,20 @@
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>HOLD (fairly valued)</t>
+          <t>BUY (undervalued)</t>
         </is>
       </c>
       <c r="K10" t="n">
-        <v>30.67</v>
+        <v>24.69</v>
       </c>
       <c r="L10" t="n">
-        <v>30.67</v>
+        <v>25.41</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>SBLK</t>
+          <t>GSL</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -922,44 +922,44 @@
         </is>
       </c>
       <c r="C11" t="n">
-        <v>25.98</v>
+        <v>38.59</v>
       </c>
       <c r="D11" t="n">
-        <v>26.57</v>
+        <v>38.59</v>
       </c>
       <c r="E11" t="n">
-        <v>2.28</v>
+        <v>0</v>
       </c>
       <c r="F11" t="n">
-        <v>-2</v>
+        <v>7.4</v>
       </c>
       <c r="G11" t="n">
-        <v>-0.2</v>
+        <v>7.4</v>
       </c>
       <c r="H11" t="n">
-        <v>1.9</v>
+        <v>0</v>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>HOLD (fairly valued)</t>
+          <t>BUY (undervalued)</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>HOLD (fairly valued)</t>
+          <t>BUY (undervalued)</t>
         </is>
       </c>
       <c r="K11" t="n">
-        <v>25.28</v>
+        <v>40.59</v>
       </c>
       <c r="L11" t="n">
-        <v>25.76</v>
+        <v>40.59</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>STNG</t>
+          <t>SBLK</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -968,22 +968,22 @@
         </is>
       </c>
       <c r="C12" t="n">
-        <v>83.87</v>
+        <v>25.98</v>
       </c>
       <c r="D12" t="n">
-        <v>80.34999999999999</v>
+        <v>26.57</v>
       </c>
       <c r="E12" t="n">
-        <v>-4.19</v>
+        <v>2.28</v>
       </c>
       <c r="F12" t="n">
-        <v>3.2</v>
+        <v>3.6</v>
       </c>
       <c r="G12" t="n">
-        <v>-0.7</v>
+        <v>5.6</v>
       </c>
       <c r="H12" t="n">
-        <v>-3.9</v>
+        <v>2</v>
       </c>
       <c r="I12" t="inlineStr">
         <is>
@@ -992,20 +992,20 @@
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>HOLD (fairly valued)</t>
+          <t>BUY (undervalued)</t>
         </is>
       </c>
       <c r="K12" t="n">
-        <v>83.16</v>
+        <v>25.28</v>
       </c>
       <c r="L12" t="n">
-        <v>79.98999999999999</v>
+        <v>25.76</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>TRMD</t>
+          <t>FLNG</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -1014,22 +1014,22 @@
         </is>
       </c>
       <c r="C13" t="n">
-        <v>26.74</v>
+        <v>28.45</v>
       </c>
       <c r="D13" t="n">
-        <v>25.43</v>
+        <v>28.45</v>
       </c>
       <c r="E13" t="n">
-        <v>-4.86</v>
+        <v>0</v>
       </c>
       <c r="F13" t="n">
-        <v>-3.3</v>
+        <v>4.1</v>
       </c>
       <c r="G13" t="n">
-        <v>-7.1</v>
+        <v>4.1</v>
       </c>
       <c r="H13" t="n">
-        <v>-3.8</v>
+        <v>0</v>
       </c>
       <c r="I13" t="inlineStr">
         <is>
@@ -1038,20 +1038,20 @@
       </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t>TRIM/SHORT (overvalued)</t>
+          <t>HOLD (fairly valued)</t>
         </is>
       </c>
       <c r="K13" t="n">
-        <v>28.45</v>
+        <v>30.67</v>
       </c>
       <c r="L13" t="n">
-        <v>27.32</v>
+        <v>30.67</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>ASC</t>
+          <t>TRMD</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1060,44 +1060,44 @@
         </is>
       </c>
       <c r="C14" t="n">
-        <v>15.96</v>
+        <v>26.74</v>
       </c>
       <c r="D14" t="n">
-        <v>15.93</v>
+        <v>25.43</v>
       </c>
       <c r="E14" t="n">
-        <v>-0.16</v>
+        <v>-4.86</v>
       </c>
       <c r="F14" t="n">
-        <v>-11.1</v>
+        <v>6.1</v>
       </c>
       <c r="G14" t="n">
-        <v>-11.3</v>
+        <v>1.9</v>
       </c>
       <c r="H14" t="n">
-        <v>-0.1</v>
+        <v>-4.2</v>
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>TRIM/SHORT (overvalued)</t>
+          <t>BUY (undervalued)</t>
         </is>
       </c>
       <c r="J14" t="inlineStr">
         <is>
-          <t>TRIM/SHORT (overvalued)</t>
+          <t>HOLD (fairly valued)</t>
         </is>
       </c>
       <c r="K14" t="n">
-        <v>15.17</v>
+        <v>28.45</v>
       </c>
       <c r="L14" t="n">
-        <v>15.15</v>
+        <v>27.32</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>MPCC</t>
+          <t>ASC</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1106,38 +1106,38 @@
         </is>
       </c>
       <c r="C15" t="n">
-        <v>2.02</v>
+        <v>15.96</v>
       </c>
       <c r="D15" t="n">
-        <v>2.02</v>
+        <v>15.93</v>
       </c>
       <c r="E15" t="n">
-        <v>0</v>
+        <v>-0.16</v>
       </c>
       <c r="F15" t="n">
-        <v>-17.1</v>
+        <v>0.3</v>
       </c>
       <c r="G15" t="n">
-        <v>-17.1</v>
+        <v>0.2</v>
       </c>
       <c r="H15" t="n">
-        <v>0</v>
+        <v>-0.2</v>
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>TRIM/SHORT (overvalued)</t>
+          <t>HOLD (fairly valued)</t>
         </is>
       </c>
       <c r="J15" t="inlineStr">
         <is>
-          <t>TRIM/SHORT (overvalued)</t>
+          <t>HOLD (fairly valued)</t>
         </is>
       </c>
       <c r="K15" t="n">
-        <v>2.11</v>
+        <v>15.17</v>
       </c>
       <c r="L15" t="n">
-        <v>2.11</v>
+        <v>15.15</v>
       </c>
     </row>
     <row r="16">
@@ -1161,13 +1161,13 @@
         <v>-2.24</v>
       </c>
       <c r="F16" t="n">
-        <v>-16.8</v>
+        <v>-13.7</v>
       </c>
       <c r="G16" t="n">
-        <v>-18.2</v>
+        <v>-15.2</v>
       </c>
       <c r="H16" t="n">
-        <v>-1.4</v>
+        <v>-1.5</v>
       </c>
       <c r="I16" t="inlineStr">
         <is>
@@ -1207,17 +1207,17 @@
         <v>-14.35</v>
       </c>
       <c r="F17" t="n">
-        <v>-10.2</v>
+        <v>-3.9</v>
       </c>
       <c r="G17" t="n">
-        <v>-21</v>
+        <v>-15.5</v>
       </c>
       <c r="H17" t="n">
-        <v>-10.8</v>
+        <v>-11.5</v>
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>TRIM/SHORT (overvalued)</t>
+          <t>HOLD (fairly valued)</t>
         </is>
       </c>
       <c r="J17" t="inlineStr">
@@ -1235,7 +1235,7 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>ECO</t>
+          <t>FRO</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1244,22 +1244,22 @@
         </is>
       </c>
       <c r="C18" t="n">
-        <v>39.93</v>
+        <v>28.47</v>
       </c>
       <c r="D18" t="n">
-        <v>33.88</v>
+        <v>24.22</v>
       </c>
       <c r="E18" t="n">
-        <v>-15.16</v>
+        <v>-14.93</v>
       </c>
       <c r="F18" t="n">
-        <v>-13.6</v>
+        <v>-7.2</v>
       </c>
       <c r="G18" t="n">
-        <v>-24.6</v>
+        <v>-18.9</v>
       </c>
       <c r="H18" t="n">
-        <v>-10.9</v>
+        <v>-11.6</v>
       </c>
       <c r="I18" t="inlineStr">
         <is>
@@ -1272,40 +1272,40 @@
         </is>
       </c>
       <c r="K18" t="n">
-        <v>45.33</v>
+        <v>32.95</v>
       </c>
       <c r="L18" t="n">
-        <v>39.59</v>
+        <v>28.82</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>INSW</t>
+          <t>MPCC</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>WHOLE-COMPANY (hybrid aggregation)</t>
+          <t>whole-company</t>
         </is>
       </c>
       <c r="C19" t="n">
-        <v>57.91</v>
+        <v>2.02</v>
       </c>
       <c r="D19" t="n">
-        <v>52.59</v>
+        <v>2.02</v>
       </c>
       <c r="E19" t="n">
-        <v>-9.18</v>
+        <v>0</v>
       </c>
       <c r="F19" t="n">
-        <v>-21.7</v>
+        <v>-19.3</v>
       </c>
       <c r="G19" t="n">
-        <v>-27.4</v>
+        <v>-19.3</v>
       </c>
       <c r="H19" t="n">
-        <v>-5.7</v>
+        <v>0</v>
       </c>
       <c r="I19" t="inlineStr">
         <is>
@@ -1318,16 +1318,16 @@
         </is>
       </c>
       <c r="K19" t="n">
-        <v>66.17</v>
+        <v>2.11</v>
       </c>
       <c r="L19" t="n">
-        <v>61.34</v>
+        <v>2.11</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>FRO</t>
+          <t>ECO</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -1336,22 +1336,22 @@
         </is>
       </c>
       <c r="C20" t="n">
-        <v>28.47</v>
+        <v>39.93</v>
       </c>
       <c r="D20" t="n">
-        <v>24.22</v>
+        <v>33.88</v>
       </c>
       <c r="E20" t="n">
-        <v>-14.93</v>
+        <v>-15.16</v>
       </c>
       <c r="F20" t="n">
-        <v>-19.5</v>
+        <v>-9.1</v>
       </c>
       <c r="G20" t="n">
-        <v>-29.6</v>
+        <v>-20.6</v>
       </c>
       <c r="H20" t="n">
-        <v>-10.1</v>
+        <v>-11.5</v>
       </c>
       <c r="I20" t="inlineStr">
         <is>
@@ -1364,55 +1364,101 @@
         </is>
       </c>
       <c r="K20" t="n">
-        <v>32.95</v>
+        <v>45.33</v>
       </c>
       <c r="L20" t="n">
-        <v>28.82</v>
+        <v>39.59</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
+          <t>INSW</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>WHOLE-COMPANY (hybrid aggregation)</t>
+        </is>
+      </c>
+      <c r="C21" t="n">
+        <v>57.91</v>
+      </c>
+      <c r="D21" t="n">
+        <v>52.59</v>
+      </c>
+      <c r="E21" t="n">
+        <v>-9.18</v>
+      </c>
+      <c r="F21" t="n">
+        <v>-16.8</v>
+      </c>
+      <c r="G21" t="n">
+        <v>-22.8</v>
+      </c>
+      <c r="H21" t="n">
+        <v>-6.1</v>
+      </c>
+      <c r="I21" t="inlineStr">
+        <is>
+          <t>TRIM/SHORT (overvalued)</t>
+        </is>
+      </c>
+      <c r="J21" t="inlineStr">
+        <is>
+          <t>TRIM/SHORT (overvalued)</t>
+        </is>
+      </c>
+      <c r="K21" t="n">
+        <v>66.17</v>
+      </c>
+      <c r="L21" t="n">
+        <v>61.34</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
           <t>NAT</t>
         </is>
       </c>
-      <c r="B21" t="inlineStr">
-        <is>
-          <t>whole-company</t>
-        </is>
-      </c>
-      <c r="C21" t="n">
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>whole-company</t>
+        </is>
+      </c>
+      <c r="C22" t="n">
         <v>2.63</v>
       </c>
-      <c r="D21" t="n">
+      <c r="D22" t="n">
         <v>2.07</v>
       </c>
-      <c r="E21" t="n">
+      <c r="E22" t="n">
         <v>-21.23</v>
       </c>
-      <c r="F21" t="n">
+      <c r="F22" t="n">
         <v>-43.9</v>
       </c>
-      <c r="G21" t="n">
+      <c r="G22" t="n">
         <v>-52.5</v>
       </c>
-      <c r="H21" t="n">
+      <c r="H22" t="n">
         <v>-8.5</v>
       </c>
-      <c r="I21" t="inlineStr">
+      <c r="I22" t="inlineStr">
         <is>
           <t>TRIM/SHORT (overvalued)</t>
         </is>
       </c>
-      <c r="J21" t="inlineStr">
+      <c r="J22" t="inlineStr">
         <is>
           <t>TRIM/SHORT (overvalued)</t>
         </is>
       </c>
-      <c r="K21" t="n">
+      <c r="K22" t="n">
         <v>3.28</v>
       </c>
-      <c r="L21" t="n">
+      <c r="L22" t="n">
         <v>2.78</v>
       </c>
     </row>

--- a/outputs/transaction_anchor_comparison.xlsx
+++ b/outputs/transaction_anchor_comparison.xlsx
@@ -683,7 +683,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>CMDB</t>
+          <t>TNK</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -692,22 +692,22 @@
         </is>
       </c>
       <c r="C6" t="n">
-        <v>32.62</v>
+        <v>83.31999999999999</v>
       </c>
       <c r="D6" t="n">
-        <v>32.49</v>
+        <v>77.51000000000001</v>
       </c>
       <c r="E6" t="n">
-        <v>-0.42</v>
+        <v>-6.97</v>
       </c>
       <c r="F6" t="n">
-        <v>21.4</v>
+        <v>24.5</v>
       </c>
       <c r="G6" t="n">
-        <v>20.9</v>
+        <v>17.1</v>
       </c>
       <c r="H6" t="n">
-        <v>-0.5</v>
+        <v>-7.4</v>
       </c>
       <c r="I6" t="inlineStr">
         <is>
@@ -720,16 +720,16 @@
         </is>
       </c>
       <c r="K6" t="n">
-        <v>21.22</v>
+        <v>84.64</v>
       </c>
       <c r="L6" t="n">
-        <v>21.13</v>
+        <v>79.59</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>TNK</t>
+          <t>CMDB</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -738,22 +738,22 @@
         </is>
       </c>
       <c r="C7" t="n">
-        <v>83.31999999999999</v>
+        <v>32.12</v>
       </c>
       <c r="D7" t="n">
-        <v>77.51000000000001</v>
+        <v>31.33</v>
       </c>
       <c r="E7" t="n">
-        <v>-6.97</v>
+        <v>-2.45</v>
       </c>
       <c r="F7" t="n">
-        <v>24.5</v>
+        <v>19.6</v>
       </c>
       <c r="G7" t="n">
-        <v>17.1</v>
+        <v>16.9</v>
       </c>
       <c r="H7" t="n">
-        <v>-7.4</v>
+        <v>-2.7</v>
       </c>
       <c r="I7" t="inlineStr">
         <is>
@@ -766,10 +766,10 @@
         </is>
       </c>
       <c r="K7" t="n">
-        <v>84.64</v>
+        <v>20.9</v>
       </c>
       <c r="L7" t="n">
-        <v>79.59</v>
+        <v>20.43</v>
       </c>
     </row>
     <row r="8">
@@ -784,22 +784,22 @@
         </is>
       </c>
       <c r="C8" t="n">
-        <v>13.97</v>
+        <v>15.24</v>
       </c>
       <c r="D8" t="n">
-        <v>15.26</v>
+        <v>15.27</v>
       </c>
       <c r="E8" t="n">
-        <v>9.18</v>
+        <v>0.18</v>
       </c>
       <c r="F8" t="n">
-        <v>2.7</v>
+        <v>11</v>
       </c>
       <c r="G8" t="n">
-        <v>11</v>
+        <v>10.9</v>
       </c>
       <c r="H8" t="n">
-        <v>8.4</v>
+        <v>-0.1</v>
       </c>
       <c r="I8" t="inlineStr">
         <is>
@@ -812,10 +812,10 @@
         </is>
       </c>
       <c r="K8" t="n">
-        <v>14.48</v>
+        <v>15.65</v>
       </c>
       <c r="L8" t="n">
-        <v>15.66</v>
+        <v>15.64</v>
       </c>
     </row>
     <row r="9">
@@ -867,7 +867,7 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>GNK</t>
+          <t>GSL</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -876,26 +876,26 @@
         </is>
       </c>
       <c r="C10" t="n">
-        <v>25.4</v>
+        <v>38.59</v>
       </c>
       <c r="D10" t="n">
-        <v>26.27</v>
+        <v>38.59</v>
       </c>
       <c r="E10" t="n">
-        <v>3.44</v>
+        <v>0</v>
       </c>
       <c r="F10" t="n">
-        <v>4.7</v>
+        <v>7.4</v>
       </c>
       <c r="G10" t="n">
-        <v>7.8</v>
+        <v>7.4</v>
       </c>
       <c r="H10" t="n">
-        <v>3.1</v>
+        <v>0</v>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>HOLD (fairly valued)</t>
+          <t>BUY (undervalued)</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
@@ -904,16 +904,16 @@
         </is>
       </c>
       <c r="K10" t="n">
-        <v>24.69</v>
+        <v>40.59</v>
       </c>
       <c r="L10" t="n">
-        <v>25.41</v>
+        <v>40.59</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>GSL</t>
+          <t>SBLK</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -922,22 +922,22 @@
         </is>
       </c>
       <c r="C11" t="n">
-        <v>38.59</v>
+        <v>27.34</v>
       </c>
       <c r="D11" t="n">
-        <v>38.59</v>
+        <v>26.91</v>
       </c>
       <c r="E11" t="n">
-        <v>0</v>
+        <v>-1.56</v>
       </c>
       <c r="F11" t="n">
-        <v>7.4</v>
+        <v>8.4</v>
       </c>
       <c r="G11" t="n">
-        <v>7.4</v>
+        <v>6.9</v>
       </c>
       <c r="H11" t="n">
-        <v>0</v>
+        <v>-1.5</v>
       </c>
       <c r="I11" t="inlineStr">
         <is>
@@ -950,16 +950,16 @@
         </is>
       </c>
       <c r="K11" t="n">
-        <v>40.59</v>
+        <v>26.45</v>
       </c>
       <c r="L11" t="n">
-        <v>40.59</v>
+        <v>26.07</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>SBLK</t>
+          <t>FLNG</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -968,22 +968,22 @@
         </is>
       </c>
       <c r="C12" t="n">
-        <v>25.98</v>
+        <v>28.45</v>
       </c>
       <c r="D12" t="n">
-        <v>26.57</v>
+        <v>28.45</v>
       </c>
       <c r="E12" t="n">
-        <v>2.28</v>
+        <v>0</v>
       </c>
       <c r="F12" t="n">
-        <v>3.6</v>
+        <v>4.1</v>
       </c>
       <c r="G12" t="n">
-        <v>5.6</v>
+        <v>4.1</v>
       </c>
       <c r="H12" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="I12" t="inlineStr">
         <is>
@@ -992,20 +992,20 @@
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>BUY (undervalued)</t>
+          <t>HOLD (fairly valued)</t>
         </is>
       </c>
       <c r="K12" t="n">
-        <v>25.28</v>
+        <v>30.67</v>
       </c>
       <c r="L12" t="n">
-        <v>25.76</v>
+        <v>30.67</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>FLNG</t>
+          <t>GNK</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -1014,22 +1014,22 @@
         </is>
       </c>
       <c r="C13" t="n">
-        <v>28.45</v>
+        <v>25.48</v>
       </c>
       <c r="D13" t="n">
-        <v>28.45</v>
+        <v>24.64</v>
       </c>
       <c r="E13" t="n">
-        <v>0</v>
+        <v>-3.29</v>
       </c>
       <c r="F13" t="n">
-        <v>4.1</v>
+        <v>5</v>
       </c>
       <c r="G13" t="n">
-        <v>4.1</v>
+        <v>1.9</v>
       </c>
       <c r="H13" t="n">
-        <v>0</v>
+        <v>-3</v>
       </c>
       <c r="I13" t="inlineStr">
         <is>
@@ -1042,10 +1042,10 @@
         </is>
       </c>
       <c r="K13" t="n">
-        <v>30.67</v>
+        <v>24.74</v>
       </c>
       <c r="L13" t="n">
-        <v>30.67</v>
+        <v>24.02</v>
       </c>
     </row>
     <row r="14">

--- a/outputs/transaction_anchor_comparison.xlsx
+++ b/outputs/transaction_anchor_comparison.xlsx
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L22"/>
+  <dimension ref="A1:L23"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="8" customWidth="1" min="1" max="1"/>
@@ -637,7 +637,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>CAPT</t>
+          <t>SB</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -646,22 +646,22 @@
         </is>
       </c>
       <c r="C5" t="n">
-        <v>15.2</v>
+        <v>9.48</v>
       </c>
       <c r="D5" t="n">
-        <v>15.03</v>
+        <v>10.14</v>
       </c>
       <c r="E5" t="n">
-        <v>-1.12</v>
+        <v>6.92</v>
       </c>
       <c r="F5" t="n">
-        <v>33.3</v>
+        <v>39.6</v>
       </c>
       <c r="G5" t="n">
-        <v>31.1</v>
+        <v>49</v>
       </c>
       <c r="H5" t="n">
-        <v>-2.2</v>
+        <v>9.4</v>
       </c>
       <c r="I5" t="inlineStr">
         <is>
@@ -674,16 +674,16 @@
         </is>
       </c>
       <c r="K5" t="n">
-        <v>17.05</v>
+        <v>8.92</v>
       </c>
       <c r="L5" t="n">
-        <v>16.77</v>
+        <v>9.52</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>TNK</t>
+          <t>CAPT</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -692,22 +692,22 @@
         </is>
       </c>
       <c r="C6" t="n">
-        <v>83.31999999999999</v>
+        <v>15.2</v>
       </c>
       <c r="D6" t="n">
-        <v>77.51000000000001</v>
+        <v>15.03</v>
       </c>
       <c r="E6" t="n">
-        <v>-6.97</v>
+        <v>-1.12</v>
       </c>
       <c r="F6" t="n">
-        <v>24.5</v>
+        <v>33.3</v>
       </c>
       <c r="G6" t="n">
-        <v>17.1</v>
+        <v>31.1</v>
       </c>
       <c r="H6" t="n">
-        <v>-7.4</v>
+        <v>-2.2</v>
       </c>
       <c r="I6" t="inlineStr">
         <is>
@@ -720,16 +720,16 @@
         </is>
       </c>
       <c r="K6" t="n">
-        <v>84.64</v>
+        <v>17.05</v>
       </c>
       <c r="L6" t="n">
-        <v>79.59</v>
+        <v>16.77</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>CMDB</t>
+          <t>TNK</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -738,22 +738,22 @@
         </is>
       </c>
       <c r="C7" t="n">
-        <v>32.12</v>
+        <v>83.31999999999999</v>
       </c>
       <c r="D7" t="n">
-        <v>31.33</v>
+        <v>77.51000000000001</v>
       </c>
       <c r="E7" t="n">
-        <v>-2.45</v>
+        <v>-6.97</v>
       </c>
       <c r="F7" t="n">
-        <v>19.6</v>
+        <v>24.5</v>
       </c>
       <c r="G7" t="n">
-        <v>16.9</v>
+        <v>17.1</v>
       </c>
       <c r="H7" t="n">
-        <v>-2.7</v>
+        <v>-7.4</v>
       </c>
       <c r="I7" t="inlineStr">
         <is>
@@ -766,40 +766,40 @@
         </is>
       </c>
       <c r="K7" t="n">
-        <v>20.9</v>
+        <v>84.64</v>
       </c>
       <c r="L7" t="n">
-        <v>20.43</v>
+        <v>79.59</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>CMBT</t>
+          <t>CMDB</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>WHOLE-COMPANY (hybrid aggregation)</t>
+          <t>whole-company</t>
         </is>
       </c>
       <c r="C8" t="n">
-        <v>15.24</v>
+        <v>32.12</v>
       </c>
       <c r="D8" t="n">
-        <v>15.27</v>
+        <v>31.33</v>
       </c>
       <c r="E8" t="n">
-        <v>0.18</v>
+        <v>-2.45</v>
       </c>
       <c r="F8" t="n">
-        <v>11</v>
+        <v>19.6</v>
       </c>
       <c r="G8" t="n">
-        <v>10.9</v>
+        <v>16.9</v>
       </c>
       <c r="H8" t="n">
-        <v>-0.1</v>
+        <v>-2.7</v>
       </c>
       <c r="I8" t="inlineStr">
         <is>
@@ -812,40 +812,40 @@
         </is>
       </c>
       <c r="K8" t="n">
-        <v>15.65</v>
+        <v>20.9</v>
       </c>
       <c r="L8" t="n">
-        <v>15.64</v>
+        <v>20.43</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>STNG</t>
+          <t>CMBT</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>whole-company</t>
+          <t>WHOLE-COMPANY (hybrid aggregation)</t>
         </is>
       </c>
       <c r="C9" t="n">
-        <v>83.87</v>
+        <v>15.24</v>
       </c>
       <c r="D9" t="n">
-        <v>80.34999999999999</v>
+        <v>15.27</v>
       </c>
       <c r="E9" t="n">
-        <v>-4.19</v>
+        <v>0.18</v>
       </c>
       <c r="F9" t="n">
-        <v>14.6</v>
+        <v>11</v>
       </c>
       <c r="G9" t="n">
-        <v>10.2</v>
+        <v>10.9</v>
       </c>
       <c r="H9" t="n">
-        <v>-4.4</v>
+        <v>-0.1</v>
       </c>
       <c r="I9" t="inlineStr">
         <is>
@@ -858,16 +858,16 @@
         </is>
       </c>
       <c r="K9" t="n">
-        <v>83.16</v>
+        <v>15.65</v>
       </c>
       <c r="L9" t="n">
-        <v>79.98999999999999</v>
+        <v>15.64</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>GSL</t>
+          <t>STNG</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -876,22 +876,22 @@
         </is>
       </c>
       <c r="C10" t="n">
-        <v>38.59</v>
+        <v>83.87</v>
       </c>
       <c r="D10" t="n">
-        <v>38.59</v>
+        <v>80.34999999999999</v>
       </c>
       <c r="E10" t="n">
-        <v>0</v>
+        <v>-4.19</v>
       </c>
       <c r="F10" t="n">
-        <v>7.4</v>
+        <v>14.6</v>
       </c>
       <c r="G10" t="n">
-        <v>7.4</v>
+        <v>10.2</v>
       </c>
       <c r="H10" t="n">
-        <v>0</v>
+        <v>-4.4</v>
       </c>
       <c r="I10" t="inlineStr">
         <is>
@@ -904,16 +904,16 @@
         </is>
       </c>
       <c r="K10" t="n">
-        <v>40.59</v>
+        <v>83.16</v>
       </c>
       <c r="L10" t="n">
-        <v>40.59</v>
+        <v>79.98999999999999</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>SBLK</t>
+          <t>GSL</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -922,22 +922,22 @@
         </is>
       </c>
       <c r="C11" t="n">
-        <v>27.34</v>
+        <v>38.59</v>
       </c>
       <c r="D11" t="n">
-        <v>26.91</v>
+        <v>38.59</v>
       </c>
       <c r="E11" t="n">
-        <v>-1.56</v>
+        <v>0</v>
       </c>
       <c r="F11" t="n">
-        <v>8.4</v>
+        <v>7.4</v>
       </c>
       <c r="G11" t="n">
-        <v>6.9</v>
+        <v>7.4</v>
       </c>
       <c r="H11" t="n">
-        <v>-1.5</v>
+        <v>0</v>
       </c>
       <c r="I11" t="inlineStr">
         <is>
@@ -950,16 +950,16 @@
         </is>
       </c>
       <c r="K11" t="n">
-        <v>26.45</v>
+        <v>40.59</v>
       </c>
       <c r="L11" t="n">
-        <v>26.07</v>
+        <v>40.59</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>FLNG</t>
+          <t>SBLK</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -968,44 +968,44 @@
         </is>
       </c>
       <c r="C12" t="n">
-        <v>28.45</v>
+        <v>27.34</v>
       </c>
       <c r="D12" t="n">
-        <v>28.45</v>
+        <v>26.91</v>
       </c>
       <c r="E12" t="n">
-        <v>0</v>
+        <v>-1.56</v>
       </c>
       <c r="F12" t="n">
-        <v>4.1</v>
+        <v>8.4</v>
       </c>
       <c r="G12" t="n">
-        <v>4.1</v>
+        <v>6.9</v>
       </c>
       <c r="H12" t="n">
-        <v>0</v>
+        <v>-1.5</v>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>HOLD (fairly valued)</t>
+          <t>BUY (undervalued)</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>HOLD (fairly valued)</t>
+          <t>BUY (undervalued)</t>
         </is>
       </c>
       <c r="K12" t="n">
-        <v>30.67</v>
+        <v>26.45</v>
       </c>
       <c r="L12" t="n">
-        <v>30.67</v>
+        <v>26.07</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>GNK</t>
+          <t>FLNG</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -1014,22 +1014,22 @@
         </is>
       </c>
       <c r="C13" t="n">
-        <v>25.48</v>
+        <v>28.45</v>
       </c>
       <c r="D13" t="n">
-        <v>24.64</v>
+        <v>28.45</v>
       </c>
       <c r="E13" t="n">
-        <v>-3.29</v>
+        <v>0</v>
       </c>
       <c r="F13" t="n">
-        <v>5</v>
+        <v>4.1</v>
       </c>
       <c r="G13" t="n">
-        <v>1.9</v>
+        <v>4.1</v>
       </c>
       <c r="H13" t="n">
-        <v>-3</v>
+        <v>0</v>
       </c>
       <c r="I13" t="inlineStr">
         <is>
@@ -1042,16 +1042,16 @@
         </is>
       </c>
       <c r="K13" t="n">
-        <v>24.74</v>
+        <v>30.67</v>
       </c>
       <c r="L13" t="n">
-        <v>24.02</v>
+        <v>30.67</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>TRMD</t>
+          <t>GNK</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1060,26 +1060,26 @@
         </is>
       </c>
       <c r="C14" t="n">
-        <v>26.74</v>
+        <v>25.48</v>
       </c>
       <c r="D14" t="n">
-        <v>25.43</v>
+        <v>24.64</v>
       </c>
       <c r="E14" t="n">
-        <v>-4.86</v>
+        <v>-3.29</v>
       </c>
       <c r="F14" t="n">
-        <v>6.1</v>
+        <v>5</v>
       </c>
       <c r="G14" t="n">
         <v>1.9</v>
       </c>
       <c r="H14" t="n">
-        <v>-4.2</v>
+        <v>-3</v>
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>BUY (undervalued)</t>
+          <t>HOLD (fairly valued)</t>
         </is>
       </c>
       <c r="J14" t="inlineStr">
@@ -1088,16 +1088,16 @@
         </is>
       </c>
       <c r="K14" t="n">
-        <v>28.45</v>
+        <v>24.74</v>
       </c>
       <c r="L14" t="n">
-        <v>27.32</v>
+        <v>24.02</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>ASC</t>
+          <t>TRMD</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1106,44 +1106,44 @@
         </is>
       </c>
       <c r="C15" t="n">
-        <v>15.96</v>
+        <v>26.74</v>
       </c>
       <c r="D15" t="n">
-        <v>15.93</v>
+        <v>25.43</v>
       </c>
       <c r="E15" t="n">
-        <v>-0.16</v>
+        <v>-4.86</v>
       </c>
       <c r="F15" t="n">
-        <v>0.3</v>
+        <v>6.1</v>
       </c>
       <c r="G15" t="n">
-        <v>0.2</v>
+        <v>1.9</v>
       </c>
       <c r="H15" t="n">
-        <v>-0.2</v>
+        <v>-4.2</v>
       </c>
       <c r="I15" t="inlineStr">
         <is>
+          <t>BUY (undervalued)</t>
+        </is>
+      </c>
+      <c r="J15" t="inlineStr">
+        <is>
           <t>HOLD (fairly valued)</t>
         </is>
       </c>
-      <c r="J15" t="inlineStr">
-        <is>
-          <t>HOLD (fairly valued)</t>
-        </is>
-      </c>
       <c r="K15" t="n">
-        <v>15.17</v>
+        <v>28.45</v>
       </c>
       <c r="L15" t="n">
-        <v>15.15</v>
+        <v>27.32</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>HAFN</t>
+          <t>ASC</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1152,44 +1152,44 @@
         </is>
       </c>
       <c r="C16" t="n">
-        <v>5.34</v>
+        <v>15.96</v>
       </c>
       <c r="D16" t="n">
-        <v>5.22</v>
+        <v>15.93</v>
       </c>
       <c r="E16" t="n">
-        <v>-2.24</v>
+        <v>-0.16</v>
       </c>
       <c r="F16" t="n">
-        <v>-13.7</v>
+        <v>0.3</v>
       </c>
       <c r="G16" t="n">
-        <v>-15.2</v>
+        <v>0.2</v>
       </c>
       <c r="H16" t="n">
-        <v>-1.5</v>
+        <v>-0.2</v>
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>TRIM/SHORT (overvalued)</t>
+          <t>HOLD (fairly valued)</t>
         </is>
       </c>
       <c r="J16" t="inlineStr">
         <is>
-          <t>TRIM/SHORT (overvalued)</t>
+          <t>HOLD (fairly valued)</t>
         </is>
       </c>
       <c r="K16" t="n">
-        <v>6.01</v>
+        <v>15.17</v>
       </c>
       <c r="L16" t="n">
-        <v>5.91</v>
+        <v>15.15</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>DHT</t>
+          <t>HAFN</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1198,26 +1198,26 @@
         </is>
       </c>
       <c r="C17" t="n">
-        <v>15.29</v>
+        <v>5.34</v>
       </c>
       <c r="D17" t="n">
-        <v>13.1</v>
+        <v>5.22</v>
       </c>
       <c r="E17" t="n">
-        <v>-14.35</v>
+        <v>-2.24</v>
       </c>
       <c r="F17" t="n">
-        <v>-3.9</v>
+        <v>-13.7</v>
       </c>
       <c r="G17" t="n">
-        <v>-15.5</v>
+        <v>-15.2</v>
       </c>
       <c r="H17" t="n">
-        <v>-11.5</v>
+        <v>-1.5</v>
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>HOLD (fairly valued)</t>
+          <t>TRIM/SHORT (overvalued)</t>
         </is>
       </c>
       <c r="J17" t="inlineStr">
@@ -1226,16 +1226,16 @@
         </is>
       </c>
       <c r="K17" t="n">
-        <v>16.96</v>
+        <v>6.01</v>
       </c>
       <c r="L17" t="n">
-        <v>14.92</v>
+        <v>5.91</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>FRO</t>
+          <t>DHT</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1244,44 +1244,44 @@
         </is>
       </c>
       <c r="C18" t="n">
-        <v>28.47</v>
+        <v>15.29</v>
       </c>
       <c r="D18" t="n">
-        <v>24.22</v>
+        <v>13.1</v>
       </c>
       <c r="E18" t="n">
-        <v>-14.93</v>
+        <v>-14.35</v>
       </c>
       <c r="F18" t="n">
-        <v>-7.2</v>
+        <v>-3.9</v>
       </c>
       <c r="G18" t="n">
-        <v>-18.9</v>
+        <v>-15.5</v>
       </c>
       <c r="H18" t="n">
-        <v>-11.6</v>
+        <v>-11.5</v>
       </c>
       <c r="I18" t="inlineStr">
         <is>
+          <t>HOLD (fairly valued)</t>
+        </is>
+      </c>
+      <c r="J18" t="inlineStr">
+        <is>
           <t>TRIM/SHORT (overvalued)</t>
         </is>
       </c>
-      <c r="J18" t="inlineStr">
-        <is>
-          <t>TRIM/SHORT (overvalued)</t>
-        </is>
-      </c>
       <c r="K18" t="n">
-        <v>32.95</v>
+        <v>16.96</v>
       </c>
       <c r="L18" t="n">
-        <v>28.82</v>
+        <v>14.92</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>MPCC</t>
+          <t>FRO</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1290,22 +1290,22 @@
         </is>
       </c>
       <c r="C19" t="n">
-        <v>2.02</v>
+        <v>28.47</v>
       </c>
       <c r="D19" t="n">
-        <v>2.02</v>
+        <v>24.22</v>
       </c>
       <c r="E19" t="n">
-        <v>0</v>
+        <v>-14.93</v>
       </c>
       <c r="F19" t="n">
-        <v>-19.3</v>
+        <v>-7.2</v>
       </c>
       <c r="G19" t="n">
-        <v>-19.3</v>
+        <v>-18.9</v>
       </c>
       <c r="H19" t="n">
-        <v>0</v>
+        <v>-11.6</v>
       </c>
       <c r="I19" t="inlineStr">
         <is>
@@ -1318,16 +1318,16 @@
         </is>
       </c>
       <c r="K19" t="n">
-        <v>2.11</v>
+        <v>32.95</v>
       </c>
       <c r="L19" t="n">
-        <v>2.11</v>
+        <v>28.82</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>ECO</t>
+          <t>MPCC</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -1336,22 +1336,22 @@
         </is>
       </c>
       <c r="C20" t="n">
-        <v>39.93</v>
+        <v>2.02</v>
       </c>
       <c r="D20" t="n">
-        <v>33.88</v>
+        <v>2.02</v>
       </c>
       <c r="E20" t="n">
-        <v>-15.16</v>
+        <v>0</v>
       </c>
       <c r="F20" t="n">
-        <v>-9.1</v>
+        <v>-19.3</v>
       </c>
       <c r="G20" t="n">
-        <v>-20.6</v>
+        <v>-19.3</v>
       </c>
       <c r="H20" t="n">
-        <v>-11.5</v>
+        <v>0</v>
       </c>
       <c r="I20" t="inlineStr">
         <is>
@@ -1364,40 +1364,40 @@
         </is>
       </c>
       <c r="K20" t="n">
-        <v>45.33</v>
+        <v>2.11</v>
       </c>
       <c r="L20" t="n">
-        <v>39.59</v>
+        <v>2.11</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>INSW</t>
+          <t>ECO</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>WHOLE-COMPANY (hybrid aggregation)</t>
+          <t>whole-company</t>
         </is>
       </c>
       <c r="C21" t="n">
-        <v>57.91</v>
+        <v>39.93</v>
       </c>
       <c r="D21" t="n">
-        <v>52.59</v>
+        <v>33.88</v>
       </c>
       <c r="E21" t="n">
-        <v>-9.18</v>
+        <v>-15.16</v>
       </c>
       <c r="F21" t="n">
-        <v>-16.8</v>
+        <v>-9.1</v>
       </c>
       <c r="G21" t="n">
-        <v>-22.8</v>
+        <v>-20.6</v>
       </c>
       <c r="H21" t="n">
-        <v>-6.1</v>
+        <v>-11.5</v>
       </c>
       <c r="I21" t="inlineStr">
         <is>
@@ -1410,55 +1410,101 @@
         </is>
       </c>
       <c r="K21" t="n">
-        <v>66.17</v>
+        <v>45.33</v>
       </c>
       <c r="L21" t="n">
-        <v>61.34</v>
+        <v>39.59</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
+          <t>INSW</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>WHOLE-COMPANY (hybrid aggregation)</t>
+        </is>
+      </c>
+      <c r="C22" t="n">
+        <v>57.91</v>
+      </c>
+      <c r="D22" t="n">
+        <v>52.59</v>
+      </c>
+      <c r="E22" t="n">
+        <v>-9.18</v>
+      </c>
+      <c r="F22" t="n">
+        <v>-16.8</v>
+      </c>
+      <c r="G22" t="n">
+        <v>-22.8</v>
+      </c>
+      <c r="H22" t="n">
+        <v>-6.1</v>
+      </c>
+      <c r="I22" t="inlineStr">
+        <is>
+          <t>TRIM/SHORT (overvalued)</t>
+        </is>
+      </c>
+      <c r="J22" t="inlineStr">
+        <is>
+          <t>TRIM/SHORT (overvalued)</t>
+        </is>
+      </c>
+      <c r="K22" t="n">
+        <v>66.17</v>
+      </c>
+      <c r="L22" t="n">
+        <v>61.34</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
           <t>NAT</t>
         </is>
       </c>
-      <c r="B22" t="inlineStr">
-        <is>
-          <t>whole-company</t>
-        </is>
-      </c>
-      <c r="C22" t="n">
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>whole-company</t>
+        </is>
+      </c>
+      <c r="C23" t="n">
         <v>2.63</v>
       </c>
-      <c r="D22" t="n">
+      <c r="D23" t="n">
         <v>2.07</v>
       </c>
-      <c r="E22" t="n">
+      <c r="E23" t="n">
         <v>-21.23</v>
       </c>
-      <c r="F22" t="n">
+      <c r="F23" t="n">
         <v>-43.9</v>
       </c>
-      <c r="G22" t="n">
+      <c r="G23" t="n">
         <v>-52.5</v>
       </c>
-      <c r="H22" t="n">
+      <c r="H23" t="n">
         <v>-8.5</v>
       </c>
-      <c r="I22" t="inlineStr">
+      <c r="I23" t="inlineStr">
         <is>
           <t>TRIM/SHORT (overvalued)</t>
         </is>
       </c>
-      <c r="J22" t="inlineStr">
+      <c r="J23" t="inlineStr">
         <is>
           <t>TRIM/SHORT (overvalued)</t>
         </is>
       </c>
-      <c r="K22" t="n">
+      <c r="K23" t="n">
         <v>3.28</v>
       </c>
-      <c r="L22" t="n">
+      <c r="L23" t="n">
         <v>2.78</v>
       </c>
     </row>

--- a/outputs/transaction_anchor_comparison.xlsx
+++ b/outputs/transaction_anchor_comparison.xlsx
@@ -646,22 +646,22 @@
         </is>
       </c>
       <c r="C5" t="n">
-        <v>9.48</v>
+        <v>9.43</v>
       </c>
       <c r="D5" t="n">
-        <v>10.14</v>
+        <v>9.82</v>
       </c>
       <c r="E5" t="n">
-        <v>6.92</v>
+        <v>4.15</v>
       </c>
       <c r="F5" t="n">
-        <v>39.6</v>
+        <v>40.5</v>
       </c>
       <c r="G5" t="n">
-        <v>49</v>
+        <v>46.3</v>
       </c>
       <c r="H5" t="n">
-        <v>9.4</v>
+        <v>5.9</v>
       </c>
       <c r="I5" t="inlineStr">
         <is>
@@ -674,10 +674,10 @@
         </is>
       </c>
       <c r="K5" t="n">
-        <v>8.92</v>
+        <v>8.98</v>
       </c>
       <c r="L5" t="n">
-        <v>9.52</v>
+        <v>9.35</v>
       </c>
     </row>
     <row r="6">

--- a/outputs/transaction_anchor_comparison.xlsx
+++ b/outputs/transaction_anchor_comparison.xlsx
@@ -499,7 +499,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>BRUT</t>
+          <t>TEN</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -508,22 +508,22 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>9.4</v>
+        <v>95.20999999999999</v>
       </c>
       <c r="D2" t="n">
-        <v>9.4</v>
+        <v>86.95</v>
       </c>
       <c r="E2" t="n">
-        <v>0</v>
+        <v>-8.67</v>
       </c>
       <c r="F2" t="n">
-        <v>104.8</v>
+        <v>90.40000000000001</v>
       </c>
       <c r="G2" t="n">
-        <v>102.4</v>
+        <v>75.7</v>
       </c>
       <c r="H2" t="n">
-        <v>-2.4</v>
+        <v>-14.6</v>
       </c>
       <c r="I2" t="inlineStr">
         <is>
@@ -536,16 +536,16 @@
         </is>
       </c>
       <c r="K2" t="n">
-        <v>10.93</v>
+        <v>69.90000000000001</v>
       </c>
       <c r="L2" t="n">
-        <v>10.81</v>
+        <v>64.54000000000001</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>TEN</t>
+          <t>CCEC</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -554,22 +554,22 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>95.95</v>
+        <v>28.1</v>
       </c>
       <c r="D3" t="n">
-        <v>87.7</v>
+        <v>28.1</v>
       </c>
       <c r="E3" t="n">
-        <v>-8.6</v>
+        <v>0</v>
       </c>
       <c r="F3" t="n">
-        <v>91.40000000000001</v>
+        <v>73.40000000000001</v>
       </c>
       <c r="G3" t="n">
-        <v>76.8</v>
+        <v>73.40000000000001</v>
       </c>
       <c r="H3" t="n">
-        <v>-14.6</v>
+        <v>0</v>
       </c>
       <c r="I3" t="inlineStr">
         <is>
@@ -582,16 +582,16 @@
         </is>
       </c>
       <c r="K3" t="n">
-        <v>70.29000000000001</v>
+        <v>35.91</v>
       </c>
       <c r="L3" t="n">
-        <v>64.93000000000001</v>
+        <v>35.91</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>CCEC</t>
+          <t>SB</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -600,22 +600,22 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>28.1</v>
+        <v>9.92</v>
       </c>
       <c r="D4" t="n">
-        <v>28.1</v>
+        <v>10.31</v>
       </c>
       <c r="E4" t="n">
-        <v>0</v>
+        <v>3.95</v>
       </c>
       <c r="F4" t="n">
-        <v>73.40000000000001</v>
+        <v>45.5</v>
       </c>
       <c r="G4" t="n">
-        <v>73.40000000000001</v>
+        <v>51.3</v>
       </c>
       <c r="H4" t="n">
-        <v>0</v>
+        <v>5.9</v>
       </c>
       <c r="I4" t="inlineStr">
         <is>
@@ -628,16 +628,16 @@
         </is>
       </c>
       <c r="K4" t="n">
-        <v>35.91</v>
+        <v>9.300000000000001</v>
       </c>
       <c r="L4" t="n">
-        <v>35.91</v>
+        <v>9.67</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>SB</t>
+          <t>TNK</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -646,22 +646,22 @@
         </is>
       </c>
       <c r="C5" t="n">
-        <v>9.43</v>
+        <v>83.31999999999999</v>
       </c>
       <c r="D5" t="n">
-        <v>9.82</v>
+        <v>77.51000000000001</v>
       </c>
       <c r="E5" t="n">
-        <v>4.15</v>
+        <v>-6.97</v>
       </c>
       <c r="F5" t="n">
-        <v>40.5</v>
+        <v>24.5</v>
       </c>
       <c r="G5" t="n">
-        <v>46.3</v>
+        <v>17.1</v>
       </c>
       <c r="H5" t="n">
-        <v>5.9</v>
+        <v>-7.4</v>
       </c>
       <c r="I5" t="inlineStr">
         <is>
@@ -674,16 +674,16 @@
         </is>
       </c>
       <c r="K5" t="n">
-        <v>8.98</v>
+        <v>84.64</v>
       </c>
       <c r="L5" t="n">
-        <v>9.35</v>
+        <v>79.59</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>CAPT</t>
+          <t>CMDB</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -692,22 +692,22 @@
         </is>
       </c>
       <c r="C6" t="n">
-        <v>15.2</v>
+        <v>32.12</v>
       </c>
       <c r="D6" t="n">
-        <v>15.03</v>
+        <v>31.33</v>
       </c>
       <c r="E6" t="n">
-        <v>-1.12</v>
+        <v>-2.45</v>
       </c>
       <c r="F6" t="n">
-        <v>33.3</v>
+        <v>19.6</v>
       </c>
       <c r="G6" t="n">
-        <v>31.1</v>
+        <v>16.9</v>
       </c>
       <c r="H6" t="n">
-        <v>-2.2</v>
+        <v>-2.7</v>
       </c>
       <c r="I6" t="inlineStr">
         <is>
@@ -720,16 +720,16 @@
         </is>
       </c>
       <c r="K6" t="n">
-        <v>17.05</v>
+        <v>20.9</v>
       </c>
       <c r="L6" t="n">
-        <v>16.77</v>
+        <v>20.43</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>TNK</t>
+          <t>BRUT</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -738,22 +738,22 @@
         </is>
       </c>
       <c r="C7" t="n">
-        <v>83.31999999999999</v>
+        <v>4.34</v>
       </c>
       <c r="D7" t="n">
-        <v>77.51000000000001</v>
+        <v>4.34</v>
       </c>
       <c r="E7" t="n">
-        <v>-6.97</v>
+        <v>0</v>
       </c>
       <c r="F7" t="n">
-        <v>24.5</v>
+        <v>14.6</v>
       </c>
       <c r="G7" t="n">
-        <v>17.1</v>
+        <v>12.2</v>
       </c>
       <c r="H7" t="n">
-        <v>-7.4</v>
+        <v>-2.4</v>
       </c>
       <c r="I7" t="inlineStr">
         <is>
@@ -766,40 +766,40 @@
         </is>
       </c>
       <c r="K7" t="n">
-        <v>84.64</v>
+        <v>6.12</v>
       </c>
       <c r="L7" t="n">
-        <v>79.59</v>
+        <v>5.99</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>CMDB</t>
+          <t>CMBT</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>whole-company</t>
+          <t>WHOLE-COMPANY (hybrid aggregation)</t>
         </is>
       </c>
       <c r="C8" t="n">
-        <v>32.12</v>
+        <v>15.37</v>
       </c>
       <c r="D8" t="n">
-        <v>31.33</v>
+        <v>15.4</v>
       </c>
       <c r="E8" t="n">
-        <v>-2.45</v>
+        <v>0.18</v>
       </c>
       <c r="F8" t="n">
-        <v>19.6</v>
+        <v>11.4</v>
       </c>
       <c r="G8" t="n">
-        <v>16.9</v>
+        <v>11.3</v>
       </c>
       <c r="H8" t="n">
-        <v>-2.7</v>
+        <v>-0.1</v>
       </c>
       <c r="I8" t="inlineStr">
         <is>
@@ -812,40 +812,40 @@
         </is>
       </c>
       <c r="K8" t="n">
-        <v>20.9</v>
+        <v>15.7</v>
       </c>
       <c r="L8" t="n">
-        <v>20.43</v>
+        <v>15.69</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>CMBT</t>
+          <t>STNG</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>WHOLE-COMPANY (hybrid aggregation)</t>
+          <t>whole-company</t>
         </is>
       </c>
       <c r="C9" t="n">
-        <v>15.24</v>
+        <v>83.87</v>
       </c>
       <c r="D9" t="n">
-        <v>15.27</v>
+        <v>80.34999999999999</v>
       </c>
       <c r="E9" t="n">
-        <v>0.18</v>
+        <v>-4.19</v>
       </c>
       <c r="F9" t="n">
-        <v>11</v>
+        <v>14.6</v>
       </c>
       <c r="G9" t="n">
-        <v>10.9</v>
+        <v>10.2</v>
       </c>
       <c r="H9" t="n">
-        <v>-0.1</v>
+        <v>-4.4</v>
       </c>
       <c r="I9" t="inlineStr">
         <is>
@@ -858,16 +858,16 @@
         </is>
       </c>
       <c r="K9" t="n">
-        <v>15.65</v>
+        <v>83.16</v>
       </c>
       <c r="L9" t="n">
-        <v>15.64</v>
+        <v>79.98999999999999</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>STNG</t>
+          <t>GSL</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -876,22 +876,22 @@
         </is>
       </c>
       <c r="C10" t="n">
-        <v>83.87</v>
+        <v>38.59</v>
       </c>
       <c r="D10" t="n">
-        <v>80.34999999999999</v>
+        <v>38.59</v>
       </c>
       <c r="E10" t="n">
-        <v>-4.19</v>
+        <v>0</v>
       </c>
       <c r="F10" t="n">
-        <v>14.6</v>
+        <v>7.4</v>
       </c>
       <c r="G10" t="n">
-        <v>10.2</v>
+        <v>7.4</v>
       </c>
       <c r="H10" t="n">
-        <v>-4.4</v>
+        <v>0</v>
       </c>
       <c r="I10" t="inlineStr">
         <is>
@@ -904,16 +904,16 @@
         </is>
       </c>
       <c r="K10" t="n">
-        <v>83.16</v>
+        <v>40.59</v>
       </c>
       <c r="L10" t="n">
-        <v>79.98999999999999</v>
+        <v>40.59</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>GSL</t>
+          <t>SBLK</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -922,22 +922,22 @@
         </is>
       </c>
       <c r="C11" t="n">
-        <v>38.59</v>
+        <v>27.34</v>
       </c>
       <c r="D11" t="n">
-        <v>38.59</v>
+        <v>26.91</v>
       </c>
       <c r="E11" t="n">
-        <v>0</v>
+        <v>-1.56</v>
       </c>
       <c r="F11" t="n">
-        <v>7.4</v>
+        <v>8.4</v>
       </c>
       <c r="G11" t="n">
-        <v>7.4</v>
+        <v>6.9</v>
       </c>
       <c r="H11" t="n">
-        <v>0</v>
+        <v>-1.5</v>
       </c>
       <c r="I11" t="inlineStr">
         <is>
@@ -950,16 +950,16 @@
         </is>
       </c>
       <c r="K11" t="n">
-        <v>40.59</v>
+        <v>26.45</v>
       </c>
       <c r="L11" t="n">
-        <v>40.59</v>
+        <v>26.07</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>SBLK</t>
+          <t>CAPT</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -968,22 +968,22 @@
         </is>
       </c>
       <c r="C12" t="n">
-        <v>27.34</v>
+        <v>11.75</v>
       </c>
       <c r="D12" t="n">
-        <v>26.91</v>
+        <v>11.58</v>
       </c>
       <c r="E12" t="n">
-        <v>-1.56</v>
+        <v>-1.44</v>
       </c>
       <c r="F12" t="n">
-        <v>8.4</v>
+        <v>8.6</v>
       </c>
       <c r="G12" t="n">
-        <v>6.9</v>
+        <v>6.5</v>
       </c>
       <c r="H12" t="n">
-        <v>-1.5</v>
+        <v>-2.2</v>
       </c>
       <c r="I12" t="inlineStr">
         <is>
@@ -996,10 +996,10 @@
         </is>
       </c>
       <c r="K12" t="n">
-        <v>26.45</v>
+        <v>13.89</v>
       </c>
       <c r="L12" t="n">
-        <v>26.07</v>
+        <v>13.62</v>
       </c>
     </row>
     <row r="13">
@@ -1060,38 +1060,38 @@
         </is>
       </c>
       <c r="C14" t="n">
-        <v>25.48</v>
+        <v>25.53</v>
       </c>
       <c r="D14" t="n">
-        <v>24.64</v>
+        <v>24.69</v>
       </c>
       <c r="E14" t="n">
-        <v>-3.29</v>
+        <v>-3.28</v>
       </c>
       <c r="F14" t="n">
-        <v>5</v>
+        <v>5.1</v>
       </c>
       <c r="G14" t="n">
-        <v>1.9</v>
+        <v>2</v>
       </c>
       <c r="H14" t="n">
         <v>-3</v>
       </c>
       <c r="I14" t="inlineStr">
         <is>
+          <t>BUY (undervalued)</t>
+        </is>
+      </c>
+      <c r="J14" t="inlineStr">
+        <is>
           <t>HOLD (fairly valued)</t>
         </is>
       </c>
-      <c r="J14" t="inlineStr">
-        <is>
-          <t>HOLD (fairly valued)</t>
-        </is>
-      </c>
       <c r="K14" t="n">
-        <v>24.74</v>
+        <v>24.77</v>
       </c>
       <c r="L14" t="n">
-        <v>24.02</v>
+        <v>24.05</v>
       </c>
     </row>
     <row r="15">
@@ -1244,26 +1244,26 @@
         </is>
       </c>
       <c r="C18" t="n">
-        <v>15.29</v>
+        <v>14.7</v>
       </c>
       <c r="D18" t="n">
-        <v>13.1</v>
+        <v>12.51</v>
       </c>
       <c r="E18" t="n">
-        <v>-14.35</v>
+        <v>-14.92</v>
       </c>
       <c r="F18" t="n">
-        <v>-3.9</v>
+        <v>-6.7</v>
       </c>
       <c r="G18" t="n">
-        <v>-15.5</v>
+        <v>-18.3</v>
       </c>
       <c r="H18" t="n">
         <v>-11.5</v>
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>HOLD (fairly valued)</t>
+          <t>TRIM/SHORT (overvalued)</t>
         </is>
       </c>
       <c r="J18" t="inlineStr">
@@ -1272,16 +1272,16 @@
         </is>
       </c>
       <c r="K18" t="n">
-        <v>16.96</v>
+        <v>16.46</v>
       </c>
       <c r="L18" t="n">
-        <v>14.92</v>
+        <v>14.42</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>FRO</t>
+          <t>MPCC</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1290,22 +1290,22 @@
         </is>
       </c>
       <c r="C19" t="n">
-        <v>28.47</v>
+        <v>2.02</v>
       </c>
       <c r="D19" t="n">
-        <v>24.22</v>
+        <v>2.02</v>
       </c>
       <c r="E19" t="n">
-        <v>-14.93</v>
+        <v>0</v>
       </c>
       <c r="F19" t="n">
-        <v>-7.2</v>
+        <v>-19.3</v>
       </c>
       <c r="G19" t="n">
-        <v>-18.9</v>
+        <v>-19.3</v>
       </c>
       <c r="H19" t="n">
-        <v>-11.6</v>
+        <v>0</v>
       </c>
       <c r="I19" t="inlineStr">
         <is>
@@ -1318,16 +1318,16 @@
         </is>
       </c>
       <c r="K19" t="n">
-        <v>32.95</v>
+        <v>2.11</v>
       </c>
       <c r="L19" t="n">
-        <v>28.82</v>
+        <v>2.11</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>MPCC</t>
+          <t>FRO</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -1336,22 +1336,22 @@
         </is>
       </c>
       <c r="C20" t="n">
-        <v>2.02</v>
+        <v>26.92</v>
       </c>
       <c r="D20" t="n">
-        <v>2.02</v>
+        <v>22.67</v>
       </c>
       <c r="E20" t="n">
-        <v>0</v>
+        <v>-15.79</v>
       </c>
       <c r="F20" t="n">
-        <v>-19.3</v>
+        <v>-10.9</v>
       </c>
       <c r="G20" t="n">
-        <v>-19.3</v>
+        <v>-22.5</v>
       </c>
       <c r="H20" t="n">
-        <v>0</v>
+        <v>-11.6</v>
       </c>
       <c r="I20" t="inlineStr">
         <is>
@@ -1364,40 +1364,40 @@
         </is>
       </c>
       <c r="K20" t="n">
-        <v>2.11</v>
+        <v>31.66</v>
       </c>
       <c r="L20" t="n">
-        <v>2.11</v>
+        <v>27.53</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>ECO</t>
+          <t>INSW</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>whole-company</t>
+          <t>WHOLE-COMPANY (hybrid aggregation)</t>
         </is>
       </c>
       <c r="C21" t="n">
-        <v>39.93</v>
+        <v>57.91</v>
       </c>
       <c r="D21" t="n">
-        <v>33.88</v>
+        <v>52.59</v>
       </c>
       <c r="E21" t="n">
-        <v>-15.16</v>
+        <v>-9.18</v>
       </c>
       <c r="F21" t="n">
-        <v>-9.1</v>
+        <v>-16.8</v>
       </c>
       <c r="G21" t="n">
-        <v>-20.6</v>
+        <v>-22.8</v>
       </c>
       <c r="H21" t="n">
-        <v>-11.5</v>
+        <v>-6.1</v>
       </c>
       <c r="I21" t="inlineStr">
         <is>
@@ -1410,40 +1410,40 @@
         </is>
       </c>
       <c r="K21" t="n">
-        <v>45.33</v>
+        <v>66.17</v>
       </c>
       <c r="L21" t="n">
-        <v>39.59</v>
+        <v>61.34</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>INSW</t>
+          <t>ECO</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>WHOLE-COMPANY (hybrid aggregation)</t>
+          <t>whole-company</t>
         </is>
       </c>
       <c r="C22" t="n">
-        <v>57.91</v>
+        <v>38.21</v>
       </c>
       <c r="D22" t="n">
-        <v>52.59</v>
+        <v>32.16</v>
       </c>
       <c r="E22" t="n">
-        <v>-9.18</v>
+        <v>-15.84</v>
       </c>
       <c r="F22" t="n">
-        <v>-16.8</v>
+        <v>-12</v>
       </c>
       <c r="G22" t="n">
-        <v>-22.8</v>
+        <v>-23.5</v>
       </c>
       <c r="H22" t="n">
-        <v>-6.1</v>
+        <v>-11.5</v>
       </c>
       <c r="I22" t="inlineStr">
         <is>
@@ -1456,10 +1456,10 @@
         </is>
       </c>
       <c r="K22" t="n">
-        <v>66.17</v>
+        <v>43.91</v>
       </c>
       <c r="L22" t="n">
-        <v>61.34</v>
+        <v>38.18</v>
       </c>
     </row>
     <row r="23">

--- a/outputs/transaction_anchor_comparison.xlsx
+++ b/outputs/transaction_anchor_comparison.xlsx
@@ -499,7 +499,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>TEN</t>
+          <t>BRUT</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -508,22 +508,22 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>95.20999999999999</v>
+        <v>9.4</v>
       </c>
       <c r="D2" t="n">
-        <v>86.95</v>
+        <v>9.4</v>
       </c>
       <c r="E2" t="n">
-        <v>-8.67</v>
+        <v>0</v>
       </c>
       <c r="F2" t="n">
-        <v>90.40000000000001</v>
+        <v>109.9</v>
       </c>
       <c r="G2" t="n">
-        <v>75.7</v>
+        <v>107.4</v>
       </c>
       <c r="H2" t="n">
-        <v>-14.6</v>
+        <v>-2.5</v>
       </c>
       <c r="I2" t="inlineStr">
         <is>
@@ -536,16 +536,16 @@
         </is>
       </c>
       <c r="K2" t="n">
-        <v>69.90000000000001</v>
+        <v>10.93</v>
       </c>
       <c r="L2" t="n">
-        <v>64.54000000000001</v>
+        <v>10.81</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>CCEC</t>
+          <t>TEN</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -554,22 +554,22 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>28.1</v>
+        <v>96.95</v>
       </c>
       <c r="D3" t="n">
-        <v>28.1</v>
+        <v>88.7</v>
       </c>
       <c r="E3" t="n">
-        <v>0</v>
+        <v>-8.51</v>
       </c>
       <c r="F3" t="n">
-        <v>73.40000000000001</v>
+        <v>98.09999999999999</v>
       </c>
       <c r="G3" t="n">
-        <v>73.40000000000001</v>
+        <v>83.09999999999999</v>
       </c>
       <c r="H3" t="n">
-        <v>0</v>
+        <v>-15</v>
       </c>
       <c r="I3" t="inlineStr">
         <is>
@@ -582,16 +582,16 @@
         </is>
       </c>
       <c r="K3" t="n">
-        <v>35.91</v>
+        <v>70.86</v>
       </c>
       <c r="L3" t="n">
-        <v>35.91</v>
+        <v>65.48999999999999</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>SB</t>
+          <t>CCEC</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -600,22 +600,22 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>9.92</v>
+        <v>28.1</v>
       </c>
       <c r="D4" t="n">
-        <v>10.31</v>
+        <v>28.1</v>
       </c>
       <c r="E4" t="n">
-        <v>3.95</v>
+        <v>0</v>
       </c>
       <c r="F4" t="n">
-        <v>45.5</v>
+        <v>72</v>
       </c>
       <c r="G4" t="n">
-        <v>51.3</v>
+        <v>72</v>
       </c>
       <c r="H4" t="n">
-        <v>5.9</v>
+        <v>0</v>
       </c>
       <c r="I4" t="inlineStr">
         <is>
@@ -628,16 +628,16 @@
         </is>
       </c>
       <c r="K4" t="n">
-        <v>9.300000000000001</v>
+        <v>35.91</v>
       </c>
       <c r="L4" t="n">
-        <v>9.67</v>
+        <v>35.91</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>TNK</t>
+          <t>SB</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -646,22 +646,22 @@
         </is>
       </c>
       <c r="C5" t="n">
-        <v>83.31999999999999</v>
+        <v>9.92</v>
       </c>
       <c r="D5" t="n">
-        <v>77.51000000000001</v>
+        <v>10.31</v>
       </c>
       <c r="E5" t="n">
-        <v>-6.97</v>
+        <v>3.95</v>
       </c>
       <c r="F5" t="n">
-        <v>24.5</v>
+        <v>46.1</v>
       </c>
       <c r="G5" t="n">
-        <v>17.1</v>
+        <v>52</v>
       </c>
       <c r="H5" t="n">
-        <v>-7.4</v>
+        <v>5.9</v>
       </c>
       <c r="I5" t="inlineStr">
         <is>
@@ -674,16 +674,16 @@
         </is>
       </c>
       <c r="K5" t="n">
-        <v>84.64</v>
+        <v>9.300000000000001</v>
       </c>
       <c r="L5" t="n">
-        <v>79.59</v>
+        <v>9.67</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>CMDB</t>
+          <t>CAPT</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -692,22 +692,22 @@
         </is>
       </c>
       <c r="C6" t="n">
-        <v>32.12</v>
+        <v>15.76</v>
       </c>
       <c r="D6" t="n">
-        <v>31.33</v>
+        <v>15.59</v>
       </c>
       <c r="E6" t="n">
-        <v>-2.45</v>
+        <v>-1.08</v>
       </c>
       <c r="F6" t="n">
-        <v>19.6</v>
+        <v>37.8</v>
       </c>
       <c r="G6" t="n">
-        <v>16.9</v>
+        <v>35.6</v>
       </c>
       <c r="H6" t="n">
-        <v>-2.7</v>
+        <v>-2.2</v>
       </c>
       <c r="I6" t="inlineStr">
         <is>
@@ -720,16 +720,16 @@
         </is>
       </c>
       <c r="K6" t="n">
-        <v>20.9</v>
+        <v>17.54</v>
       </c>
       <c r="L6" t="n">
-        <v>20.43</v>
+        <v>17.26</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>BRUT</t>
+          <t>TNK</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -738,22 +738,22 @@
         </is>
       </c>
       <c r="C7" t="n">
-        <v>4.34</v>
+        <v>83.31999999999999</v>
       </c>
       <c r="D7" t="n">
-        <v>4.34</v>
+        <v>77.51000000000001</v>
       </c>
       <c r="E7" t="n">
-        <v>0</v>
+        <v>-6.97</v>
       </c>
       <c r="F7" t="n">
-        <v>14.6</v>
+        <v>28.3</v>
       </c>
       <c r="G7" t="n">
-        <v>12.2</v>
+        <v>20.6</v>
       </c>
       <c r="H7" t="n">
-        <v>-2.4</v>
+        <v>-7.6</v>
       </c>
       <c r="I7" t="inlineStr">
         <is>
@@ -766,10 +766,10 @@
         </is>
       </c>
       <c r="K7" t="n">
-        <v>6.12</v>
+        <v>84.64</v>
       </c>
       <c r="L7" t="n">
-        <v>5.99</v>
+        <v>79.59</v>
       </c>
     </row>
     <row r="8">
@@ -784,19 +784,19 @@
         </is>
       </c>
       <c r="C8" t="n">
-        <v>15.37</v>
+        <v>15.84</v>
       </c>
       <c r="D8" t="n">
-        <v>15.4</v>
+        <v>15.87</v>
       </c>
       <c r="E8" t="n">
         <v>0.18</v>
       </c>
       <c r="F8" t="n">
-        <v>11.4</v>
+        <v>14.2</v>
       </c>
       <c r="G8" t="n">
-        <v>11.3</v>
+        <v>14.1</v>
       </c>
       <c r="H8" t="n">
         <v>-0.1</v>
@@ -812,10 +812,10 @@
         </is>
       </c>
       <c r="K8" t="n">
-        <v>15.7</v>
+        <v>16.08</v>
       </c>
       <c r="L8" t="n">
-        <v>15.69</v>
+        <v>16.07</v>
       </c>
     </row>
     <row r="9">
@@ -839,13 +839,13 @@
         <v>-4.19</v>
       </c>
       <c r="F9" t="n">
-        <v>14.6</v>
+        <v>18.6</v>
       </c>
       <c r="G9" t="n">
-        <v>10.2</v>
+        <v>14.1</v>
       </c>
       <c r="H9" t="n">
-        <v>-4.4</v>
+        <v>-4.5</v>
       </c>
       <c r="I9" t="inlineStr">
         <is>
@@ -867,7 +867,7 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>GSL</t>
+          <t>CMDB</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -876,22 +876,22 @@
         </is>
       </c>
       <c r="C10" t="n">
-        <v>38.59</v>
+        <v>32.12</v>
       </c>
       <c r="D10" t="n">
-        <v>38.59</v>
+        <v>31.33</v>
       </c>
       <c r="E10" t="n">
-        <v>0</v>
+        <v>-2.45</v>
       </c>
       <c r="F10" t="n">
-        <v>7.4</v>
+        <v>16.2</v>
       </c>
       <c r="G10" t="n">
-        <v>7.4</v>
+        <v>13.6</v>
       </c>
       <c r="H10" t="n">
-        <v>0</v>
+        <v>-2.6</v>
       </c>
       <c r="I10" t="inlineStr">
         <is>
@@ -904,16 +904,16 @@
         </is>
       </c>
       <c r="K10" t="n">
-        <v>40.59</v>
+        <v>20.9</v>
       </c>
       <c r="L10" t="n">
-        <v>40.59</v>
+        <v>20.43</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>SBLK</t>
+          <t>GSL</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -922,22 +922,22 @@
         </is>
       </c>
       <c r="C11" t="n">
-        <v>27.34</v>
+        <v>38.59</v>
       </c>
       <c r="D11" t="n">
-        <v>26.91</v>
+        <v>38.59</v>
       </c>
       <c r="E11" t="n">
-        <v>-1.56</v>
+        <v>0</v>
       </c>
       <c r="F11" t="n">
-        <v>8.4</v>
+        <v>7.6</v>
       </c>
       <c r="G11" t="n">
-        <v>6.9</v>
+        <v>7.6</v>
       </c>
       <c r="H11" t="n">
-        <v>-1.5</v>
+        <v>0</v>
       </c>
       <c r="I11" t="inlineStr">
         <is>
@@ -950,16 +950,16 @@
         </is>
       </c>
       <c r="K11" t="n">
-        <v>26.45</v>
+        <v>40.59</v>
       </c>
       <c r="L11" t="n">
-        <v>26.07</v>
+        <v>40.59</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>CAPT</t>
+          <t>SBLK</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -968,22 +968,22 @@
         </is>
       </c>
       <c r="C12" t="n">
-        <v>11.75</v>
+        <v>27.34</v>
       </c>
       <c r="D12" t="n">
-        <v>11.58</v>
+        <v>26.91</v>
       </c>
       <c r="E12" t="n">
-        <v>-1.44</v>
+        <v>-1.56</v>
       </c>
       <c r="F12" t="n">
-        <v>8.6</v>
+        <v>7.4</v>
       </c>
       <c r="G12" t="n">
-        <v>6.5</v>
+        <v>5.8</v>
       </c>
       <c r="H12" t="n">
-        <v>-2.2</v>
+        <v>-1.5</v>
       </c>
       <c r="I12" t="inlineStr">
         <is>
@@ -996,10 +996,10 @@
         </is>
       </c>
       <c r="K12" t="n">
-        <v>13.89</v>
+        <v>26.45</v>
       </c>
       <c r="L12" t="n">
-        <v>13.62</v>
+        <v>26.07</v>
       </c>
     </row>
     <row r="13">
@@ -1023,10 +1023,10 @@
         <v>0</v>
       </c>
       <c r="F13" t="n">
-        <v>4.1</v>
+        <v>4.7</v>
       </c>
       <c r="G13" t="n">
-        <v>4.1</v>
+        <v>4.7</v>
       </c>
       <c r="H13" t="n">
         <v>0</v>
@@ -1051,7 +1051,7 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>GNK</t>
+          <t>TRMD</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1060,22 +1060,22 @@
         </is>
       </c>
       <c r="C14" t="n">
-        <v>25.53</v>
+        <v>26.74</v>
       </c>
       <c r="D14" t="n">
-        <v>24.69</v>
+        <v>25.43</v>
       </c>
       <c r="E14" t="n">
-        <v>-3.28</v>
+        <v>-4.86</v>
       </c>
       <c r="F14" t="n">
-        <v>5.1</v>
+        <v>8.1</v>
       </c>
       <c r="G14" t="n">
-        <v>2</v>
+        <v>3.8</v>
       </c>
       <c r="H14" t="n">
-        <v>-3</v>
+        <v>-4.3</v>
       </c>
       <c r="I14" t="inlineStr">
         <is>
@@ -1088,16 +1088,16 @@
         </is>
       </c>
       <c r="K14" t="n">
-        <v>24.77</v>
+        <v>28.45</v>
       </c>
       <c r="L14" t="n">
-        <v>24.05</v>
+        <v>27.32</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>TRMD</t>
+          <t>GNK</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1106,26 +1106,26 @@
         </is>
       </c>
       <c r="C15" t="n">
-        <v>26.74</v>
+        <v>25.53</v>
       </c>
       <c r="D15" t="n">
-        <v>25.43</v>
+        <v>24.69</v>
       </c>
       <c r="E15" t="n">
-        <v>-4.86</v>
+        <v>-3.28</v>
       </c>
       <c r="F15" t="n">
-        <v>6.1</v>
+        <v>1.6</v>
       </c>
       <c r="G15" t="n">
-        <v>1.9</v>
+        <v>-1.4</v>
       </c>
       <c r="H15" t="n">
-        <v>-4.2</v>
+        <v>-2.9</v>
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>BUY (undervalued)</t>
+          <t>HOLD (fairly valued)</t>
         </is>
       </c>
       <c r="J15" t="inlineStr">
@@ -1134,10 +1134,10 @@
         </is>
       </c>
       <c r="K15" t="n">
-        <v>28.45</v>
+        <v>24.77</v>
       </c>
       <c r="L15" t="n">
-        <v>27.32</v>
+        <v>24.05</v>
       </c>
     </row>
     <row r="16">
@@ -1161,22 +1161,22 @@
         <v>-0.16</v>
       </c>
       <c r="F16" t="n">
-        <v>0.3</v>
+        <v>-5.2</v>
       </c>
       <c r="G16" t="n">
-        <v>0.2</v>
+        <v>-5.3</v>
       </c>
       <c r="H16" t="n">
-        <v>-0.2</v>
+        <v>-0.1</v>
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>HOLD (fairly valued)</t>
+          <t>TRIM/SHORT (overvalued)</t>
         </is>
       </c>
       <c r="J16" t="inlineStr">
         <is>
-          <t>HOLD (fairly valued)</t>
+          <t>TRIM/SHORT (overvalued)</t>
         </is>
       </c>
       <c r="K16" t="n">
@@ -1189,7 +1189,7 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>HAFN</t>
+          <t>DHT</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1198,44 +1198,44 @@
         </is>
       </c>
       <c r="C17" t="n">
-        <v>5.34</v>
+        <v>15.29</v>
       </c>
       <c r="D17" t="n">
-        <v>5.22</v>
+        <v>13.1</v>
       </c>
       <c r="E17" t="n">
-        <v>-2.24</v>
+        <v>-14.35</v>
       </c>
       <c r="F17" t="n">
-        <v>-13.7</v>
+        <v>-0.7</v>
       </c>
       <c r="G17" t="n">
-        <v>-15.2</v>
+        <v>-12.7</v>
       </c>
       <c r="H17" t="n">
-        <v>-1.5</v>
+        <v>-11.9</v>
       </c>
       <c r="I17" t="inlineStr">
         <is>
+          <t>HOLD (fairly valued)</t>
+        </is>
+      </c>
+      <c r="J17" t="inlineStr">
+        <is>
           <t>TRIM/SHORT (overvalued)</t>
         </is>
       </c>
-      <c r="J17" t="inlineStr">
-        <is>
-          <t>TRIM/SHORT (overvalued)</t>
-        </is>
-      </c>
       <c r="K17" t="n">
-        <v>6.01</v>
+        <v>16.96</v>
       </c>
       <c r="L17" t="n">
-        <v>5.91</v>
+        <v>14.92</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>DHT</t>
+          <t>HAFN</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1244,22 +1244,22 @@
         </is>
       </c>
       <c r="C18" t="n">
-        <v>14.7</v>
+        <v>5.34</v>
       </c>
       <c r="D18" t="n">
-        <v>12.51</v>
+        <v>5.22</v>
       </c>
       <c r="E18" t="n">
-        <v>-14.92</v>
+        <v>-2.24</v>
       </c>
       <c r="F18" t="n">
-        <v>-6.7</v>
+        <v>-12.3</v>
       </c>
       <c r="G18" t="n">
-        <v>-18.3</v>
+        <v>-13.8</v>
       </c>
       <c r="H18" t="n">
-        <v>-11.5</v>
+        <v>-1.5</v>
       </c>
       <c r="I18" t="inlineStr">
         <is>
@@ -1272,16 +1272,16 @@
         </is>
       </c>
       <c r="K18" t="n">
-        <v>16.46</v>
+        <v>6.01</v>
       </c>
       <c r="L18" t="n">
-        <v>14.42</v>
+        <v>5.91</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>MPCC</t>
+          <t>FRO</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1290,22 +1290,22 @@
         </is>
       </c>
       <c r="C19" t="n">
-        <v>2.02</v>
+        <v>28.47</v>
       </c>
       <c r="D19" t="n">
-        <v>2.02</v>
+        <v>24.22</v>
       </c>
       <c r="E19" t="n">
-        <v>0</v>
+        <v>-14.93</v>
       </c>
       <c r="F19" t="n">
-        <v>-19.3</v>
+        <v>-7</v>
       </c>
       <c r="G19" t="n">
-        <v>-19.3</v>
+        <v>-18.7</v>
       </c>
       <c r="H19" t="n">
-        <v>0</v>
+        <v>-11.6</v>
       </c>
       <c r="I19" t="inlineStr">
         <is>
@@ -1318,16 +1318,16 @@
         </is>
       </c>
       <c r="K19" t="n">
-        <v>2.11</v>
+        <v>32.95</v>
       </c>
       <c r="L19" t="n">
-        <v>2.11</v>
+        <v>28.82</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>FRO</t>
+          <t>ECO</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -1336,19 +1336,19 @@
         </is>
       </c>
       <c r="C20" t="n">
-        <v>26.92</v>
+        <v>40.61</v>
       </c>
       <c r="D20" t="n">
-        <v>22.67</v>
+        <v>34.56</v>
       </c>
       <c r="E20" t="n">
-        <v>-15.79</v>
+        <v>-14.9</v>
       </c>
       <c r="F20" t="n">
-        <v>-10.9</v>
+        <v>-7.5</v>
       </c>
       <c r="G20" t="n">
-        <v>-22.5</v>
+        <v>-19</v>
       </c>
       <c r="H20" t="n">
         <v>-11.6</v>
@@ -1364,40 +1364,40 @@
         </is>
       </c>
       <c r="K20" t="n">
-        <v>31.66</v>
+        <v>45.9</v>
       </c>
       <c r="L20" t="n">
-        <v>27.53</v>
+        <v>40.17</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>INSW</t>
+          <t>MPCC</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>WHOLE-COMPANY (hybrid aggregation)</t>
+          <t>whole-company</t>
         </is>
       </c>
       <c r="C21" t="n">
-        <v>57.91</v>
+        <v>2.02</v>
       </c>
       <c r="D21" t="n">
-        <v>52.59</v>
+        <v>2.02</v>
       </c>
       <c r="E21" t="n">
-        <v>-9.18</v>
+        <v>0</v>
       </c>
       <c r="F21" t="n">
-        <v>-16.8</v>
+        <v>-19.6</v>
       </c>
       <c r="G21" t="n">
-        <v>-22.8</v>
+        <v>-19.6</v>
       </c>
       <c r="H21" t="n">
-        <v>-6.1</v>
+        <v>0</v>
       </c>
       <c r="I21" t="inlineStr">
         <is>
@@ -1410,40 +1410,40 @@
         </is>
       </c>
       <c r="K21" t="n">
-        <v>66.17</v>
+        <v>2.11</v>
       </c>
       <c r="L21" t="n">
-        <v>61.34</v>
+        <v>2.11</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>ECO</t>
+          <t>INSW</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>whole-company</t>
+          <t>WHOLE-COMPANY (hybrid aggregation)</t>
         </is>
       </c>
       <c r="C22" t="n">
-        <v>38.21</v>
+        <v>57.91</v>
       </c>
       <c r="D22" t="n">
-        <v>32.16</v>
+        <v>52.59</v>
       </c>
       <c r="E22" t="n">
-        <v>-15.84</v>
+        <v>-9.18</v>
       </c>
       <c r="F22" t="n">
-        <v>-12</v>
+        <v>-15</v>
       </c>
       <c r="G22" t="n">
-        <v>-23.5</v>
+        <v>-21.2</v>
       </c>
       <c r="H22" t="n">
-        <v>-11.5</v>
+        <v>-6.2</v>
       </c>
       <c r="I22" t="inlineStr">
         <is>
@@ -1456,10 +1456,10 @@
         </is>
       </c>
       <c r="K22" t="n">
-        <v>43.91</v>
+        <v>66.17</v>
       </c>
       <c r="L22" t="n">
-        <v>38.18</v>
+        <v>61.34</v>
       </c>
     </row>
     <row r="23">
@@ -1483,13 +1483,13 @@
         <v>-21.23</v>
       </c>
       <c r="F23" t="n">
-        <v>-43.9</v>
+        <v>-43.2</v>
       </c>
       <c r="G23" t="n">
-        <v>-52.5</v>
+        <v>-51.9</v>
       </c>
       <c r="H23" t="n">
-        <v>-8.5</v>
+        <v>-8.6</v>
       </c>
       <c r="I23" t="inlineStr">
         <is>

--- a/outputs/transaction_anchor_comparison.xlsx
+++ b/outputs/transaction_anchor_comparison.xlsx
@@ -646,22 +646,22 @@
         </is>
       </c>
       <c r="C5" t="n">
-        <v>9.92</v>
+        <v>10.22</v>
       </c>
       <c r="D5" t="n">
-        <v>10.31</v>
+        <v>10.61</v>
       </c>
       <c r="E5" t="n">
-        <v>3.95</v>
+        <v>3.83</v>
       </c>
       <c r="F5" t="n">
-        <v>46.1</v>
+        <v>52.6</v>
       </c>
       <c r="G5" t="n">
-        <v>52</v>
+        <v>58.8</v>
       </c>
       <c r="H5" t="n">
-        <v>5.9</v>
+        <v>6.2</v>
       </c>
       <c r="I5" t="inlineStr">
         <is>
@@ -674,10 +674,10 @@
         </is>
       </c>
       <c r="K5" t="n">
-        <v>9.300000000000001</v>
+        <v>9.710000000000001</v>
       </c>
       <c r="L5" t="n">
-        <v>9.67</v>
+        <v>10.1</v>
       </c>
     </row>
     <row r="6">
@@ -775,31 +775,31 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>CMBT</t>
+          <t>SBLK</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>WHOLE-COMPANY (hybrid aggregation)</t>
+          <t>whole-company</t>
         </is>
       </c>
       <c r="C8" t="n">
-        <v>15.84</v>
+        <v>29.77</v>
       </c>
       <c r="D8" t="n">
-        <v>15.87</v>
+        <v>29.34</v>
       </c>
       <c r="E8" t="n">
-        <v>0.18</v>
+        <v>-1.43</v>
       </c>
       <c r="F8" t="n">
-        <v>14.2</v>
+        <v>16.5</v>
       </c>
       <c r="G8" t="n">
-        <v>14.1</v>
+        <v>15.1</v>
       </c>
       <c r="H8" t="n">
-        <v>-0.1</v>
+        <v>-1.4</v>
       </c>
       <c r="I8" t="inlineStr">
         <is>
@@ -812,40 +812,40 @@
         </is>
       </c>
       <c r="K8" t="n">
-        <v>16.08</v>
+        <v>28.71</v>
       </c>
       <c r="L8" t="n">
-        <v>16.07</v>
+        <v>28.37</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>STNG</t>
+          <t>CMBT</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>whole-company</t>
+          <t>WHOLE-COMPANY (hybrid aggregation)</t>
         </is>
       </c>
       <c r="C9" t="n">
-        <v>83.87</v>
+        <v>15.84</v>
       </c>
       <c r="D9" t="n">
-        <v>80.34999999999999</v>
+        <v>15.87</v>
       </c>
       <c r="E9" t="n">
-        <v>-4.19</v>
+        <v>0.18</v>
       </c>
       <c r="F9" t="n">
-        <v>18.6</v>
+        <v>14.2</v>
       </c>
       <c r="G9" t="n">
         <v>14.1</v>
       </c>
       <c r="H9" t="n">
-        <v>-4.5</v>
+        <v>-0.1</v>
       </c>
       <c r="I9" t="inlineStr">
         <is>
@@ -858,16 +858,16 @@
         </is>
       </c>
       <c r="K9" t="n">
-        <v>83.16</v>
+        <v>16.08</v>
       </c>
       <c r="L9" t="n">
-        <v>79.98999999999999</v>
+        <v>16.07</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>CMDB</t>
+          <t>STNG</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -876,22 +876,22 @@
         </is>
       </c>
       <c r="C10" t="n">
-        <v>32.12</v>
+        <v>83.87</v>
       </c>
       <c r="D10" t="n">
-        <v>31.33</v>
+        <v>80.34999999999999</v>
       </c>
       <c r="E10" t="n">
-        <v>-2.45</v>
+        <v>-4.19</v>
       </c>
       <c r="F10" t="n">
-        <v>16.2</v>
+        <v>18.6</v>
       </c>
       <c r="G10" t="n">
-        <v>13.6</v>
+        <v>14.1</v>
       </c>
       <c r="H10" t="n">
-        <v>-2.6</v>
+        <v>-4.5</v>
       </c>
       <c r="I10" t="inlineStr">
         <is>
@@ -904,16 +904,16 @@
         </is>
       </c>
       <c r="K10" t="n">
-        <v>20.9</v>
+        <v>83.16</v>
       </c>
       <c r="L10" t="n">
-        <v>20.43</v>
+        <v>79.98999999999999</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>GSL</t>
+          <t>CMDB</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -922,22 +922,22 @@
         </is>
       </c>
       <c r="C11" t="n">
-        <v>38.59</v>
+        <v>32.12</v>
       </c>
       <c r="D11" t="n">
-        <v>38.59</v>
+        <v>31.33</v>
       </c>
       <c r="E11" t="n">
-        <v>0</v>
+        <v>-2.45</v>
       </c>
       <c r="F11" t="n">
-        <v>7.6</v>
+        <v>16.2</v>
       </c>
       <c r="G11" t="n">
-        <v>7.6</v>
+        <v>13.6</v>
       </c>
       <c r="H11" t="n">
-        <v>0</v>
+        <v>-2.6</v>
       </c>
       <c r="I11" t="inlineStr">
         <is>
@@ -950,16 +950,16 @@
         </is>
       </c>
       <c r="K11" t="n">
-        <v>40.59</v>
+        <v>20.9</v>
       </c>
       <c r="L11" t="n">
-        <v>40.59</v>
+        <v>20.43</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>SBLK</t>
+          <t>GSL</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -968,22 +968,22 @@
         </is>
       </c>
       <c r="C12" t="n">
-        <v>27.34</v>
+        <v>38.59</v>
       </c>
       <c r="D12" t="n">
-        <v>26.91</v>
+        <v>38.59</v>
       </c>
       <c r="E12" t="n">
-        <v>-1.56</v>
+        <v>0</v>
       </c>
       <c r="F12" t="n">
-        <v>7.4</v>
+        <v>7.6</v>
       </c>
       <c r="G12" t="n">
-        <v>5.8</v>
+        <v>7.6</v>
       </c>
       <c r="H12" t="n">
-        <v>-1.5</v>
+        <v>0</v>
       </c>
       <c r="I12" t="inlineStr">
         <is>
@@ -996,10 +996,10 @@
         </is>
       </c>
       <c r="K12" t="n">
-        <v>26.45</v>
+        <v>40.59</v>
       </c>
       <c r="L12" t="n">
-        <v>26.07</v>
+        <v>40.59</v>
       </c>
     </row>
     <row r="13">

--- a/outputs/transaction_anchor_comparison.xlsx
+++ b/outputs/transaction_anchor_comparison.xlsx
@@ -646,19 +646,19 @@
         </is>
       </c>
       <c r="C5" t="n">
-        <v>10.22</v>
+        <v>10.08</v>
       </c>
       <c r="D5" t="n">
-        <v>10.61</v>
+        <v>10.47</v>
       </c>
       <c r="E5" t="n">
-        <v>3.83</v>
+        <v>3.88</v>
       </c>
       <c r="F5" t="n">
-        <v>52.6</v>
+        <v>50.6</v>
       </c>
       <c r="G5" t="n">
-        <v>58.8</v>
+        <v>56.8</v>
       </c>
       <c r="H5" t="n">
         <v>6.2</v>
@@ -674,10 +674,10 @@
         </is>
       </c>
       <c r="K5" t="n">
-        <v>9.710000000000001</v>
+        <v>9.58</v>
       </c>
       <c r="L5" t="n">
-        <v>10.1</v>
+        <v>9.970000000000001</v>
       </c>
     </row>
     <row r="6">

--- a/outputs/transaction_anchor_comparison.xlsx
+++ b/outputs/transaction_anchor_comparison.xlsx
@@ -692,22 +692,22 @@
         </is>
       </c>
       <c r="C6" t="n">
-        <v>15.76</v>
+        <v>15.61</v>
       </c>
       <c r="D6" t="n">
-        <v>15.59</v>
+        <v>15.49</v>
       </c>
       <c r="E6" t="n">
-        <v>-1.08</v>
+        <v>-0.74</v>
       </c>
       <c r="F6" t="n">
-        <v>37.8</v>
+        <v>36.8</v>
       </c>
       <c r="G6" t="n">
-        <v>35.6</v>
+        <v>34.8</v>
       </c>
       <c r="H6" t="n">
-        <v>-2.2</v>
+        <v>-2</v>
       </c>
       <c r="I6" t="inlineStr">
         <is>
@@ -720,10 +720,10 @@
         </is>
       </c>
       <c r="K6" t="n">
-        <v>17.54</v>
+        <v>17.41</v>
       </c>
       <c r="L6" t="n">
-        <v>17.26</v>
+        <v>17.16</v>
       </c>
     </row>
     <row r="7">

--- a/outputs/transaction_anchor_comparison.xlsx
+++ b/outputs/transaction_anchor_comparison.xlsx
@@ -1198,22 +1198,22 @@
         </is>
       </c>
       <c r="C17" t="n">
-        <v>15.29</v>
+        <v>16.07</v>
       </c>
       <c r="D17" t="n">
-        <v>13.1</v>
+        <v>13.88</v>
       </c>
       <c r="E17" t="n">
-        <v>-14.35</v>
+        <v>-13.65</v>
       </c>
       <c r="F17" t="n">
-        <v>-0.7</v>
+        <v>4.3</v>
       </c>
       <c r="G17" t="n">
-        <v>-12.7</v>
+        <v>-7.7</v>
       </c>
       <c r="H17" t="n">
-        <v>-11.9</v>
+        <v>-12</v>
       </c>
       <c r="I17" t="inlineStr">
         <is>
@@ -1226,10 +1226,10 @@
         </is>
       </c>
       <c r="K17" t="n">
-        <v>16.96</v>
+        <v>17.82</v>
       </c>
       <c r="L17" t="n">
-        <v>14.92</v>
+        <v>15.77</v>
       </c>
     </row>
     <row r="18">

--- a/outputs/transaction_anchor_comparison.xlsx
+++ b/outputs/transaction_anchor_comparison.xlsx
@@ -563,13 +563,13 @@
         <v>-8.51</v>
       </c>
       <c r="F3" t="n">
-        <v>98.09999999999999</v>
+        <v>100.3</v>
       </c>
       <c r="G3" t="n">
-        <v>83.09999999999999</v>
+        <v>85.2</v>
       </c>
       <c r="H3" t="n">
-        <v>-15</v>
+        <v>-15.2</v>
       </c>
       <c r="I3" t="inlineStr">
         <is>
@@ -609,10 +609,10 @@
         <v>0</v>
       </c>
       <c r="F4" t="n">
-        <v>72</v>
+        <v>68.2</v>
       </c>
       <c r="G4" t="n">
-        <v>72</v>
+        <v>68.2</v>
       </c>
       <c r="H4" t="n">
         <v>0</v>
@@ -655,10 +655,10 @@
         <v>3.88</v>
       </c>
       <c r="F5" t="n">
-        <v>50.6</v>
+        <v>51.8</v>
       </c>
       <c r="G5" t="n">
-        <v>56.8</v>
+        <v>58</v>
       </c>
       <c r="H5" t="n">
         <v>6.2</v>
@@ -701,10 +701,10 @@
         <v>-0.74</v>
       </c>
       <c r="F6" t="n">
-        <v>36.8</v>
+        <v>38.4</v>
       </c>
       <c r="G6" t="n">
-        <v>34.8</v>
+        <v>36.4</v>
       </c>
       <c r="H6" t="n">
         <v>-2</v>
@@ -729,7 +729,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>TNK</t>
+          <t>CMDB</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -738,22 +738,22 @@
         </is>
       </c>
       <c r="C7" t="n">
-        <v>83.31999999999999</v>
+        <v>32.12</v>
       </c>
       <c r="D7" t="n">
-        <v>77.51000000000001</v>
+        <v>31.33</v>
       </c>
       <c r="E7" t="n">
-        <v>-6.97</v>
+        <v>-2.45</v>
       </c>
       <c r="F7" t="n">
-        <v>28.3</v>
+        <v>19</v>
       </c>
       <c r="G7" t="n">
-        <v>20.6</v>
+        <v>16.3</v>
       </c>
       <c r="H7" t="n">
-        <v>-7.6</v>
+        <v>-2.7</v>
       </c>
       <c r="I7" t="inlineStr">
         <is>
@@ -766,40 +766,40 @@
         </is>
       </c>
       <c r="K7" t="n">
-        <v>84.64</v>
+        <v>20.9</v>
       </c>
       <c r="L7" t="n">
-        <v>79.59</v>
+        <v>20.43</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>SBLK</t>
+          <t>CMBT</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>whole-company</t>
+          <t>WHOLE-COMPANY (hybrid aggregation)</t>
         </is>
       </c>
       <c r="C8" t="n">
-        <v>29.77</v>
+        <v>15.84</v>
       </c>
       <c r="D8" t="n">
-        <v>29.34</v>
+        <v>15.87</v>
       </c>
       <c r="E8" t="n">
-        <v>-1.43</v>
+        <v>0.18</v>
       </c>
       <c r="F8" t="n">
-        <v>16.5</v>
+        <v>14.9</v>
       </c>
       <c r="G8" t="n">
-        <v>15.1</v>
+        <v>14.9</v>
       </c>
       <c r="H8" t="n">
-        <v>-1.4</v>
+        <v>-0.1</v>
       </c>
       <c r="I8" t="inlineStr">
         <is>
@@ -812,40 +812,40 @@
         </is>
       </c>
       <c r="K8" t="n">
-        <v>28.71</v>
+        <v>16.08</v>
       </c>
       <c r="L8" t="n">
-        <v>28.37</v>
+        <v>16.07</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>CMBT</t>
+          <t>SBLK</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>WHOLE-COMPANY (hybrid aggregation)</t>
+          <t>whole-company</t>
         </is>
       </c>
       <c r="C9" t="n">
-        <v>15.84</v>
+        <v>29.77</v>
       </c>
       <c r="D9" t="n">
-        <v>15.87</v>
+        <v>29.34</v>
       </c>
       <c r="E9" t="n">
-        <v>0.18</v>
+        <v>-1.43</v>
       </c>
       <c r="F9" t="n">
-        <v>14.2</v>
+        <v>15</v>
       </c>
       <c r="G9" t="n">
-        <v>14.1</v>
+        <v>13.6</v>
       </c>
       <c r="H9" t="n">
-        <v>-0.1</v>
+        <v>-1.4</v>
       </c>
       <c r="I9" t="inlineStr">
         <is>
@@ -858,16 +858,16 @@
         </is>
       </c>
       <c r="K9" t="n">
-        <v>16.08</v>
+        <v>28.71</v>
       </c>
       <c r="L9" t="n">
-        <v>16.07</v>
+        <v>28.37</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>STNG</t>
+          <t>TNK</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -876,22 +876,22 @@
         </is>
       </c>
       <c r="C10" t="n">
-        <v>83.87</v>
+        <v>83.31999999999999</v>
       </c>
       <c r="D10" t="n">
-        <v>80.34999999999999</v>
+        <v>77.51000000000001</v>
       </c>
       <c r="E10" t="n">
-        <v>-4.19</v>
+        <v>-6.97</v>
       </c>
       <c r="F10" t="n">
-        <v>18.6</v>
+        <v>19.5</v>
       </c>
       <c r="G10" t="n">
-        <v>14.1</v>
+        <v>12.4</v>
       </c>
       <c r="H10" t="n">
-        <v>-4.5</v>
+        <v>-7.1</v>
       </c>
       <c r="I10" t="inlineStr">
         <is>
@@ -904,16 +904,16 @@
         </is>
       </c>
       <c r="K10" t="n">
-        <v>83.16</v>
+        <v>84.64</v>
       </c>
       <c r="L10" t="n">
-        <v>79.98999999999999</v>
+        <v>79.59</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>CMDB</t>
+          <t>FLNG</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -922,22 +922,22 @@
         </is>
       </c>
       <c r="C11" t="n">
-        <v>32.12</v>
+        <v>28.45</v>
       </c>
       <c r="D11" t="n">
-        <v>31.33</v>
+        <v>28.45</v>
       </c>
       <c r="E11" t="n">
-        <v>-2.45</v>
+        <v>0</v>
       </c>
       <c r="F11" t="n">
-        <v>16.2</v>
+        <v>9.300000000000001</v>
       </c>
       <c r="G11" t="n">
-        <v>13.6</v>
+        <v>9.300000000000001</v>
       </c>
       <c r="H11" t="n">
-        <v>-2.6</v>
+        <v>0</v>
       </c>
       <c r="I11" t="inlineStr">
         <is>
@@ -950,10 +950,10 @@
         </is>
       </c>
       <c r="K11" t="n">
-        <v>20.9</v>
+        <v>30.67</v>
       </c>
       <c r="L11" t="n">
-        <v>20.43</v>
+        <v>30.67</v>
       </c>
     </row>
     <row r="12">
@@ -977,10 +977,10 @@
         <v>0</v>
       </c>
       <c r="F12" t="n">
-        <v>7.6</v>
+        <v>8</v>
       </c>
       <c r="G12" t="n">
-        <v>7.6</v>
+        <v>8</v>
       </c>
       <c r="H12" t="n">
         <v>0</v>
@@ -1005,7 +1005,7 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>FLNG</t>
+          <t>STNG</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -1014,38 +1014,38 @@
         </is>
       </c>
       <c r="C13" t="n">
-        <v>28.45</v>
+        <v>83.87</v>
       </c>
       <c r="D13" t="n">
-        <v>28.45</v>
+        <v>80.34999999999999</v>
       </c>
       <c r="E13" t="n">
-        <v>0</v>
+        <v>-4.19</v>
       </c>
       <c r="F13" t="n">
-        <v>4.7</v>
+        <v>10</v>
       </c>
       <c r="G13" t="n">
-        <v>4.7</v>
+        <v>5.8</v>
       </c>
       <c r="H13" t="n">
-        <v>0</v>
+        <v>-4.2</v>
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>HOLD (fairly valued)</t>
+          <t>BUY (undervalued)</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t>HOLD (fairly valued)</t>
+          <t>BUY (undervalued)</t>
         </is>
       </c>
       <c r="K13" t="n">
-        <v>30.67</v>
+        <v>83.16</v>
       </c>
       <c r="L13" t="n">
-        <v>30.67</v>
+        <v>79.98999999999999</v>
       </c>
     </row>
     <row r="14">
@@ -1069,10 +1069,10 @@
         <v>-4.86</v>
       </c>
       <c r="F14" t="n">
-        <v>8.1</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="G14" t="n">
-        <v>3.8</v>
+        <v>4.8</v>
       </c>
       <c r="H14" t="n">
         <v>-4.3</v>
@@ -1115,10 +1115,10 @@
         <v>-3.28</v>
       </c>
       <c r="F15" t="n">
-        <v>1.6</v>
+        <v>-0</v>
       </c>
       <c r="G15" t="n">
-        <v>-1.4</v>
+        <v>-2.9</v>
       </c>
       <c r="H15" t="n">
         <v>-2.9</v>
@@ -1143,7 +1143,7 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>ASC</t>
+          <t>DHT</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1152,44 +1152,44 @@
         </is>
       </c>
       <c r="C16" t="n">
-        <v>15.96</v>
+        <v>16.07</v>
       </c>
       <c r="D16" t="n">
-        <v>15.93</v>
+        <v>13.88</v>
       </c>
       <c r="E16" t="n">
-        <v>-0.16</v>
+        <v>-13.65</v>
       </c>
       <c r="F16" t="n">
-        <v>-5.2</v>
+        <v>8.699999999999999</v>
       </c>
       <c r="G16" t="n">
-        <v>-5.3</v>
+        <v>-3.9</v>
       </c>
       <c r="H16" t="n">
-        <v>-0.1</v>
+        <v>-12.5</v>
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>TRIM/SHORT (overvalued)</t>
+          <t>BUY (undervalued)</t>
         </is>
       </c>
       <c r="J16" t="inlineStr">
         <is>
-          <t>TRIM/SHORT (overvalued)</t>
+          <t>HOLD (fairly valued)</t>
         </is>
       </c>
       <c r="K16" t="n">
-        <v>15.17</v>
+        <v>17.82</v>
       </c>
       <c r="L16" t="n">
-        <v>15.15</v>
+        <v>15.77</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>DHT</t>
+          <t>ASC</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1198,26 +1198,26 @@
         </is>
       </c>
       <c r="C17" t="n">
-        <v>16.07</v>
+        <v>15.96</v>
       </c>
       <c r="D17" t="n">
-        <v>13.88</v>
+        <v>15.93</v>
       </c>
       <c r="E17" t="n">
-        <v>-13.65</v>
+        <v>-0.16</v>
       </c>
       <c r="F17" t="n">
-        <v>4.3</v>
+        <v>-5.2</v>
       </c>
       <c r="G17" t="n">
-        <v>-7.7</v>
+        <v>-5.3</v>
       </c>
       <c r="H17" t="n">
-        <v>-12</v>
+        <v>-0.1</v>
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>HOLD (fairly valued)</t>
+          <t>TRIM/SHORT (overvalued)</t>
         </is>
       </c>
       <c r="J17" t="inlineStr">
@@ -1226,10 +1226,10 @@
         </is>
       </c>
       <c r="K17" t="n">
-        <v>17.82</v>
+        <v>15.17</v>
       </c>
       <c r="L17" t="n">
-        <v>15.77</v>
+        <v>15.15</v>
       </c>
     </row>
     <row r="18">
@@ -1253,10 +1253,10 @@
         <v>-2.24</v>
       </c>
       <c r="F18" t="n">
-        <v>-12.3</v>
+        <v>-9.4</v>
       </c>
       <c r="G18" t="n">
-        <v>-13.8</v>
+        <v>-11</v>
       </c>
       <c r="H18" t="n">
         <v>-1.5</v>
@@ -1299,17 +1299,17 @@
         <v>-14.93</v>
       </c>
       <c r="F19" t="n">
-        <v>-7</v>
+        <v>-4.5</v>
       </c>
       <c r="G19" t="n">
-        <v>-18.7</v>
+        <v>-16.5</v>
       </c>
       <c r="H19" t="n">
-        <v>-11.6</v>
+        <v>-12</v>
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>TRIM/SHORT (overvalued)</t>
+          <t>HOLD (fairly valued)</t>
         </is>
       </c>
       <c r="J19" t="inlineStr">
@@ -1327,7 +1327,7 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>ECO</t>
+          <t>MPCC</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -1336,22 +1336,22 @@
         </is>
       </c>
       <c r="C20" t="n">
-        <v>40.61</v>
+        <v>2.02</v>
       </c>
       <c r="D20" t="n">
-        <v>34.56</v>
+        <v>2.02</v>
       </c>
       <c r="E20" t="n">
-        <v>-14.9</v>
+        <v>0</v>
       </c>
       <c r="F20" t="n">
-        <v>-7.5</v>
+        <v>-17.4</v>
       </c>
       <c r="G20" t="n">
-        <v>-19</v>
+        <v>-17.4</v>
       </c>
       <c r="H20" t="n">
-        <v>-11.6</v>
+        <v>0</v>
       </c>
       <c r="I20" t="inlineStr">
         <is>
@@ -1364,16 +1364,16 @@
         </is>
       </c>
       <c r="K20" t="n">
-        <v>45.9</v>
+        <v>2.11</v>
       </c>
       <c r="L20" t="n">
-        <v>40.17</v>
+        <v>2.11</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>MPCC</t>
+          <t>ECO</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -1382,22 +1382,22 @@
         </is>
       </c>
       <c r="C21" t="n">
-        <v>2.02</v>
+        <v>40.61</v>
       </c>
       <c r="D21" t="n">
-        <v>2.02</v>
+        <v>34.56</v>
       </c>
       <c r="E21" t="n">
-        <v>0</v>
+        <v>-14.9</v>
       </c>
       <c r="F21" t="n">
-        <v>-19.6</v>
+        <v>-8.4</v>
       </c>
       <c r="G21" t="n">
-        <v>-19.6</v>
+        <v>-19.9</v>
       </c>
       <c r="H21" t="n">
-        <v>0</v>
+        <v>-11.4</v>
       </c>
       <c r="I21" t="inlineStr">
         <is>
@@ -1410,10 +1410,10 @@
         </is>
       </c>
       <c r="K21" t="n">
-        <v>2.11</v>
+        <v>45.9</v>
       </c>
       <c r="L21" t="n">
-        <v>2.11</v>
+        <v>40.17</v>
       </c>
     </row>
     <row r="22">
@@ -1437,13 +1437,13 @@
         <v>-9.18</v>
       </c>
       <c r="F22" t="n">
-        <v>-15</v>
+        <v>-13.6</v>
       </c>
       <c r="G22" t="n">
-        <v>-21.2</v>
+        <v>-19.9</v>
       </c>
       <c r="H22" t="n">
-        <v>-6.2</v>
+        <v>-6.3</v>
       </c>
       <c r="I22" t="inlineStr">
         <is>
@@ -1474,22 +1474,22 @@
         </is>
       </c>
       <c r="C23" t="n">
-        <v>2.63</v>
+        <v>3.32</v>
       </c>
       <c r="D23" t="n">
-        <v>2.07</v>
+        <v>2.79</v>
       </c>
       <c r="E23" t="n">
-        <v>-21.23</v>
+        <v>-15.76</v>
       </c>
       <c r="F23" t="n">
-        <v>-43.2</v>
+        <v>-31.4</v>
       </c>
       <c r="G23" t="n">
-        <v>-51.9</v>
+        <v>-39.9</v>
       </c>
       <c r="H23" t="n">
-        <v>-8.6</v>
+        <v>-8.4</v>
       </c>
       <c r="I23" t="inlineStr">
         <is>
@@ -1502,10 +1502,10 @@
         </is>
       </c>
       <c r="K23" t="n">
-        <v>3.28</v>
+        <v>3.8</v>
       </c>
       <c r="L23" t="n">
-        <v>2.78</v>
+        <v>3.33</v>
       </c>
     </row>
   </sheetData>

--- a/outputs/transaction_anchor_comparison.xlsx
+++ b/outputs/transaction_anchor_comparison.xlsx
@@ -646,19 +646,19 @@
         </is>
       </c>
       <c r="C5" t="n">
-        <v>10.08</v>
+        <v>9.720000000000001</v>
       </c>
       <c r="D5" t="n">
-        <v>10.47</v>
+        <v>10.12</v>
       </c>
       <c r="E5" t="n">
-        <v>3.88</v>
+        <v>4.09</v>
       </c>
       <c r="F5" t="n">
-        <v>51.8</v>
+        <v>47.1</v>
       </c>
       <c r="G5" t="n">
-        <v>58</v>
+        <v>53.4</v>
       </c>
       <c r="H5" t="n">
         <v>6.2</v>
@@ -674,10 +674,10 @@
         </is>
       </c>
       <c r="K5" t="n">
-        <v>9.58</v>
+        <v>9.279999999999999</v>
       </c>
       <c r="L5" t="n">
-        <v>9.970000000000001</v>
+        <v>9.68</v>
       </c>
     </row>
     <row r="6">
@@ -1051,7 +1051,7 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>TRMD</t>
+          <t>ASC</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1060,22 +1060,22 @@
         </is>
       </c>
       <c r="C14" t="n">
-        <v>26.74</v>
+        <v>17.82</v>
       </c>
       <c r="D14" t="n">
-        <v>25.43</v>
+        <v>17.8</v>
       </c>
       <c r="E14" t="n">
-        <v>-4.86</v>
+        <v>-0.13</v>
       </c>
       <c r="F14" t="n">
-        <v>9.199999999999999</v>
+        <v>5.3</v>
       </c>
       <c r="G14" t="n">
-        <v>4.8</v>
+        <v>5.2</v>
       </c>
       <c r="H14" t="n">
-        <v>-4.3</v>
+        <v>-0.1</v>
       </c>
       <c r="I14" t="inlineStr">
         <is>
@@ -1084,20 +1084,20 @@
       </c>
       <c r="J14" t="inlineStr">
         <is>
-          <t>HOLD (fairly valued)</t>
+          <t>BUY (undervalued)</t>
         </is>
       </c>
       <c r="K14" t="n">
-        <v>28.45</v>
+        <v>16.85</v>
       </c>
       <c r="L14" t="n">
-        <v>27.32</v>
+        <v>16.83</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>GNK</t>
+          <t>TRMD</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1106,44 +1106,44 @@
         </is>
       </c>
       <c r="C15" t="n">
-        <v>25.53</v>
+        <v>26.74</v>
       </c>
       <c r="D15" t="n">
-        <v>24.69</v>
+        <v>25.43</v>
       </c>
       <c r="E15" t="n">
-        <v>-3.28</v>
+        <v>-4.86</v>
       </c>
       <c r="F15" t="n">
-        <v>-0</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="G15" t="n">
-        <v>-2.9</v>
+        <v>4.8</v>
       </c>
       <c r="H15" t="n">
-        <v>-2.9</v>
+        <v>-4.3</v>
       </c>
       <c r="I15" t="inlineStr">
         <is>
+          <t>BUY (undervalued)</t>
+        </is>
+      </c>
+      <c r="J15" t="inlineStr">
+        <is>
           <t>HOLD (fairly valued)</t>
         </is>
       </c>
-      <c r="J15" t="inlineStr">
-        <is>
-          <t>HOLD (fairly valued)</t>
-        </is>
-      </c>
       <c r="K15" t="n">
-        <v>24.77</v>
+        <v>28.45</v>
       </c>
       <c r="L15" t="n">
-        <v>24.05</v>
+        <v>27.32</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>DHT</t>
+          <t>GNK</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1152,26 +1152,26 @@
         </is>
       </c>
       <c r="C16" t="n">
-        <v>16.07</v>
+        <v>25.53</v>
       </c>
       <c r="D16" t="n">
-        <v>13.88</v>
+        <v>24.69</v>
       </c>
       <c r="E16" t="n">
-        <v>-13.65</v>
+        <v>-3.28</v>
       </c>
       <c r="F16" t="n">
-        <v>8.699999999999999</v>
+        <v>-0</v>
       </c>
       <c r="G16" t="n">
-        <v>-3.9</v>
+        <v>-2.9</v>
       </c>
       <c r="H16" t="n">
-        <v>-12.5</v>
+        <v>-2.9</v>
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>BUY (undervalued)</t>
+          <t>HOLD (fairly valued)</t>
         </is>
       </c>
       <c r="J16" t="inlineStr">
@@ -1180,16 +1180,16 @@
         </is>
       </c>
       <c r="K16" t="n">
-        <v>17.82</v>
+        <v>24.77</v>
       </c>
       <c r="L16" t="n">
-        <v>15.77</v>
+        <v>24.05</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>ASC</t>
+          <t>DHT</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1198,38 +1198,38 @@
         </is>
       </c>
       <c r="C17" t="n">
-        <v>15.96</v>
+        <v>16.07</v>
       </c>
       <c r="D17" t="n">
-        <v>15.93</v>
+        <v>13.88</v>
       </c>
       <c r="E17" t="n">
-        <v>-0.16</v>
+        <v>-13.65</v>
       </c>
       <c r="F17" t="n">
-        <v>-5.2</v>
+        <v>8.699999999999999</v>
       </c>
       <c r="G17" t="n">
-        <v>-5.3</v>
+        <v>-3.9</v>
       </c>
       <c r="H17" t="n">
-        <v>-0.1</v>
+        <v>-12.5</v>
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>TRIM/SHORT (overvalued)</t>
+          <t>BUY (undervalued)</t>
         </is>
       </c>
       <c r="J17" t="inlineStr">
         <is>
-          <t>TRIM/SHORT (overvalued)</t>
+          <t>HOLD (fairly valued)</t>
         </is>
       </c>
       <c r="K17" t="n">
-        <v>15.17</v>
+        <v>17.82</v>
       </c>
       <c r="L17" t="n">
-        <v>15.15</v>
+        <v>15.77</v>
       </c>
     </row>
     <row r="18">

--- a/outputs/transaction_anchor_comparison.xlsx
+++ b/outputs/transaction_anchor_comparison.xlsx
@@ -508,22 +508,22 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>9.4</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="D2" t="n">
-        <v>9.4</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="E2" t="n">
         <v>0</v>
       </c>
       <c r="F2" t="n">
-        <v>109.9</v>
+        <v>99</v>
       </c>
       <c r="G2" t="n">
-        <v>107.4</v>
+        <v>96.59999999999999</v>
       </c>
       <c r="H2" t="n">
-        <v>-2.5</v>
+        <v>-2.4</v>
       </c>
       <c r="I2" t="inlineStr">
         <is>
@@ -536,10 +536,10 @@
         </is>
       </c>
       <c r="K2" t="n">
-        <v>10.93</v>
+        <v>10.37</v>
       </c>
       <c r="L2" t="n">
-        <v>10.81</v>
+        <v>10.24</v>
       </c>
     </row>
     <row r="3">

--- a/outputs/transaction_anchor_comparison.xlsx
+++ b/outputs/transaction_anchor_comparison.xlsx
@@ -1373,31 +1373,31 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>ECO</t>
+          <t>INSW</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>whole-company</t>
+          <t>WHOLE-COMPANY (hybrid aggregation)</t>
         </is>
       </c>
       <c r="C21" t="n">
-        <v>40.61</v>
+        <v>57.91</v>
       </c>
       <c r="D21" t="n">
-        <v>34.56</v>
+        <v>52.59</v>
       </c>
       <c r="E21" t="n">
-        <v>-14.9</v>
+        <v>-9.18</v>
       </c>
       <c r="F21" t="n">
-        <v>-8.4</v>
+        <v>-13.6</v>
       </c>
       <c r="G21" t="n">
         <v>-19.9</v>
       </c>
       <c r="H21" t="n">
-        <v>-11.4</v>
+        <v>-6.3</v>
       </c>
       <c r="I21" t="inlineStr">
         <is>
@@ -1410,40 +1410,40 @@
         </is>
       </c>
       <c r="K21" t="n">
-        <v>45.9</v>
+        <v>66.17</v>
       </c>
       <c r="L21" t="n">
-        <v>40.17</v>
+        <v>61.34</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>INSW</t>
+          <t>ECO</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>WHOLE-COMPANY (hybrid aggregation)</t>
+          <t>whole-company</t>
         </is>
       </c>
       <c r="C22" t="n">
-        <v>57.91</v>
+        <v>40.4</v>
       </c>
       <c r="D22" t="n">
-        <v>52.59</v>
+        <v>34.35</v>
       </c>
       <c r="E22" t="n">
-        <v>-9.18</v>
+        <v>-14.98</v>
       </c>
       <c r="F22" t="n">
-        <v>-13.6</v>
+        <v>-8.699999999999999</v>
       </c>
       <c r="G22" t="n">
-        <v>-19.9</v>
+        <v>-20.2</v>
       </c>
       <c r="H22" t="n">
-        <v>-6.3</v>
+        <v>-11.4</v>
       </c>
       <c r="I22" t="inlineStr">
         <is>
@@ -1456,10 +1456,10 @@
         </is>
       </c>
       <c r="K22" t="n">
-        <v>66.17</v>
+        <v>45.75</v>
       </c>
       <c r="L22" t="n">
-        <v>61.34</v>
+        <v>40.02</v>
       </c>
     </row>
     <row r="23">

--- a/outputs/transaction_anchor_comparison.xlsx
+++ b/outputs/transaction_anchor_comparison.xlsx
@@ -1244,38 +1244,38 @@
         </is>
       </c>
       <c r="C18" t="n">
-        <v>5.34</v>
+        <v>5.69</v>
       </c>
       <c r="D18" t="n">
-        <v>5.22</v>
+        <v>5.57</v>
       </c>
       <c r="E18" t="n">
-        <v>-2.24</v>
+        <v>-2.07</v>
       </c>
       <c r="F18" t="n">
-        <v>-9.4</v>
+        <v>-4.7</v>
       </c>
       <c r="G18" t="n">
-        <v>-11</v>
+        <v>-6.2</v>
       </c>
       <c r="H18" t="n">
         <v>-1.5</v>
       </c>
       <c r="I18" t="inlineStr">
         <is>
+          <t>HOLD (fairly valued)</t>
+        </is>
+      </c>
+      <c r="J18" t="inlineStr">
+        <is>
           <t>TRIM/SHORT (overvalued)</t>
         </is>
       </c>
-      <c r="J18" t="inlineStr">
-        <is>
-          <t>TRIM/SHORT (overvalued)</t>
-        </is>
-      </c>
       <c r="K18" t="n">
-        <v>6.01</v>
+        <v>6.33</v>
       </c>
       <c r="L18" t="n">
-        <v>5.91</v>
+        <v>6.23</v>
       </c>
     </row>
     <row r="19">

--- a/outputs/transaction_anchor_comparison.xlsx
+++ b/outputs/transaction_anchor_comparison.xlsx
@@ -1005,7 +1005,7 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>STNG</t>
+          <t>ASC</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -1014,22 +1014,22 @@
         </is>
       </c>
       <c r="C13" t="n">
-        <v>83.87</v>
+        <v>17.82</v>
       </c>
       <c r="D13" t="n">
-        <v>80.34999999999999</v>
+        <v>17.8</v>
       </c>
       <c r="E13" t="n">
-        <v>-4.19</v>
+        <v>-0.13</v>
       </c>
       <c r="F13" t="n">
-        <v>10</v>
+        <v>5.3</v>
       </c>
       <c r="G13" t="n">
-        <v>5.8</v>
+        <v>5.2</v>
       </c>
       <c r="H13" t="n">
-        <v>-4.2</v>
+        <v>-0.1</v>
       </c>
       <c r="I13" t="inlineStr">
         <is>
@@ -1042,16 +1042,16 @@
         </is>
       </c>
       <c r="K13" t="n">
-        <v>83.16</v>
+        <v>16.85</v>
       </c>
       <c r="L13" t="n">
-        <v>79.98999999999999</v>
+        <v>16.83</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>ASC</t>
+          <t>TRMD</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1060,22 +1060,22 @@
         </is>
       </c>
       <c r="C14" t="n">
-        <v>17.82</v>
+        <v>26.74</v>
       </c>
       <c r="D14" t="n">
-        <v>17.8</v>
+        <v>25.43</v>
       </c>
       <c r="E14" t="n">
-        <v>-0.13</v>
+        <v>-4.86</v>
       </c>
       <c r="F14" t="n">
-        <v>5.3</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="G14" t="n">
-        <v>5.2</v>
+        <v>4.8</v>
       </c>
       <c r="H14" t="n">
-        <v>-0.1</v>
+        <v>-4.3</v>
       </c>
       <c r="I14" t="inlineStr">
         <is>
@@ -1084,20 +1084,20 @@
       </c>
       <c r="J14" t="inlineStr">
         <is>
-          <t>BUY (undervalued)</t>
+          <t>HOLD (fairly valued)</t>
         </is>
       </c>
       <c r="K14" t="n">
-        <v>16.85</v>
+        <v>28.45</v>
       </c>
       <c r="L14" t="n">
-        <v>16.83</v>
+        <v>27.32</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>TRMD</t>
+          <t>STNG</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1106,22 +1106,22 @@
         </is>
       </c>
       <c r="C15" t="n">
-        <v>26.74</v>
+        <v>80.97</v>
       </c>
       <c r="D15" t="n">
-        <v>25.43</v>
+        <v>77.47</v>
       </c>
       <c r="E15" t="n">
-        <v>-4.86</v>
+        <v>-4.33</v>
       </c>
       <c r="F15" t="n">
-        <v>9.199999999999999</v>
+        <v>6.2</v>
       </c>
       <c r="G15" t="n">
-        <v>4.8</v>
+        <v>2</v>
       </c>
       <c r="H15" t="n">
-        <v>-4.3</v>
+        <v>-4.2</v>
       </c>
       <c r="I15" t="inlineStr">
         <is>
@@ -1134,10 +1134,10 @@
         </is>
       </c>
       <c r="K15" t="n">
-        <v>28.45</v>
+        <v>80.3</v>
       </c>
       <c r="L15" t="n">
-        <v>27.32</v>
+        <v>77.13</v>
       </c>
     </row>
     <row r="16">

--- a/outputs/transaction_anchor_comparison.xlsx
+++ b/outputs/transaction_anchor_comparison.xlsx
@@ -729,7 +729,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>CMDB</t>
+          <t>TRMD</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -738,22 +738,22 @@
         </is>
       </c>
       <c r="C7" t="n">
-        <v>32.12</v>
+        <v>31.65</v>
       </c>
       <c r="D7" t="n">
-        <v>31.33</v>
+        <v>30.34</v>
       </c>
       <c r="E7" t="n">
-        <v>-2.45</v>
+        <v>-4.11</v>
       </c>
       <c r="F7" t="n">
-        <v>19</v>
+        <v>26.7</v>
       </c>
       <c r="G7" t="n">
-        <v>16.3</v>
+        <v>22.4</v>
       </c>
       <c r="H7" t="n">
-        <v>-2.7</v>
+        <v>-4.3</v>
       </c>
       <c r="I7" t="inlineStr">
         <is>
@@ -766,40 +766,40 @@
         </is>
       </c>
       <c r="K7" t="n">
-        <v>20.9</v>
+        <v>33.03</v>
       </c>
       <c r="L7" t="n">
-        <v>20.43</v>
+        <v>31.9</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>CMBT</t>
+          <t>CMDB</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>WHOLE-COMPANY (hybrid aggregation)</t>
+          <t>whole-company</t>
         </is>
       </c>
       <c r="C8" t="n">
-        <v>15.84</v>
+        <v>32.12</v>
       </c>
       <c r="D8" t="n">
-        <v>15.87</v>
+        <v>31.33</v>
       </c>
       <c r="E8" t="n">
-        <v>0.18</v>
+        <v>-2.45</v>
       </c>
       <c r="F8" t="n">
-        <v>14.9</v>
+        <v>19</v>
       </c>
       <c r="G8" t="n">
-        <v>14.9</v>
+        <v>16.3</v>
       </c>
       <c r="H8" t="n">
-        <v>-0.1</v>
+        <v>-2.7</v>
       </c>
       <c r="I8" t="inlineStr">
         <is>
@@ -812,40 +812,40 @@
         </is>
       </c>
       <c r="K8" t="n">
-        <v>16.08</v>
+        <v>20.9</v>
       </c>
       <c r="L8" t="n">
-        <v>16.07</v>
+        <v>20.43</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>SBLK</t>
+          <t>CMBT</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>whole-company</t>
+          <t>WHOLE-COMPANY (hybrid aggregation)</t>
         </is>
       </c>
       <c r="C9" t="n">
-        <v>29.77</v>
+        <v>15.84</v>
       </c>
       <c r="D9" t="n">
-        <v>29.34</v>
+        <v>15.87</v>
       </c>
       <c r="E9" t="n">
-        <v>-1.43</v>
+        <v>0.18</v>
       </c>
       <c r="F9" t="n">
-        <v>15</v>
+        <v>14.9</v>
       </c>
       <c r="G9" t="n">
-        <v>13.6</v>
+        <v>14.9</v>
       </c>
       <c r="H9" t="n">
-        <v>-1.4</v>
+        <v>-0.1</v>
       </c>
       <c r="I9" t="inlineStr">
         <is>
@@ -858,16 +858,16 @@
         </is>
       </c>
       <c r="K9" t="n">
-        <v>28.71</v>
+        <v>16.08</v>
       </c>
       <c r="L9" t="n">
-        <v>28.37</v>
+        <v>16.07</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>TNK</t>
+          <t>SBLK</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -876,22 +876,22 @@
         </is>
       </c>
       <c r="C10" t="n">
-        <v>83.31999999999999</v>
+        <v>29.77</v>
       </c>
       <c r="D10" t="n">
-        <v>77.51000000000001</v>
+        <v>29.34</v>
       </c>
       <c r="E10" t="n">
-        <v>-6.97</v>
+        <v>-1.43</v>
       </c>
       <c r="F10" t="n">
-        <v>19.5</v>
+        <v>15</v>
       </c>
       <c r="G10" t="n">
-        <v>12.4</v>
+        <v>13.6</v>
       </c>
       <c r="H10" t="n">
-        <v>-7.1</v>
+        <v>-1.4</v>
       </c>
       <c r="I10" t="inlineStr">
         <is>
@@ -904,16 +904,16 @@
         </is>
       </c>
       <c r="K10" t="n">
-        <v>84.64</v>
+        <v>28.71</v>
       </c>
       <c r="L10" t="n">
-        <v>79.59</v>
+        <v>28.37</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>FLNG</t>
+          <t>TNK</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -922,22 +922,22 @@
         </is>
       </c>
       <c r="C11" t="n">
-        <v>28.45</v>
+        <v>83.31999999999999</v>
       </c>
       <c r="D11" t="n">
-        <v>28.45</v>
+        <v>77.51000000000001</v>
       </c>
       <c r="E11" t="n">
-        <v>0</v>
+        <v>-6.97</v>
       </c>
       <c r="F11" t="n">
-        <v>9.300000000000001</v>
+        <v>19.5</v>
       </c>
       <c r="G11" t="n">
-        <v>9.300000000000001</v>
+        <v>12.4</v>
       </c>
       <c r="H11" t="n">
-        <v>0</v>
+        <v>-7.1</v>
       </c>
       <c r="I11" t="inlineStr">
         <is>
@@ -950,16 +950,16 @@
         </is>
       </c>
       <c r="K11" t="n">
-        <v>30.67</v>
+        <v>84.64</v>
       </c>
       <c r="L11" t="n">
-        <v>30.67</v>
+        <v>79.59</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>GSL</t>
+          <t>FLNG</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -968,19 +968,19 @@
         </is>
       </c>
       <c r="C12" t="n">
-        <v>38.59</v>
+        <v>28.45</v>
       </c>
       <c r="D12" t="n">
-        <v>38.59</v>
+        <v>28.45</v>
       </c>
       <c r="E12" t="n">
         <v>0</v>
       </c>
       <c r="F12" t="n">
-        <v>8</v>
+        <v>9.300000000000001</v>
       </c>
       <c r="G12" t="n">
-        <v>8</v>
+        <v>9.300000000000001</v>
       </c>
       <c r="H12" t="n">
         <v>0</v>
@@ -996,16 +996,16 @@
         </is>
       </c>
       <c r="K12" t="n">
-        <v>40.59</v>
+        <v>30.67</v>
       </c>
       <c r="L12" t="n">
-        <v>40.59</v>
+        <v>30.67</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>ASC</t>
+          <t>GSL</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -1014,22 +1014,22 @@
         </is>
       </c>
       <c r="C13" t="n">
-        <v>17.82</v>
+        <v>38.59</v>
       </c>
       <c r="D13" t="n">
-        <v>17.8</v>
+        <v>38.59</v>
       </c>
       <c r="E13" t="n">
-        <v>-0.13</v>
+        <v>0</v>
       </c>
       <c r="F13" t="n">
-        <v>5.3</v>
+        <v>8</v>
       </c>
       <c r="G13" t="n">
-        <v>5.2</v>
+        <v>8</v>
       </c>
       <c r="H13" t="n">
-        <v>-0.1</v>
+        <v>0</v>
       </c>
       <c r="I13" t="inlineStr">
         <is>
@@ -1042,16 +1042,16 @@
         </is>
       </c>
       <c r="K13" t="n">
-        <v>16.85</v>
+        <v>40.59</v>
       </c>
       <c r="L13" t="n">
-        <v>16.83</v>
+        <v>40.59</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>TRMD</t>
+          <t>ASC</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1060,22 +1060,22 @@
         </is>
       </c>
       <c r="C14" t="n">
-        <v>26.74</v>
+        <v>17.82</v>
       </c>
       <c r="D14" t="n">
-        <v>25.43</v>
+        <v>17.8</v>
       </c>
       <c r="E14" t="n">
-        <v>-4.86</v>
+        <v>-0.13</v>
       </c>
       <c r="F14" t="n">
-        <v>9.199999999999999</v>
+        <v>5.3</v>
       </c>
       <c r="G14" t="n">
-        <v>4.8</v>
+        <v>5.2</v>
       </c>
       <c r="H14" t="n">
-        <v>-4.3</v>
+        <v>-0.1</v>
       </c>
       <c r="I14" t="inlineStr">
         <is>
@@ -1084,14 +1084,14 @@
       </c>
       <c r="J14" t="inlineStr">
         <is>
-          <t>HOLD (fairly valued)</t>
+          <t>BUY (undervalued)</t>
         </is>
       </c>
       <c r="K14" t="n">
-        <v>28.45</v>
+        <v>16.85</v>
       </c>
       <c r="L14" t="n">
-        <v>27.32</v>
+        <v>16.83</v>
       </c>
     </row>
     <row r="15">

--- a/outputs/transaction_anchor_comparison.xlsx
+++ b/outputs/transaction_anchor_comparison.xlsx
@@ -517,13 +517,13 @@
         <v>0</v>
       </c>
       <c r="F2" t="n">
-        <v>99</v>
+        <v>100.6</v>
       </c>
       <c r="G2" t="n">
-        <v>96.59999999999999</v>
+        <v>98.09999999999999</v>
       </c>
       <c r="H2" t="n">
-        <v>-2.4</v>
+        <v>-2.5</v>
       </c>
       <c r="I2" t="inlineStr">
         <is>
@@ -609,10 +609,10 @@
         <v>0</v>
       </c>
       <c r="F4" t="n">
-        <v>68.2</v>
+        <v>65.59999999999999</v>
       </c>
       <c r="G4" t="n">
-        <v>68.2</v>
+        <v>65.59999999999999</v>
       </c>
       <c r="H4" t="n">
         <v>0</v>
@@ -701,10 +701,10 @@
         <v>-0.74</v>
       </c>
       <c r="F6" t="n">
-        <v>38.4</v>
+        <v>39.4</v>
       </c>
       <c r="G6" t="n">
-        <v>36.4</v>
+        <v>37.4</v>
       </c>
       <c r="H6" t="n">
         <v>-2</v>
@@ -729,7 +729,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>TRMD</t>
+          <t>TNK</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -738,22 +738,22 @@
         </is>
       </c>
       <c r="C7" t="n">
-        <v>31.65</v>
+        <v>83.31999999999999</v>
       </c>
       <c r="D7" t="n">
-        <v>30.34</v>
+        <v>77.51000000000001</v>
       </c>
       <c r="E7" t="n">
-        <v>-4.11</v>
+        <v>-6.97</v>
       </c>
       <c r="F7" t="n">
-        <v>26.7</v>
+        <v>31.6</v>
       </c>
       <c r="G7" t="n">
-        <v>22.4</v>
+        <v>23.7</v>
       </c>
       <c r="H7" t="n">
-        <v>-4.3</v>
+        <v>-7.8</v>
       </c>
       <c r="I7" t="inlineStr">
         <is>
@@ -766,16 +766,16 @@
         </is>
       </c>
       <c r="K7" t="n">
-        <v>33.03</v>
+        <v>84.64</v>
       </c>
       <c r="L7" t="n">
-        <v>31.9</v>
+        <v>79.59</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>CMDB</t>
+          <t>TRMD</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -784,22 +784,22 @@
         </is>
       </c>
       <c r="C8" t="n">
-        <v>32.12</v>
+        <v>31.65</v>
       </c>
       <c r="D8" t="n">
-        <v>31.33</v>
+        <v>30.34</v>
       </c>
       <c r="E8" t="n">
-        <v>-2.45</v>
+        <v>-4.11</v>
       </c>
       <c r="F8" t="n">
-        <v>19</v>
+        <v>25.8</v>
       </c>
       <c r="G8" t="n">
-        <v>16.3</v>
+        <v>21.5</v>
       </c>
       <c r="H8" t="n">
-        <v>-2.7</v>
+        <v>-4.3</v>
       </c>
       <c r="I8" t="inlineStr">
         <is>
@@ -812,40 +812,40 @@
         </is>
       </c>
       <c r="K8" t="n">
-        <v>20.9</v>
+        <v>33.03</v>
       </c>
       <c r="L8" t="n">
-        <v>20.43</v>
+        <v>31.9</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>CMBT</t>
+          <t>ASC</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>WHOLE-COMPANY (hybrid aggregation)</t>
+          <t>whole-company</t>
         </is>
       </c>
       <c r="C9" t="n">
-        <v>15.84</v>
+        <v>17.82</v>
       </c>
       <c r="D9" t="n">
-        <v>15.87</v>
+        <v>17.8</v>
       </c>
       <c r="E9" t="n">
-        <v>0.18</v>
+        <v>-0.13</v>
       </c>
       <c r="F9" t="n">
-        <v>14.9</v>
+        <v>18.3</v>
       </c>
       <c r="G9" t="n">
-        <v>14.9</v>
+        <v>18.1</v>
       </c>
       <c r="H9" t="n">
-        <v>-0.1</v>
+        <v>-0.2</v>
       </c>
       <c r="I9" t="inlineStr">
         <is>
@@ -858,40 +858,40 @@
         </is>
       </c>
       <c r="K9" t="n">
-        <v>16.08</v>
+        <v>16.85</v>
       </c>
       <c r="L9" t="n">
-        <v>16.07</v>
+        <v>16.83</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>SBLK</t>
+          <t>CMBT</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>whole-company</t>
+          <t>WHOLE-COMPANY (hybrid aggregation)</t>
         </is>
       </c>
       <c r="C10" t="n">
-        <v>29.77</v>
+        <v>15.84</v>
       </c>
       <c r="D10" t="n">
-        <v>29.34</v>
+        <v>15.87</v>
       </c>
       <c r="E10" t="n">
-        <v>-1.43</v>
+        <v>0.18</v>
       </c>
       <c r="F10" t="n">
-        <v>15</v>
+        <v>14.4</v>
       </c>
       <c r="G10" t="n">
-        <v>13.6</v>
+        <v>14.4</v>
       </c>
       <c r="H10" t="n">
-        <v>-1.4</v>
+        <v>-0.1</v>
       </c>
       <c r="I10" t="inlineStr">
         <is>
@@ -904,16 +904,16 @@
         </is>
       </c>
       <c r="K10" t="n">
-        <v>28.71</v>
+        <v>16.08</v>
       </c>
       <c r="L10" t="n">
-        <v>28.37</v>
+        <v>16.07</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>TNK</t>
+          <t>SBLK</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -922,22 +922,22 @@
         </is>
       </c>
       <c r="C11" t="n">
-        <v>83.31999999999999</v>
+        <v>29.77</v>
       </c>
       <c r="D11" t="n">
-        <v>77.51000000000001</v>
+        <v>29.34</v>
       </c>
       <c r="E11" t="n">
-        <v>-6.97</v>
+        <v>-1.43</v>
       </c>
       <c r="F11" t="n">
-        <v>19.5</v>
+        <v>15.7</v>
       </c>
       <c r="G11" t="n">
-        <v>12.4</v>
+        <v>14.3</v>
       </c>
       <c r="H11" t="n">
-        <v>-7.1</v>
+        <v>-1.4</v>
       </c>
       <c r="I11" t="inlineStr">
         <is>
@@ -950,16 +950,16 @@
         </is>
       </c>
       <c r="K11" t="n">
-        <v>84.64</v>
+        <v>28.71</v>
       </c>
       <c r="L11" t="n">
-        <v>79.59</v>
+        <v>28.37</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>FLNG</t>
+          <t>CMDB</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -968,22 +968,22 @@
         </is>
       </c>
       <c r="C12" t="n">
-        <v>28.45</v>
+        <v>32.12</v>
       </c>
       <c r="D12" t="n">
-        <v>28.45</v>
+        <v>31.33</v>
       </c>
       <c r="E12" t="n">
-        <v>0</v>
+        <v>-2.45</v>
       </c>
       <c r="F12" t="n">
-        <v>9.300000000000001</v>
+        <v>14.8</v>
       </c>
       <c r="G12" t="n">
-        <v>9.300000000000001</v>
+        <v>12.2</v>
       </c>
       <c r="H12" t="n">
-        <v>0</v>
+        <v>-2.6</v>
       </c>
       <c r="I12" t="inlineStr">
         <is>
@@ -996,16 +996,16 @@
         </is>
       </c>
       <c r="K12" t="n">
-        <v>30.67</v>
+        <v>20.9</v>
       </c>
       <c r="L12" t="n">
-        <v>30.67</v>
+        <v>20.43</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>GSL</t>
+          <t>STNG</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -1014,22 +1014,22 @@
         </is>
       </c>
       <c r="C13" t="n">
-        <v>38.59</v>
+        <v>80.97</v>
       </c>
       <c r="D13" t="n">
-        <v>38.59</v>
+        <v>77.47</v>
       </c>
       <c r="E13" t="n">
-        <v>0</v>
+        <v>-4.33</v>
       </c>
       <c r="F13" t="n">
-        <v>8</v>
+        <v>15.5</v>
       </c>
       <c r="G13" t="n">
-        <v>8</v>
+        <v>10.9</v>
       </c>
       <c r="H13" t="n">
-        <v>0</v>
+        <v>-4.6</v>
       </c>
       <c r="I13" t="inlineStr">
         <is>
@@ -1042,16 +1042,16 @@
         </is>
       </c>
       <c r="K13" t="n">
-        <v>40.59</v>
+        <v>80.3</v>
       </c>
       <c r="L13" t="n">
-        <v>40.59</v>
+        <v>77.13</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>ASC</t>
+          <t>GSL</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1060,22 +1060,22 @@
         </is>
       </c>
       <c r="C14" t="n">
-        <v>17.82</v>
+        <v>38.59</v>
       </c>
       <c r="D14" t="n">
-        <v>17.8</v>
+        <v>38.59</v>
       </c>
       <c r="E14" t="n">
-        <v>-0.13</v>
+        <v>0</v>
       </c>
       <c r="F14" t="n">
-        <v>5.3</v>
+        <v>7.4</v>
       </c>
       <c r="G14" t="n">
-        <v>5.2</v>
+        <v>7.4</v>
       </c>
       <c r="H14" t="n">
-        <v>-0.1</v>
+        <v>0</v>
       </c>
       <c r="I14" t="inlineStr">
         <is>
@@ -1088,16 +1088,16 @@
         </is>
       </c>
       <c r="K14" t="n">
-        <v>16.85</v>
+        <v>40.59</v>
       </c>
       <c r="L14" t="n">
-        <v>16.83</v>
+        <v>40.59</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>STNG</t>
+          <t>FLNG</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1106,22 +1106,22 @@
         </is>
       </c>
       <c r="C15" t="n">
-        <v>80.97</v>
+        <v>28.45</v>
       </c>
       <c r="D15" t="n">
-        <v>77.47</v>
+        <v>28.45</v>
       </c>
       <c r="E15" t="n">
-        <v>-4.33</v>
+        <v>0</v>
       </c>
       <c r="F15" t="n">
-        <v>6.2</v>
+        <v>7.2</v>
       </c>
       <c r="G15" t="n">
-        <v>2</v>
+        <v>7.2</v>
       </c>
       <c r="H15" t="n">
-        <v>-4.2</v>
+        <v>0</v>
       </c>
       <c r="I15" t="inlineStr">
         <is>
@@ -1130,14 +1130,14 @@
       </c>
       <c r="J15" t="inlineStr">
         <is>
-          <t>HOLD (fairly valued)</t>
+          <t>BUY (undervalued)</t>
         </is>
       </c>
       <c r="K15" t="n">
-        <v>80.3</v>
+        <v>30.67</v>
       </c>
       <c r="L15" t="n">
-        <v>77.13</v>
+        <v>30.67</v>
       </c>
     </row>
     <row r="16">
@@ -1161,10 +1161,10 @@
         <v>-3.28</v>
       </c>
       <c r="F16" t="n">
-        <v>-0</v>
+        <v>0.4</v>
       </c>
       <c r="G16" t="n">
-        <v>-2.9</v>
+        <v>-2.5</v>
       </c>
       <c r="H16" t="n">
         <v>-2.9</v>
@@ -1207,13 +1207,13 @@
         <v>-13.65</v>
       </c>
       <c r="F17" t="n">
-        <v>8.699999999999999</v>
+        <v>7.8</v>
       </c>
       <c r="G17" t="n">
-        <v>-3.9</v>
+        <v>-4.6</v>
       </c>
       <c r="H17" t="n">
-        <v>-12.5</v>
+        <v>-12.4</v>
       </c>
       <c r="I17" t="inlineStr">
         <is>
@@ -1253,10 +1253,10 @@
         <v>-2.07</v>
       </c>
       <c r="F18" t="n">
-        <v>-4.7</v>
+        <v>-3.5</v>
       </c>
       <c r="G18" t="n">
-        <v>-6.2</v>
+        <v>-5.1</v>
       </c>
       <c r="H18" t="n">
         <v>-1.5</v>
@@ -1281,7 +1281,7 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>FRO</t>
+          <t>MPCC</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1290,26 +1290,26 @@
         </is>
       </c>
       <c r="C19" t="n">
-        <v>28.47</v>
+        <v>2.02</v>
       </c>
       <c r="D19" t="n">
-        <v>24.22</v>
+        <v>2.02</v>
       </c>
       <c r="E19" t="n">
-        <v>-14.93</v>
+        <v>0</v>
       </c>
       <c r="F19" t="n">
-        <v>-4.5</v>
+        <v>-13</v>
       </c>
       <c r="G19" t="n">
-        <v>-16.5</v>
+        <v>-13</v>
       </c>
       <c r="H19" t="n">
-        <v>-12</v>
+        <v>0</v>
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>HOLD (fairly valued)</t>
+          <t>TRIM/SHORT (overvalued)</t>
         </is>
       </c>
       <c r="J19" t="inlineStr">
@@ -1318,16 +1318,16 @@
         </is>
       </c>
       <c r="K19" t="n">
-        <v>32.95</v>
+        <v>2.11</v>
       </c>
       <c r="L19" t="n">
-        <v>28.82</v>
+        <v>2.11</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>MPCC</t>
+          <t>FRO</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -1336,22 +1336,22 @@
         </is>
       </c>
       <c r="C20" t="n">
-        <v>2.02</v>
+        <v>28.47</v>
       </c>
       <c r="D20" t="n">
-        <v>2.02</v>
+        <v>24.22</v>
       </c>
       <c r="E20" t="n">
-        <v>0</v>
+        <v>-14.93</v>
       </c>
       <c r="F20" t="n">
-        <v>-17.4</v>
+        <v>-5.1</v>
       </c>
       <c r="G20" t="n">
-        <v>-17.4</v>
+        <v>-16.9</v>
       </c>
       <c r="H20" t="n">
-        <v>0</v>
+        <v>-11.9</v>
       </c>
       <c r="I20" t="inlineStr">
         <is>
@@ -1364,40 +1364,40 @@
         </is>
       </c>
       <c r="K20" t="n">
-        <v>2.11</v>
+        <v>32.95</v>
       </c>
       <c r="L20" t="n">
-        <v>2.11</v>
+        <v>28.82</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>INSW</t>
+          <t>ECO</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>WHOLE-COMPANY (hybrid aggregation)</t>
+          <t>whole-company</t>
         </is>
       </c>
       <c r="C21" t="n">
-        <v>57.91</v>
+        <v>40.4</v>
       </c>
       <c r="D21" t="n">
-        <v>52.59</v>
+        <v>34.35</v>
       </c>
       <c r="E21" t="n">
-        <v>-9.18</v>
+        <v>-14.98</v>
       </c>
       <c r="F21" t="n">
-        <v>-13.6</v>
+        <v>-8.4</v>
       </c>
       <c r="G21" t="n">
         <v>-19.9</v>
       </c>
       <c r="H21" t="n">
-        <v>-6.3</v>
+        <v>-11.5</v>
       </c>
       <c r="I21" t="inlineStr">
         <is>
@@ -1410,40 +1410,40 @@
         </is>
       </c>
       <c r="K21" t="n">
-        <v>66.17</v>
+        <v>45.75</v>
       </c>
       <c r="L21" t="n">
-        <v>61.34</v>
+        <v>40.02</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>ECO</t>
+          <t>INSW</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>whole-company</t>
+          <t>WHOLE-COMPANY (hybrid aggregation)</t>
         </is>
       </c>
       <c r="C22" t="n">
-        <v>40.4</v>
+        <v>57.91</v>
       </c>
       <c r="D22" t="n">
-        <v>34.35</v>
+        <v>52.59</v>
       </c>
       <c r="E22" t="n">
-        <v>-14.98</v>
+        <v>-9.18</v>
       </c>
       <c r="F22" t="n">
-        <v>-8.699999999999999</v>
+        <v>-14.9</v>
       </c>
       <c r="G22" t="n">
-        <v>-20.2</v>
+        <v>-21.1</v>
       </c>
       <c r="H22" t="n">
-        <v>-11.4</v>
+        <v>-6.2</v>
       </c>
       <c r="I22" t="inlineStr">
         <is>
@@ -1456,10 +1456,10 @@
         </is>
       </c>
       <c r="K22" t="n">
-        <v>45.75</v>
+        <v>66.17</v>
       </c>
       <c r="L22" t="n">
-        <v>40.02</v>
+        <v>61.34</v>
       </c>
     </row>
     <row r="23">
@@ -1483,10 +1483,10 @@
         <v>-15.76</v>
       </c>
       <c r="F23" t="n">
-        <v>-31.4</v>
+        <v>-31.7</v>
       </c>
       <c r="G23" t="n">
-        <v>-39.9</v>
+        <v>-40.1</v>
       </c>
       <c r="H23" t="n">
         <v>-8.4</v>

--- a/outputs/transaction_anchor_comparison.xlsx
+++ b/outputs/transaction_anchor_comparison.xlsx
@@ -563,13 +563,13 @@
         <v>-8.51</v>
       </c>
       <c r="F3" t="n">
-        <v>100.3</v>
+        <v>97.09999999999999</v>
       </c>
       <c r="G3" t="n">
-        <v>85.2</v>
+        <v>81.90000000000001</v>
       </c>
       <c r="H3" t="n">
-        <v>-15.2</v>
+        <v>-15.1</v>
       </c>
       <c r="I3" t="inlineStr">
         <is>
@@ -582,10 +582,10 @@
         </is>
       </c>
       <c r="K3" t="n">
-        <v>70.86</v>
+        <v>69.70999999999999</v>
       </c>
       <c r="L3" t="n">
-        <v>65.48999999999999</v>
+        <v>64.34999999999999</v>
       </c>
     </row>
     <row r="4">
@@ -867,31 +867,31 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>CMBT</t>
+          <t>SBLK</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>WHOLE-COMPANY (hybrid aggregation)</t>
+          <t>whole-company</t>
         </is>
       </c>
       <c r="C10" t="n">
-        <v>15.84</v>
+        <v>29.77</v>
       </c>
       <c r="D10" t="n">
-        <v>15.87</v>
+        <v>29.34</v>
       </c>
       <c r="E10" t="n">
-        <v>0.18</v>
+        <v>-1.43</v>
       </c>
       <c r="F10" t="n">
-        <v>14.4</v>
+        <v>15.7</v>
       </c>
       <c r="G10" t="n">
-        <v>14.4</v>
+        <v>14.3</v>
       </c>
       <c r="H10" t="n">
-        <v>-0.1</v>
+        <v>-1.4</v>
       </c>
       <c r="I10" t="inlineStr">
         <is>
@@ -904,16 +904,16 @@
         </is>
       </c>
       <c r="K10" t="n">
-        <v>16.08</v>
+        <v>28.71</v>
       </c>
       <c r="L10" t="n">
-        <v>16.07</v>
+        <v>28.37</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>SBLK</t>
+          <t>CMDB</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -922,22 +922,22 @@
         </is>
       </c>
       <c r="C11" t="n">
-        <v>29.77</v>
+        <v>32.12</v>
       </c>
       <c r="D11" t="n">
-        <v>29.34</v>
+        <v>31.33</v>
       </c>
       <c r="E11" t="n">
-        <v>-1.43</v>
+        <v>-2.45</v>
       </c>
       <c r="F11" t="n">
-        <v>15.7</v>
+        <v>14.8</v>
       </c>
       <c r="G11" t="n">
-        <v>14.3</v>
+        <v>12.2</v>
       </c>
       <c r="H11" t="n">
-        <v>-1.4</v>
+        <v>-2.6</v>
       </c>
       <c r="I11" t="inlineStr">
         <is>
@@ -950,16 +950,16 @@
         </is>
       </c>
       <c r="K11" t="n">
-        <v>28.71</v>
+        <v>20.9</v>
       </c>
       <c r="L11" t="n">
-        <v>28.37</v>
+        <v>20.43</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>CMDB</t>
+          <t>STNG</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -968,22 +968,22 @@
         </is>
       </c>
       <c r="C12" t="n">
-        <v>32.12</v>
+        <v>80.97</v>
       </c>
       <c r="D12" t="n">
-        <v>31.33</v>
+        <v>77.47</v>
       </c>
       <c r="E12" t="n">
-        <v>-2.45</v>
+        <v>-4.33</v>
       </c>
       <c r="F12" t="n">
-        <v>14.8</v>
+        <v>15.5</v>
       </c>
       <c r="G12" t="n">
-        <v>12.2</v>
+        <v>10.9</v>
       </c>
       <c r="H12" t="n">
-        <v>-2.6</v>
+        <v>-4.6</v>
       </c>
       <c r="I12" t="inlineStr">
         <is>
@@ -996,40 +996,40 @@
         </is>
       </c>
       <c r="K12" t="n">
-        <v>20.9</v>
+        <v>80.3</v>
       </c>
       <c r="L12" t="n">
-        <v>20.43</v>
+        <v>77.13</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>STNG</t>
+          <t>CMBT</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>whole-company</t>
+          <t>WHOLE-COMPANY (hybrid aggregation)</t>
         </is>
       </c>
       <c r="C13" t="n">
-        <v>80.97</v>
+        <v>15.84</v>
       </c>
       <c r="D13" t="n">
-        <v>77.47</v>
+        <v>15.87</v>
       </c>
       <c r="E13" t="n">
-        <v>-4.33</v>
+        <v>0.18</v>
       </c>
       <c r="F13" t="n">
-        <v>15.5</v>
+        <v>10.9</v>
       </c>
       <c r="G13" t="n">
-        <v>10.9</v>
+        <v>10.7</v>
       </c>
       <c r="H13" t="n">
-        <v>-4.6</v>
+        <v>-0.1</v>
       </c>
       <c r="I13" t="inlineStr">
         <is>
@@ -1042,10 +1042,10 @@
         </is>
       </c>
       <c r="K13" t="n">
-        <v>80.3</v>
+        <v>15.58</v>
       </c>
       <c r="L13" t="n">
-        <v>77.13</v>
+        <v>15.56</v>
       </c>
     </row>
     <row r="14">
@@ -1437,10 +1437,10 @@
         <v>-9.18</v>
       </c>
       <c r="F22" t="n">
-        <v>-14.9</v>
+        <v>-16.4</v>
       </c>
       <c r="G22" t="n">
-        <v>-21.1</v>
+        <v>-22.6</v>
       </c>
       <c r="H22" t="n">
         <v>-6.2</v>
@@ -1456,10 +1456,10 @@
         </is>
       </c>
       <c r="K22" t="n">
-        <v>66.17</v>
+        <v>65.01000000000001</v>
       </c>
       <c r="L22" t="n">
-        <v>61.34</v>
+        <v>60.19</v>
       </c>
     </row>
     <row r="23">

--- a/outputs/transaction_anchor_comparison.xlsx
+++ b/outputs/transaction_anchor_comparison.xlsx
@@ -499,7 +499,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>BRUT</t>
+          <t>SB</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -508,22 +508,22 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>8.800000000000001</v>
+        <v>9.720000000000001</v>
       </c>
       <c r="D2" t="n">
-        <v>8.800000000000001</v>
+        <v>10.12</v>
       </c>
       <c r="E2" t="n">
-        <v>0</v>
+        <v>4.09</v>
       </c>
       <c r="F2" t="n">
-        <v>100.6</v>
+        <v>49.3</v>
       </c>
       <c r="G2" t="n">
-        <v>98.09999999999999</v>
+        <v>55.6</v>
       </c>
       <c r="H2" t="n">
-        <v>-2.5</v>
+        <v>6.3</v>
       </c>
       <c r="I2" t="inlineStr">
         <is>
@@ -536,16 +536,16 @@
         </is>
       </c>
       <c r="K2" t="n">
-        <v>10.37</v>
+        <v>9.42</v>
       </c>
       <c r="L2" t="n">
-        <v>10.24</v>
+        <v>9.82</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>TEN</t>
+          <t>CCEC</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -554,22 +554,22 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>96.95</v>
+        <v>28.1</v>
       </c>
       <c r="D3" t="n">
-        <v>88.7</v>
+        <v>28.1</v>
       </c>
       <c r="E3" t="n">
-        <v>-8.51</v>
+        <v>0</v>
       </c>
       <c r="F3" t="n">
-        <v>97.09999999999999</v>
+        <v>54.5</v>
       </c>
       <c r="G3" t="n">
-        <v>81.90000000000001</v>
+        <v>54.5</v>
       </c>
       <c r="H3" t="n">
-        <v>-15.1</v>
+        <v>0</v>
       </c>
       <c r="I3" t="inlineStr">
         <is>
@@ -582,16 +582,16 @@
         </is>
       </c>
       <c r="K3" t="n">
-        <v>69.70999999999999</v>
+        <v>33.5</v>
       </c>
       <c r="L3" t="n">
-        <v>64.34999999999999</v>
+        <v>33.5</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>CCEC</t>
+          <t>TEN</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -600,22 +600,22 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>28.1</v>
+        <v>96.95</v>
       </c>
       <c r="D4" t="n">
-        <v>28.1</v>
+        <v>88.7</v>
       </c>
       <c r="E4" t="n">
-        <v>0</v>
+        <v>-8.51</v>
       </c>
       <c r="F4" t="n">
-        <v>65.59999999999999</v>
+        <v>55.9</v>
       </c>
       <c r="G4" t="n">
-        <v>65.59999999999999</v>
+        <v>44</v>
       </c>
       <c r="H4" t="n">
-        <v>0</v>
+        <v>-12</v>
       </c>
       <c r="I4" t="inlineStr">
         <is>
@@ -628,16 +628,16 @@
         </is>
       </c>
       <c r="K4" t="n">
-        <v>35.91</v>
+        <v>55.15</v>
       </c>
       <c r="L4" t="n">
-        <v>35.91</v>
+        <v>50.92</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>SB</t>
+          <t>ASC</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -646,22 +646,22 @@
         </is>
       </c>
       <c r="C5" t="n">
-        <v>9.720000000000001</v>
+        <v>17.82</v>
       </c>
       <c r="D5" t="n">
-        <v>10.12</v>
+        <v>17.8</v>
       </c>
       <c r="E5" t="n">
-        <v>4.09</v>
+        <v>-0.13</v>
       </c>
       <c r="F5" t="n">
-        <v>47.1</v>
+        <v>14.4</v>
       </c>
       <c r="G5" t="n">
-        <v>53.4</v>
+        <v>14.2</v>
       </c>
       <c r="H5" t="n">
-        <v>6.2</v>
+        <v>-0.1</v>
       </c>
       <c r="I5" t="inlineStr">
         <is>
@@ -674,16 +674,16 @@
         </is>
       </c>
       <c r="K5" t="n">
-        <v>9.279999999999999</v>
+        <v>16.3</v>
       </c>
       <c r="L5" t="n">
-        <v>9.68</v>
+        <v>16.28</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>CAPT</t>
+          <t>SBLK</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -692,22 +692,22 @@
         </is>
       </c>
       <c r="C6" t="n">
-        <v>15.61</v>
+        <v>29.77</v>
       </c>
       <c r="D6" t="n">
-        <v>15.49</v>
+        <v>29.34</v>
       </c>
       <c r="E6" t="n">
-        <v>-0.74</v>
+        <v>-1.43</v>
       </c>
       <c r="F6" t="n">
-        <v>39.4</v>
+        <v>15</v>
       </c>
       <c r="G6" t="n">
-        <v>37.4</v>
+        <v>13.6</v>
       </c>
       <c r="H6" t="n">
-        <v>-2</v>
+        <v>-1.4</v>
       </c>
       <c r="I6" t="inlineStr">
         <is>
@@ -720,16 +720,16 @@
         </is>
       </c>
       <c r="K6" t="n">
-        <v>17.41</v>
+        <v>28.54</v>
       </c>
       <c r="L6" t="n">
-        <v>17.16</v>
+        <v>28.19</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>TNK</t>
+          <t>CMDB</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -738,22 +738,22 @@
         </is>
       </c>
       <c r="C7" t="n">
-        <v>83.31999999999999</v>
+        <v>32.12</v>
       </c>
       <c r="D7" t="n">
-        <v>77.51000000000001</v>
+        <v>31.33</v>
       </c>
       <c r="E7" t="n">
-        <v>-6.97</v>
+        <v>-2.45</v>
       </c>
       <c r="F7" t="n">
-        <v>31.6</v>
+        <v>14.3</v>
       </c>
       <c r="G7" t="n">
-        <v>23.7</v>
+        <v>11.7</v>
       </c>
       <c r="H7" t="n">
-        <v>-7.8</v>
+        <v>-2.6</v>
       </c>
       <c r="I7" t="inlineStr">
         <is>
@@ -766,10 +766,10 @@
         </is>
       </c>
       <c r="K7" t="n">
-        <v>84.64</v>
+        <v>20.82</v>
       </c>
       <c r="L7" t="n">
-        <v>79.59</v>
+        <v>20.34</v>
       </c>
     </row>
     <row r="8">
@@ -793,13 +793,13 @@
         <v>-4.11</v>
       </c>
       <c r="F8" t="n">
-        <v>25.8</v>
+        <v>13.1</v>
       </c>
       <c r="G8" t="n">
-        <v>21.5</v>
+        <v>9.1</v>
       </c>
       <c r="H8" t="n">
-        <v>-4.3</v>
+        <v>-3.9</v>
       </c>
       <c r="I8" t="inlineStr">
         <is>
@@ -812,16 +812,16 @@
         </is>
       </c>
       <c r="K8" t="n">
-        <v>33.03</v>
+        <v>29.68</v>
       </c>
       <c r="L8" t="n">
-        <v>31.9</v>
+        <v>28.65</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>ASC</t>
+          <t>GSL</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -830,22 +830,22 @@
         </is>
       </c>
       <c r="C9" t="n">
-        <v>17.82</v>
+        <v>38.59</v>
       </c>
       <c r="D9" t="n">
-        <v>17.8</v>
+        <v>38.59</v>
       </c>
       <c r="E9" t="n">
-        <v>-0.13</v>
+        <v>0</v>
       </c>
       <c r="F9" t="n">
-        <v>18.3</v>
+        <v>7.4</v>
       </c>
       <c r="G9" t="n">
-        <v>18.1</v>
+        <v>7.4</v>
       </c>
       <c r="H9" t="n">
-        <v>-0.2</v>
+        <v>0</v>
       </c>
       <c r="I9" t="inlineStr">
         <is>
@@ -858,16 +858,16 @@
         </is>
       </c>
       <c r="K9" t="n">
-        <v>16.85</v>
+        <v>40.59</v>
       </c>
       <c r="L9" t="n">
-        <v>16.83</v>
+        <v>40.59</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>SBLK</t>
+          <t>TNK</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -876,22 +876,22 @@
         </is>
       </c>
       <c r="C10" t="n">
-        <v>29.77</v>
+        <v>83.31999999999999</v>
       </c>
       <c r="D10" t="n">
-        <v>29.34</v>
+        <v>77.51000000000001</v>
       </c>
       <c r="E10" t="n">
-        <v>-1.43</v>
+        <v>-6.97</v>
       </c>
       <c r="F10" t="n">
-        <v>15.7</v>
+        <v>11.3</v>
       </c>
       <c r="G10" t="n">
-        <v>14.3</v>
+        <v>5.1</v>
       </c>
       <c r="H10" t="n">
-        <v>-1.4</v>
+        <v>-6.2</v>
       </c>
       <c r="I10" t="inlineStr">
         <is>
@@ -904,16 +904,16 @@
         </is>
       </c>
       <c r="K10" t="n">
-        <v>28.71</v>
+        <v>71.58</v>
       </c>
       <c r="L10" t="n">
-        <v>28.37</v>
+        <v>67.61</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>CMDB</t>
+          <t>FLNG</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -922,38 +922,38 @@
         </is>
       </c>
       <c r="C11" t="n">
-        <v>32.12</v>
+        <v>28.45</v>
       </c>
       <c r="D11" t="n">
-        <v>31.33</v>
+        <v>28.45</v>
       </c>
       <c r="E11" t="n">
-        <v>-2.45</v>
+        <v>0</v>
       </c>
       <c r="F11" t="n">
-        <v>14.8</v>
+        <v>2</v>
       </c>
       <c r="G11" t="n">
-        <v>12.2</v>
+        <v>2</v>
       </c>
       <c r="H11" t="n">
-        <v>-2.6</v>
+        <v>0</v>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>BUY (undervalued)</t>
+          <t>HOLD (fairly valued)</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>BUY (undervalued)</t>
+          <t>HOLD (fairly valued)</t>
         </is>
       </c>
       <c r="K11" t="n">
-        <v>20.9</v>
+        <v>29.19</v>
       </c>
       <c r="L11" t="n">
-        <v>20.43</v>
+        <v>29.19</v>
       </c>
     </row>
     <row r="12">
@@ -977,13 +977,13 @@
         <v>-4.33</v>
       </c>
       <c r="F12" t="n">
-        <v>15.5</v>
+        <v>6.2</v>
       </c>
       <c r="G12" t="n">
-        <v>10.9</v>
+        <v>2</v>
       </c>
       <c r="H12" t="n">
-        <v>-4.6</v>
+        <v>-4.2</v>
       </c>
       <c r="I12" t="inlineStr">
         <is>
@@ -992,112 +992,112 @@
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>BUY (undervalued)</t>
+          <t>HOLD (fairly valued)</t>
         </is>
       </c>
       <c r="K12" t="n">
-        <v>80.3</v>
+        <v>73.81</v>
       </c>
       <c r="L12" t="n">
-        <v>77.13</v>
+        <v>70.90000000000001</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>CMBT</t>
+          <t>GNK</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>WHOLE-COMPANY (hybrid aggregation)</t>
+          <t>whole-company</t>
         </is>
       </c>
       <c r="C13" t="n">
-        <v>15.84</v>
+        <v>25.53</v>
       </c>
       <c r="D13" t="n">
-        <v>15.87</v>
+        <v>24.69</v>
       </c>
       <c r="E13" t="n">
-        <v>0.18</v>
+        <v>-3.28</v>
       </c>
       <c r="F13" t="n">
-        <v>10.9</v>
+        <v>-1.5</v>
       </c>
       <c r="G13" t="n">
-        <v>10.7</v>
+        <v>-4.5</v>
       </c>
       <c r="H13" t="n">
-        <v>-0.1</v>
+        <v>-3</v>
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>BUY (undervalued)</t>
+          <t>HOLD (fairly valued)</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t>BUY (undervalued)</t>
+          <t>HOLD (fairly valued)</t>
         </is>
       </c>
       <c r="K13" t="n">
-        <v>15.58</v>
+        <v>24.28</v>
       </c>
       <c r="L13" t="n">
-        <v>15.56</v>
+        <v>23.56</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>GSL</t>
+          <t>CMBT</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>whole-company</t>
+          <t>WHOLE-COMPANY (hybrid aggregation)</t>
         </is>
       </c>
       <c r="C14" t="n">
-        <v>38.59</v>
+        <v>15.84</v>
       </c>
       <c r="D14" t="n">
-        <v>38.59</v>
+        <v>15.87</v>
       </c>
       <c r="E14" t="n">
-        <v>0</v>
+        <v>0.18</v>
       </c>
       <c r="F14" t="n">
-        <v>7.4</v>
+        <v>-5.5</v>
       </c>
       <c r="G14" t="n">
-        <v>7.4</v>
+        <v>-5</v>
       </c>
       <c r="H14" t="n">
-        <v>0</v>
+        <v>0.5</v>
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>BUY (undervalued)</t>
+          <t>TRIM/SHORT (overvalued)</t>
         </is>
       </c>
       <c r="J14" t="inlineStr">
         <is>
-          <t>BUY (undervalued)</t>
+          <t>TRIM/SHORT (overvalued)</t>
         </is>
       </c>
       <c r="K14" t="n">
-        <v>40.59</v>
+        <v>13.27</v>
       </c>
       <c r="L14" t="n">
-        <v>40.59</v>
+        <v>13.34</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>FLNG</t>
+          <t>MPCC</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1106,44 +1106,44 @@
         </is>
       </c>
       <c r="C15" t="n">
-        <v>28.45</v>
+        <v>2.02</v>
       </c>
       <c r="D15" t="n">
-        <v>28.45</v>
+        <v>2.02</v>
       </c>
       <c r="E15" t="n">
         <v>0</v>
       </c>
       <c r="F15" t="n">
-        <v>7.2</v>
+        <v>-13</v>
       </c>
       <c r="G15" t="n">
-        <v>7.2</v>
+        <v>-13</v>
       </c>
       <c r="H15" t="n">
         <v>0</v>
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>BUY (undervalued)</t>
+          <t>TRIM/SHORT (overvalued)</t>
         </is>
       </c>
       <c r="J15" t="inlineStr">
         <is>
-          <t>BUY (undervalued)</t>
+          <t>TRIM/SHORT (overvalued)</t>
         </is>
       </c>
       <c r="K15" t="n">
-        <v>30.67</v>
+        <v>2.11</v>
       </c>
       <c r="L15" t="n">
-        <v>30.67</v>
+        <v>2.11</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>GNK</t>
+          <t>HAFN</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1152,44 +1152,44 @@
         </is>
       </c>
       <c r="C16" t="n">
-        <v>25.53</v>
+        <v>5.69</v>
       </c>
       <c r="D16" t="n">
-        <v>24.69</v>
+        <v>5.57</v>
       </c>
       <c r="E16" t="n">
-        <v>-3.28</v>
+        <v>-2.07</v>
       </c>
       <c r="F16" t="n">
-        <v>0.4</v>
+        <v>-13.1</v>
       </c>
       <c r="G16" t="n">
-        <v>-2.5</v>
+        <v>-14.5</v>
       </c>
       <c r="H16" t="n">
-        <v>-2.9</v>
+        <v>-1.4</v>
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>HOLD (fairly valued)</t>
+          <t>TRIM/SHORT (overvalued)</t>
         </is>
       </c>
       <c r="J16" t="inlineStr">
         <is>
-          <t>HOLD (fairly valued)</t>
+          <t>TRIM/SHORT (overvalued)</t>
         </is>
       </c>
       <c r="K16" t="n">
-        <v>24.77</v>
+        <v>5.7</v>
       </c>
       <c r="L16" t="n">
-        <v>24.05</v>
+        <v>5.61</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>DHT</t>
+          <t>CAPT</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1198,44 +1198,44 @@
         </is>
       </c>
       <c r="C17" t="n">
-        <v>16.07</v>
+        <v>15.61</v>
       </c>
       <c r="D17" t="n">
-        <v>13.88</v>
+        <v>15.49</v>
       </c>
       <c r="E17" t="n">
-        <v>-13.65</v>
+        <v>-0.74</v>
       </c>
       <c r="F17" t="n">
-        <v>7.8</v>
+        <v>-17.7</v>
       </c>
       <c r="G17" t="n">
-        <v>-4.6</v>
+        <v>-19.4</v>
       </c>
       <c r="H17" t="n">
-        <v>-12.4</v>
+        <v>-1.7</v>
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>BUY (undervalued)</t>
+          <t>TRIM/SHORT (overvalued)</t>
         </is>
       </c>
       <c r="J17" t="inlineStr">
         <is>
-          <t>HOLD (fairly valued)</t>
+          <t>TRIM/SHORT (overvalued)</t>
         </is>
       </c>
       <c r="K17" t="n">
-        <v>17.82</v>
+        <v>10.27</v>
       </c>
       <c r="L17" t="n">
-        <v>15.77</v>
+        <v>10.07</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>HAFN</t>
+          <t>DHT</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1244,26 +1244,26 @@
         </is>
       </c>
       <c r="C18" t="n">
-        <v>5.69</v>
+        <v>16.07</v>
       </c>
       <c r="D18" t="n">
-        <v>5.57</v>
+        <v>13.88</v>
       </c>
       <c r="E18" t="n">
-        <v>-2.07</v>
+        <v>-13.65</v>
       </c>
       <c r="F18" t="n">
-        <v>-3.5</v>
+        <v>-21.7</v>
       </c>
       <c r="G18" t="n">
-        <v>-5.1</v>
+        <v>-31.3</v>
       </c>
       <c r="H18" t="n">
-        <v>-1.5</v>
+        <v>-9.6</v>
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>HOLD (fairly valued)</t>
+          <t>TRIM/SHORT (overvalued)</t>
         </is>
       </c>
       <c r="J18" t="inlineStr">
@@ -1272,40 +1272,40 @@
         </is>
       </c>
       <c r="K18" t="n">
-        <v>6.33</v>
+        <v>12.94</v>
       </c>
       <c r="L18" t="n">
-        <v>6.23</v>
+        <v>11.35</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>MPCC</t>
+          <t>INSW</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>whole-company</t>
+          <t>WHOLE-COMPANY (hybrid aggregation)</t>
         </is>
       </c>
       <c r="C19" t="n">
-        <v>2.02</v>
+        <v>57.91</v>
       </c>
       <c r="D19" t="n">
-        <v>2.02</v>
+        <v>52.59</v>
       </c>
       <c r="E19" t="n">
-        <v>0</v>
+        <v>-9.18</v>
       </c>
       <c r="F19" t="n">
-        <v>-13</v>
+        <v>-33.4</v>
       </c>
       <c r="G19" t="n">
-        <v>-13</v>
+        <v>-38.3</v>
       </c>
       <c r="H19" t="n">
-        <v>0</v>
+        <v>-4.8</v>
       </c>
       <c r="I19" t="inlineStr">
         <is>
@@ -1318,16 +1318,16 @@
         </is>
       </c>
       <c r="K19" t="n">
-        <v>2.11</v>
+        <v>51.76</v>
       </c>
       <c r="L19" t="n">
-        <v>2.11</v>
+        <v>48</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>FRO</t>
+          <t>BRUT</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -1336,22 +1336,22 @@
         </is>
       </c>
       <c r="C20" t="n">
-        <v>28.47</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="D20" t="n">
-        <v>24.22</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="E20" t="n">
-        <v>-14.93</v>
+        <v>0</v>
       </c>
       <c r="F20" t="n">
-        <v>-5.1</v>
+        <v>-37.8</v>
       </c>
       <c r="G20" t="n">
-        <v>-16.9</v>
+        <v>-39.7</v>
       </c>
       <c r="H20" t="n">
-        <v>-11.9</v>
+        <v>-1.9</v>
       </c>
       <c r="I20" t="inlineStr">
         <is>
@@ -1364,16 +1364,16 @@
         </is>
       </c>
       <c r="K20" t="n">
-        <v>32.95</v>
+        <v>3.22</v>
       </c>
       <c r="L20" t="n">
-        <v>28.82</v>
+        <v>3.12</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>ECO</t>
+          <t>FRO</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -1382,22 +1382,22 @@
         </is>
       </c>
       <c r="C21" t="n">
-        <v>40.4</v>
+        <v>28.47</v>
       </c>
       <c r="D21" t="n">
-        <v>34.35</v>
+        <v>24.22</v>
       </c>
       <c r="E21" t="n">
-        <v>-14.98</v>
+        <v>-14.93</v>
       </c>
       <c r="F21" t="n">
-        <v>-8.4</v>
+        <v>-38.4</v>
       </c>
       <c r="G21" t="n">
-        <v>-19.9</v>
+        <v>-47.6</v>
       </c>
       <c r="H21" t="n">
-        <v>-11.5</v>
+        <v>-9.199999999999999</v>
       </c>
       <c r="I21" t="inlineStr">
         <is>
@@ -1410,40 +1410,40 @@
         </is>
       </c>
       <c r="K21" t="n">
-        <v>45.75</v>
+        <v>21.37</v>
       </c>
       <c r="L21" t="n">
-        <v>40.02</v>
+        <v>18.17</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>INSW</t>
+          <t>ECO</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>WHOLE-COMPANY (hybrid aggregation)</t>
+          <t>whole-company</t>
         </is>
       </c>
       <c r="C22" t="n">
-        <v>57.91</v>
+        <v>40.4</v>
       </c>
       <c r="D22" t="n">
-        <v>52.59</v>
+        <v>34.35</v>
       </c>
       <c r="E22" t="n">
-        <v>-9.18</v>
+        <v>-14.98</v>
       </c>
       <c r="F22" t="n">
-        <v>-16.4</v>
+        <v>-39.6</v>
       </c>
       <c r="G22" t="n">
-        <v>-22.6</v>
+        <v>-48.5</v>
       </c>
       <c r="H22" t="n">
-        <v>-6.2</v>
+        <v>-8.9</v>
       </c>
       <c r="I22" t="inlineStr">
         <is>
@@ -1456,10 +1456,10 @@
         </is>
       </c>
       <c r="K22" t="n">
-        <v>65.01000000000001</v>
+        <v>30.18</v>
       </c>
       <c r="L22" t="n">
-        <v>60.19</v>
+        <v>25.73</v>
       </c>
     </row>
     <row r="23">
@@ -1483,13 +1483,13 @@
         <v>-15.76</v>
       </c>
       <c r="F23" t="n">
-        <v>-31.7</v>
+        <v>-52.9</v>
       </c>
       <c r="G23" t="n">
-        <v>-40.1</v>
+        <v>-59.5</v>
       </c>
       <c r="H23" t="n">
-        <v>-8.4</v>
+        <v>-6.6</v>
       </c>
       <c r="I23" t="inlineStr">
         <is>
@@ -1502,10 +1502,10 @@
         </is>
       </c>
       <c r="K23" t="n">
-        <v>3.8</v>
+        <v>2.62</v>
       </c>
       <c r="L23" t="n">
-        <v>3.33</v>
+        <v>2.25</v>
       </c>
     </row>
   </sheetData>

--- a/outputs/transaction_anchor_comparison.xlsx
+++ b/outputs/transaction_anchor_comparison.xlsx
@@ -499,7 +499,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>SB</t>
+          <t>CCEC</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -508,22 +508,22 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>9.720000000000001</v>
+        <v>28.1</v>
       </c>
       <c r="D2" t="n">
-        <v>10.12</v>
+        <v>28.1</v>
       </c>
       <c r="E2" t="n">
-        <v>4.09</v>
+        <v>0</v>
       </c>
       <c r="F2" t="n">
-        <v>49.3</v>
+        <v>55.1</v>
       </c>
       <c r="G2" t="n">
-        <v>55.6</v>
+        <v>55.1</v>
       </c>
       <c r="H2" t="n">
-        <v>6.3</v>
+        <v>0</v>
       </c>
       <c r="I2" t="inlineStr">
         <is>
@@ -536,16 +536,16 @@
         </is>
       </c>
       <c r="K2" t="n">
-        <v>9.42</v>
+        <v>33.5</v>
       </c>
       <c r="L2" t="n">
-        <v>9.82</v>
+        <v>33.5</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>CCEC</t>
+          <t>SB</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -554,22 +554,22 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>28.1</v>
+        <v>9.720000000000001</v>
       </c>
       <c r="D3" t="n">
-        <v>28.1</v>
+        <v>10.12</v>
       </c>
       <c r="E3" t="n">
-        <v>0</v>
+        <v>4.09</v>
       </c>
       <c r="F3" t="n">
-        <v>54.5</v>
+        <v>47.2</v>
       </c>
       <c r="G3" t="n">
-        <v>54.5</v>
+        <v>53.4</v>
       </c>
       <c r="H3" t="n">
-        <v>0</v>
+        <v>6.2</v>
       </c>
       <c r="I3" t="inlineStr">
         <is>
@@ -582,10 +582,10 @@
         </is>
       </c>
       <c r="K3" t="n">
-        <v>33.5</v>
+        <v>9.42</v>
       </c>
       <c r="L3" t="n">
-        <v>33.5</v>
+        <v>9.82</v>
       </c>
     </row>
     <row r="4">
@@ -609,13 +609,13 @@
         <v>-8.51</v>
       </c>
       <c r="F4" t="n">
-        <v>55.9</v>
+        <v>47.6</v>
       </c>
       <c r="G4" t="n">
-        <v>44</v>
+        <v>36.3</v>
       </c>
       <c r="H4" t="n">
-        <v>-12</v>
+        <v>-11.3</v>
       </c>
       <c r="I4" t="inlineStr">
         <is>
@@ -637,7 +637,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>ASC</t>
+          <t>SBLK</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -646,22 +646,22 @@
         </is>
       </c>
       <c r="C5" t="n">
-        <v>17.82</v>
+        <v>29.77</v>
       </c>
       <c r="D5" t="n">
-        <v>17.8</v>
+        <v>29.34</v>
       </c>
       <c r="E5" t="n">
-        <v>-0.13</v>
+        <v>-1.43</v>
       </c>
       <c r="F5" t="n">
-        <v>14.4</v>
+        <v>15</v>
       </c>
       <c r="G5" t="n">
-        <v>14.2</v>
+        <v>13.6</v>
       </c>
       <c r="H5" t="n">
-        <v>-0.1</v>
+        <v>-1.4</v>
       </c>
       <c r="I5" t="inlineStr">
         <is>
@@ -674,16 +674,16 @@
         </is>
       </c>
       <c r="K5" t="n">
-        <v>16.3</v>
+        <v>28.54</v>
       </c>
       <c r="L5" t="n">
-        <v>16.28</v>
+        <v>28.19</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>SBLK</t>
+          <t>CMDB</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -692,22 +692,22 @@
         </is>
       </c>
       <c r="C6" t="n">
-        <v>29.77</v>
+        <v>32.12</v>
       </c>
       <c r="D6" t="n">
-        <v>29.34</v>
+        <v>31.33</v>
       </c>
       <c r="E6" t="n">
-        <v>-1.43</v>
+        <v>-2.45</v>
       </c>
       <c r="F6" t="n">
-        <v>15</v>
+        <v>14.5</v>
       </c>
       <c r="G6" t="n">
-        <v>13.6</v>
+        <v>11.9</v>
       </c>
       <c r="H6" t="n">
-        <v>-1.4</v>
+        <v>-2.6</v>
       </c>
       <c r="I6" t="inlineStr">
         <is>
@@ -720,16 +720,16 @@
         </is>
       </c>
       <c r="K6" t="n">
-        <v>28.54</v>
+        <v>20.82</v>
       </c>
       <c r="L6" t="n">
-        <v>28.19</v>
+        <v>20.34</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>CMDB</t>
+          <t>ASC</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -738,22 +738,22 @@
         </is>
       </c>
       <c r="C7" t="n">
-        <v>32.12</v>
+        <v>17.82</v>
       </c>
       <c r="D7" t="n">
-        <v>31.33</v>
+        <v>17.8</v>
       </c>
       <c r="E7" t="n">
-        <v>-2.45</v>
+        <v>-0.13</v>
       </c>
       <c r="F7" t="n">
-        <v>14.3</v>
+        <v>9.699999999999999</v>
       </c>
       <c r="G7" t="n">
-        <v>11.7</v>
+        <v>9.6</v>
       </c>
       <c r="H7" t="n">
-        <v>-2.6</v>
+        <v>-0.1</v>
       </c>
       <c r="I7" t="inlineStr">
         <is>
@@ -766,16 +766,16 @@
         </is>
       </c>
       <c r="K7" t="n">
-        <v>20.82</v>
+        <v>16.3</v>
       </c>
       <c r="L7" t="n">
-        <v>20.34</v>
+        <v>16.28</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>TRMD</t>
+          <t>GSL</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -784,22 +784,22 @@
         </is>
       </c>
       <c r="C8" t="n">
-        <v>31.65</v>
+        <v>38.59</v>
       </c>
       <c r="D8" t="n">
-        <v>30.34</v>
+        <v>38.59</v>
       </c>
       <c r="E8" t="n">
-        <v>-4.11</v>
+        <v>0</v>
       </c>
       <c r="F8" t="n">
-        <v>13.1</v>
+        <v>6.5</v>
       </c>
       <c r="G8" t="n">
-        <v>9.1</v>
+        <v>6.5</v>
       </c>
       <c r="H8" t="n">
-        <v>-3.9</v>
+        <v>0</v>
       </c>
       <c r="I8" t="inlineStr">
         <is>
@@ -812,16 +812,16 @@
         </is>
       </c>
       <c r="K8" t="n">
-        <v>29.68</v>
+        <v>40.59</v>
       </c>
       <c r="L8" t="n">
-        <v>28.65</v>
+        <v>40.59</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>GSL</t>
+          <t>TRMD</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -830,22 +830,22 @@
         </is>
       </c>
       <c r="C9" t="n">
-        <v>38.59</v>
+        <v>31.65</v>
       </c>
       <c r="D9" t="n">
-        <v>38.59</v>
+        <v>30.34</v>
       </c>
       <c r="E9" t="n">
-        <v>0</v>
+        <v>-4.11</v>
       </c>
       <c r="F9" t="n">
-        <v>7.4</v>
+        <v>7.2</v>
       </c>
       <c r="G9" t="n">
-        <v>7.4</v>
+        <v>3.4</v>
       </c>
       <c r="H9" t="n">
-        <v>0</v>
+        <v>-3.7</v>
       </c>
       <c r="I9" t="inlineStr">
         <is>
@@ -854,14 +854,14 @@
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>BUY (undervalued)</t>
+          <t>HOLD (fairly valued)</t>
         </is>
       </c>
       <c r="K9" t="n">
-        <v>40.59</v>
+        <v>29.68</v>
       </c>
       <c r="L9" t="n">
-        <v>40.59</v>
+        <v>28.65</v>
       </c>
     </row>
     <row r="10">
@@ -885,13 +885,13 @@
         <v>-6.97</v>
       </c>
       <c r="F10" t="n">
-        <v>11.3</v>
+        <v>5.9</v>
       </c>
       <c r="G10" t="n">
-        <v>5.1</v>
+        <v>0</v>
       </c>
       <c r="H10" t="n">
-        <v>-6.2</v>
+        <v>-5.9</v>
       </c>
       <c r="I10" t="inlineStr">
         <is>
@@ -900,7 +900,7 @@
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>BUY (undervalued)</t>
+          <t>HOLD (fairly valued)</t>
         </is>
       </c>
       <c r="K10" t="n">
@@ -931,10 +931,10 @@
         <v>0</v>
       </c>
       <c r="F11" t="n">
-        <v>2</v>
+        <v>-0.4</v>
       </c>
       <c r="G11" t="n">
-        <v>2</v>
+        <v>-0.4</v>
       </c>
       <c r="H11" t="n">
         <v>0</v>
@@ -977,17 +977,17 @@
         <v>-4.33</v>
       </c>
       <c r="F12" t="n">
-        <v>6.2</v>
+        <v>1.1</v>
       </c>
       <c r="G12" t="n">
-        <v>2</v>
+        <v>-2.9</v>
       </c>
       <c r="H12" t="n">
-        <v>-4.2</v>
+        <v>-4</v>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>BUY (undervalued)</t>
+          <t>HOLD (fairly valued)</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
@@ -1023,10 +1023,10 @@
         <v>-3.28</v>
       </c>
       <c r="F13" t="n">
-        <v>-1.5</v>
+        <v>-0.9</v>
       </c>
       <c r="G13" t="n">
-        <v>-4.5</v>
+        <v>-3.9</v>
       </c>
       <c r="H13" t="n">
         <v>-3</v>
@@ -1069,10 +1069,10 @@
         <v>0.18</v>
       </c>
       <c r="F14" t="n">
-        <v>-5.5</v>
+        <v>-8.800000000000001</v>
       </c>
       <c r="G14" t="n">
-        <v>-5</v>
+        <v>-8.4</v>
       </c>
       <c r="H14" t="n">
         <v>0.5</v>
@@ -1115,10 +1115,10 @@
         <v>0</v>
       </c>
       <c r="F15" t="n">
-        <v>-13</v>
+        <v>-13.7</v>
       </c>
       <c r="G15" t="n">
-        <v>-13</v>
+        <v>-13.7</v>
       </c>
       <c r="H15" t="n">
         <v>0</v>
@@ -1161,13 +1161,13 @@
         <v>-2.07</v>
       </c>
       <c r="F16" t="n">
-        <v>-13.1</v>
+        <v>-18.8</v>
       </c>
       <c r="G16" t="n">
-        <v>-14.5</v>
+        <v>-20.1</v>
       </c>
       <c r="H16" t="n">
-        <v>-1.4</v>
+        <v>-1.3</v>
       </c>
       <c r="I16" t="inlineStr">
         <is>
@@ -1207,13 +1207,13 @@
         <v>-0.74</v>
       </c>
       <c r="F17" t="n">
-        <v>-17.7</v>
+        <v>-22.6</v>
       </c>
       <c r="G17" t="n">
-        <v>-19.4</v>
+        <v>-24.2</v>
       </c>
       <c r="H17" t="n">
-        <v>-1.7</v>
+        <v>-1.6</v>
       </c>
       <c r="I17" t="inlineStr">
         <is>
@@ -1253,13 +1253,13 @@
         <v>-13.65</v>
       </c>
       <c r="F18" t="n">
-        <v>-21.7</v>
+        <v>-24.7</v>
       </c>
       <c r="G18" t="n">
-        <v>-31.3</v>
+        <v>-33.9</v>
       </c>
       <c r="H18" t="n">
-        <v>-9.6</v>
+        <v>-9.199999999999999</v>
       </c>
       <c r="I18" t="inlineStr">
         <is>
@@ -1281,31 +1281,31 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>INSW</t>
+          <t>BRUT</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>WHOLE-COMPANY (hybrid aggregation)</t>
+          <t>whole-company</t>
         </is>
       </c>
       <c r="C19" t="n">
-        <v>57.91</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="D19" t="n">
-        <v>52.59</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="E19" t="n">
-        <v>-9.18</v>
+        <v>0</v>
       </c>
       <c r="F19" t="n">
-        <v>-33.4</v>
+        <v>-39.2</v>
       </c>
       <c r="G19" t="n">
-        <v>-38.3</v>
+        <v>-41</v>
       </c>
       <c r="H19" t="n">
-        <v>-4.8</v>
+        <v>-1.9</v>
       </c>
       <c r="I19" t="inlineStr">
         <is>
@@ -1318,40 +1318,40 @@
         </is>
       </c>
       <c r="K19" t="n">
-        <v>51.76</v>
+        <v>3.22</v>
       </c>
       <c r="L19" t="n">
-        <v>48</v>
+        <v>3.12</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>BRUT</t>
+          <t>INSW</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>whole-company</t>
+          <t>WHOLE-COMPANY (hybrid aggregation)</t>
         </is>
       </c>
       <c r="C20" t="n">
-        <v>8.800000000000001</v>
+        <v>57.91</v>
       </c>
       <c r="D20" t="n">
-        <v>8.800000000000001</v>
+        <v>52.59</v>
       </c>
       <c r="E20" t="n">
-        <v>0</v>
+        <v>-9.18</v>
       </c>
       <c r="F20" t="n">
-        <v>-37.8</v>
+        <v>-37.2</v>
       </c>
       <c r="G20" t="n">
-        <v>-39.7</v>
+        <v>-41.8</v>
       </c>
       <c r="H20" t="n">
-        <v>-1.9</v>
+        <v>-4.6</v>
       </c>
       <c r="I20" t="inlineStr">
         <is>
@@ -1364,10 +1364,10 @@
         </is>
       </c>
       <c r="K20" t="n">
-        <v>3.22</v>
+        <v>51.76</v>
       </c>
       <c r="L20" t="n">
-        <v>3.12</v>
+        <v>48</v>
       </c>
     </row>
     <row r="21">
@@ -1391,13 +1391,13 @@
         <v>-14.93</v>
       </c>
       <c r="F21" t="n">
-        <v>-38.4</v>
+        <v>-41.9</v>
       </c>
       <c r="G21" t="n">
-        <v>-47.6</v>
+        <v>-50.6</v>
       </c>
       <c r="H21" t="n">
-        <v>-9.199999999999999</v>
+        <v>-8.699999999999999</v>
       </c>
       <c r="I21" t="inlineStr">
         <is>
@@ -1437,13 +1437,13 @@
         <v>-14.98</v>
       </c>
       <c r="F22" t="n">
-        <v>-39.6</v>
+        <v>-43.2</v>
       </c>
       <c r="G22" t="n">
-        <v>-48.5</v>
+        <v>-51.6</v>
       </c>
       <c r="H22" t="n">
-        <v>-8.9</v>
+        <v>-8.4</v>
       </c>
       <c r="I22" t="inlineStr">
         <is>
@@ -1483,13 +1483,13 @@
         <v>-15.76</v>
       </c>
       <c r="F23" t="n">
-        <v>-52.9</v>
+        <v>-54.9</v>
       </c>
       <c r="G23" t="n">
-        <v>-59.5</v>
+        <v>-61.2</v>
       </c>
       <c r="H23" t="n">
-        <v>-6.6</v>
+        <v>-6.3</v>
       </c>
       <c r="I23" t="inlineStr">
         <is>

--- a/outputs/transaction_anchor_comparison.xlsx
+++ b/outputs/transaction_anchor_comparison.xlsx
@@ -655,10 +655,10 @@
         <v>-1.43</v>
       </c>
       <c r="F5" t="n">
-        <v>15</v>
+        <v>13.5</v>
       </c>
       <c r="G5" t="n">
-        <v>13.6</v>
+        <v>12.1</v>
       </c>
       <c r="H5" t="n">
         <v>-1.4</v>
@@ -793,10 +793,10 @@
         <v>0</v>
       </c>
       <c r="F8" t="n">
-        <v>6.5</v>
+        <v>6.4</v>
       </c>
       <c r="G8" t="n">
-        <v>6.5</v>
+        <v>6.4</v>
       </c>
       <c r="H8" t="n">
         <v>0</v>
@@ -812,10 +812,10 @@
         </is>
       </c>
       <c r="K8" t="n">
-        <v>40.59</v>
+        <v>40.54</v>
       </c>
       <c r="L8" t="n">
-        <v>40.59</v>
+        <v>40.54</v>
       </c>
     </row>
     <row r="9">
@@ -1072,7 +1072,7 @@
         <v>-8.800000000000001</v>
       </c>
       <c r="G14" t="n">
-        <v>-8.4</v>
+        <v>-8.300000000000001</v>
       </c>
       <c r="H14" t="n">
         <v>0.5</v>
@@ -1091,7 +1091,7 @@
         <v>13.27</v>
       </c>
       <c r="L14" t="n">
-        <v>13.34</v>
+        <v>13.35</v>
       </c>
     </row>
     <row r="15">
@@ -1106,19 +1106,19 @@
         </is>
       </c>
       <c r="C15" t="n">
-        <v>2.02</v>
+        <v>2.04</v>
       </c>
       <c r="D15" t="n">
-        <v>2.02</v>
+        <v>2.04</v>
       </c>
       <c r="E15" t="n">
         <v>0</v>
       </c>
       <c r="F15" t="n">
-        <v>-13.7</v>
+        <v>-18.1</v>
       </c>
       <c r="G15" t="n">
-        <v>-13.7</v>
+        <v>-18.1</v>
       </c>
       <c r="H15" t="n">
         <v>0</v>
@@ -1134,10 +1134,10 @@
         </is>
       </c>
       <c r="K15" t="n">
-        <v>2.11</v>
+        <v>2.06</v>
       </c>
       <c r="L15" t="n">
-        <v>2.11</v>
+        <v>2.06</v>
       </c>
     </row>
     <row r="16">
@@ -1207,13 +1207,13 @@
         <v>-0.74</v>
       </c>
       <c r="F17" t="n">
-        <v>-22.6</v>
+        <v>-24.9</v>
       </c>
       <c r="G17" t="n">
-        <v>-24.2</v>
+        <v>-26.4</v>
       </c>
       <c r="H17" t="n">
-        <v>-1.6</v>
+        <v>-1.5</v>
       </c>
       <c r="I17" t="inlineStr">
         <is>
@@ -1299,10 +1299,10 @@
         <v>0</v>
       </c>
       <c r="F19" t="n">
-        <v>-39.2</v>
+        <v>-39.5</v>
       </c>
       <c r="G19" t="n">
-        <v>-41</v>
+        <v>-41.4</v>
       </c>
       <c r="H19" t="n">
         <v>-1.9</v>

--- a/outputs/transaction_anchor_comparison.xlsx
+++ b/outputs/transaction_anchor_comparison.xlsx
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L23"/>
+  <dimension ref="A1:L25"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="8" customWidth="1" min="1" max="1"/>
@@ -517,10 +517,10 @@
         <v>0</v>
       </c>
       <c r="F2" t="n">
-        <v>55.1</v>
+        <v>49</v>
       </c>
       <c r="G2" t="n">
-        <v>55.1</v>
+        <v>49</v>
       </c>
       <c r="H2" t="n">
         <v>0</v>
@@ -563,13 +563,13 @@
         <v>4.09</v>
       </c>
       <c r="F3" t="n">
-        <v>47.2</v>
+        <v>40.6</v>
       </c>
       <c r="G3" t="n">
-        <v>53.4</v>
+        <v>46.6</v>
       </c>
       <c r="H3" t="n">
-        <v>6.2</v>
+        <v>5.9</v>
       </c>
       <c r="I3" t="inlineStr">
         <is>
@@ -609,13 +609,13 @@
         <v>-8.51</v>
       </c>
       <c r="F4" t="n">
-        <v>47.6</v>
+        <v>44.3</v>
       </c>
       <c r="G4" t="n">
-        <v>36.3</v>
+        <v>33.2</v>
       </c>
       <c r="H4" t="n">
-        <v>-11.3</v>
+        <v>-11.1</v>
       </c>
       <c r="I4" t="inlineStr">
         <is>
@@ -655,10 +655,10 @@
         <v>-1.43</v>
       </c>
       <c r="F5" t="n">
-        <v>13.5</v>
+        <v>10.3</v>
       </c>
       <c r="G5" t="n">
-        <v>12.1</v>
+        <v>8.9</v>
       </c>
       <c r="H5" t="n">
         <v>-1.4</v>
@@ -701,13 +701,13 @@
         <v>-2.45</v>
       </c>
       <c r="F6" t="n">
-        <v>14.5</v>
+        <v>9.1</v>
       </c>
       <c r="G6" t="n">
-        <v>11.9</v>
+        <v>6.6</v>
       </c>
       <c r="H6" t="n">
-        <v>-2.6</v>
+        <v>-2.5</v>
       </c>
       <c r="I6" t="inlineStr">
         <is>
@@ -747,10 +747,10 @@
         <v>-0.13</v>
       </c>
       <c r="F7" t="n">
-        <v>9.699999999999999</v>
+        <v>6.4</v>
       </c>
       <c r="G7" t="n">
-        <v>9.6</v>
+        <v>6.3</v>
       </c>
       <c r="H7" t="n">
         <v>-0.1</v>
@@ -793,22 +793,22 @@
         <v>0</v>
       </c>
       <c r="F8" t="n">
-        <v>6.4</v>
+        <v>2.8</v>
       </c>
       <c r="G8" t="n">
-        <v>6.4</v>
+        <v>2.8</v>
       </c>
       <c r="H8" t="n">
         <v>0</v>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>BUY (undervalued)</t>
+          <t>HOLD (fairly valued)</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>BUY (undervalued)</t>
+          <t>HOLD (fairly valued)</t>
         </is>
       </c>
       <c r="K8" t="n">
@@ -839,10 +839,10 @@
         <v>-4.11</v>
       </c>
       <c r="F9" t="n">
-        <v>7.2</v>
+        <v>5.8</v>
       </c>
       <c r="G9" t="n">
-        <v>3.4</v>
+        <v>2.1</v>
       </c>
       <c r="H9" t="n">
         <v>-3.7</v>
@@ -867,7 +867,7 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>TNK</t>
+          <t>FLNG</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -876,26 +876,26 @@
         </is>
       </c>
       <c r="C10" t="n">
-        <v>83.31999999999999</v>
+        <v>28.45</v>
       </c>
       <c r="D10" t="n">
-        <v>77.51000000000001</v>
+        <v>28.45</v>
       </c>
       <c r="E10" t="n">
-        <v>-6.97</v>
+        <v>0</v>
       </c>
       <c r="F10" t="n">
-        <v>5.9</v>
+        <v>0.1</v>
       </c>
       <c r="G10" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="H10" t="n">
         <v>0</v>
       </c>
-      <c r="H10" t="n">
-        <v>-5.9</v>
-      </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>BUY (undervalued)</t>
+          <t>HOLD (fairly valued)</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
@@ -904,16 +904,16 @@
         </is>
       </c>
       <c r="K10" t="n">
-        <v>71.58</v>
+        <v>29.19</v>
       </c>
       <c r="L10" t="n">
-        <v>67.61</v>
+        <v>29.19</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>FLNG</t>
+          <t>TNK</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -922,22 +922,22 @@
         </is>
       </c>
       <c r="C11" t="n">
-        <v>28.45</v>
+        <v>83.31999999999999</v>
       </c>
       <c r="D11" t="n">
-        <v>28.45</v>
+        <v>77.51000000000001</v>
       </c>
       <c r="E11" t="n">
-        <v>0</v>
+        <v>-6.97</v>
       </c>
       <c r="F11" t="n">
-        <v>-0.4</v>
+        <v>3.3</v>
       </c>
       <c r="G11" t="n">
-        <v>-0.4</v>
+        <v>-2.4</v>
       </c>
       <c r="H11" t="n">
-        <v>0</v>
+        <v>-5.7</v>
       </c>
       <c r="I11" t="inlineStr">
         <is>
@@ -950,16 +950,16 @@
         </is>
       </c>
       <c r="K11" t="n">
-        <v>29.19</v>
+        <v>71.58</v>
       </c>
       <c r="L11" t="n">
-        <v>29.19</v>
+        <v>67.61</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>STNG</t>
+          <t>GNK</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -968,22 +968,22 @@
         </is>
       </c>
       <c r="C12" t="n">
-        <v>80.97</v>
+        <v>25.53</v>
       </c>
       <c r="D12" t="n">
-        <v>77.47</v>
+        <v>24.69</v>
       </c>
       <c r="E12" t="n">
-        <v>-4.33</v>
+        <v>-3.28</v>
       </c>
       <c r="F12" t="n">
-        <v>1.1</v>
+        <v>-0.1</v>
       </c>
       <c r="G12" t="n">
-        <v>-2.9</v>
+        <v>-3.1</v>
       </c>
       <c r="H12" t="n">
-        <v>-4</v>
+        <v>-3</v>
       </c>
       <c r="I12" t="inlineStr">
         <is>
@@ -996,16 +996,16 @@
         </is>
       </c>
       <c r="K12" t="n">
-        <v>73.81</v>
+        <v>24.28</v>
       </c>
       <c r="L12" t="n">
-        <v>70.90000000000001</v>
+        <v>23.56</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>GNK</t>
+          <t>STNG</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -1014,22 +1014,22 @@
         </is>
       </c>
       <c r="C13" t="n">
-        <v>25.53</v>
+        <v>80.97</v>
       </c>
       <c r="D13" t="n">
-        <v>24.69</v>
+        <v>77.47</v>
       </c>
       <c r="E13" t="n">
-        <v>-3.28</v>
+        <v>-4.33</v>
       </c>
       <c r="F13" t="n">
-        <v>-0.9</v>
+        <v>-3.2</v>
       </c>
       <c r="G13" t="n">
-        <v>-3.9</v>
+        <v>-7</v>
       </c>
       <c r="H13" t="n">
-        <v>-3</v>
+        <v>-3.8</v>
       </c>
       <c r="I13" t="inlineStr">
         <is>
@@ -1038,14 +1038,14 @@
       </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t>HOLD (fairly valued)</t>
+          <t>TRIM/SHORT (overvalued)</t>
         </is>
       </c>
       <c r="K13" t="n">
-        <v>24.28</v>
+        <v>73.81</v>
       </c>
       <c r="L13" t="n">
-        <v>23.56</v>
+        <v>70.90000000000001</v>
       </c>
     </row>
     <row r="14">
@@ -1069,10 +1069,10 @@
         <v>0.18</v>
       </c>
       <c r="F14" t="n">
-        <v>-8.800000000000001</v>
+        <v>-11.1</v>
       </c>
       <c r="G14" t="n">
-        <v>-8.300000000000001</v>
+        <v>-10.6</v>
       </c>
       <c r="H14" t="n">
         <v>0.5</v>
@@ -1097,7 +1097,7 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>MPCC</t>
+          <t>LPG</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1106,22 +1106,22 @@
         </is>
       </c>
       <c r="C15" t="n">
-        <v>2.04</v>
+        <v>34.12</v>
       </c>
       <c r="D15" t="n">
-        <v>2.04</v>
+        <v>34.11</v>
       </c>
       <c r="E15" t="n">
-        <v>0</v>
+        <v>-0.05</v>
       </c>
       <c r="F15" t="n">
-        <v>-18.1</v>
+        <v>-15.1</v>
       </c>
       <c r="G15" t="n">
-        <v>-18.1</v>
+        <v>-15.1</v>
       </c>
       <c r="H15" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="I15" t="inlineStr">
         <is>
@@ -1134,16 +1134,16 @@
         </is>
       </c>
       <c r="K15" t="n">
-        <v>2.06</v>
+        <v>30.56</v>
       </c>
       <c r="L15" t="n">
-        <v>2.06</v>
+        <v>30.55</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>HAFN</t>
+          <t>MPCC</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1152,22 +1152,22 @@
         </is>
       </c>
       <c r="C16" t="n">
-        <v>5.69</v>
+        <v>2.04</v>
       </c>
       <c r="D16" t="n">
-        <v>5.57</v>
+        <v>2.04</v>
       </c>
       <c r="E16" t="n">
-        <v>-2.07</v>
+        <v>0</v>
       </c>
       <c r="F16" t="n">
-        <v>-18.8</v>
+        <v>-17.1</v>
       </c>
       <c r="G16" t="n">
-        <v>-20.1</v>
+        <v>-17.1</v>
       </c>
       <c r="H16" t="n">
-        <v>-1.3</v>
+        <v>0</v>
       </c>
       <c r="I16" t="inlineStr">
         <is>
@@ -1180,16 +1180,16 @@
         </is>
       </c>
       <c r="K16" t="n">
-        <v>5.7</v>
+        <v>2.06</v>
       </c>
       <c r="L16" t="n">
-        <v>5.61</v>
+        <v>2.06</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>CAPT</t>
+          <t>HAFN</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1198,22 +1198,22 @@
         </is>
       </c>
       <c r="C17" t="n">
-        <v>15.61</v>
+        <v>5.69</v>
       </c>
       <c r="D17" t="n">
-        <v>15.49</v>
+        <v>5.57</v>
       </c>
       <c r="E17" t="n">
-        <v>-0.74</v>
+        <v>-2.07</v>
       </c>
       <c r="F17" t="n">
-        <v>-24.9</v>
+        <v>-18.8</v>
       </c>
       <c r="G17" t="n">
-        <v>-26.4</v>
+        <v>-20.1</v>
       </c>
       <c r="H17" t="n">
-        <v>-1.5</v>
+        <v>-1.3</v>
       </c>
       <c r="I17" t="inlineStr">
         <is>
@@ -1226,16 +1226,16 @@
         </is>
       </c>
       <c r="K17" t="n">
-        <v>10.27</v>
+        <v>5.7</v>
       </c>
       <c r="L17" t="n">
-        <v>10.07</v>
+        <v>5.61</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>DHT</t>
+          <t>BWLP</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1244,22 +1244,22 @@
         </is>
       </c>
       <c r="C18" t="n">
-        <v>16.07</v>
+        <v>15.81</v>
       </c>
       <c r="D18" t="n">
-        <v>13.88</v>
+        <v>15.8</v>
       </c>
       <c r="E18" t="n">
-        <v>-13.65</v>
+        <v>-0.07000000000000001</v>
       </c>
       <c r="F18" t="n">
-        <v>-24.7</v>
+        <v>-21.9</v>
       </c>
       <c r="G18" t="n">
-        <v>-33.9</v>
+        <v>-21.9</v>
       </c>
       <c r="H18" t="n">
-        <v>-9.199999999999999</v>
+        <v>-0</v>
       </c>
       <c r="I18" t="inlineStr">
         <is>
@@ -1272,16 +1272,16 @@
         </is>
       </c>
       <c r="K18" t="n">
-        <v>12.94</v>
+        <v>14.47</v>
       </c>
       <c r="L18" t="n">
-        <v>11.35</v>
+        <v>14.46</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>BRUT</t>
+          <t>CAPT</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1290,22 +1290,22 @@
         </is>
       </c>
       <c r="C19" t="n">
-        <v>8.800000000000001</v>
+        <v>15.61</v>
       </c>
       <c r="D19" t="n">
-        <v>8.800000000000001</v>
+        <v>15.49</v>
       </c>
       <c r="E19" t="n">
-        <v>0</v>
+        <v>-0.74</v>
       </c>
       <c r="F19" t="n">
-        <v>-39.5</v>
+        <v>-21.3</v>
       </c>
       <c r="G19" t="n">
-        <v>-41.4</v>
+        <v>-22.9</v>
       </c>
       <c r="H19" t="n">
-        <v>-1.9</v>
+        <v>-1.6</v>
       </c>
       <c r="I19" t="inlineStr">
         <is>
@@ -1318,40 +1318,40 @@
         </is>
       </c>
       <c r="K19" t="n">
-        <v>3.22</v>
+        <v>10.27</v>
       </c>
       <c r="L19" t="n">
-        <v>3.12</v>
+        <v>10.07</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>INSW</t>
+          <t>DHT</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>WHOLE-COMPANY (hybrid aggregation)</t>
+          <t>whole-company</t>
         </is>
       </c>
       <c r="C20" t="n">
-        <v>57.91</v>
+        <v>16.07</v>
       </c>
       <c r="D20" t="n">
-        <v>52.59</v>
+        <v>13.88</v>
       </c>
       <c r="E20" t="n">
-        <v>-9.18</v>
+        <v>-13.65</v>
       </c>
       <c r="F20" t="n">
-        <v>-37.2</v>
+        <v>-23.6</v>
       </c>
       <c r="G20" t="n">
-        <v>-41.8</v>
+        <v>-33</v>
       </c>
       <c r="H20" t="n">
-        <v>-4.6</v>
+        <v>-9.4</v>
       </c>
       <c r="I20" t="inlineStr">
         <is>
@@ -1364,40 +1364,40 @@
         </is>
       </c>
       <c r="K20" t="n">
-        <v>51.76</v>
+        <v>12.94</v>
       </c>
       <c r="L20" t="n">
-        <v>48</v>
+        <v>11.35</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>FRO</t>
+          <t>INSW</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>whole-company</t>
+          <t>WHOLE-COMPANY (hybrid aggregation)</t>
         </is>
       </c>
       <c r="C21" t="n">
-        <v>28.47</v>
+        <v>57.91</v>
       </c>
       <c r="D21" t="n">
-        <v>24.22</v>
+        <v>52.59</v>
       </c>
       <c r="E21" t="n">
-        <v>-14.93</v>
+        <v>-9.18</v>
       </c>
       <c r="F21" t="n">
-        <v>-41.9</v>
+        <v>-37.6</v>
       </c>
       <c r="G21" t="n">
-        <v>-50.6</v>
+        <v>-42.2</v>
       </c>
       <c r="H21" t="n">
-        <v>-8.699999999999999</v>
+        <v>-4.5</v>
       </c>
       <c r="I21" t="inlineStr">
         <is>
@@ -1410,16 +1410,16 @@
         </is>
       </c>
       <c r="K21" t="n">
-        <v>21.37</v>
+        <v>51.76</v>
       </c>
       <c r="L21" t="n">
-        <v>18.17</v>
+        <v>48</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>ECO</t>
+          <t>BRUT</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -1428,22 +1428,22 @@
         </is>
       </c>
       <c r="C22" t="n">
-        <v>40.4</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="D22" t="n">
-        <v>34.35</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="E22" t="n">
-        <v>-14.98</v>
+        <v>0</v>
       </c>
       <c r="F22" t="n">
         <v>-43.2</v>
       </c>
       <c r="G22" t="n">
-        <v>-51.6</v>
+        <v>-44.9</v>
       </c>
       <c r="H22" t="n">
-        <v>-8.4</v>
+        <v>-1.7</v>
       </c>
       <c r="I22" t="inlineStr">
         <is>
@@ -1456,55 +1456,147 @@
         </is>
       </c>
       <c r="K22" t="n">
-        <v>30.18</v>
+        <v>3.22</v>
       </c>
       <c r="L22" t="n">
-        <v>25.73</v>
+        <v>3.12</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
+          <t>FRO</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>whole-company</t>
+        </is>
+      </c>
+      <c r="C23" t="n">
+        <v>28.47</v>
+      </c>
+      <c r="D23" t="n">
+        <v>24.22</v>
+      </c>
+      <c r="E23" t="n">
+        <v>-14.93</v>
+      </c>
+      <c r="F23" t="n">
+        <v>-41.5</v>
+      </c>
+      <c r="G23" t="n">
+        <v>-50.3</v>
+      </c>
+      <c r="H23" t="n">
+        <v>-8.699999999999999</v>
+      </c>
+      <c r="I23" t="inlineStr">
+        <is>
+          <t>TRIM/SHORT (overvalued)</t>
+        </is>
+      </c>
+      <c r="J23" t="inlineStr">
+        <is>
+          <t>TRIM/SHORT (overvalued)</t>
+        </is>
+      </c>
+      <c r="K23" t="n">
+        <v>21.37</v>
+      </c>
+      <c r="L23" t="n">
+        <v>18.17</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>ECO</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>whole-company</t>
+        </is>
+      </c>
+      <c r="C24" t="n">
+        <v>40.4</v>
+      </c>
+      <c r="D24" t="n">
+        <v>34.35</v>
+      </c>
+      <c r="E24" t="n">
+        <v>-14.98</v>
+      </c>
+      <c r="F24" t="n">
+        <v>-42.2</v>
+      </c>
+      <c r="G24" t="n">
+        <v>-50.7</v>
+      </c>
+      <c r="H24" t="n">
+        <v>-8.5</v>
+      </c>
+      <c r="I24" t="inlineStr">
+        <is>
+          <t>TRIM/SHORT (overvalued)</t>
+        </is>
+      </c>
+      <c r="J24" t="inlineStr">
+        <is>
+          <t>TRIM/SHORT (overvalued)</t>
+        </is>
+      </c>
+      <c r="K24" t="n">
+        <v>30.18</v>
+      </c>
+      <c r="L24" t="n">
+        <v>25.73</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
           <t>NAT</t>
         </is>
       </c>
-      <c r="B23" t="inlineStr">
-        <is>
-          <t>whole-company</t>
-        </is>
-      </c>
-      <c r="C23" t="n">
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>whole-company</t>
+        </is>
+      </c>
+      <c r="C25" t="n">
         <v>3.32</v>
       </c>
-      <c r="D23" t="n">
+      <c r="D25" t="n">
         <v>2.79</v>
       </c>
-      <c r="E23" t="n">
+      <c r="E25" t="n">
         <v>-15.76</v>
       </c>
-      <c r="F23" t="n">
-        <v>-54.9</v>
-      </c>
-      <c r="G23" t="n">
-        <v>-61.2</v>
-      </c>
-      <c r="H23" t="n">
-        <v>-6.3</v>
-      </c>
-      <c r="I23" t="inlineStr">
-        <is>
-          <t>TRIM/SHORT (overvalued)</t>
-        </is>
-      </c>
-      <c r="J23" t="inlineStr">
-        <is>
-          <t>TRIM/SHORT (overvalued)</t>
-        </is>
-      </c>
-      <c r="K23" t="n">
+      <c r="F25" t="n">
+        <v>-55.6</v>
+      </c>
+      <c r="G25" t="n">
+        <v>-61.8</v>
+      </c>
+      <c r="H25" t="n">
+        <v>-6.2</v>
+      </c>
+      <c r="I25" t="inlineStr">
+        <is>
+          <t>TRIM/SHORT (overvalued)</t>
+        </is>
+      </c>
+      <c r="J25" t="inlineStr">
+        <is>
+          <t>TRIM/SHORT (overvalued)</t>
+        </is>
+      </c>
+      <c r="K25" t="n">
         <v>2.62</v>
       </c>
-      <c r="L23" t="n">
+      <c r="L25" t="n">
         <v>2.25</v>
       </c>
     </row>

--- a/outputs/transaction_anchor_comparison.xlsx
+++ b/outputs/transaction_anchor_comparison.xlsx
@@ -517,10 +517,10 @@
         <v>0</v>
       </c>
       <c r="F2" t="n">
-        <v>49</v>
+        <v>50.2</v>
       </c>
       <c r="G2" t="n">
-        <v>49</v>
+        <v>50.2</v>
       </c>
       <c r="H2" t="n">
         <v>0</v>
@@ -563,13 +563,13 @@
         <v>4.09</v>
       </c>
       <c r="F3" t="n">
-        <v>40.6</v>
+        <v>36.5</v>
       </c>
       <c r="G3" t="n">
-        <v>46.6</v>
+        <v>42.3</v>
       </c>
       <c r="H3" t="n">
-        <v>5.9</v>
+        <v>5.8</v>
       </c>
       <c r="I3" t="inlineStr">
         <is>
@@ -609,13 +609,13 @@
         <v>-8.51</v>
       </c>
       <c r="F4" t="n">
-        <v>44.3</v>
+        <v>54</v>
       </c>
       <c r="G4" t="n">
-        <v>33.2</v>
+        <v>42.1</v>
       </c>
       <c r="H4" t="n">
-        <v>-11.1</v>
+        <v>-11.9</v>
       </c>
       <c r="I4" t="inlineStr">
         <is>
@@ -628,16 +628,16 @@
         </is>
       </c>
       <c r="K4" t="n">
-        <v>55.15</v>
+        <v>61.09</v>
       </c>
       <c r="L4" t="n">
-        <v>50.92</v>
+        <v>56.36</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>SBLK</t>
+          <t>BRUT</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -646,22 +646,22 @@
         </is>
       </c>
       <c r="C5" t="n">
-        <v>29.77</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="D5" t="n">
-        <v>29.34</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="E5" t="n">
-        <v>-1.43</v>
+        <v>0</v>
       </c>
       <c r="F5" t="n">
-        <v>10.3</v>
+        <v>13.2</v>
       </c>
       <c r="G5" t="n">
-        <v>8.9</v>
+        <v>11.2</v>
       </c>
       <c r="H5" t="n">
-        <v>-1.4</v>
+        <v>-2</v>
       </c>
       <c r="I5" t="inlineStr">
         <is>
@@ -674,16 +674,16 @@
         </is>
       </c>
       <c r="K5" t="n">
-        <v>28.54</v>
+        <v>6.32</v>
       </c>
       <c r="L5" t="n">
-        <v>28.19</v>
+        <v>6.2</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>CMDB</t>
+          <t>SBLK</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -692,22 +692,22 @@
         </is>
       </c>
       <c r="C6" t="n">
-        <v>32.12</v>
+        <v>29.77</v>
       </c>
       <c r="D6" t="n">
-        <v>31.33</v>
+        <v>29.34</v>
       </c>
       <c r="E6" t="n">
-        <v>-2.45</v>
+        <v>-1.43</v>
       </c>
       <c r="F6" t="n">
-        <v>9.1</v>
+        <v>8.300000000000001</v>
       </c>
       <c r="G6" t="n">
-        <v>6.6</v>
+        <v>7</v>
       </c>
       <c r="H6" t="n">
-        <v>-2.5</v>
+        <v>-1.3</v>
       </c>
       <c r="I6" t="inlineStr">
         <is>
@@ -720,16 +720,16 @@
         </is>
       </c>
       <c r="K6" t="n">
-        <v>20.82</v>
+        <v>28.54</v>
       </c>
       <c r="L6" t="n">
-        <v>20.34</v>
+        <v>28.19</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>ASC</t>
+          <t>CMDB</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -738,22 +738,22 @@
         </is>
       </c>
       <c r="C7" t="n">
-        <v>17.82</v>
+        <v>32.12</v>
       </c>
       <c r="D7" t="n">
-        <v>17.8</v>
+        <v>31.33</v>
       </c>
       <c r="E7" t="n">
-        <v>-0.13</v>
+        <v>-2.45</v>
       </c>
       <c r="F7" t="n">
-        <v>6.4</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="G7" t="n">
-        <v>6.3</v>
+        <v>6.7</v>
       </c>
       <c r="H7" t="n">
-        <v>-0.1</v>
+        <v>-2.5</v>
       </c>
       <c r="I7" t="inlineStr">
         <is>
@@ -766,10 +766,10 @@
         </is>
       </c>
       <c r="K7" t="n">
-        <v>16.3</v>
+        <v>20.82</v>
       </c>
       <c r="L7" t="n">
-        <v>16.28</v>
+        <v>20.34</v>
       </c>
     </row>
     <row r="8">
@@ -793,10 +793,10 @@
         <v>0</v>
       </c>
       <c r="F8" t="n">
-        <v>2.8</v>
+        <v>1.2</v>
       </c>
       <c r="G8" t="n">
-        <v>2.8</v>
+        <v>1.2</v>
       </c>
       <c r="H8" t="n">
         <v>0</v>
@@ -821,7 +821,7 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>TRMD</t>
+          <t>CAPT</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -830,26 +830,26 @@
         </is>
       </c>
       <c r="C9" t="n">
-        <v>31.65</v>
+        <v>15.61</v>
       </c>
       <c r="D9" t="n">
-        <v>30.34</v>
+        <v>15.49</v>
       </c>
       <c r="E9" t="n">
-        <v>-4.11</v>
+        <v>-0.74</v>
       </c>
       <c r="F9" t="n">
-        <v>5.8</v>
+        <v>2.8</v>
       </c>
       <c r="G9" t="n">
-        <v>2.1</v>
+        <v>1.1</v>
       </c>
       <c r="H9" t="n">
-        <v>-3.7</v>
+        <v>-1.7</v>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>BUY (undervalued)</t>
+          <t>HOLD (fairly valued)</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
@@ -858,16 +858,16 @@
         </is>
       </c>
       <c r="K9" t="n">
-        <v>29.68</v>
+        <v>13.37</v>
       </c>
       <c r="L9" t="n">
-        <v>28.65</v>
+        <v>13.14</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>FLNG</t>
+          <t>TNK</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -876,44 +876,44 @@
         </is>
       </c>
       <c r="C10" t="n">
-        <v>28.45</v>
+        <v>83.31999999999999</v>
       </c>
       <c r="D10" t="n">
-        <v>28.45</v>
+        <v>77.51000000000001</v>
       </c>
       <c r="E10" t="n">
-        <v>0</v>
+        <v>-6.97</v>
       </c>
       <c r="F10" t="n">
-        <v>0.1</v>
+        <v>7.2</v>
       </c>
       <c r="G10" t="n">
-        <v>0.1</v>
+        <v>1</v>
       </c>
       <c r="H10" t="n">
-        <v>0</v>
+        <v>-6.2</v>
       </c>
       <c r="I10" t="inlineStr">
         <is>
+          <t>BUY (undervalued)</t>
+        </is>
+      </c>
+      <c r="J10" t="inlineStr">
+        <is>
           <t>HOLD (fairly valued)</t>
         </is>
       </c>
-      <c r="J10" t="inlineStr">
-        <is>
-          <t>HOLD (fairly valued)</t>
-        </is>
-      </c>
       <c r="K10" t="n">
-        <v>29.19</v>
+        <v>77.67</v>
       </c>
       <c r="L10" t="n">
-        <v>29.19</v>
+        <v>73.18000000000001</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>TNK</t>
+          <t>ASC</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -922,22 +922,22 @@
         </is>
       </c>
       <c r="C11" t="n">
-        <v>83.31999999999999</v>
+        <v>17.82</v>
       </c>
       <c r="D11" t="n">
-        <v>77.51000000000001</v>
+        <v>17.8</v>
       </c>
       <c r="E11" t="n">
-        <v>-6.97</v>
+        <v>-0.13</v>
       </c>
       <c r="F11" t="n">
-        <v>3.3</v>
+        <v>-0.5</v>
       </c>
       <c r="G11" t="n">
-        <v>-2.4</v>
+        <v>-0.7</v>
       </c>
       <c r="H11" t="n">
-        <v>-5.7</v>
+        <v>-0.1</v>
       </c>
       <c r="I11" t="inlineStr">
         <is>
@@ -950,16 +950,16 @@
         </is>
       </c>
       <c r="K11" t="n">
-        <v>71.58</v>
+        <v>16.3</v>
       </c>
       <c r="L11" t="n">
-        <v>67.61</v>
+        <v>16.28</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>GNK</t>
+          <t>FLNG</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -968,22 +968,22 @@
         </is>
       </c>
       <c r="C12" t="n">
-        <v>25.53</v>
+        <v>28.45</v>
       </c>
       <c r="D12" t="n">
-        <v>24.69</v>
+        <v>28.45</v>
       </c>
       <c r="E12" t="n">
-        <v>-3.28</v>
+        <v>0</v>
       </c>
       <c r="F12" t="n">
-        <v>-0.1</v>
+        <v>-2.7</v>
       </c>
       <c r="G12" t="n">
-        <v>-3.1</v>
+        <v>-2.7</v>
       </c>
       <c r="H12" t="n">
-        <v>-3</v>
+        <v>0</v>
       </c>
       <c r="I12" t="inlineStr">
         <is>
@@ -996,16 +996,16 @@
         </is>
       </c>
       <c r="K12" t="n">
-        <v>24.28</v>
+        <v>29.19</v>
       </c>
       <c r="L12" t="n">
-        <v>23.56</v>
+        <v>29.19</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>STNG</t>
+          <t>TRMD</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -1014,22 +1014,22 @@
         </is>
       </c>
       <c r="C13" t="n">
-        <v>80.97</v>
+        <v>31.65</v>
       </c>
       <c r="D13" t="n">
-        <v>77.47</v>
+        <v>30.34</v>
       </c>
       <c r="E13" t="n">
-        <v>-4.33</v>
+        <v>-4.11</v>
       </c>
       <c r="F13" t="n">
-        <v>-3.2</v>
+        <v>0.7</v>
       </c>
       <c r="G13" t="n">
-        <v>-7</v>
+        <v>-2.8</v>
       </c>
       <c r="H13" t="n">
-        <v>-3.8</v>
+        <v>-3.5</v>
       </c>
       <c r="I13" t="inlineStr">
         <is>
@@ -1038,48 +1038,48 @@
       </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t>TRIM/SHORT (overvalued)</t>
+          <t>HOLD (fairly valued)</t>
         </is>
       </c>
       <c r="K13" t="n">
-        <v>73.81</v>
+        <v>29.68</v>
       </c>
       <c r="L13" t="n">
-        <v>70.90000000000001</v>
+        <v>28.65</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>CMBT</t>
+          <t>GNK</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>WHOLE-COMPANY (hybrid aggregation)</t>
+          <t>whole-company</t>
         </is>
       </c>
       <c r="C14" t="n">
-        <v>15.84</v>
+        <v>25.53</v>
       </c>
       <c r="D14" t="n">
-        <v>15.87</v>
+        <v>24.69</v>
       </c>
       <c r="E14" t="n">
-        <v>0.18</v>
+        <v>-3.28</v>
       </c>
       <c r="F14" t="n">
-        <v>-11.1</v>
+        <v>-4.8</v>
       </c>
       <c r="G14" t="n">
-        <v>-10.6</v>
+        <v>-7.7</v>
       </c>
       <c r="H14" t="n">
-        <v>0.5</v>
+        <v>-2.9</v>
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>TRIM/SHORT (overvalued)</t>
+          <t>HOLD (fairly valued)</t>
         </is>
       </c>
       <c r="J14" t="inlineStr">
@@ -1088,40 +1088,40 @@
         </is>
       </c>
       <c r="K14" t="n">
-        <v>13.27</v>
+        <v>24.28</v>
       </c>
       <c r="L14" t="n">
-        <v>13.35</v>
+        <v>23.56</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>LPG</t>
+          <t>CMBT</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>whole-company</t>
+          <t>WHOLE-COMPANY (hybrid aggregation)</t>
         </is>
       </c>
       <c r="C15" t="n">
-        <v>34.12</v>
+        <v>15.84</v>
       </c>
       <c r="D15" t="n">
-        <v>34.11</v>
+        <v>15.87</v>
       </c>
       <c r="E15" t="n">
-        <v>-0.05</v>
+        <v>0.18</v>
       </c>
       <c r="F15" t="n">
-        <v>-15.1</v>
+        <v>-9.300000000000001</v>
       </c>
       <c r="G15" t="n">
-        <v>-15.1</v>
+        <v>-9.1</v>
       </c>
       <c r="H15" t="n">
-        <v>-0</v>
+        <v>0.2</v>
       </c>
       <c r="I15" t="inlineStr">
         <is>
@@ -1134,16 +1134,16 @@
         </is>
       </c>
       <c r="K15" t="n">
-        <v>30.56</v>
+        <v>14.12</v>
       </c>
       <c r="L15" t="n">
-        <v>30.55</v>
+        <v>14.15</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>MPCC</t>
+          <t>STNG</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1152,22 +1152,22 @@
         </is>
       </c>
       <c r="C16" t="n">
-        <v>2.04</v>
+        <v>80.97</v>
       </c>
       <c r="D16" t="n">
-        <v>2.04</v>
+        <v>77.47</v>
       </c>
       <c r="E16" t="n">
-        <v>0</v>
+        <v>-4.33</v>
       </c>
       <c r="F16" t="n">
-        <v>-17.1</v>
+        <v>-6.9</v>
       </c>
       <c r="G16" t="n">
-        <v>-17.1</v>
+        <v>-10.6</v>
       </c>
       <c r="H16" t="n">
-        <v>0</v>
+        <v>-3.7</v>
       </c>
       <c r="I16" t="inlineStr">
         <is>
@@ -1180,16 +1180,16 @@
         </is>
       </c>
       <c r="K16" t="n">
-        <v>2.06</v>
+        <v>73.81</v>
       </c>
       <c r="L16" t="n">
-        <v>2.06</v>
+        <v>70.90000000000001</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>HAFN</t>
+          <t>MPCC</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1198,22 +1198,22 @@
         </is>
       </c>
       <c r="C17" t="n">
-        <v>5.69</v>
+        <v>2.04</v>
       </c>
       <c r="D17" t="n">
-        <v>5.57</v>
+        <v>2.04</v>
       </c>
       <c r="E17" t="n">
-        <v>-2.07</v>
+        <v>0</v>
       </c>
       <c r="F17" t="n">
-        <v>-18.8</v>
+        <v>-15.4</v>
       </c>
       <c r="G17" t="n">
-        <v>-20.1</v>
+        <v>-15.4</v>
       </c>
       <c r="H17" t="n">
-        <v>-1.3</v>
+        <v>0</v>
       </c>
       <c r="I17" t="inlineStr">
         <is>
@@ -1226,16 +1226,16 @@
         </is>
       </c>
       <c r="K17" t="n">
-        <v>5.7</v>
+        <v>2.06</v>
       </c>
       <c r="L17" t="n">
-        <v>5.61</v>
+        <v>2.06</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>BWLP</t>
+          <t>HAFN</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1244,22 +1244,22 @@
         </is>
       </c>
       <c r="C18" t="n">
-        <v>15.81</v>
+        <v>5.69</v>
       </c>
       <c r="D18" t="n">
-        <v>15.8</v>
+        <v>5.57</v>
       </c>
       <c r="E18" t="n">
-        <v>-0.07000000000000001</v>
+        <v>-2.07</v>
       </c>
       <c r="F18" t="n">
-        <v>-21.9</v>
+        <v>-21.6</v>
       </c>
       <c r="G18" t="n">
-        <v>-21.9</v>
+        <v>-22.9</v>
       </c>
       <c r="H18" t="n">
-        <v>-0</v>
+        <v>-1.3</v>
       </c>
       <c r="I18" t="inlineStr">
         <is>
@@ -1272,16 +1272,16 @@
         </is>
       </c>
       <c r="K18" t="n">
-        <v>14.47</v>
+        <v>5.7</v>
       </c>
       <c r="L18" t="n">
-        <v>14.46</v>
+        <v>5.61</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>CAPT</t>
+          <t>LPG</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1290,22 +1290,22 @@
         </is>
       </c>
       <c r="C19" t="n">
-        <v>15.61</v>
+        <v>34.12</v>
       </c>
       <c r="D19" t="n">
-        <v>15.49</v>
+        <v>34.11</v>
       </c>
       <c r="E19" t="n">
-        <v>-0.74</v>
+        <v>-0.05</v>
       </c>
       <c r="F19" t="n">
-        <v>-21.3</v>
+        <v>-23.7</v>
       </c>
       <c r="G19" t="n">
-        <v>-22.9</v>
+        <v>-23.7</v>
       </c>
       <c r="H19" t="n">
-        <v>-1.6</v>
+        <v>-0</v>
       </c>
       <c r="I19" t="inlineStr">
         <is>
@@ -1318,10 +1318,10 @@
         </is>
       </c>
       <c r="K19" t="n">
-        <v>10.27</v>
+        <v>30.56</v>
       </c>
       <c r="L19" t="n">
-        <v>10.07</v>
+        <v>30.55</v>
       </c>
     </row>
     <row r="20">
@@ -1345,13 +1345,13 @@
         <v>-13.65</v>
       </c>
       <c r="F20" t="n">
-        <v>-23.6</v>
+        <v>-14.8</v>
       </c>
       <c r="G20" t="n">
-        <v>-33</v>
+        <v>-24.9</v>
       </c>
       <c r="H20" t="n">
-        <v>-9.4</v>
+        <v>-10.1</v>
       </c>
       <c r="I20" t="inlineStr">
         <is>
@@ -1364,40 +1364,40 @@
         </is>
       </c>
       <c r="K20" t="n">
-        <v>12.94</v>
+        <v>15.13</v>
       </c>
       <c r="L20" t="n">
-        <v>11.35</v>
+        <v>13.34</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>INSW</t>
+          <t>BWLP</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>WHOLE-COMPANY (hybrid aggregation)</t>
+          <t>whole-company</t>
         </is>
       </c>
       <c r="C21" t="n">
-        <v>57.91</v>
+        <v>15.81</v>
       </c>
       <c r="D21" t="n">
-        <v>52.59</v>
+        <v>15.8</v>
       </c>
       <c r="E21" t="n">
-        <v>-9.18</v>
+        <v>-0.07000000000000001</v>
       </c>
       <c r="F21" t="n">
-        <v>-37.6</v>
+        <v>-25.6</v>
       </c>
       <c r="G21" t="n">
-        <v>-42.2</v>
+        <v>-25.6</v>
       </c>
       <c r="H21" t="n">
-        <v>-4.5</v>
+        <v>-0</v>
       </c>
       <c r="I21" t="inlineStr">
         <is>
@@ -1410,16 +1410,16 @@
         </is>
       </c>
       <c r="K21" t="n">
-        <v>51.76</v>
+        <v>14.47</v>
       </c>
       <c r="L21" t="n">
-        <v>48</v>
+        <v>14.46</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>BRUT</t>
+          <t>FRO</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -1428,22 +1428,22 @@
         </is>
       </c>
       <c r="C22" t="n">
-        <v>8.800000000000001</v>
+        <v>28.47</v>
       </c>
       <c r="D22" t="n">
-        <v>8.800000000000001</v>
+        <v>24.22</v>
       </c>
       <c r="E22" t="n">
-        <v>0</v>
+        <v>-14.93</v>
       </c>
       <c r="F22" t="n">
-        <v>-43.2</v>
+        <v>-30.5</v>
       </c>
       <c r="G22" t="n">
-        <v>-44.9</v>
+        <v>-39.9</v>
       </c>
       <c r="H22" t="n">
-        <v>-1.7</v>
+        <v>-9.4</v>
       </c>
       <c r="I22" t="inlineStr">
         <is>
@@ -1456,40 +1456,40 @@
         </is>
       </c>
       <c r="K22" t="n">
-        <v>3.22</v>
+        <v>26.5</v>
       </c>
       <c r="L22" t="n">
-        <v>3.12</v>
+        <v>22.91</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>FRO</t>
+          <t>INSW</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>whole-company</t>
+          <t>WHOLE-COMPANY (hybrid aggregation)</t>
         </is>
       </c>
       <c r="C23" t="n">
-        <v>28.47</v>
+        <v>57.91</v>
       </c>
       <c r="D23" t="n">
-        <v>24.22</v>
+        <v>52.59</v>
       </c>
       <c r="E23" t="n">
-        <v>-14.93</v>
+        <v>-9.18</v>
       </c>
       <c r="F23" t="n">
-        <v>-41.5</v>
+        <v>-35.4</v>
       </c>
       <c r="G23" t="n">
-        <v>-50.3</v>
+        <v>-40.2</v>
       </c>
       <c r="H23" t="n">
-        <v>-8.699999999999999</v>
+        <v>-4.8</v>
       </c>
       <c r="I23" t="inlineStr">
         <is>
@@ -1502,10 +1502,10 @@
         </is>
       </c>
       <c r="K23" t="n">
-        <v>21.37</v>
+        <v>57.15</v>
       </c>
       <c r="L23" t="n">
-        <v>18.17</v>
+        <v>52.93</v>
       </c>
     </row>
     <row r="24">
@@ -1529,13 +1529,13 @@
         <v>-14.98</v>
       </c>
       <c r="F24" t="n">
-        <v>-42.2</v>
+        <v>-32.5</v>
       </c>
       <c r="G24" t="n">
-        <v>-50.7</v>
+        <v>-41.6</v>
       </c>
       <c r="H24" t="n">
-        <v>-8.5</v>
+        <v>-9.1</v>
       </c>
       <c r="I24" t="inlineStr">
         <is>
@@ -1548,10 +1548,10 @@
         </is>
       </c>
       <c r="K24" t="n">
-        <v>30.18</v>
+        <v>37.09</v>
       </c>
       <c r="L24" t="n">
-        <v>25.73</v>
+        <v>32.09</v>
       </c>
     </row>
     <row r="25">
@@ -1575,13 +1575,13 @@
         <v>-15.76</v>
       </c>
       <c r="F25" t="n">
-        <v>-55.6</v>
+        <v>-49.3</v>
       </c>
       <c r="G25" t="n">
-        <v>-61.8</v>
+        <v>-56</v>
       </c>
       <c r="H25" t="n">
-        <v>-6.2</v>
+        <v>-6.7</v>
       </c>
       <c r="I25" t="inlineStr">
         <is>
@@ -1594,10 +1594,10 @@
         </is>
       </c>
       <c r="K25" t="n">
-        <v>2.62</v>
+        <v>3.13</v>
       </c>
       <c r="L25" t="n">
-        <v>2.25</v>
+        <v>2.72</v>
       </c>
     </row>
   </sheetData>

--- a/outputs/transaction_anchor_comparison.xlsx
+++ b/outputs/transaction_anchor_comparison.xlsx
@@ -545,7 +545,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>SB</t>
+          <t>TEN</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -554,22 +554,22 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>9.720000000000001</v>
+        <v>96.95</v>
       </c>
       <c r="D3" t="n">
-        <v>10.12</v>
+        <v>88.7</v>
       </c>
       <c r="E3" t="n">
-        <v>4.09</v>
+        <v>-8.51</v>
       </c>
       <c r="F3" t="n">
-        <v>36.5</v>
+        <v>54</v>
       </c>
       <c r="G3" t="n">
-        <v>42.3</v>
+        <v>42.1</v>
       </c>
       <c r="H3" t="n">
-        <v>5.8</v>
+        <v>-11.9</v>
       </c>
       <c r="I3" t="inlineStr">
         <is>
@@ -582,16 +582,16 @@
         </is>
       </c>
       <c r="K3" t="n">
-        <v>9.42</v>
+        <v>61.09</v>
       </c>
       <c r="L3" t="n">
-        <v>9.82</v>
+        <v>56.36</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>TEN</t>
+          <t>SB</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -600,22 +600,22 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>96.95</v>
+        <v>9.720000000000001</v>
       </c>
       <c r="D4" t="n">
-        <v>88.7</v>
+        <v>10.12</v>
       </c>
       <c r="E4" t="n">
-        <v>-8.51</v>
+        <v>4.09</v>
       </c>
       <c r="F4" t="n">
-        <v>54</v>
+        <v>32.9</v>
       </c>
       <c r="G4" t="n">
-        <v>42.1</v>
+        <v>38.6</v>
       </c>
       <c r="H4" t="n">
-        <v>-11.9</v>
+        <v>5.7</v>
       </c>
       <c r="I4" t="inlineStr">
         <is>
@@ -628,10 +628,10 @@
         </is>
       </c>
       <c r="K4" t="n">
-        <v>61.09</v>
+        <v>9.17</v>
       </c>
       <c r="L4" t="n">
-        <v>56.36</v>
+        <v>9.56</v>
       </c>
     </row>
     <row r="5">
@@ -683,7 +683,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>SBLK</t>
+          <t>CMDB</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -692,22 +692,22 @@
         </is>
       </c>
       <c r="C6" t="n">
-        <v>29.77</v>
+        <v>32.12</v>
       </c>
       <c r="D6" t="n">
-        <v>29.34</v>
+        <v>31.33</v>
       </c>
       <c r="E6" t="n">
-        <v>-1.43</v>
+        <v>-2.45</v>
       </c>
       <c r="F6" t="n">
-        <v>8.300000000000001</v>
+        <v>7.9</v>
       </c>
       <c r="G6" t="n">
-        <v>7</v>
+        <v>5.4</v>
       </c>
       <c r="H6" t="n">
-        <v>-1.3</v>
+        <v>-2.5</v>
       </c>
       <c r="I6" t="inlineStr">
         <is>
@@ -720,16 +720,16 @@
         </is>
       </c>
       <c r="K6" t="n">
-        <v>28.54</v>
+        <v>20.57</v>
       </c>
       <c r="L6" t="n">
-        <v>28.19</v>
+        <v>20.1</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>CMDB</t>
+          <t>SBLK</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -738,22 +738,22 @@
         </is>
       </c>
       <c r="C7" t="n">
-        <v>32.12</v>
+        <v>29.77</v>
       </c>
       <c r="D7" t="n">
-        <v>31.33</v>
+        <v>29.34</v>
       </c>
       <c r="E7" t="n">
-        <v>-2.45</v>
+        <v>-1.43</v>
       </c>
       <c r="F7" t="n">
-        <v>9.199999999999999</v>
+        <v>6.4</v>
       </c>
       <c r="G7" t="n">
-        <v>6.7</v>
+        <v>5.1</v>
       </c>
       <c r="H7" t="n">
-        <v>-2.5</v>
+        <v>-1.3</v>
       </c>
       <c r="I7" t="inlineStr">
         <is>
@@ -766,10 +766,10 @@
         </is>
       </c>
       <c r="K7" t="n">
-        <v>20.82</v>
+        <v>28.04</v>
       </c>
       <c r="L7" t="n">
-        <v>20.34</v>
+        <v>27.69</v>
       </c>
     </row>
     <row r="8">
@@ -1069,17 +1069,17 @@
         <v>-3.28</v>
       </c>
       <c r="F14" t="n">
-        <v>-4.8</v>
+        <v>-6.4</v>
       </c>
       <c r="G14" t="n">
-        <v>-7.7</v>
+        <v>-9.199999999999999</v>
       </c>
       <c r="H14" t="n">
-        <v>-2.9</v>
+        <v>-2.8</v>
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>HOLD (fairly valued)</t>
+          <t>TRIM/SHORT (overvalued)</t>
         </is>
       </c>
       <c r="J14" t="inlineStr">
@@ -1088,40 +1088,40 @@
         </is>
       </c>
       <c r="K14" t="n">
-        <v>24.28</v>
+        <v>23.87</v>
       </c>
       <c r="L14" t="n">
-        <v>23.56</v>
+        <v>23.15</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>CMBT</t>
+          <t>STNG</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>WHOLE-COMPANY (hybrid aggregation)</t>
+          <t>whole-company</t>
         </is>
       </c>
       <c r="C15" t="n">
-        <v>15.84</v>
+        <v>80.97</v>
       </c>
       <c r="D15" t="n">
-        <v>15.87</v>
+        <v>77.47</v>
       </c>
       <c r="E15" t="n">
-        <v>0.18</v>
+        <v>-4.33</v>
       </c>
       <c r="F15" t="n">
-        <v>-9.300000000000001</v>
+        <v>-6.9</v>
       </c>
       <c r="G15" t="n">
-        <v>-9.1</v>
+        <v>-10.6</v>
       </c>
       <c r="H15" t="n">
-        <v>0.2</v>
+        <v>-3.7</v>
       </c>
       <c r="I15" t="inlineStr">
         <is>
@@ -1134,40 +1134,40 @@
         </is>
       </c>
       <c r="K15" t="n">
-        <v>14.12</v>
+        <v>73.81</v>
       </c>
       <c r="L15" t="n">
-        <v>14.15</v>
+        <v>70.90000000000001</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>STNG</t>
+          <t>CMBT</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>whole-company</t>
+          <t>WHOLE-COMPANY (hybrid aggregation)</t>
         </is>
       </c>
       <c r="C16" t="n">
-        <v>80.97</v>
+        <v>15.84</v>
       </c>
       <c r="D16" t="n">
-        <v>77.47</v>
+        <v>15.87</v>
       </c>
       <c r="E16" t="n">
-        <v>-4.33</v>
+        <v>0.18</v>
       </c>
       <c r="F16" t="n">
-        <v>-6.9</v>
+        <v>-11.1</v>
       </c>
       <c r="G16" t="n">
-        <v>-10.6</v>
+        <v>-10.9</v>
       </c>
       <c r="H16" t="n">
-        <v>-3.7</v>
+        <v>0.2</v>
       </c>
       <c r="I16" t="inlineStr">
         <is>
@@ -1180,10 +1180,10 @@
         </is>
       </c>
       <c r="K16" t="n">
-        <v>73.81</v>
+        <v>13.85</v>
       </c>
       <c r="L16" t="n">
-        <v>70.90000000000001</v>
+        <v>13.87</v>
       </c>
     </row>
     <row r="17">

--- a/outputs/transaction_anchor_comparison.xlsx
+++ b/outputs/transaction_anchor_comparison.xlsx
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L25"/>
+  <dimension ref="A1:L26"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="8" customWidth="1" min="1" max="1"/>
@@ -517,10 +517,10 @@
         <v>0</v>
       </c>
       <c r="F2" t="n">
-        <v>50.2</v>
+        <v>49.7</v>
       </c>
       <c r="G2" t="n">
-        <v>50.2</v>
+        <v>49.7</v>
       </c>
       <c r="H2" t="n">
         <v>0</v>
@@ -563,13 +563,13 @@
         <v>-8.51</v>
       </c>
       <c r="F3" t="n">
-        <v>54</v>
+        <v>57.3</v>
       </c>
       <c r="G3" t="n">
-        <v>42.1</v>
+        <v>45.1</v>
       </c>
       <c r="H3" t="n">
-        <v>-11.9</v>
+        <v>-12.2</v>
       </c>
       <c r="I3" t="inlineStr">
         <is>
@@ -609,13 +609,13 @@
         <v>4.09</v>
       </c>
       <c r="F4" t="n">
-        <v>32.9</v>
+        <v>31.8</v>
       </c>
       <c r="G4" t="n">
-        <v>38.6</v>
+        <v>37.4</v>
       </c>
       <c r="H4" t="n">
-        <v>5.7</v>
+        <v>5.6</v>
       </c>
       <c r="I4" t="inlineStr">
         <is>
@@ -655,10 +655,10 @@
         <v>0</v>
       </c>
       <c r="F5" t="n">
-        <v>13.2</v>
+        <v>14</v>
       </c>
       <c r="G5" t="n">
-        <v>11.2</v>
+        <v>12</v>
       </c>
       <c r="H5" t="n">
         <v>-2</v>
@@ -683,7 +683,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>CMDB</t>
+          <t>SBLK</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -692,22 +692,22 @@
         </is>
       </c>
       <c r="C6" t="n">
-        <v>32.12</v>
+        <v>29.77</v>
       </c>
       <c r="D6" t="n">
-        <v>31.33</v>
+        <v>29.34</v>
       </c>
       <c r="E6" t="n">
-        <v>-2.45</v>
+        <v>-1.43</v>
       </c>
       <c r="F6" t="n">
-        <v>7.9</v>
+        <v>5.7</v>
       </c>
       <c r="G6" t="n">
-        <v>5.4</v>
+        <v>4.3</v>
       </c>
       <c r="H6" t="n">
-        <v>-2.5</v>
+        <v>-1.3</v>
       </c>
       <c r="I6" t="inlineStr">
         <is>
@@ -716,20 +716,20 @@
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>BUY (undervalued)</t>
+          <t>HOLD (fairly valued)</t>
         </is>
       </c>
       <c r="K6" t="n">
-        <v>20.57</v>
+        <v>28.04</v>
       </c>
       <c r="L6" t="n">
-        <v>20.1</v>
+        <v>27.69</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>SBLK</t>
+          <t>TNK</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -738,22 +738,22 @@
         </is>
       </c>
       <c r="C7" t="n">
-        <v>29.77</v>
+        <v>83.31999999999999</v>
       </c>
       <c r="D7" t="n">
-        <v>29.34</v>
+        <v>77.51000000000001</v>
       </c>
       <c r="E7" t="n">
-        <v>-1.43</v>
+        <v>-6.97</v>
       </c>
       <c r="F7" t="n">
-        <v>6.4</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="G7" t="n">
-        <v>5.1</v>
+        <v>3.5</v>
       </c>
       <c r="H7" t="n">
-        <v>-1.3</v>
+        <v>-6.3</v>
       </c>
       <c r="I7" t="inlineStr">
         <is>
@@ -762,20 +762,20 @@
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>BUY (undervalued)</t>
+          <t>HOLD (fairly valued)</t>
         </is>
       </c>
       <c r="K7" t="n">
-        <v>28.04</v>
+        <v>77.67</v>
       </c>
       <c r="L7" t="n">
-        <v>27.69</v>
+        <v>73.18000000000001</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>GSL</t>
+          <t>ASC</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -784,22 +784,22 @@
         </is>
       </c>
       <c r="C8" t="n">
-        <v>38.59</v>
+        <v>17.82</v>
       </c>
       <c r="D8" t="n">
-        <v>38.59</v>
+        <v>17.8</v>
       </c>
       <c r="E8" t="n">
-        <v>0</v>
+        <v>-0.13</v>
       </c>
       <c r="F8" t="n">
-        <v>1.2</v>
+        <v>3</v>
       </c>
       <c r="G8" t="n">
-        <v>1.2</v>
+        <v>2.8</v>
       </c>
       <c r="H8" t="n">
-        <v>0</v>
+        <v>-0.1</v>
       </c>
       <c r="I8" t="inlineStr">
         <is>
@@ -812,16 +812,16 @@
         </is>
       </c>
       <c r="K8" t="n">
-        <v>40.54</v>
+        <v>16.3</v>
       </c>
       <c r="L8" t="n">
-        <v>40.54</v>
+        <v>16.28</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>CAPT</t>
+          <t>CMDB</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -830,44 +830,44 @@
         </is>
       </c>
       <c r="C9" t="n">
-        <v>15.61</v>
+        <v>32.12</v>
       </c>
       <c r="D9" t="n">
-        <v>15.49</v>
+        <v>31.33</v>
       </c>
       <c r="E9" t="n">
-        <v>-0.74</v>
+        <v>-2.45</v>
       </c>
       <c r="F9" t="n">
+        <v>5.2</v>
+      </c>
+      <c r="G9" t="n">
         <v>2.8</v>
       </c>
-      <c r="G9" t="n">
-        <v>1.1</v>
-      </c>
       <c r="H9" t="n">
-        <v>-1.7</v>
+        <v>-2.4</v>
       </c>
       <c r="I9" t="inlineStr">
         <is>
+          <t>BUY (undervalued)</t>
+        </is>
+      </c>
+      <c r="J9" t="inlineStr">
+        <is>
           <t>HOLD (fairly valued)</t>
         </is>
       </c>
-      <c r="J9" t="inlineStr">
-        <is>
-          <t>HOLD (fairly valued)</t>
-        </is>
-      </c>
       <c r="K9" t="n">
-        <v>13.37</v>
+        <v>20.57</v>
       </c>
       <c r="L9" t="n">
-        <v>13.14</v>
+        <v>20.1</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>TNK</t>
+          <t>GSL</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -876,26 +876,26 @@
         </is>
       </c>
       <c r="C10" t="n">
-        <v>83.31999999999999</v>
+        <v>38.59</v>
       </c>
       <c r="D10" t="n">
-        <v>77.51000000000001</v>
+        <v>38.59</v>
       </c>
       <c r="E10" t="n">
-        <v>-6.97</v>
+        <v>0</v>
       </c>
       <c r="F10" t="n">
-        <v>7.2</v>
+        <v>-0.7</v>
       </c>
       <c r="G10" t="n">
-        <v>1</v>
+        <v>-0.7</v>
       </c>
       <c r="H10" t="n">
-        <v>-6.2</v>
+        <v>0</v>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>BUY (undervalued)</t>
+          <t>HOLD (fairly valued)</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
@@ -904,16 +904,16 @@
         </is>
       </c>
       <c r="K10" t="n">
-        <v>77.67</v>
+        <v>40.54</v>
       </c>
       <c r="L10" t="n">
-        <v>73.18000000000001</v>
+        <v>40.54</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>ASC</t>
+          <t>TRMD</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -922,22 +922,22 @@
         </is>
       </c>
       <c r="C11" t="n">
-        <v>17.82</v>
+        <v>31.65</v>
       </c>
       <c r="D11" t="n">
-        <v>17.8</v>
+        <v>30.34</v>
       </c>
       <c r="E11" t="n">
-        <v>-0.13</v>
+        <v>-4.11</v>
       </c>
       <c r="F11" t="n">
-        <v>-0.5</v>
+        <v>2.9</v>
       </c>
       <c r="G11" t="n">
         <v>-0.7</v>
       </c>
       <c r="H11" t="n">
-        <v>-0.1</v>
+        <v>-3.6</v>
       </c>
       <c r="I11" t="inlineStr">
         <is>
@@ -950,16 +950,16 @@
         </is>
       </c>
       <c r="K11" t="n">
-        <v>16.3</v>
+        <v>29.68</v>
       </c>
       <c r="L11" t="n">
-        <v>16.28</v>
+        <v>28.65</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>FLNG</t>
+          <t>CAPT</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -968,22 +968,22 @@
         </is>
       </c>
       <c r="C12" t="n">
-        <v>28.45</v>
+        <v>15.61</v>
       </c>
       <c r="D12" t="n">
-        <v>28.45</v>
+        <v>15.49</v>
       </c>
       <c r="E12" t="n">
-        <v>0</v>
+        <v>-0.74</v>
       </c>
       <c r="F12" t="n">
-        <v>-2.7</v>
+        <v>0.6</v>
       </c>
       <c r="G12" t="n">
-        <v>-2.7</v>
+        <v>-1.1</v>
       </c>
       <c r="H12" t="n">
-        <v>0</v>
+        <v>-1.7</v>
       </c>
       <c r="I12" t="inlineStr">
         <is>
@@ -996,16 +996,16 @@
         </is>
       </c>
       <c r="K12" t="n">
-        <v>29.19</v>
+        <v>13.37</v>
       </c>
       <c r="L12" t="n">
-        <v>29.19</v>
+        <v>13.14</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>TRMD</t>
+          <t>FLNG</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -1014,22 +1014,22 @@
         </is>
       </c>
       <c r="C13" t="n">
-        <v>31.65</v>
+        <v>28.45</v>
       </c>
       <c r="D13" t="n">
-        <v>30.34</v>
+        <v>28.45</v>
       </c>
       <c r="E13" t="n">
-        <v>-4.11</v>
+        <v>0</v>
       </c>
       <c r="F13" t="n">
-        <v>0.7</v>
+        <v>-3.2</v>
       </c>
       <c r="G13" t="n">
-        <v>-2.8</v>
+        <v>-3.2</v>
       </c>
       <c r="H13" t="n">
-        <v>-3.5</v>
+        <v>0</v>
       </c>
       <c r="I13" t="inlineStr">
         <is>
@@ -1042,16 +1042,16 @@
         </is>
       </c>
       <c r="K13" t="n">
-        <v>29.68</v>
+        <v>29.19</v>
       </c>
       <c r="L13" t="n">
-        <v>28.65</v>
+        <v>29.19</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>GNK</t>
+          <t>2343</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1060,38 +1060,38 @@
         </is>
       </c>
       <c r="C14" t="n">
-        <v>25.53</v>
+        <v>0.4</v>
       </c>
       <c r="D14" t="n">
-        <v>24.69</v>
+        <v>0.39</v>
       </c>
       <c r="E14" t="n">
-        <v>-3.28</v>
+        <v>-4.64</v>
       </c>
       <c r="F14" t="n">
-        <v>-6.4</v>
+        <v>0.9</v>
       </c>
       <c r="G14" t="n">
-        <v>-9.199999999999999</v>
+        <v>-3.2</v>
       </c>
       <c r="H14" t="n">
-        <v>-2.8</v>
+        <v>-4.1</v>
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>TRIM/SHORT (overvalued)</t>
+          <t>HOLD (fairly valued)</t>
         </is>
       </c>
       <c r="J14" t="inlineStr">
         <is>
-          <t>TRIM/SHORT (overvalued)</t>
+          <t>HOLD (fairly valued)</t>
         </is>
       </c>
       <c r="K14" t="n">
-        <v>23.87</v>
+        <v>0.39</v>
       </c>
       <c r="L14" t="n">
-        <v>23.15</v>
+        <v>0.38</v>
       </c>
     </row>
     <row r="15">
@@ -1115,17 +1115,17 @@
         <v>-4.33</v>
       </c>
       <c r="F15" t="n">
-        <v>-6.9</v>
+        <v>-4.5</v>
       </c>
       <c r="G15" t="n">
-        <v>-10.6</v>
+        <v>-8.300000000000001</v>
       </c>
       <c r="H15" t="n">
-        <v>-3.7</v>
+        <v>-3.8</v>
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>TRIM/SHORT (overvalued)</t>
+          <t>HOLD (fairly valued)</t>
         </is>
       </c>
       <c r="J15" t="inlineStr">
@@ -1143,31 +1143,31 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>CMBT</t>
+          <t>GNK</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>WHOLE-COMPANY (hybrid aggregation)</t>
+          <t>whole-company</t>
         </is>
       </c>
       <c r="C16" t="n">
-        <v>15.84</v>
+        <v>25.53</v>
       </c>
       <c r="D16" t="n">
-        <v>15.87</v>
+        <v>24.69</v>
       </c>
       <c r="E16" t="n">
-        <v>0.18</v>
+        <v>-3.28</v>
       </c>
       <c r="F16" t="n">
-        <v>-11.1</v>
+        <v>-5.8</v>
       </c>
       <c r="G16" t="n">
-        <v>-10.9</v>
+        <v>-8.699999999999999</v>
       </c>
       <c r="H16" t="n">
-        <v>0.2</v>
+        <v>-2.8</v>
       </c>
       <c r="I16" t="inlineStr">
         <is>
@@ -1180,40 +1180,40 @@
         </is>
       </c>
       <c r="K16" t="n">
-        <v>13.85</v>
+        <v>23.87</v>
       </c>
       <c r="L16" t="n">
-        <v>13.87</v>
+        <v>23.15</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>MPCC</t>
+          <t>CMBT</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>whole-company</t>
+          <t>WHOLE-COMPANY (hybrid aggregation)</t>
         </is>
       </c>
       <c r="C17" t="n">
-        <v>2.04</v>
+        <v>15.84</v>
       </c>
       <c r="D17" t="n">
-        <v>2.04</v>
+        <v>15.87</v>
       </c>
       <c r="E17" t="n">
-        <v>0</v>
+        <v>0.18</v>
       </c>
       <c r="F17" t="n">
-        <v>-15.4</v>
+        <v>-10.3</v>
       </c>
       <c r="G17" t="n">
-        <v>-15.4</v>
+        <v>-10.2</v>
       </c>
       <c r="H17" t="n">
-        <v>0</v>
+        <v>0.2</v>
       </c>
       <c r="I17" t="inlineStr">
         <is>
@@ -1226,16 +1226,16 @@
         </is>
       </c>
       <c r="K17" t="n">
-        <v>2.06</v>
+        <v>13.85</v>
       </c>
       <c r="L17" t="n">
-        <v>2.06</v>
+        <v>13.87</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>HAFN</t>
+          <t>MPCC</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1244,22 +1244,22 @@
         </is>
       </c>
       <c r="C18" t="n">
-        <v>5.69</v>
+        <v>2.04</v>
       </c>
       <c r="D18" t="n">
-        <v>5.57</v>
+        <v>2.04</v>
       </c>
       <c r="E18" t="n">
-        <v>-2.07</v>
+        <v>0</v>
       </c>
       <c r="F18" t="n">
-        <v>-21.6</v>
+        <v>-17.8</v>
       </c>
       <c r="G18" t="n">
-        <v>-22.9</v>
+        <v>-17.8</v>
       </c>
       <c r="H18" t="n">
-        <v>-1.3</v>
+        <v>0</v>
       </c>
       <c r="I18" t="inlineStr">
         <is>
@@ -1272,16 +1272,16 @@
         </is>
       </c>
       <c r="K18" t="n">
-        <v>5.7</v>
+        <v>2.06</v>
       </c>
       <c r="L18" t="n">
-        <v>5.61</v>
+        <v>2.06</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>LPG</t>
+          <t>DHT</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1290,22 +1290,22 @@
         </is>
       </c>
       <c r="C19" t="n">
-        <v>34.12</v>
+        <v>16.07</v>
       </c>
       <c r="D19" t="n">
-        <v>34.11</v>
+        <v>13.88</v>
       </c>
       <c r="E19" t="n">
-        <v>-0.05</v>
+        <v>-13.65</v>
       </c>
       <c r="F19" t="n">
-        <v>-23.7</v>
+        <v>-12.6</v>
       </c>
       <c r="G19" t="n">
-        <v>-23.7</v>
+        <v>-22.9</v>
       </c>
       <c r="H19" t="n">
-        <v>-0</v>
+        <v>-10.3</v>
       </c>
       <c r="I19" t="inlineStr">
         <is>
@@ -1318,16 +1318,16 @@
         </is>
       </c>
       <c r="K19" t="n">
-        <v>30.56</v>
+        <v>15.13</v>
       </c>
       <c r="L19" t="n">
-        <v>30.55</v>
+        <v>13.34</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>DHT</t>
+          <t>HAFN</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -1336,22 +1336,22 @@
         </is>
       </c>
       <c r="C20" t="n">
-        <v>16.07</v>
+        <v>5.69</v>
       </c>
       <c r="D20" t="n">
-        <v>13.88</v>
+        <v>5.57</v>
       </c>
       <c r="E20" t="n">
-        <v>-13.65</v>
+        <v>-2.07</v>
       </c>
       <c r="F20" t="n">
-        <v>-14.8</v>
+        <v>-22.1</v>
       </c>
       <c r="G20" t="n">
-        <v>-24.9</v>
+        <v>-23.4</v>
       </c>
       <c r="H20" t="n">
-        <v>-10.1</v>
+        <v>-1.3</v>
       </c>
       <c r="I20" t="inlineStr">
         <is>
@@ -1364,16 +1364,16 @@
         </is>
       </c>
       <c r="K20" t="n">
-        <v>15.13</v>
+        <v>5.7</v>
       </c>
       <c r="L20" t="n">
-        <v>13.34</v>
+        <v>5.61</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>BWLP</t>
+          <t>LPG</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -1382,19 +1382,19 @@
         </is>
       </c>
       <c r="C21" t="n">
-        <v>15.81</v>
+        <v>34.12</v>
       </c>
       <c r="D21" t="n">
-        <v>15.8</v>
+        <v>34.11</v>
       </c>
       <c r="E21" t="n">
-        <v>-0.07000000000000001</v>
+        <v>-0.05</v>
       </c>
       <c r="F21" t="n">
-        <v>-25.6</v>
+        <v>-23.9</v>
       </c>
       <c r="G21" t="n">
-        <v>-25.6</v>
+        <v>-23.9</v>
       </c>
       <c r="H21" t="n">
         <v>-0</v>
@@ -1410,16 +1410,16 @@
         </is>
       </c>
       <c r="K21" t="n">
-        <v>14.47</v>
+        <v>30.56</v>
       </c>
       <c r="L21" t="n">
-        <v>14.46</v>
+        <v>30.55</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>FRO</t>
+          <t>BWLP</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -1428,22 +1428,22 @@
         </is>
       </c>
       <c r="C22" t="n">
-        <v>28.47</v>
+        <v>15.81</v>
       </c>
       <c r="D22" t="n">
-        <v>24.22</v>
+        <v>15.8</v>
       </c>
       <c r="E22" t="n">
-        <v>-14.93</v>
+        <v>-0.07000000000000001</v>
       </c>
       <c r="F22" t="n">
-        <v>-30.5</v>
+        <v>-28</v>
       </c>
       <c r="G22" t="n">
-        <v>-39.9</v>
+        <v>-28</v>
       </c>
       <c r="H22" t="n">
-        <v>-9.4</v>
+        <v>-0</v>
       </c>
       <c r="I22" t="inlineStr">
         <is>
@@ -1456,40 +1456,40 @@
         </is>
       </c>
       <c r="K22" t="n">
-        <v>26.5</v>
+        <v>14.47</v>
       </c>
       <c r="L22" t="n">
-        <v>22.91</v>
+        <v>14.46</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>INSW</t>
+          <t>FRO</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>WHOLE-COMPANY (hybrid aggregation)</t>
+          <t>whole-company</t>
         </is>
       </c>
       <c r="C23" t="n">
-        <v>57.91</v>
+        <v>28.47</v>
       </c>
       <c r="D23" t="n">
-        <v>52.59</v>
+        <v>24.22</v>
       </c>
       <c r="E23" t="n">
-        <v>-9.18</v>
+        <v>-14.93</v>
       </c>
       <c r="F23" t="n">
-        <v>-35.4</v>
+        <v>-28.2</v>
       </c>
       <c r="G23" t="n">
-        <v>-40.2</v>
+        <v>-37.9</v>
       </c>
       <c r="H23" t="n">
-        <v>-4.8</v>
+        <v>-9.699999999999999</v>
       </c>
       <c r="I23" t="inlineStr">
         <is>
@@ -1502,40 +1502,40 @@
         </is>
       </c>
       <c r="K23" t="n">
-        <v>57.15</v>
+        <v>26.5</v>
       </c>
       <c r="L23" t="n">
-        <v>52.93</v>
+        <v>22.91</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>ECO</t>
+          <t>INSW</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>whole-company</t>
+          <t>WHOLE-COMPANY (hybrid aggregation)</t>
         </is>
       </c>
       <c r="C24" t="n">
-        <v>40.4</v>
+        <v>57.91</v>
       </c>
       <c r="D24" t="n">
-        <v>34.35</v>
+        <v>52.59</v>
       </c>
       <c r="E24" t="n">
-        <v>-14.98</v>
+        <v>-9.18</v>
       </c>
       <c r="F24" t="n">
-        <v>-32.5</v>
+        <v>-33.7</v>
       </c>
       <c r="G24" t="n">
-        <v>-41.6</v>
+        <v>-38.6</v>
       </c>
       <c r="H24" t="n">
-        <v>-9.1</v>
+        <v>-4.9</v>
       </c>
       <c r="I24" t="inlineStr">
         <is>
@@ -1548,55 +1548,101 @@
         </is>
       </c>
       <c r="K24" t="n">
-        <v>37.09</v>
+        <v>57.15</v>
       </c>
       <c r="L24" t="n">
-        <v>32.09</v>
+        <v>52.93</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
+          <t>ECO</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>whole-company</t>
+        </is>
+      </c>
+      <c r="C25" t="n">
+        <v>40.4</v>
+      </c>
+      <c r="D25" t="n">
+        <v>34.35</v>
+      </c>
+      <c r="E25" t="n">
+        <v>-14.98</v>
+      </c>
+      <c r="F25" t="n">
+        <v>-31.6</v>
+      </c>
+      <c r="G25" t="n">
+        <v>-40.8</v>
+      </c>
+      <c r="H25" t="n">
+        <v>-9.199999999999999</v>
+      </c>
+      <c r="I25" t="inlineStr">
+        <is>
+          <t>TRIM/SHORT (overvalued)</t>
+        </is>
+      </c>
+      <c r="J25" t="inlineStr">
+        <is>
+          <t>TRIM/SHORT (overvalued)</t>
+        </is>
+      </c>
+      <c r="K25" t="n">
+        <v>37.09</v>
+      </c>
+      <c r="L25" t="n">
+        <v>32.09</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
           <t>NAT</t>
         </is>
       </c>
-      <c r="B25" t="inlineStr">
-        <is>
-          <t>whole-company</t>
-        </is>
-      </c>
-      <c r="C25" t="n">
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>whole-company</t>
+        </is>
+      </c>
+      <c r="C26" t="n">
         <v>3.32</v>
       </c>
-      <c r="D25" t="n">
+      <c r="D26" t="n">
         <v>2.79</v>
       </c>
-      <c r="E25" t="n">
+      <c r="E26" t="n">
         <v>-15.76</v>
       </c>
-      <c r="F25" t="n">
-        <v>-49.3</v>
-      </c>
-      <c r="G25" t="n">
-        <v>-56</v>
-      </c>
-      <c r="H25" t="n">
+      <c r="F26" t="n">
+        <v>-48.6</v>
+      </c>
+      <c r="G26" t="n">
+        <v>-55.4</v>
+      </c>
+      <c r="H26" t="n">
         <v>-6.7</v>
       </c>
-      <c r="I25" t="inlineStr">
-        <is>
-          <t>TRIM/SHORT (overvalued)</t>
-        </is>
-      </c>
-      <c r="J25" t="inlineStr">
-        <is>
-          <t>TRIM/SHORT (overvalued)</t>
-        </is>
-      </c>
-      <c r="K25" t="n">
+      <c r="I26" t="inlineStr">
+        <is>
+          <t>TRIM/SHORT (overvalued)</t>
+        </is>
+      </c>
+      <c r="J26" t="inlineStr">
+        <is>
+          <t>TRIM/SHORT (overvalued)</t>
+        </is>
+      </c>
+      <c r="K26" t="n">
         <v>3.13</v>
       </c>
-      <c r="L25" t="n">
+      <c r="L26" t="n">
         <v>2.72</v>
       </c>
     </row>

--- a/outputs/transaction_anchor_comparison.xlsx
+++ b/outputs/transaction_anchor_comparison.xlsx
@@ -517,10 +517,10 @@
         <v>0</v>
       </c>
       <c r="F2" t="n">
-        <v>49.7</v>
+        <v>58.3</v>
       </c>
       <c r="G2" t="n">
-        <v>49.7</v>
+        <v>58.3</v>
       </c>
       <c r="H2" t="n">
         <v>0</v>
@@ -536,10 +536,10 @@
         </is>
       </c>
       <c r="K2" t="n">
-        <v>33.5</v>
+        <v>35.91</v>
       </c>
       <c r="L2" t="n">
-        <v>33.5</v>
+        <v>35.91</v>
       </c>
     </row>
     <row r="3">
@@ -563,13 +563,13 @@
         <v>-8.51</v>
       </c>
       <c r="F3" t="n">
-        <v>57.3</v>
+        <v>56.8</v>
       </c>
       <c r="G3" t="n">
-        <v>45.1</v>
+        <v>44.9</v>
       </c>
       <c r="H3" t="n">
-        <v>-12.2</v>
+        <v>-11.9</v>
       </c>
       <c r="I3" t="inlineStr">
         <is>
@@ -582,10 +582,10 @@
         </is>
       </c>
       <c r="K3" t="n">
-        <v>61.09</v>
+        <v>62.35</v>
       </c>
       <c r="L3" t="n">
-        <v>56.36</v>
+        <v>57.6</v>
       </c>
     </row>
     <row r="4">
@@ -609,13 +609,13 @@
         <v>4.09</v>
       </c>
       <c r="F4" t="n">
-        <v>31.8</v>
+        <v>28.6</v>
       </c>
       <c r="G4" t="n">
-        <v>37.4</v>
+        <v>34.1</v>
       </c>
       <c r="H4" t="n">
-        <v>5.6</v>
+        <v>5.5</v>
       </c>
       <c r="I4" t="inlineStr">
         <is>
@@ -655,10 +655,10 @@
         <v>0</v>
       </c>
       <c r="F5" t="n">
-        <v>14</v>
+        <v>13.3</v>
       </c>
       <c r="G5" t="n">
-        <v>12</v>
+        <v>11.3</v>
       </c>
       <c r="H5" t="n">
         <v>-2</v>
@@ -683,7 +683,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>SBLK</t>
+          <t>TRMD</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -692,22 +692,22 @@
         </is>
       </c>
       <c r="C6" t="n">
-        <v>29.77</v>
+        <v>31.65</v>
       </c>
       <c r="D6" t="n">
-        <v>29.34</v>
+        <v>30.34</v>
       </c>
       <c r="E6" t="n">
-        <v>-1.43</v>
+        <v>-4.11</v>
       </c>
       <c r="F6" t="n">
-        <v>5.7</v>
+        <v>12.3</v>
       </c>
       <c r="G6" t="n">
-        <v>4.3</v>
+        <v>8.4</v>
       </c>
       <c r="H6" t="n">
-        <v>-1.3</v>
+        <v>-3.8</v>
       </c>
       <c r="I6" t="inlineStr">
         <is>
@@ -716,20 +716,20 @@
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>HOLD (fairly valued)</t>
+          <t>BUY (undervalued)</t>
         </is>
       </c>
       <c r="K6" t="n">
-        <v>28.04</v>
+        <v>33.03</v>
       </c>
       <c r="L6" t="n">
-        <v>27.69</v>
+        <v>31.9</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>TNK</t>
+          <t>SBLK</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -738,22 +738,22 @@
         </is>
       </c>
       <c r="C7" t="n">
-        <v>83.31999999999999</v>
+        <v>29.77</v>
       </c>
       <c r="D7" t="n">
-        <v>77.51000000000001</v>
+        <v>29.34</v>
       </c>
       <c r="E7" t="n">
-        <v>-6.97</v>
+        <v>-1.43</v>
       </c>
       <c r="F7" t="n">
-        <v>9.800000000000001</v>
+        <v>5.6</v>
       </c>
       <c r="G7" t="n">
-        <v>3.5</v>
+        <v>4.3</v>
       </c>
       <c r="H7" t="n">
-        <v>-6.3</v>
+        <v>-1.3</v>
       </c>
       <c r="I7" t="inlineStr">
         <is>
@@ -766,10 +766,10 @@
         </is>
       </c>
       <c r="K7" t="n">
-        <v>77.67</v>
+        <v>28.04</v>
       </c>
       <c r="L7" t="n">
-        <v>73.18000000000001</v>
+        <v>27.69</v>
       </c>
     </row>
     <row r="8">
@@ -793,10 +793,10 @@
         <v>-0.13</v>
       </c>
       <c r="F8" t="n">
-        <v>3</v>
+        <v>4.2</v>
       </c>
       <c r="G8" t="n">
-        <v>2.8</v>
+        <v>4</v>
       </c>
       <c r="H8" t="n">
         <v>-0.1</v>
@@ -812,16 +812,16 @@
         </is>
       </c>
       <c r="K8" t="n">
-        <v>16.3</v>
+        <v>16.85</v>
       </c>
       <c r="L8" t="n">
-        <v>16.28</v>
+        <v>16.83</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>CMDB</t>
+          <t>TNK</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -830,22 +830,22 @@
         </is>
       </c>
       <c r="C9" t="n">
-        <v>32.12</v>
+        <v>83.31999999999999</v>
       </c>
       <c r="D9" t="n">
-        <v>31.33</v>
+        <v>77.51000000000001</v>
       </c>
       <c r="E9" t="n">
-        <v>-2.45</v>
+        <v>-6.97</v>
       </c>
       <c r="F9" t="n">
-        <v>5.2</v>
+        <v>7.5</v>
       </c>
       <c r="G9" t="n">
-        <v>2.8</v>
+        <v>1.3</v>
       </c>
       <c r="H9" t="n">
-        <v>-2.4</v>
+        <v>-6.2</v>
       </c>
       <c r="I9" t="inlineStr">
         <is>
@@ -858,16 +858,16 @@
         </is>
       </c>
       <c r="K9" t="n">
-        <v>20.57</v>
+        <v>77.67</v>
       </c>
       <c r="L9" t="n">
-        <v>20.1</v>
+        <v>73.18000000000001</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>GSL</t>
+          <t>CMDB</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -876,22 +876,22 @@
         </is>
       </c>
       <c r="C10" t="n">
-        <v>38.59</v>
+        <v>32.12</v>
       </c>
       <c r="D10" t="n">
-        <v>38.59</v>
+        <v>31.33</v>
       </c>
       <c r="E10" t="n">
-        <v>0</v>
+        <v>-2.45</v>
       </c>
       <c r="F10" t="n">
-        <v>-0.7</v>
+        <v>3.2</v>
       </c>
       <c r="G10" t="n">
-        <v>-0.7</v>
+        <v>0.8</v>
       </c>
       <c r="H10" t="n">
-        <v>0</v>
+        <v>-2.4</v>
       </c>
       <c r="I10" t="inlineStr">
         <is>
@@ -904,16 +904,16 @@
         </is>
       </c>
       <c r="K10" t="n">
-        <v>40.54</v>
+        <v>20.57</v>
       </c>
       <c r="L10" t="n">
-        <v>40.54</v>
+        <v>20.1</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>TRMD</t>
+          <t>FLNG</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -922,22 +922,22 @@
         </is>
       </c>
       <c r="C11" t="n">
-        <v>31.65</v>
+        <v>28.45</v>
       </c>
       <c r="D11" t="n">
-        <v>30.34</v>
+        <v>28.45</v>
       </c>
       <c r="E11" t="n">
-        <v>-4.11</v>
+        <v>0</v>
       </c>
       <c r="F11" t="n">
-        <v>2.9</v>
+        <v>-0.4</v>
       </c>
       <c r="G11" t="n">
-        <v>-0.7</v>
+        <v>-0.4</v>
       </c>
       <c r="H11" t="n">
-        <v>-3.6</v>
+        <v>0</v>
       </c>
       <c r="I11" t="inlineStr">
         <is>
@@ -950,16 +950,16 @@
         </is>
       </c>
       <c r="K11" t="n">
-        <v>29.68</v>
+        <v>30.67</v>
       </c>
       <c r="L11" t="n">
-        <v>28.65</v>
+        <v>30.67</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>CAPT</t>
+          <t>STNG</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -968,22 +968,22 @@
         </is>
       </c>
       <c r="C12" t="n">
-        <v>15.61</v>
+        <v>80.97</v>
       </c>
       <c r="D12" t="n">
-        <v>15.49</v>
+        <v>77.47</v>
       </c>
       <c r="E12" t="n">
-        <v>-0.74</v>
+        <v>-4.33</v>
       </c>
       <c r="F12" t="n">
-        <v>0.6</v>
+        <v>3.1</v>
       </c>
       <c r="G12" t="n">
-        <v>-1.1</v>
+        <v>-1</v>
       </c>
       <c r="H12" t="n">
-        <v>-1.7</v>
+        <v>-4.1</v>
       </c>
       <c r="I12" t="inlineStr">
         <is>
@@ -996,16 +996,16 @@
         </is>
       </c>
       <c r="K12" t="n">
-        <v>13.37</v>
+        <v>80.3</v>
       </c>
       <c r="L12" t="n">
-        <v>13.14</v>
+        <v>77.13</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>FLNG</t>
+          <t>GSL</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -1014,19 +1014,19 @@
         </is>
       </c>
       <c r="C13" t="n">
-        <v>28.45</v>
+        <v>38.59</v>
       </c>
       <c r="D13" t="n">
-        <v>28.45</v>
+        <v>38.59</v>
       </c>
       <c r="E13" t="n">
         <v>0</v>
       </c>
       <c r="F13" t="n">
-        <v>-3.2</v>
+        <v>-1.7</v>
       </c>
       <c r="G13" t="n">
-        <v>-3.2</v>
+        <v>-1.7</v>
       </c>
       <c r="H13" t="n">
         <v>0</v>
@@ -1042,16 +1042,16 @@
         </is>
       </c>
       <c r="K13" t="n">
-        <v>29.19</v>
+        <v>40.54</v>
       </c>
       <c r="L13" t="n">
-        <v>29.19</v>
+        <v>40.54</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>2343</t>
+          <t>CAPT</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1060,22 +1060,22 @@
         </is>
       </c>
       <c r="C14" t="n">
-        <v>0.4</v>
+        <v>15.61</v>
       </c>
       <c r="D14" t="n">
-        <v>0.39</v>
+        <v>15.49</v>
       </c>
       <c r="E14" t="n">
-        <v>-4.64</v>
+        <v>-0.74</v>
       </c>
       <c r="F14" t="n">
-        <v>0.9</v>
+        <v>-0.2</v>
       </c>
       <c r="G14" t="n">
-        <v>-3.2</v>
+        <v>-1.9</v>
       </c>
       <c r="H14" t="n">
-        <v>-4.1</v>
+        <v>-1.7</v>
       </c>
       <c r="I14" t="inlineStr">
         <is>
@@ -1088,16 +1088,16 @@
         </is>
       </c>
       <c r="K14" t="n">
-        <v>0.39</v>
+        <v>13.37</v>
       </c>
       <c r="L14" t="n">
-        <v>0.38</v>
+        <v>13.14</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>STNG</t>
+          <t>2343</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1106,22 +1106,22 @@
         </is>
       </c>
       <c r="C15" t="n">
-        <v>80.97</v>
+        <v>0.4</v>
       </c>
       <c r="D15" t="n">
-        <v>77.47</v>
+        <v>0.39</v>
       </c>
       <c r="E15" t="n">
-        <v>-4.33</v>
+        <v>-4.64</v>
       </c>
       <c r="F15" t="n">
-        <v>-4.5</v>
+        <v>0.7</v>
       </c>
       <c r="G15" t="n">
-        <v>-8.300000000000001</v>
+        <v>-3.3</v>
       </c>
       <c r="H15" t="n">
-        <v>-3.8</v>
+        <v>-4.1</v>
       </c>
       <c r="I15" t="inlineStr">
         <is>
@@ -1130,14 +1130,14 @@
       </c>
       <c r="J15" t="inlineStr">
         <is>
-          <t>TRIM/SHORT (overvalued)</t>
+          <t>HOLD (fairly valued)</t>
         </is>
       </c>
       <c r="K15" t="n">
-        <v>73.81</v>
+        <v>0.39</v>
       </c>
       <c r="L15" t="n">
-        <v>70.90000000000001</v>
+        <v>0.38</v>
       </c>
     </row>
     <row r="16">
@@ -1161,10 +1161,10 @@
         <v>-3.28</v>
       </c>
       <c r="F16" t="n">
-        <v>-5.8</v>
+        <v>-6.2</v>
       </c>
       <c r="G16" t="n">
-        <v>-8.699999999999999</v>
+        <v>-9</v>
       </c>
       <c r="H16" t="n">
         <v>-2.8</v>
@@ -1207,13 +1207,13 @@
         <v>0.18</v>
       </c>
       <c r="F17" t="n">
-        <v>-10.3</v>
+        <v>-12.3</v>
       </c>
       <c r="G17" t="n">
-        <v>-10.2</v>
+        <v>-12.1</v>
       </c>
       <c r="H17" t="n">
-        <v>0.2</v>
+        <v>0.1</v>
       </c>
       <c r="I17" t="inlineStr">
         <is>
@@ -1235,7 +1235,7 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>MPCC</t>
+          <t>HAFN</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1244,22 +1244,22 @@
         </is>
       </c>
       <c r="C18" t="n">
-        <v>2.04</v>
+        <v>5.69</v>
       </c>
       <c r="D18" t="n">
-        <v>2.04</v>
+        <v>5.57</v>
       </c>
       <c r="E18" t="n">
-        <v>0</v>
+        <v>-2.07</v>
       </c>
       <c r="F18" t="n">
-        <v>-17.8</v>
+        <v>-15.4</v>
       </c>
       <c r="G18" t="n">
-        <v>-17.8</v>
+        <v>-16.7</v>
       </c>
       <c r="H18" t="n">
-        <v>0</v>
+        <v>-1.4</v>
       </c>
       <c r="I18" t="inlineStr">
         <is>
@@ -1272,16 +1272,16 @@
         </is>
       </c>
       <c r="K18" t="n">
-        <v>2.06</v>
+        <v>6.33</v>
       </c>
       <c r="L18" t="n">
-        <v>2.06</v>
+        <v>6.23</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>DHT</t>
+          <t>MPCC</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1290,22 +1290,22 @@
         </is>
       </c>
       <c r="C19" t="n">
-        <v>16.07</v>
+        <v>2.04</v>
       </c>
       <c r="D19" t="n">
-        <v>13.88</v>
+        <v>2.04</v>
       </c>
       <c r="E19" t="n">
-        <v>-13.65</v>
+        <v>0</v>
       </c>
       <c r="F19" t="n">
-        <v>-12.6</v>
+        <v>-18.7</v>
       </c>
       <c r="G19" t="n">
-        <v>-22.9</v>
+        <v>-18.7</v>
       </c>
       <c r="H19" t="n">
-        <v>-10.3</v>
+        <v>0</v>
       </c>
       <c r="I19" t="inlineStr">
         <is>
@@ -1318,16 +1318,16 @@
         </is>
       </c>
       <c r="K19" t="n">
-        <v>15.13</v>
+        <v>2.06</v>
       </c>
       <c r="L19" t="n">
-        <v>13.34</v>
+        <v>2.06</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>HAFN</t>
+          <t>LPG</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -1336,22 +1336,22 @@
         </is>
       </c>
       <c r="C20" t="n">
-        <v>5.69</v>
+        <v>34.12</v>
       </c>
       <c r="D20" t="n">
-        <v>5.57</v>
+        <v>34.11</v>
       </c>
       <c r="E20" t="n">
-        <v>-2.07</v>
+        <v>-0.05</v>
       </c>
       <c r="F20" t="n">
-        <v>-22.1</v>
+        <v>-26.6</v>
       </c>
       <c r="G20" t="n">
-        <v>-23.4</v>
+        <v>-26.6</v>
       </c>
       <c r="H20" t="n">
-        <v>-1.3</v>
+        <v>-0</v>
       </c>
       <c r="I20" t="inlineStr">
         <is>
@@ -1364,16 +1364,16 @@
         </is>
       </c>
       <c r="K20" t="n">
-        <v>5.7</v>
+        <v>30.56</v>
       </c>
       <c r="L20" t="n">
-        <v>5.61</v>
+        <v>30.55</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>LPG</t>
+          <t>DHT</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -1382,22 +1382,22 @@
         </is>
       </c>
       <c r="C21" t="n">
-        <v>34.12</v>
+        <v>16.07</v>
       </c>
       <c r="D21" t="n">
-        <v>34.11</v>
+        <v>13.88</v>
       </c>
       <c r="E21" t="n">
-        <v>-0.05</v>
+        <v>-13.65</v>
       </c>
       <c r="F21" t="n">
-        <v>-23.9</v>
+        <v>-16.8</v>
       </c>
       <c r="G21" t="n">
-        <v>-23.9</v>
+        <v>-26.6</v>
       </c>
       <c r="H21" t="n">
-        <v>-0</v>
+        <v>-9.800000000000001</v>
       </c>
       <c r="I21" t="inlineStr">
         <is>
@@ -1410,10 +1410,10 @@
         </is>
       </c>
       <c r="K21" t="n">
-        <v>30.56</v>
+        <v>15.13</v>
       </c>
       <c r="L21" t="n">
-        <v>30.55</v>
+        <v>13.34</v>
       </c>
     </row>
     <row r="22">
@@ -1437,10 +1437,10 @@
         <v>-0.07000000000000001</v>
       </c>
       <c r="F22" t="n">
-        <v>-28</v>
+        <v>-31.6</v>
       </c>
       <c r="G22" t="n">
-        <v>-28</v>
+        <v>-31.6</v>
       </c>
       <c r="H22" t="n">
         <v>-0</v>
@@ -1465,31 +1465,31 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>FRO</t>
+          <t>INSW</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>whole-company</t>
+          <t>WHOLE-COMPANY (hybrid aggregation)</t>
         </is>
       </c>
       <c r="C23" t="n">
-        <v>28.47</v>
+        <v>57.91</v>
       </c>
       <c r="D23" t="n">
-        <v>24.22</v>
+        <v>52.59</v>
       </c>
       <c r="E23" t="n">
-        <v>-14.93</v>
+        <v>-9.18</v>
       </c>
       <c r="F23" t="n">
-        <v>-28.2</v>
+        <v>-33.7</v>
       </c>
       <c r="G23" t="n">
-        <v>-37.9</v>
+        <v>-38.5</v>
       </c>
       <c r="H23" t="n">
-        <v>-9.699999999999999</v>
+        <v>-4.8</v>
       </c>
       <c r="I23" t="inlineStr">
         <is>
@@ -1502,40 +1502,40 @@
         </is>
       </c>
       <c r="K23" t="n">
-        <v>26.5</v>
+        <v>58.44</v>
       </c>
       <c r="L23" t="n">
-        <v>22.91</v>
+        <v>54.21</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>INSW</t>
+          <t>FRO</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>WHOLE-COMPANY (hybrid aggregation)</t>
+          <t>whole-company</t>
         </is>
       </c>
       <c r="C24" t="n">
-        <v>57.91</v>
+        <v>28.47</v>
       </c>
       <c r="D24" t="n">
-        <v>52.59</v>
+        <v>24.22</v>
       </c>
       <c r="E24" t="n">
-        <v>-9.18</v>
+        <v>-14.93</v>
       </c>
       <c r="F24" t="n">
-        <v>-33.7</v>
+        <v>-30.9</v>
       </c>
       <c r="G24" t="n">
-        <v>-38.6</v>
+        <v>-40.3</v>
       </c>
       <c r="H24" t="n">
-        <v>-4.9</v>
+        <v>-9.4</v>
       </c>
       <c r="I24" t="inlineStr">
         <is>
@@ -1548,10 +1548,10 @@
         </is>
       </c>
       <c r="K24" t="n">
-        <v>57.15</v>
+        <v>26.5</v>
       </c>
       <c r="L24" t="n">
-        <v>52.93</v>
+        <v>22.91</v>
       </c>
     </row>
     <row r="25">
@@ -1575,13 +1575,13 @@
         <v>-14.98</v>
       </c>
       <c r="F25" t="n">
-        <v>-31.6</v>
+        <v>-34.6</v>
       </c>
       <c r="G25" t="n">
-        <v>-40.8</v>
+        <v>-43.4</v>
       </c>
       <c r="H25" t="n">
-        <v>-9.199999999999999</v>
+        <v>-8.800000000000001</v>
       </c>
       <c r="I25" t="inlineStr">
         <is>
@@ -1621,13 +1621,13 @@
         <v>-15.76</v>
       </c>
       <c r="F26" t="n">
-        <v>-48.6</v>
+        <v>-50.3</v>
       </c>
       <c r="G26" t="n">
-        <v>-55.4</v>
+        <v>-56.8</v>
       </c>
       <c r="H26" t="n">
-        <v>-6.7</v>
+        <v>-6.5</v>
       </c>
       <c r="I26" t="inlineStr">
         <is>

--- a/outputs/transaction_anchor_comparison.xlsx
+++ b/outputs/transaction_anchor_comparison.xlsx
@@ -554,19 +554,19 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>96.95</v>
+        <v>97.01000000000001</v>
       </c>
       <c r="D3" t="n">
-        <v>88.7</v>
+        <v>88.76000000000001</v>
       </c>
       <c r="E3" t="n">
         <v>-8.51</v>
       </c>
       <c r="F3" t="n">
-        <v>56.8</v>
+        <v>56.9</v>
       </c>
       <c r="G3" t="n">
-        <v>44.9</v>
+        <v>45</v>
       </c>
       <c r="H3" t="n">
         <v>-11.9</v>
@@ -582,10 +582,10 @@
         </is>
       </c>
       <c r="K3" t="n">
-        <v>62.35</v>
+        <v>62.38</v>
       </c>
       <c r="L3" t="n">
-        <v>57.6</v>
+        <v>57.64</v>
       </c>
     </row>
     <row r="4">

--- a/outputs/transaction_anchor_comparison.xlsx
+++ b/outputs/transaction_anchor_comparison.xlsx
@@ -554,22 +554,22 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>97.01000000000001</v>
+        <v>94.58</v>
       </c>
       <c r="D3" t="n">
-        <v>88.76000000000001</v>
+        <v>87.34999999999999</v>
       </c>
       <c r="E3" t="n">
-        <v>-8.51</v>
+        <v>-7.65</v>
       </c>
       <c r="F3" t="n">
-        <v>56.9</v>
+        <v>52.6</v>
       </c>
       <c r="G3" t="n">
-        <v>45</v>
+        <v>42</v>
       </c>
       <c r="H3" t="n">
-        <v>-11.9</v>
+        <v>-10.6</v>
       </c>
       <c r="I3" t="inlineStr">
         <is>
@@ -582,10 +582,10 @@
         </is>
       </c>
       <c r="K3" t="n">
-        <v>62.38</v>
+        <v>60.66</v>
       </c>
       <c r="L3" t="n">
-        <v>57.64</v>
+        <v>56.46</v>
       </c>
     </row>
     <row r="4">

--- a/outputs/transaction_anchor_comparison.xlsx
+++ b/outputs/transaction_anchor_comparison.xlsx
@@ -517,10 +517,10 @@
         <v>0</v>
       </c>
       <c r="F2" t="n">
-        <v>58.3</v>
+        <v>61.8</v>
       </c>
       <c r="G2" t="n">
-        <v>58.3</v>
+        <v>61.8</v>
       </c>
       <c r="H2" t="n">
         <v>0</v>
@@ -563,13 +563,13 @@
         <v>-7.65</v>
       </c>
       <c r="F3" t="n">
-        <v>52.6</v>
+        <v>61.2</v>
       </c>
       <c r="G3" t="n">
-        <v>42</v>
+        <v>50.1</v>
       </c>
       <c r="H3" t="n">
-        <v>-10.6</v>
+        <v>-11.2</v>
       </c>
       <c r="I3" t="inlineStr">
         <is>
@@ -609,13 +609,13 @@
         <v>4.09</v>
       </c>
       <c r="F4" t="n">
-        <v>28.6</v>
+        <v>34.5</v>
       </c>
       <c r="G4" t="n">
-        <v>34.1</v>
+        <v>40.2</v>
       </c>
       <c r="H4" t="n">
-        <v>5.5</v>
+        <v>5.7</v>
       </c>
       <c r="I4" t="inlineStr">
         <is>
@@ -655,10 +655,10 @@
         <v>0</v>
       </c>
       <c r="F5" t="n">
-        <v>13.3</v>
+        <v>14.8</v>
       </c>
       <c r="G5" t="n">
-        <v>11.3</v>
+        <v>12.8</v>
       </c>
       <c r="H5" t="n">
         <v>-2</v>
@@ -701,13 +701,13 @@
         <v>-4.11</v>
       </c>
       <c r="F6" t="n">
-        <v>12.3</v>
+        <v>16.1</v>
       </c>
       <c r="G6" t="n">
-        <v>8.4</v>
+        <v>12.1</v>
       </c>
       <c r="H6" t="n">
-        <v>-3.8</v>
+        <v>-4</v>
       </c>
       <c r="I6" t="inlineStr">
         <is>
@@ -747,13 +747,13 @@
         <v>-1.43</v>
       </c>
       <c r="F7" t="n">
-        <v>5.6</v>
+        <v>12.6</v>
       </c>
       <c r="G7" t="n">
-        <v>4.3</v>
+        <v>11.2</v>
       </c>
       <c r="H7" t="n">
-        <v>-1.3</v>
+        <v>-1.4</v>
       </c>
       <c r="I7" t="inlineStr">
         <is>
@@ -762,7 +762,7 @@
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>HOLD (fairly valued)</t>
+          <t>BUY (undervalued)</t>
         </is>
       </c>
       <c r="K7" t="n">
@@ -793,22 +793,22 @@
         <v>-0.13</v>
       </c>
       <c r="F8" t="n">
-        <v>4.2</v>
+        <v>9.4</v>
       </c>
       <c r="G8" t="n">
-        <v>4</v>
+        <v>9.300000000000001</v>
       </c>
       <c r="H8" t="n">
         <v>-0.1</v>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>HOLD (fairly valued)</t>
+          <t>BUY (undervalued)</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>HOLD (fairly valued)</t>
+          <t>BUY (undervalued)</t>
         </is>
       </c>
       <c r="K8" t="n">
@@ -821,7 +821,7 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>TNK</t>
+          <t>CMDB</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -830,22 +830,22 @@
         </is>
       </c>
       <c r="C9" t="n">
-        <v>83.31999999999999</v>
+        <v>32.12</v>
       </c>
       <c r="D9" t="n">
-        <v>77.51000000000001</v>
+        <v>31.33</v>
       </c>
       <c r="E9" t="n">
-        <v>-6.97</v>
+        <v>-2.45</v>
       </c>
       <c r="F9" t="n">
-        <v>7.5</v>
+        <v>9.4</v>
       </c>
       <c r="G9" t="n">
-        <v>1.3</v>
+        <v>6.8</v>
       </c>
       <c r="H9" t="n">
-        <v>-6.2</v>
+        <v>-2.5</v>
       </c>
       <c r="I9" t="inlineStr">
         <is>
@@ -854,20 +854,20 @@
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>HOLD (fairly valued)</t>
+          <t>BUY (undervalued)</t>
         </is>
       </c>
       <c r="K9" t="n">
-        <v>77.67</v>
+        <v>20.57</v>
       </c>
       <c r="L9" t="n">
-        <v>73.18000000000001</v>
+        <v>20.1</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>CMDB</t>
+          <t>TNK</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -876,44 +876,44 @@
         </is>
       </c>
       <c r="C10" t="n">
-        <v>32.12</v>
+        <v>83.31999999999999</v>
       </c>
       <c r="D10" t="n">
-        <v>31.33</v>
+        <v>77.51000000000001</v>
       </c>
       <c r="E10" t="n">
-        <v>-2.45</v>
+        <v>-6.97</v>
       </c>
       <c r="F10" t="n">
-        <v>3.2</v>
+        <v>10.8</v>
       </c>
       <c r="G10" t="n">
-        <v>0.8</v>
+        <v>4.4</v>
       </c>
       <c r="H10" t="n">
-        <v>-2.4</v>
+        <v>-6.4</v>
       </c>
       <c r="I10" t="inlineStr">
         <is>
+          <t>BUY (undervalued)</t>
+        </is>
+      </c>
+      <c r="J10" t="inlineStr">
+        <is>
           <t>HOLD (fairly valued)</t>
         </is>
       </c>
-      <c r="J10" t="inlineStr">
-        <is>
-          <t>HOLD (fairly valued)</t>
-        </is>
-      </c>
       <c r="K10" t="n">
-        <v>20.57</v>
+        <v>77.67</v>
       </c>
       <c r="L10" t="n">
-        <v>20.1</v>
+        <v>73.18000000000001</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>FLNG</t>
+          <t>CAPT</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -922,44 +922,44 @@
         </is>
       </c>
       <c r="C11" t="n">
-        <v>28.45</v>
+        <v>15.61</v>
       </c>
       <c r="D11" t="n">
-        <v>28.45</v>
+        <v>15.49</v>
       </c>
       <c r="E11" t="n">
-        <v>0</v>
+        <v>-0.74</v>
       </c>
       <c r="F11" t="n">
-        <v>-0.4</v>
+        <v>5.1</v>
       </c>
       <c r="G11" t="n">
-        <v>-0.4</v>
+        <v>3.3</v>
       </c>
       <c r="H11" t="n">
-        <v>0</v>
+        <v>-1.8</v>
       </c>
       <c r="I11" t="inlineStr">
         <is>
+          <t>BUY (undervalued)</t>
+        </is>
+      </c>
+      <c r="J11" t="inlineStr">
+        <is>
           <t>HOLD (fairly valued)</t>
         </is>
       </c>
-      <c r="J11" t="inlineStr">
-        <is>
-          <t>HOLD (fairly valued)</t>
-        </is>
-      </c>
       <c r="K11" t="n">
-        <v>30.67</v>
+        <v>13.37</v>
       </c>
       <c r="L11" t="n">
-        <v>30.67</v>
+        <v>13.14</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>STNG</t>
+          <t>GSL</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -968,22 +968,22 @@
         </is>
       </c>
       <c r="C12" t="n">
-        <v>80.97</v>
+        <v>38.59</v>
       </c>
       <c r="D12" t="n">
-        <v>77.47</v>
+        <v>38.59</v>
       </c>
       <c r="E12" t="n">
-        <v>-4.33</v>
+        <v>0</v>
       </c>
       <c r="F12" t="n">
-        <v>3.1</v>
+        <v>0.9</v>
       </c>
       <c r="G12" t="n">
-        <v>-1</v>
+        <v>0.9</v>
       </c>
       <c r="H12" t="n">
-        <v>-4.1</v>
+        <v>0</v>
       </c>
       <c r="I12" t="inlineStr">
         <is>
@@ -996,16 +996,16 @@
         </is>
       </c>
       <c r="K12" t="n">
-        <v>80.3</v>
+        <v>40.54</v>
       </c>
       <c r="L12" t="n">
-        <v>77.13</v>
+        <v>40.54</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>GSL</t>
+          <t>STNG</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -1014,22 +1014,22 @@
         </is>
       </c>
       <c r="C13" t="n">
-        <v>38.59</v>
+        <v>80.97</v>
       </c>
       <c r="D13" t="n">
-        <v>38.59</v>
+        <v>77.47</v>
       </c>
       <c r="E13" t="n">
-        <v>0</v>
+        <v>-4.33</v>
       </c>
       <c r="F13" t="n">
-        <v>-1.7</v>
+        <v>5</v>
       </c>
       <c r="G13" t="n">
-        <v>-1.7</v>
+        <v>0.8</v>
       </c>
       <c r="H13" t="n">
-        <v>0</v>
+        <v>-4.1</v>
       </c>
       <c r="I13" t="inlineStr">
         <is>
@@ -1042,16 +1042,16 @@
         </is>
       </c>
       <c r="K13" t="n">
-        <v>40.54</v>
+        <v>80.3</v>
       </c>
       <c r="L13" t="n">
-        <v>40.54</v>
+        <v>77.13</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>CAPT</t>
+          <t>FLNG</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1060,22 +1060,22 @@
         </is>
       </c>
       <c r="C14" t="n">
-        <v>15.61</v>
+        <v>28.45</v>
       </c>
       <c r="D14" t="n">
-        <v>15.49</v>
+        <v>28.45</v>
       </c>
       <c r="E14" t="n">
-        <v>-0.74</v>
+        <v>0</v>
       </c>
       <c r="F14" t="n">
-        <v>-0.2</v>
+        <v>0</v>
       </c>
       <c r="G14" t="n">
-        <v>-1.9</v>
+        <v>0</v>
       </c>
       <c r="H14" t="n">
-        <v>-1.7</v>
+        <v>0</v>
       </c>
       <c r="I14" t="inlineStr">
         <is>
@@ -1088,16 +1088,16 @@
         </is>
       </c>
       <c r="K14" t="n">
-        <v>13.37</v>
+        <v>30.67</v>
       </c>
       <c r="L14" t="n">
-        <v>13.14</v>
+        <v>30.67</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>2343</t>
+          <t>GNK</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1106,22 +1106,22 @@
         </is>
       </c>
       <c r="C15" t="n">
-        <v>0.4</v>
+        <v>25.53</v>
       </c>
       <c r="D15" t="n">
-        <v>0.39</v>
+        <v>24.69</v>
       </c>
       <c r="E15" t="n">
-        <v>-4.64</v>
+        <v>-3.28</v>
       </c>
       <c r="F15" t="n">
-        <v>0.7</v>
+        <v>-1</v>
       </c>
       <c r="G15" t="n">
-        <v>-3.3</v>
+        <v>-4</v>
       </c>
       <c r="H15" t="n">
-        <v>-4.1</v>
+        <v>-3</v>
       </c>
       <c r="I15" t="inlineStr">
         <is>
@@ -1134,16 +1134,16 @@
         </is>
       </c>
       <c r="K15" t="n">
-        <v>0.39</v>
+        <v>23.87</v>
       </c>
       <c r="L15" t="n">
-        <v>0.38</v>
+        <v>23.15</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>GNK</t>
+          <t>2343</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1152,38 +1152,38 @@
         </is>
       </c>
       <c r="C16" t="n">
-        <v>25.53</v>
+        <v>0.4</v>
       </c>
       <c r="D16" t="n">
-        <v>24.69</v>
+        <v>0.39</v>
       </c>
       <c r="E16" t="n">
-        <v>-3.28</v>
+        <v>-4.64</v>
       </c>
       <c r="F16" t="n">
-        <v>-6.2</v>
+        <v>-0.5</v>
       </c>
       <c r="G16" t="n">
-        <v>-9</v>
+        <v>-4.6</v>
       </c>
       <c r="H16" t="n">
-        <v>-2.8</v>
+        <v>-4</v>
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>TRIM/SHORT (overvalued)</t>
+          <t>HOLD (fairly valued)</t>
         </is>
       </c>
       <c r="J16" t="inlineStr">
         <is>
-          <t>TRIM/SHORT (overvalued)</t>
+          <t>HOLD (fairly valued)</t>
         </is>
       </c>
       <c r="K16" t="n">
-        <v>23.87</v>
+        <v>0.39</v>
       </c>
       <c r="L16" t="n">
-        <v>23.15</v>
+        <v>0.38</v>
       </c>
     </row>
     <row r="17">
@@ -1207,13 +1207,13 @@
         <v>0.18</v>
       </c>
       <c r="F17" t="n">
-        <v>-12.3</v>
+        <v>-7.5</v>
       </c>
       <c r="G17" t="n">
-        <v>-12.1</v>
+        <v>-7.3</v>
       </c>
       <c r="H17" t="n">
-        <v>0.1</v>
+        <v>0.2</v>
       </c>
       <c r="I17" t="inlineStr">
         <is>
@@ -1253,10 +1253,10 @@
         <v>-2.07</v>
       </c>
       <c r="F18" t="n">
-        <v>-15.4</v>
+        <v>-12.7</v>
       </c>
       <c r="G18" t="n">
-        <v>-16.7</v>
+        <v>-14.1</v>
       </c>
       <c r="H18" t="n">
         <v>-1.4</v>
@@ -1299,10 +1299,10 @@
         <v>0</v>
       </c>
       <c r="F19" t="n">
-        <v>-18.7</v>
+        <v>-16.9</v>
       </c>
       <c r="G19" t="n">
-        <v>-18.7</v>
+        <v>-16.9</v>
       </c>
       <c r="H19" t="n">
         <v>0</v>
@@ -1327,7 +1327,7 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>LPG</t>
+          <t>DHT</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -1336,22 +1336,22 @@
         </is>
       </c>
       <c r="C20" t="n">
-        <v>34.12</v>
+        <v>16.07</v>
       </c>
       <c r="D20" t="n">
-        <v>34.11</v>
+        <v>13.88</v>
       </c>
       <c r="E20" t="n">
-        <v>-0.05</v>
+        <v>-13.65</v>
       </c>
       <c r="F20" t="n">
-        <v>-26.6</v>
+        <v>-13.1</v>
       </c>
       <c r="G20" t="n">
-        <v>-26.6</v>
+        <v>-23.4</v>
       </c>
       <c r="H20" t="n">
-        <v>-0</v>
+        <v>-10.3</v>
       </c>
       <c r="I20" t="inlineStr">
         <is>
@@ -1364,16 +1364,16 @@
         </is>
       </c>
       <c r="K20" t="n">
-        <v>30.56</v>
+        <v>15.13</v>
       </c>
       <c r="L20" t="n">
-        <v>30.55</v>
+        <v>13.34</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>DHT</t>
+          <t>LPG</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -1382,22 +1382,22 @@
         </is>
       </c>
       <c r="C21" t="n">
-        <v>16.07</v>
+        <v>34.12</v>
       </c>
       <c r="D21" t="n">
-        <v>13.88</v>
+        <v>34.11</v>
       </c>
       <c r="E21" t="n">
-        <v>-13.65</v>
+        <v>-0.05</v>
       </c>
       <c r="F21" t="n">
-        <v>-16.8</v>
+        <v>-25.5</v>
       </c>
       <c r="G21" t="n">
-        <v>-26.6</v>
+        <v>-25.5</v>
       </c>
       <c r="H21" t="n">
-        <v>-9.800000000000001</v>
+        <v>-0</v>
       </c>
       <c r="I21" t="inlineStr">
         <is>
@@ -1410,10 +1410,10 @@
         </is>
       </c>
       <c r="K21" t="n">
-        <v>15.13</v>
+        <v>30.56</v>
       </c>
       <c r="L21" t="n">
-        <v>13.34</v>
+        <v>30.55</v>
       </c>
     </row>
     <row r="22">
@@ -1437,10 +1437,10 @@
         <v>-0.07000000000000001</v>
       </c>
       <c r="F22" t="n">
-        <v>-31.6</v>
+        <v>-28.9</v>
       </c>
       <c r="G22" t="n">
-        <v>-31.6</v>
+        <v>-28.9</v>
       </c>
       <c r="H22" t="n">
         <v>-0</v>
@@ -1465,31 +1465,31 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>INSW</t>
+          <t>FRO</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>WHOLE-COMPANY (hybrid aggregation)</t>
+          <t>whole-company</t>
         </is>
       </c>
       <c r="C23" t="n">
-        <v>57.91</v>
+        <v>28.47</v>
       </c>
       <c r="D23" t="n">
-        <v>52.59</v>
+        <v>24.22</v>
       </c>
       <c r="E23" t="n">
-        <v>-9.18</v>
+        <v>-14.93</v>
       </c>
       <c r="F23" t="n">
-        <v>-33.7</v>
+        <v>-27.4</v>
       </c>
       <c r="G23" t="n">
-        <v>-38.5</v>
+        <v>-37.2</v>
       </c>
       <c r="H23" t="n">
-        <v>-4.8</v>
+        <v>-9.800000000000001</v>
       </c>
       <c r="I23" t="inlineStr">
         <is>
@@ -1502,40 +1502,40 @@
         </is>
       </c>
       <c r="K23" t="n">
-        <v>58.44</v>
+        <v>26.5</v>
       </c>
       <c r="L23" t="n">
-        <v>54.21</v>
+        <v>22.91</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>FRO</t>
+          <t>INSW</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>whole-company</t>
+          <t>WHOLE-COMPANY (hybrid aggregation)</t>
         </is>
       </c>
       <c r="C24" t="n">
-        <v>28.47</v>
+        <v>57.91</v>
       </c>
       <c r="D24" t="n">
-        <v>24.22</v>
+        <v>52.59</v>
       </c>
       <c r="E24" t="n">
-        <v>-14.93</v>
+        <v>-9.18</v>
       </c>
       <c r="F24" t="n">
-        <v>-30.9</v>
+        <v>-32.6</v>
       </c>
       <c r="G24" t="n">
-        <v>-40.3</v>
+        <v>-37.5</v>
       </c>
       <c r="H24" t="n">
-        <v>-9.4</v>
+        <v>-4.9</v>
       </c>
       <c r="I24" t="inlineStr">
         <is>
@@ -1548,10 +1548,10 @@
         </is>
       </c>
       <c r="K24" t="n">
-        <v>26.5</v>
+        <v>58.44</v>
       </c>
       <c r="L24" t="n">
-        <v>22.91</v>
+        <v>54.21</v>
       </c>
     </row>
     <row r="25">
@@ -1575,13 +1575,13 @@
         <v>-14.98</v>
       </c>
       <c r="F25" t="n">
-        <v>-34.6</v>
+        <v>-31.2</v>
       </c>
       <c r="G25" t="n">
-        <v>-43.4</v>
+        <v>-40.4</v>
       </c>
       <c r="H25" t="n">
-        <v>-8.800000000000001</v>
+        <v>-9.300000000000001</v>
       </c>
       <c r="I25" t="inlineStr">
         <is>
@@ -1621,13 +1621,13 @@
         <v>-15.76</v>
       </c>
       <c r="F26" t="n">
-        <v>-50.3</v>
+        <v>-48.3</v>
       </c>
       <c r="G26" t="n">
-        <v>-56.8</v>
+        <v>-55.1</v>
       </c>
       <c r="H26" t="n">
-        <v>-6.5</v>
+        <v>-6.8</v>
       </c>
       <c r="I26" t="inlineStr">
         <is>

--- a/outputs/transaction_anchor_comparison.xlsx
+++ b/outputs/transaction_anchor_comparison.xlsx
@@ -557,19 +557,19 @@
         <v>94.58</v>
       </c>
       <c r="D3" t="n">
-        <v>87.34999999999999</v>
+        <v>87.56999999999999</v>
       </c>
       <c r="E3" t="n">
-        <v>-7.65</v>
+        <v>-7.42</v>
       </c>
       <c r="F3" t="n">
         <v>61.2</v>
       </c>
       <c r="G3" t="n">
-        <v>50.1</v>
+        <v>50.4</v>
       </c>
       <c r="H3" t="n">
-        <v>-11.2</v>
+        <v>-10.9</v>
       </c>
       <c r="I3" t="inlineStr">
         <is>
@@ -585,7 +585,7 @@
         <v>60.66</v>
       </c>
       <c r="L3" t="n">
-        <v>56.46</v>
+        <v>56.56</v>
       </c>
     </row>
     <row r="4">
@@ -603,19 +603,19 @@
         <v>9.720000000000001</v>
       </c>
       <c r="D4" t="n">
-        <v>10.12</v>
+        <v>10.17</v>
       </c>
       <c r="E4" t="n">
-        <v>4.09</v>
+        <v>4.61</v>
       </c>
       <c r="F4" t="n">
         <v>34.5</v>
       </c>
       <c r="G4" t="n">
-        <v>40.2</v>
+        <v>40.8</v>
       </c>
       <c r="H4" t="n">
-        <v>5.7</v>
+        <v>6.3</v>
       </c>
       <c r="I4" t="inlineStr">
         <is>
@@ -631,13 +631,13 @@
         <v>9.17</v>
       </c>
       <c r="L4" t="n">
-        <v>9.56</v>
+        <v>9.6</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>BRUT</t>
+          <t>SBLK</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -646,22 +646,22 @@
         </is>
       </c>
       <c r="C5" t="n">
-        <v>8.800000000000001</v>
+        <v>29.77</v>
       </c>
       <c r="D5" t="n">
-        <v>8.800000000000001</v>
+        <v>30.13</v>
       </c>
       <c r="E5" t="n">
-        <v>0</v>
+        <v>1.21</v>
       </c>
       <c r="F5" t="n">
-        <v>14.8</v>
+        <v>12.6</v>
       </c>
       <c r="G5" t="n">
-        <v>12.8</v>
+        <v>13.8</v>
       </c>
       <c r="H5" t="n">
-        <v>-2</v>
+        <v>1.2</v>
       </c>
       <c r="I5" t="inlineStr">
         <is>
@@ -674,16 +674,16 @@
         </is>
       </c>
       <c r="K5" t="n">
-        <v>6.32</v>
+        <v>28.04</v>
       </c>
       <c r="L5" t="n">
-        <v>6.2</v>
+        <v>28.35</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>TRMD</t>
+          <t>BRUT</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -692,22 +692,22 @@
         </is>
       </c>
       <c r="C6" t="n">
-        <v>31.65</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="D6" t="n">
-        <v>30.34</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="E6" t="n">
-        <v>-4.11</v>
+        <v>0</v>
       </c>
       <c r="F6" t="n">
-        <v>16.1</v>
+        <v>14.8</v>
       </c>
       <c r="G6" t="n">
-        <v>12.1</v>
+        <v>12.8</v>
       </c>
       <c r="H6" t="n">
-        <v>-4</v>
+        <v>-2</v>
       </c>
       <c r="I6" t="inlineStr">
         <is>
@@ -720,16 +720,16 @@
         </is>
       </c>
       <c r="K6" t="n">
-        <v>33.03</v>
+        <v>6.32</v>
       </c>
       <c r="L6" t="n">
-        <v>31.9</v>
+        <v>6.21</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>SBLK</t>
+          <t>TRMD</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -738,22 +738,22 @@
         </is>
       </c>
       <c r="C7" t="n">
-        <v>29.77</v>
+        <v>31.65</v>
       </c>
       <c r="D7" t="n">
-        <v>29.34</v>
+        <v>30.3</v>
       </c>
       <c r="E7" t="n">
-        <v>-1.43</v>
+        <v>-4.25</v>
       </c>
       <c r="F7" t="n">
-        <v>12.6</v>
+        <v>16.1</v>
       </c>
       <c r="G7" t="n">
-        <v>11.2</v>
+        <v>12</v>
       </c>
       <c r="H7" t="n">
-        <v>-1.4</v>
+        <v>-4.1</v>
       </c>
       <c r="I7" t="inlineStr">
         <is>
@@ -766,10 +766,10 @@
         </is>
       </c>
       <c r="K7" t="n">
-        <v>28.04</v>
+        <v>33.03</v>
       </c>
       <c r="L7" t="n">
-        <v>27.69</v>
+        <v>31.87</v>
       </c>
     </row>
     <row r="8">
@@ -787,19 +787,19 @@
         <v>17.82</v>
       </c>
       <c r="D8" t="n">
-        <v>17.8</v>
+        <v>17.82</v>
       </c>
       <c r="E8" t="n">
-        <v>-0.13</v>
+        <v>-0.02</v>
       </c>
       <c r="F8" t="n">
         <v>9.4</v>
       </c>
       <c r="G8" t="n">
-        <v>9.300000000000001</v>
+        <v>9.4</v>
       </c>
       <c r="H8" t="n">
-        <v>-0.1</v>
+        <v>-0</v>
       </c>
       <c r="I8" t="inlineStr">
         <is>
@@ -815,7 +815,7 @@
         <v>16.85</v>
       </c>
       <c r="L8" t="n">
-        <v>16.83</v>
+        <v>16.85</v>
       </c>
     </row>
     <row r="9">
@@ -833,19 +833,19 @@
         <v>32.12</v>
       </c>
       <c r="D9" t="n">
-        <v>31.33</v>
+        <v>32.1</v>
       </c>
       <c r="E9" t="n">
-        <v>-2.45</v>
+        <v>-0.04</v>
       </c>
       <c r="F9" t="n">
         <v>9.4</v>
       </c>
       <c r="G9" t="n">
-        <v>6.8</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="H9" t="n">
-        <v>-2.5</v>
+        <v>-0.1</v>
       </c>
       <c r="I9" t="inlineStr">
         <is>
@@ -861,7 +861,7 @@
         <v>20.57</v>
       </c>
       <c r="L9" t="n">
-        <v>20.1</v>
+        <v>20.55</v>
       </c>
     </row>
     <row r="10">
@@ -879,19 +879,19 @@
         <v>83.31999999999999</v>
       </c>
       <c r="D10" t="n">
-        <v>77.51000000000001</v>
+        <v>77.73</v>
       </c>
       <c r="E10" t="n">
-        <v>-6.97</v>
+        <v>-6.71</v>
       </c>
       <c r="F10" t="n">
         <v>10.8</v>
       </c>
       <c r="G10" t="n">
-        <v>4.4</v>
+        <v>4.7</v>
       </c>
       <c r="H10" t="n">
-        <v>-6.4</v>
+        <v>-6.2</v>
       </c>
       <c r="I10" t="inlineStr">
         <is>
@@ -907,7 +907,7 @@
         <v>77.67</v>
       </c>
       <c r="L10" t="n">
-        <v>73.18000000000001</v>
+        <v>73.34999999999999</v>
       </c>
     </row>
     <row r="11">
@@ -928,7 +928,7 @@
         <v>15.49</v>
       </c>
       <c r="E11" t="n">
-        <v>-0.74</v>
+        <v>-0.77</v>
       </c>
       <c r="F11" t="n">
         <v>5.1</v>
@@ -1017,19 +1017,19 @@
         <v>80.97</v>
       </c>
       <c r="D13" t="n">
-        <v>77.47</v>
+        <v>77.13</v>
       </c>
       <c r="E13" t="n">
-        <v>-4.33</v>
+        <v>-4.74</v>
       </c>
       <c r="F13" t="n">
         <v>5</v>
       </c>
       <c r="G13" t="n">
-        <v>0.8</v>
+        <v>0.5</v>
       </c>
       <c r="H13" t="n">
-        <v>-4.1</v>
+        <v>-4.5</v>
       </c>
       <c r="I13" t="inlineStr">
         <is>
@@ -1045,7 +1045,7 @@
         <v>80.3</v>
       </c>
       <c r="L13" t="n">
-        <v>77.13</v>
+        <v>76.87</v>
       </c>
     </row>
     <row r="14">
@@ -1109,19 +1109,19 @@
         <v>25.53</v>
       </c>
       <c r="D15" t="n">
-        <v>24.69</v>
+        <v>25.48</v>
       </c>
       <c r="E15" t="n">
-        <v>-3.28</v>
+        <v>-0.17</v>
       </c>
       <c r="F15" t="n">
         <v>-1</v>
       </c>
       <c r="G15" t="n">
-        <v>-4</v>
+        <v>-1.2</v>
       </c>
       <c r="H15" t="n">
-        <v>-3</v>
+        <v>-0.2</v>
       </c>
       <c r="I15" t="inlineStr">
         <is>
@@ -1137,7 +1137,7 @@
         <v>23.87</v>
       </c>
       <c r="L15" t="n">
-        <v>23.15</v>
+        <v>23.82</v>
       </c>
     </row>
     <row r="16">
@@ -1158,16 +1158,16 @@
         <v>0.39</v>
       </c>
       <c r="E16" t="n">
-        <v>-4.64</v>
+        <v>-2.67</v>
       </c>
       <c r="F16" t="n">
         <v>-0.5</v>
       </c>
       <c r="G16" t="n">
-        <v>-4.6</v>
+        <v>-2.8</v>
       </c>
       <c r="H16" t="n">
-        <v>-4</v>
+        <v>-2.3</v>
       </c>
       <c r="I16" t="inlineStr">
         <is>
@@ -1201,19 +1201,19 @@
         <v>15.84</v>
       </c>
       <c r="D17" t="n">
-        <v>15.87</v>
+        <v>16.12</v>
       </c>
       <c r="E17" t="n">
-        <v>0.18</v>
+        <v>1.76</v>
       </c>
       <c r="F17" t="n">
         <v>-7.5</v>
       </c>
       <c r="G17" t="n">
-        <v>-7.3</v>
+        <v>-5.8</v>
       </c>
       <c r="H17" t="n">
-        <v>0.2</v>
+        <v>1.7</v>
       </c>
       <c r="I17" t="inlineStr">
         <is>
@@ -1229,7 +1229,7 @@
         <v>13.85</v>
       </c>
       <c r="L17" t="n">
-        <v>13.87</v>
+        <v>14.09</v>
       </c>
     </row>
     <row r="18">
@@ -1250,7 +1250,7 @@
         <v>5.57</v>
       </c>
       <c r="E18" t="n">
-        <v>-2.07</v>
+        <v>-2.09</v>
       </c>
       <c r="F18" t="n">
         <v>-12.7</v>
@@ -1339,19 +1339,19 @@
         <v>16.07</v>
       </c>
       <c r="D20" t="n">
-        <v>13.88</v>
+        <v>13.58</v>
       </c>
       <c r="E20" t="n">
-        <v>-13.65</v>
+        <v>-15.47</v>
       </c>
       <c r="F20" t="n">
         <v>-13.1</v>
       </c>
       <c r="G20" t="n">
-        <v>-23.4</v>
+        <v>-24.8</v>
       </c>
       <c r="H20" t="n">
-        <v>-10.3</v>
+        <v>-11.7</v>
       </c>
       <c r="I20" t="inlineStr">
         <is>
@@ -1367,7 +1367,7 @@
         <v>15.13</v>
       </c>
       <c r="L20" t="n">
-        <v>13.34</v>
+        <v>13.1</v>
       </c>
     </row>
     <row r="21">
@@ -1477,19 +1477,19 @@
         <v>28.47</v>
       </c>
       <c r="D23" t="n">
-        <v>24.22</v>
+        <v>24.11</v>
       </c>
       <c r="E23" t="n">
-        <v>-14.93</v>
+        <v>-15.33</v>
       </c>
       <c r="F23" t="n">
         <v>-27.4</v>
       </c>
       <c r="G23" t="n">
-        <v>-37.2</v>
+        <v>-37.5</v>
       </c>
       <c r="H23" t="n">
-        <v>-9.800000000000001</v>
+        <v>-10.2</v>
       </c>
       <c r="I23" t="inlineStr">
         <is>
@@ -1505,7 +1505,7 @@
         <v>26.5</v>
       </c>
       <c r="L23" t="n">
-        <v>22.91</v>
+        <v>22.8</v>
       </c>
     </row>
     <row r="24">
@@ -1523,19 +1523,19 @@
         <v>57.91</v>
       </c>
       <c r="D24" t="n">
-        <v>52.59</v>
+        <v>52.48</v>
       </c>
       <c r="E24" t="n">
-        <v>-9.18</v>
+        <v>-9.380000000000001</v>
       </c>
       <c r="F24" t="n">
         <v>-32.6</v>
       </c>
       <c r="G24" t="n">
-        <v>-37.5</v>
+        <v>-37.6</v>
       </c>
       <c r="H24" t="n">
-        <v>-4.9</v>
+        <v>-5</v>
       </c>
       <c r="I24" t="inlineStr">
         <is>
@@ -1551,7 +1551,7 @@
         <v>58.44</v>
       </c>
       <c r="L24" t="n">
-        <v>54.21</v>
+        <v>54.12</v>
       </c>
     </row>
     <row r="25">
@@ -1569,10 +1569,10 @@
         <v>40.4</v>
       </c>
       <c r="D25" t="n">
-        <v>34.35</v>
+        <v>34.42</v>
       </c>
       <c r="E25" t="n">
-        <v>-14.98</v>
+        <v>-14.81</v>
       </c>
       <c r="F25" t="n">
         <v>-31.2</v>
@@ -1597,7 +1597,7 @@
         <v>37.09</v>
       </c>
       <c r="L25" t="n">
-        <v>32.09</v>
+        <v>32.1</v>
       </c>
     </row>
     <row r="26">
@@ -1615,19 +1615,19 @@
         <v>3.32</v>
       </c>
       <c r="D26" t="n">
-        <v>2.79</v>
+        <v>2.85</v>
       </c>
       <c r="E26" t="n">
-        <v>-15.76</v>
+        <v>-14.2</v>
       </c>
       <c r="F26" t="n">
         <v>-48.3</v>
       </c>
       <c r="G26" t="n">
-        <v>-55.1</v>
+        <v>-54.4</v>
       </c>
       <c r="H26" t="n">
-        <v>-6.8</v>
+        <v>-6.1</v>
       </c>
       <c r="I26" t="inlineStr">
         <is>
@@ -1643,7 +1643,7 @@
         <v>3.13</v>
       </c>
       <c r="L26" t="n">
-        <v>2.72</v>
+        <v>2.76</v>
       </c>
     </row>
   </sheetData>

--- a/outputs/transaction_anchor_comparison.xlsx
+++ b/outputs/transaction_anchor_comparison.xlsx
@@ -603,19 +603,19 @@
         <v>9.720000000000001</v>
       </c>
       <c r="D4" t="n">
-        <v>10.17</v>
+        <v>10.02</v>
       </c>
       <c r="E4" t="n">
-        <v>4.61</v>
+        <v>3.1</v>
       </c>
       <c r="F4" t="n">
         <v>34.5</v>
       </c>
       <c r="G4" t="n">
-        <v>40.8</v>
+        <v>38.9</v>
       </c>
       <c r="H4" t="n">
-        <v>6.3</v>
+        <v>4.4</v>
       </c>
       <c r="I4" t="inlineStr">
         <is>
@@ -631,7 +631,7 @@
         <v>9.17</v>
       </c>
       <c r="L4" t="n">
-        <v>9.6</v>
+        <v>9.470000000000001</v>
       </c>
     </row>
     <row r="5">

--- a/outputs/transaction_anchor_comparison.xlsx
+++ b/outputs/transaction_anchor_comparison.xlsx
@@ -517,10 +517,10 @@
         <v>0</v>
       </c>
       <c r="F2" t="n">
-        <v>61.8</v>
+        <v>59.9</v>
       </c>
       <c r="G2" t="n">
-        <v>61.8</v>
+        <v>59.9</v>
       </c>
       <c r="H2" t="n">
         <v>0</v>
@@ -563,13 +563,13 @@
         <v>-7.42</v>
       </c>
       <c r="F3" t="n">
-        <v>61.2</v>
+        <v>56.1</v>
       </c>
       <c r="G3" t="n">
-        <v>50.4</v>
+        <v>45.6</v>
       </c>
       <c r="H3" t="n">
-        <v>-10.9</v>
+        <v>-10.5</v>
       </c>
       <c r="I3" t="inlineStr">
         <is>
@@ -609,13 +609,13 @@
         <v>3.1</v>
       </c>
       <c r="F4" t="n">
-        <v>34.5</v>
+        <v>28.1</v>
       </c>
       <c r="G4" t="n">
-        <v>38.9</v>
+        <v>32.3</v>
       </c>
       <c r="H4" t="n">
-        <v>4.4</v>
+        <v>4.2</v>
       </c>
       <c r="I4" t="inlineStr">
         <is>
@@ -637,7 +637,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>SBLK</t>
+          <t>BRUT</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -646,22 +646,22 @@
         </is>
       </c>
       <c r="C5" t="n">
-        <v>29.77</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="D5" t="n">
-        <v>30.13</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="E5" t="n">
-        <v>1.21</v>
+        <v>0</v>
       </c>
       <c r="F5" t="n">
-        <v>12.6</v>
+        <v>16.6</v>
       </c>
       <c r="G5" t="n">
-        <v>13.8</v>
+        <v>14.6</v>
       </c>
       <c r="H5" t="n">
-        <v>1.2</v>
+        <v>-2</v>
       </c>
       <c r="I5" t="inlineStr">
         <is>
@@ -674,16 +674,16 @@
         </is>
       </c>
       <c r="K5" t="n">
-        <v>28.04</v>
+        <v>6.32</v>
       </c>
       <c r="L5" t="n">
-        <v>28.35</v>
+        <v>6.21</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>BRUT</t>
+          <t>CMDB</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -692,22 +692,22 @@
         </is>
       </c>
       <c r="C6" t="n">
-        <v>8.800000000000001</v>
+        <v>32.12</v>
       </c>
       <c r="D6" t="n">
-        <v>8.800000000000001</v>
+        <v>32.1</v>
       </c>
       <c r="E6" t="n">
-        <v>0</v>
+        <v>-0.04</v>
       </c>
       <c r="F6" t="n">
-        <v>14.8</v>
+        <v>10.4</v>
       </c>
       <c r="G6" t="n">
-        <v>12.8</v>
+        <v>10.3</v>
       </c>
       <c r="H6" t="n">
-        <v>-2</v>
+        <v>-0.1</v>
       </c>
       <c r="I6" t="inlineStr">
         <is>
@@ -720,10 +720,10 @@
         </is>
       </c>
       <c r="K6" t="n">
-        <v>6.32</v>
+        <v>20.57</v>
       </c>
       <c r="L6" t="n">
-        <v>6.21</v>
+        <v>20.55</v>
       </c>
     </row>
     <row r="7">
@@ -747,13 +747,13 @@
         <v>-4.25</v>
       </c>
       <c r="F7" t="n">
-        <v>16.1</v>
+        <v>13.6</v>
       </c>
       <c r="G7" t="n">
-        <v>12</v>
+        <v>9.6</v>
       </c>
       <c r="H7" t="n">
-        <v>-4.1</v>
+        <v>-4</v>
       </c>
       <c r="I7" t="inlineStr">
         <is>
@@ -775,7 +775,7 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>ASC</t>
+          <t>SBLK</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -784,22 +784,22 @@
         </is>
       </c>
       <c r="C8" t="n">
-        <v>17.82</v>
+        <v>29.77</v>
       </c>
       <c r="D8" t="n">
-        <v>17.82</v>
+        <v>30.13</v>
       </c>
       <c r="E8" t="n">
-        <v>-0.02</v>
+        <v>1.21</v>
       </c>
       <c r="F8" t="n">
-        <v>9.4</v>
+        <v>7.5</v>
       </c>
       <c r="G8" t="n">
-        <v>9.4</v>
+        <v>8.699999999999999</v>
       </c>
       <c r="H8" t="n">
-        <v>-0</v>
+        <v>1.2</v>
       </c>
       <c r="I8" t="inlineStr">
         <is>
@@ -812,16 +812,16 @@
         </is>
       </c>
       <c r="K8" t="n">
-        <v>16.85</v>
+        <v>28.04</v>
       </c>
       <c r="L8" t="n">
-        <v>16.85</v>
+        <v>28.35</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>CMDB</t>
+          <t>ASC</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -830,22 +830,22 @@
         </is>
       </c>
       <c r="C9" t="n">
-        <v>32.12</v>
+        <v>17.82</v>
       </c>
       <c r="D9" t="n">
-        <v>32.1</v>
+        <v>17.82</v>
       </c>
       <c r="E9" t="n">
-        <v>-0.04</v>
+        <v>-0.02</v>
       </c>
       <c r="F9" t="n">
-        <v>9.4</v>
+        <v>6.5</v>
       </c>
       <c r="G9" t="n">
-        <v>9.199999999999999</v>
+        <v>6.5</v>
       </c>
       <c r="H9" t="n">
-        <v>-0.1</v>
+        <v>-0</v>
       </c>
       <c r="I9" t="inlineStr">
         <is>
@@ -858,16 +858,16 @@
         </is>
       </c>
       <c r="K9" t="n">
-        <v>20.57</v>
+        <v>16.85</v>
       </c>
       <c r="L9" t="n">
-        <v>20.55</v>
+        <v>16.85</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>TNK</t>
+          <t>CAPT</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -876,22 +876,22 @@
         </is>
       </c>
       <c r="C10" t="n">
-        <v>83.31999999999999</v>
+        <v>15.61</v>
       </c>
       <c r="D10" t="n">
-        <v>77.73</v>
+        <v>15.49</v>
       </c>
       <c r="E10" t="n">
-        <v>-6.71</v>
+        <v>-0.77</v>
       </c>
       <c r="F10" t="n">
-        <v>10.8</v>
+        <v>6</v>
       </c>
       <c r="G10" t="n">
-        <v>4.7</v>
+        <v>4.3</v>
       </c>
       <c r="H10" t="n">
-        <v>-6.2</v>
+        <v>-1.8</v>
       </c>
       <c r="I10" t="inlineStr">
         <is>
@@ -904,16 +904,16 @@
         </is>
       </c>
       <c r="K10" t="n">
-        <v>77.67</v>
+        <v>13.37</v>
       </c>
       <c r="L10" t="n">
-        <v>73.34999999999999</v>
+        <v>13.14</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>CAPT</t>
+          <t>TNK</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -922,22 +922,22 @@
         </is>
       </c>
       <c r="C11" t="n">
-        <v>15.61</v>
+        <v>83.31999999999999</v>
       </c>
       <c r="D11" t="n">
-        <v>15.49</v>
+        <v>77.73</v>
       </c>
       <c r="E11" t="n">
-        <v>-0.77</v>
+        <v>-6.71</v>
       </c>
       <c r="F11" t="n">
-        <v>5.1</v>
+        <v>8</v>
       </c>
       <c r="G11" t="n">
-        <v>3.3</v>
+        <v>2</v>
       </c>
       <c r="H11" t="n">
-        <v>-1.8</v>
+        <v>-6</v>
       </c>
       <c r="I11" t="inlineStr">
         <is>
@@ -950,16 +950,16 @@
         </is>
       </c>
       <c r="K11" t="n">
-        <v>13.37</v>
+        <v>77.67</v>
       </c>
       <c r="L11" t="n">
-        <v>13.14</v>
+        <v>73.34999999999999</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>GSL</t>
+          <t>FLNG</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -968,19 +968,19 @@
         </is>
       </c>
       <c r="C12" t="n">
-        <v>38.59</v>
+        <v>28.45</v>
       </c>
       <c r="D12" t="n">
-        <v>38.59</v>
+        <v>28.45</v>
       </c>
       <c r="E12" t="n">
         <v>0</v>
       </c>
       <c r="F12" t="n">
-        <v>0.9</v>
+        <v>0.4</v>
       </c>
       <c r="G12" t="n">
-        <v>0.9</v>
+        <v>0.4</v>
       </c>
       <c r="H12" t="n">
         <v>0</v>
@@ -996,16 +996,16 @@
         </is>
       </c>
       <c r="K12" t="n">
-        <v>40.54</v>
+        <v>30.67</v>
       </c>
       <c r="L12" t="n">
-        <v>40.54</v>
+        <v>30.67</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>STNG</t>
+          <t>GSL</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -1014,22 +1014,22 @@
         </is>
       </c>
       <c r="C13" t="n">
-        <v>80.97</v>
+        <v>38.59</v>
       </c>
       <c r="D13" t="n">
-        <v>77.13</v>
+        <v>38.59</v>
       </c>
       <c r="E13" t="n">
-        <v>-4.74</v>
+        <v>0</v>
       </c>
       <c r="F13" t="n">
-        <v>5</v>
+        <v>-1.4</v>
       </c>
       <c r="G13" t="n">
-        <v>0.5</v>
+        <v>-1.4</v>
       </c>
       <c r="H13" t="n">
-        <v>-4.5</v>
+        <v>0</v>
       </c>
       <c r="I13" t="inlineStr">
         <is>
@@ -1042,16 +1042,16 @@
         </is>
       </c>
       <c r="K13" t="n">
-        <v>80.3</v>
+        <v>40.54</v>
       </c>
       <c r="L13" t="n">
-        <v>76.87</v>
+        <v>40.54</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>FLNG</t>
+          <t>STNG</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1060,22 +1060,22 @@
         </is>
       </c>
       <c r="C14" t="n">
-        <v>28.45</v>
+        <v>80.97</v>
       </c>
       <c r="D14" t="n">
-        <v>28.45</v>
+        <v>77.13</v>
       </c>
       <c r="E14" t="n">
-        <v>0</v>
+        <v>-4.74</v>
       </c>
       <c r="F14" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="G14" t="n">
-        <v>0</v>
+        <v>-1.4</v>
       </c>
       <c r="H14" t="n">
-        <v>0</v>
+        <v>-4.4</v>
       </c>
       <c r="I14" t="inlineStr">
         <is>
@@ -1088,16 +1088,16 @@
         </is>
       </c>
       <c r="K14" t="n">
-        <v>30.67</v>
+        <v>80.3</v>
       </c>
       <c r="L14" t="n">
-        <v>30.67</v>
+        <v>76.87</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>GNK</t>
+          <t>2343</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1106,22 +1106,22 @@
         </is>
       </c>
       <c r="C15" t="n">
-        <v>25.53</v>
+        <v>0.4</v>
       </c>
       <c r="D15" t="n">
-        <v>25.48</v>
+        <v>0.39</v>
       </c>
       <c r="E15" t="n">
-        <v>-0.17</v>
+        <v>-2.67</v>
       </c>
       <c r="F15" t="n">
-        <v>-1</v>
+        <v>-0.2</v>
       </c>
       <c r="G15" t="n">
-        <v>-1.2</v>
+        <v>-2.5</v>
       </c>
       <c r="H15" t="n">
-        <v>-0.2</v>
+        <v>-2.3</v>
       </c>
       <c r="I15" t="inlineStr">
         <is>
@@ -1134,16 +1134,16 @@
         </is>
       </c>
       <c r="K15" t="n">
-        <v>23.87</v>
+        <v>0.39</v>
       </c>
       <c r="L15" t="n">
-        <v>23.82</v>
+        <v>0.38</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>2343</t>
+          <t>GNK</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1152,38 +1152,38 @@
         </is>
       </c>
       <c r="C16" t="n">
-        <v>0.4</v>
+        <v>25.53</v>
       </c>
       <c r="D16" t="n">
-        <v>0.39</v>
+        <v>25.48</v>
       </c>
       <c r="E16" t="n">
-        <v>-2.67</v>
+        <v>-0.17</v>
       </c>
       <c r="F16" t="n">
-        <v>-0.5</v>
+        <v>-5.5</v>
       </c>
       <c r="G16" t="n">
-        <v>-2.8</v>
+        <v>-5.7</v>
       </c>
       <c r="H16" t="n">
-        <v>-2.3</v>
+        <v>-0.2</v>
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>HOLD (fairly valued)</t>
+          <t>TRIM/SHORT (overvalued)</t>
         </is>
       </c>
       <c r="J16" t="inlineStr">
         <is>
-          <t>HOLD (fairly valued)</t>
+          <t>TRIM/SHORT (overvalued)</t>
         </is>
       </c>
       <c r="K16" t="n">
-        <v>0.39</v>
+        <v>23.87</v>
       </c>
       <c r="L16" t="n">
-        <v>0.38</v>
+        <v>23.82</v>
       </c>
     </row>
     <row r="17">
@@ -1207,10 +1207,10 @@
         <v>1.76</v>
       </c>
       <c r="F17" t="n">
-        <v>-7.5</v>
+        <v>-8.199999999999999</v>
       </c>
       <c r="G17" t="n">
-        <v>-5.8</v>
+        <v>-6.5</v>
       </c>
       <c r="H17" t="n">
         <v>1.7</v>
@@ -1253,10 +1253,10 @@
         <v>-2.09</v>
       </c>
       <c r="F18" t="n">
-        <v>-12.7</v>
+        <v>-13.7</v>
       </c>
       <c r="G18" t="n">
-        <v>-14.1</v>
+        <v>-15</v>
       </c>
       <c r="H18" t="n">
         <v>-1.4</v>
@@ -1299,10 +1299,10 @@
         <v>0</v>
       </c>
       <c r="F19" t="n">
-        <v>-16.9</v>
+        <v>-16.3</v>
       </c>
       <c r="G19" t="n">
-        <v>-16.9</v>
+        <v>-16.3</v>
       </c>
       <c r="H19" t="n">
         <v>0</v>
@@ -1345,13 +1345,13 @@
         <v>-15.47</v>
       </c>
       <c r="F20" t="n">
-        <v>-13.1</v>
+        <v>-15.5</v>
       </c>
       <c r="G20" t="n">
-        <v>-24.8</v>
+        <v>-26.8</v>
       </c>
       <c r="H20" t="n">
-        <v>-11.7</v>
+        <v>-11.3</v>
       </c>
       <c r="I20" t="inlineStr">
         <is>
@@ -1391,10 +1391,10 @@
         <v>-0.05</v>
       </c>
       <c r="F21" t="n">
-        <v>-25.5</v>
+        <v>-29.1</v>
       </c>
       <c r="G21" t="n">
-        <v>-25.5</v>
+        <v>-29.1</v>
       </c>
       <c r="H21" t="n">
         <v>-0</v>
@@ -1437,10 +1437,10 @@
         <v>-0.07000000000000001</v>
       </c>
       <c r="F22" t="n">
-        <v>-28.9</v>
+        <v>-31.4</v>
       </c>
       <c r="G22" t="n">
-        <v>-28.9</v>
+        <v>-31.5</v>
       </c>
       <c r="H22" t="n">
         <v>-0</v>
@@ -1483,13 +1483,13 @@
         <v>-15.33</v>
       </c>
       <c r="F23" t="n">
-        <v>-27.4</v>
+        <v>-28.2</v>
       </c>
       <c r="G23" t="n">
-        <v>-37.5</v>
+        <v>-38.3</v>
       </c>
       <c r="H23" t="n">
-        <v>-10.2</v>
+        <v>-10</v>
       </c>
       <c r="I23" t="inlineStr">
         <is>
@@ -1529,13 +1529,13 @@
         <v>-9.380000000000001</v>
       </c>
       <c r="F24" t="n">
-        <v>-32.6</v>
+        <v>-33.9</v>
       </c>
       <c r="G24" t="n">
-        <v>-37.6</v>
+        <v>-38.8</v>
       </c>
       <c r="H24" t="n">
-        <v>-5</v>
+        <v>-4.9</v>
       </c>
       <c r="I24" t="inlineStr">
         <is>
@@ -1575,13 +1575,13 @@
         <v>-14.81</v>
       </c>
       <c r="F25" t="n">
-        <v>-31.2</v>
+        <v>-31.6</v>
       </c>
       <c r="G25" t="n">
-        <v>-40.4</v>
+        <v>-40.8</v>
       </c>
       <c r="H25" t="n">
-        <v>-9.300000000000001</v>
+        <v>-9.199999999999999</v>
       </c>
       <c r="I25" t="inlineStr">
         <is>
@@ -1621,13 +1621,13 @@
         <v>-14.2</v>
       </c>
       <c r="F26" t="n">
-        <v>-48.3</v>
+        <v>-49.2</v>
       </c>
       <c r="G26" t="n">
-        <v>-54.4</v>
+        <v>-55.2</v>
       </c>
       <c r="H26" t="n">
-        <v>-6.1</v>
+        <v>-6</v>
       </c>
       <c r="I26" t="inlineStr">
         <is>

--- a/outputs/transaction_anchor_comparison.xlsx
+++ b/outputs/transaction_anchor_comparison.xlsx
@@ -609,10 +609,10 @@
         <v>3.1</v>
       </c>
       <c r="F4" t="n">
-        <v>28.1</v>
+        <v>27.4</v>
       </c>
       <c r="G4" t="n">
-        <v>32.3</v>
+        <v>31.6</v>
       </c>
       <c r="H4" t="n">
         <v>4.2</v>
@@ -628,10 +628,10 @@
         </is>
       </c>
       <c r="K4" t="n">
-        <v>9.17</v>
+        <v>9.119999999999999</v>
       </c>
       <c r="L4" t="n">
-        <v>9.470000000000001</v>
+        <v>9.42</v>
       </c>
     </row>
     <row r="5">
@@ -701,10 +701,10 @@
         <v>-0.04</v>
       </c>
       <c r="F6" t="n">
-        <v>10.4</v>
+        <v>10</v>
       </c>
       <c r="G6" t="n">
-        <v>10.3</v>
+        <v>9.9</v>
       </c>
       <c r="H6" t="n">
         <v>-0.1</v>
@@ -720,10 +720,10 @@
         </is>
       </c>
       <c r="K6" t="n">
-        <v>20.57</v>
+        <v>20.49</v>
       </c>
       <c r="L6" t="n">
-        <v>20.55</v>
+        <v>20.47</v>
       </c>
     </row>
     <row r="7">
@@ -793,10 +793,10 @@
         <v>1.21</v>
       </c>
       <c r="F8" t="n">
-        <v>7.5</v>
+        <v>6.9</v>
       </c>
       <c r="G8" t="n">
-        <v>8.699999999999999</v>
+        <v>8</v>
       </c>
       <c r="H8" t="n">
         <v>1.2</v>
@@ -812,10 +812,10 @@
         </is>
       </c>
       <c r="K8" t="n">
-        <v>28.04</v>
+        <v>27.89</v>
       </c>
       <c r="L8" t="n">
-        <v>28.35</v>
+        <v>28.19</v>
       </c>
     </row>
     <row r="9">
@@ -1115,10 +1115,10 @@
         <v>-2.67</v>
       </c>
       <c r="F15" t="n">
-        <v>-0.2</v>
+        <v>-0.6</v>
       </c>
       <c r="G15" t="n">
-        <v>-2.5</v>
+        <v>-2.9</v>
       </c>
       <c r="H15" t="n">
         <v>-2.3</v>
@@ -1161,10 +1161,10 @@
         <v>-0.17</v>
       </c>
       <c r="F16" t="n">
-        <v>-5.5</v>
+        <v>-6.1</v>
       </c>
       <c r="G16" t="n">
-        <v>-5.7</v>
+        <v>-6.4</v>
       </c>
       <c r="H16" t="n">
         <v>-0.2</v>
@@ -1180,10 +1180,10 @@
         </is>
       </c>
       <c r="K16" t="n">
-        <v>23.87</v>
+        <v>23.71</v>
       </c>
       <c r="L16" t="n">
-        <v>23.82</v>
+        <v>23.66</v>
       </c>
     </row>
     <row r="17">
@@ -1207,13 +1207,13 @@
         <v>1.76</v>
       </c>
       <c r="F17" t="n">
-        <v>-8.199999999999999</v>
+        <v>-8.9</v>
       </c>
       <c r="G17" t="n">
-        <v>-6.5</v>
+        <v>-7.3</v>
       </c>
       <c r="H17" t="n">
-        <v>1.7</v>
+        <v>1.6</v>
       </c>
       <c r="I17" t="inlineStr">
         <is>
@@ -1226,10 +1226,10 @@
         </is>
       </c>
       <c r="K17" t="n">
-        <v>13.85</v>
+        <v>13.74</v>
       </c>
       <c r="L17" t="n">
-        <v>14.09</v>
+        <v>13.99</v>
       </c>
     </row>
     <row r="18">

--- a/outputs/transaction_anchor_comparison.xlsx
+++ b/outputs/transaction_anchor_comparison.xlsx
@@ -517,10 +517,10 @@
         <v>0</v>
       </c>
       <c r="F2" t="n">
-        <v>59.9</v>
+        <v>53.8</v>
       </c>
       <c r="G2" t="n">
-        <v>59.9</v>
+        <v>53.8</v>
       </c>
       <c r="H2" t="n">
         <v>0</v>
@@ -563,13 +563,13 @@
         <v>-7.42</v>
       </c>
       <c r="F3" t="n">
-        <v>56.1</v>
+        <v>54</v>
       </c>
       <c r="G3" t="n">
-        <v>45.6</v>
+        <v>43.6</v>
       </c>
       <c r="H3" t="n">
-        <v>-10.5</v>
+        <v>-10.4</v>
       </c>
       <c r="I3" t="inlineStr">
         <is>
@@ -609,13 +609,13 @@
         <v>3.1</v>
       </c>
       <c r="F4" t="n">
-        <v>27.4</v>
+        <v>18.9</v>
       </c>
       <c r="G4" t="n">
-        <v>31.6</v>
+        <v>22.9</v>
       </c>
       <c r="H4" t="n">
-        <v>4.2</v>
+        <v>3.9</v>
       </c>
       <c r="I4" t="inlineStr">
         <is>
@@ -637,7 +637,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>BRUT</t>
+          <t>CMDB</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -646,22 +646,22 @@
         </is>
       </c>
       <c r="C5" t="n">
-        <v>8.800000000000001</v>
+        <v>32.12</v>
       </c>
       <c r="D5" t="n">
-        <v>8.800000000000001</v>
+        <v>32.1</v>
       </c>
       <c r="E5" t="n">
-        <v>0</v>
+        <v>-0.04</v>
       </c>
       <c r="F5" t="n">
-        <v>16.6</v>
+        <v>8.699999999999999</v>
       </c>
       <c r="G5" t="n">
-        <v>14.6</v>
+        <v>8.6</v>
       </c>
       <c r="H5" t="n">
-        <v>-2</v>
+        <v>-0.1</v>
       </c>
       <c r="I5" t="inlineStr">
         <is>
@@ -674,16 +674,16 @@
         </is>
       </c>
       <c r="K5" t="n">
-        <v>6.32</v>
+        <v>20.49</v>
       </c>
       <c r="L5" t="n">
-        <v>6.21</v>
+        <v>20.47</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>CMDB</t>
+          <t>BRUT</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -692,22 +692,22 @@
         </is>
       </c>
       <c r="C6" t="n">
-        <v>32.12</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="D6" t="n">
-        <v>32.1</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="E6" t="n">
-        <v>-0.04</v>
+        <v>0</v>
       </c>
       <c r="F6" t="n">
-        <v>10</v>
+        <v>10.3</v>
       </c>
       <c r="G6" t="n">
-        <v>9.9</v>
+        <v>8.4</v>
       </c>
       <c r="H6" t="n">
-        <v>-0.1</v>
+        <v>-1.9</v>
       </c>
       <c r="I6" t="inlineStr">
         <is>
@@ -720,10 +720,10 @@
         </is>
       </c>
       <c r="K6" t="n">
-        <v>20.49</v>
+        <v>6.32</v>
       </c>
       <c r="L6" t="n">
-        <v>20.47</v>
+        <v>6.21</v>
       </c>
     </row>
     <row r="7">
@@ -747,13 +747,13 @@
         <v>-4.25</v>
       </c>
       <c r="F7" t="n">
-        <v>13.6</v>
+        <v>9.1</v>
       </c>
       <c r="G7" t="n">
-        <v>9.6</v>
+        <v>5.2</v>
       </c>
       <c r="H7" t="n">
-        <v>-4</v>
+        <v>-3.8</v>
       </c>
       <c r="I7" t="inlineStr">
         <is>
@@ -775,7 +775,7 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>SBLK</t>
+          <t>ASC</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -784,44 +784,44 @@
         </is>
       </c>
       <c r="C8" t="n">
-        <v>29.77</v>
+        <v>17.82</v>
       </c>
       <c r="D8" t="n">
-        <v>30.13</v>
+        <v>17.82</v>
       </c>
       <c r="E8" t="n">
-        <v>1.21</v>
+        <v>-0.02</v>
       </c>
       <c r="F8" t="n">
-        <v>6.9</v>
+        <v>1.5</v>
       </c>
       <c r="G8" t="n">
-        <v>8</v>
+        <v>1.4</v>
       </c>
       <c r="H8" t="n">
-        <v>1.2</v>
+        <v>-0</v>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>BUY (undervalued)</t>
+          <t>HOLD (fairly valued)</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>BUY (undervalued)</t>
+          <t>HOLD (fairly valued)</t>
         </is>
       </c>
       <c r="K8" t="n">
-        <v>27.89</v>
+        <v>16.85</v>
       </c>
       <c r="L8" t="n">
-        <v>28.19</v>
+        <v>16.85</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>ASC</t>
+          <t>CAPT</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -830,44 +830,44 @@
         </is>
       </c>
       <c r="C9" t="n">
-        <v>17.82</v>
+        <v>15.61</v>
       </c>
       <c r="D9" t="n">
-        <v>17.82</v>
+        <v>15.49</v>
       </c>
       <c r="E9" t="n">
-        <v>-0.02</v>
+        <v>-0.77</v>
       </c>
       <c r="F9" t="n">
-        <v>6.5</v>
+        <v>2.7</v>
       </c>
       <c r="G9" t="n">
-        <v>6.5</v>
+        <v>1</v>
       </c>
       <c r="H9" t="n">
-        <v>-0</v>
+        <v>-1.7</v>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>BUY (undervalued)</t>
+          <t>HOLD (fairly valued)</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>BUY (undervalued)</t>
+          <t>HOLD (fairly valued)</t>
         </is>
       </c>
       <c r="K9" t="n">
-        <v>16.85</v>
+        <v>13.37</v>
       </c>
       <c r="L9" t="n">
-        <v>16.85</v>
+        <v>13.14</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>CAPT</t>
+          <t>SBLK</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -876,26 +876,26 @@
         </is>
       </c>
       <c r="C10" t="n">
-        <v>15.61</v>
+        <v>29.77</v>
       </c>
       <c r="D10" t="n">
-        <v>15.49</v>
+        <v>30.13</v>
       </c>
       <c r="E10" t="n">
-        <v>-0.77</v>
+        <v>1.21</v>
       </c>
       <c r="F10" t="n">
-        <v>6</v>
+        <v>-0.9</v>
       </c>
       <c r="G10" t="n">
-        <v>4.3</v>
+        <v>0.2</v>
       </c>
       <c r="H10" t="n">
-        <v>-1.8</v>
+        <v>1.1</v>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>BUY (undervalued)</t>
+          <t>HOLD (fairly valued)</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
@@ -904,16 +904,16 @@
         </is>
       </c>
       <c r="K10" t="n">
-        <v>13.37</v>
+        <v>27.89</v>
       </c>
       <c r="L10" t="n">
-        <v>13.14</v>
+        <v>28.19</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>TNK</t>
+          <t>FLNG</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -922,26 +922,26 @@
         </is>
       </c>
       <c r="C11" t="n">
-        <v>83.31999999999999</v>
+        <v>28.45</v>
       </c>
       <c r="D11" t="n">
-        <v>77.73</v>
+        <v>28.45</v>
       </c>
       <c r="E11" t="n">
-        <v>-6.71</v>
+        <v>0</v>
       </c>
       <c r="F11" t="n">
-        <v>8</v>
+        <v>-0.6</v>
       </c>
       <c r="G11" t="n">
-        <v>2</v>
+        <v>-0.6</v>
       </c>
       <c r="H11" t="n">
-        <v>-6</v>
+        <v>0</v>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>BUY (undervalued)</t>
+          <t>HOLD (fairly valued)</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
@@ -950,16 +950,16 @@
         </is>
       </c>
       <c r="K11" t="n">
-        <v>77.67</v>
+        <v>30.67</v>
       </c>
       <c r="L11" t="n">
-        <v>73.34999999999999</v>
+        <v>30.67</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>FLNG</t>
+          <t>TNK</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -968,22 +968,22 @@
         </is>
       </c>
       <c r="C12" t="n">
-        <v>28.45</v>
+        <v>83.31999999999999</v>
       </c>
       <c r="D12" t="n">
-        <v>28.45</v>
+        <v>77.73</v>
       </c>
       <c r="E12" t="n">
-        <v>0</v>
+        <v>-6.71</v>
       </c>
       <c r="F12" t="n">
-        <v>0.4</v>
+        <v>2.5</v>
       </c>
       <c r="G12" t="n">
-        <v>0.4</v>
+        <v>-3.2</v>
       </c>
       <c r="H12" t="n">
-        <v>0</v>
+        <v>-5.7</v>
       </c>
       <c r="I12" t="inlineStr">
         <is>
@@ -996,16 +996,16 @@
         </is>
       </c>
       <c r="K12" t="n">
-        <v>30.67</v>
+        <v>77.67</v>
       </c>
       <c r="L12" t="n">
-        <v>30.67</v>
+        <v>73.34999999999999</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>GSL</t>
+          <t>STNG</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -1014,22 +1014,22 @@
         </is>
       </c>
       <c r="C13" t="n">
-        <v>38.59</v>
+        <v>80.97</v>
       </c>
       <c r="D13" t="n">
-        <v>38.59</v>
+        <v>77.13</v>
       </c>
       <c r="E13" t="n">
-        <v>0</v>
+        <v>-4.74</v>
       </c>
       <c r="F13" t="n">
-        <v>-1.4</v>
+        <v>1</v>
       </c>
       <c r="G13" t="n">
-        <v>-1.4</v>
+        <v>-3.3</v>
       </c>
       <c r="H13" t="n">
-        <v>0</v>
+        <v>-4.3</v>
       </c>
       <c r="I13" t="inlineStr">
         <is>
@@ -1042,16 +1042,16 @@
         </is>
       </c>
       <c r="K13" t="n">
-        <v>40.54</v>
+        <v>80.3</v>
       </c>
       <c r="L13" t="n">
-        <v>40.54</v>
+        <v>76.87</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>STNG</t>
+          <t>GSL</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1060,38 +1060,38 @@
         </is>
       </c>
       <c r="C14" t="n">
-        <v>80.97</v>
+        <v>38.59</v>
       </c>
       <c r="D14" t="n">
-        <v>77.13</v>
+        <v>38.59</v>
       </c>
       <c r="E14" t="n">
-        <v>-4.74</v>
+        <v>0</v>
       </c>
       <c r="F14" t="n">
-        <v>3</v>
+        <v>-7</v>
       </c>
       <c r="G14" t="n">
-        <v>-1.4</v>
+        <v>-7</v>
       </c>
       <c r="H14" t="n">
-        <v>-4.4</v>
+        <v>0</v>
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>HOLD (fairly valued)</t>
+          <t>TRIM/SHORT (overvalued)</t>
         </is>
       </c>
       <c r="J14" t="inlineStr">
         <is>
-          <t>HOLD (fairly valued)</t>
+          <t>TRIM/SHORT (overvalued)</t>
         </is>
       </c>
       <c r="K14" t="n">
-        <v>80.3</v>
+        <v>40.54</v>
       </c>
       <c r="L14" t="n">
-        <v>76.87</v>
+        <v>40.54</v>
       </c>
     </row>
     <row r="15">
@@ -1115,22 +1115,22 @@
         <v>-2.67</v>
       </c>
       <c r="F15" t="n">
-        <v>-0.6</v>
+        <v>-6.9</v>
       </c>
       <c r="G15" t="n">
-        <v>-2.9</v>
+        <v>-9</v>
       </c>
       <c r="H15" t="n">
-        <v>-2.3</v>
+        <v>-2.1</v>
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>HOLD (fairly valued)</t>
+          <t>TRIM/SHORT (overvalued)</t>
         </is>
       </c>
       <c r="J15" t="inlineStr">
         <is>
-          <t>HOLD (fairly valued)</t>
+          <t>TRIM/SHORT (overvalued)</t>
         </is>
       </c>
       <c r="K15" t="n">
@@ -1143,31 +1143,31 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>GNK</t>
+          <t>CMBT</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>whole-company</t>
+          <t>WHOLE-COMPANY (hybrid aggregation)</t>
         </is>
       </c>
       <c r="C16" t="n">
-        <v>25.53</v>
+        <v>15.84</v>
       </c>
       <c r="D16" t="n">
-        <v>25.48</v>
+        <v>16.12</v>
       </c>
       <c r="E16" t="n">
-        <v>-0.17</v>
+        <v>1.76</v>
       </c>
       <c r="F16" t="n">
-        <v>-6.1</v>
+        <v>-12.7</v>
       </c>
       <c r="G16" t="n">
-        <v>-6.4</v>
+        <v>-11.1</v>
       </c>
       <c r="H16" t="n">
-        <v>-0.2</v>
+        <v>1.6</v>
       </c>
       <c r="I16" t="inlineStr">
         <is>
@@ -1180,40 +1180,40 @@
         </is>
       </c>
       <c r="K16" t="n">
-        <v>23.71</v>
+        <v>13.74</v>
       </c>
       <c r="L16" t="n">
-        <v>23.66</v>
+        <v>13.99</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>CMBT</t>
+          <t>GNK</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>WHOLE-COMPANY (hybrid aggregation)</t>
+          <t>whole-company</t>
         </is>
       </c>
       <c r="C17" t="n">
-        <v>15.84</v>
+        <v>25.53</v>
       </c>
       <c r="D17" t="n">
-        <v>16.12</v>
+        <v>25.48</v>
       </c>
       <c r="E17" t="n">
-        <v>1.76</v>
+        <v>-0.17</v>
       </c>
       <c r="F17" t="n">
-        <v>-8.9</v>
+        <v>-11.4</v>
       </c>
       <c r="G17" t="n">
-        <v>-7.3</v>
+        <v>-11.6</v>
       </c>
       <c r="H17" t="n">
-        <v>1.6</v>
+        <v>-0.2</v>
       </c>
       <c r="I17" t="inlineStr">
         <is>
@@ -1226,10 +1226,10 @@
         </is>
       </c>
       <c r="K17" t="n">
-        <v>13.74</v>
+        <v>23.71</v>
       </c>
       <c r="L17" t="n">
-        <v>13.99</v>
+        <v>23.66</v>
       </c>
     </row>
     <row r="18">
@@ -1253,13 +1253,13 @@
         <v>-2.09</v>
       </c>
       <c r="F18" t="n">
-        <v>-13.7</v>
+        <v>-17.3</v>
       </c>
       <c r="G18" t="n">
-        <v>-15</v>
+        <v>-18.6</v>
       </c>
       <c r="H18" t="n">
-        <v>-1.4</v>
+        <v>-1.3</v>
       </c>
       <c r="I18" t="inlineStr">
         <is>
@@ -1299,10 +1299,10 @@
         <v>0</v>
       </c>
       <c r="F19" t="n">
-        <v>-16.3</v>
+        <v>-20.6</v>
       </c>
       <c r="G19" t="n">
-        <v>-16.3</v>
+        <v>-20.6</v>
       </c>
       <c r="H19" t="n">
         <v>0</v>
@@ -1345,13 +1345,13 @@
         <v>-15.47</v>
       </c>
       <c r="F20" t="n">
-        <v>-15.5</v>
+        <v>-18</v>
       </c>
       <c r="G20" t="n">
-        <v>-26.8</v>
+        <v>-29</v>
       </c>
       <c r="H20" t="n">
-        <v>-11.3</v>
+        <v>-11</v>
       </c>
       <c r="I20" t="inlineStr">
         <is>
@@ -1391,10 +1391,10 @@
         <v>-0.05</v>
       </c>
       <c r="F21" t="n">
-        <v>-29.1</v>
+        <v>-32.6</v>
       </c>
       <c r="G21" t="n">
-        <v>-29.1</v>
+        <v>-32.6</v>
       </c>
       <c r="H21" t="n">
         <v>-0</v>
@@ -1437,10 +1437,10 @@
         <v>-0.07000000000000001</v>
       </c>
       <c r="F22" t="n">
-        <v>-31.4</v>
+        <v>-34.2</v>
       </c>
       <c r="G22" t="n">
-        <v>-31.5</v>
+        <v>-34.2</v>
       </c>
       <c r="H22" t="n">
         <v>-0</v>
@@ -1465,31 +1465,31 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>FRO</t>
+          <t>INSW</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>whole-company</t>
+          <t>WHOLE-COMPANY (hybrid aggregation)</t>
         </is>
       </c>
       <c r="C23" t="n">
-        <v>28.47</v>
+        <v>57.91</v>
       </c>
       <c r="D23" t="n">
-        <v>24.11</v>
+        <v>52.48</v>
       </c>
       <c r="E23" t="n">
-        <v>-15.33</v>
+        <v>-9.380000000000001</v>
       </c>
       <c r="F23" t="n">
-        <v>-28.2</v>
+        <v>-36.7</v>
       </c>
       <c r="G23" t="n">
-        <v>-38.3</v>
+        <v>-41.4</v>
       </c>
       <c r="H23" t="n">
-        <v>-10</v>
+        <v>-4.7</v>
       </c>
       <c r="I23" t="inlineStr">
         <is>
@@ -1502,40 +1502,40 @@
         </is>
       </c>
       <c r="K23" t="n">
-        <v>26.5</v>
+        <v>58.44</v>
       </c>
       <c r="L23" t="n">
-        <v>22.8</v>
+        <v>54.12</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>INSW</t>
+          <t>FRO</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>WHOLE-COMPANY (hybrid aggregation)</t>
+          <t>whole-company</t>
         </is>
       </c>
       <c r="C24" t="n">
-        <v>57.91</v>
+        <v>28.47</v>
       </c>
       <c r="D24" t="n">
-        <v>52.48</v>
+        <v>24.11</v>
       </c>
       <c r="E24" t="n">
-        <v>-9.380000000000001</v>
+        <v>-15.33</v>
       </c>
       <c r="F24" t="n">
-        <v>-33.9</v>
+        <v>-32.5</v>
       </c>
       <c r="G24" t="n">
-        <v>-38.8</v>
+        <v>-42</v>
       </c>
       <c r="H24" t="n">
-        <v>-4.9</v>
+        <v>-9.4</v>
       </c>
       <c r="I24" t="inlineStr">
         <is>
@@ -1548,10 +1548,10 @@
         </is>
       </c>
       <c r="K24" t="n">
-        <v>58.44</v>
+        <v>26.5</v>
       </c>
       <c r="L24" t="n">
-        <v>54.12</v>
+        <v>22.8</v>
       </c>
     </row>
     <row r="25">
@@ -1575,13 +1575,13 @@
         <v>-14.81</v>
       </c>
       <c r="F25" t="n">
-        <v>-31.6</v>
+        <v>-35.9</v>
       </c>
       <c r="G25" t="n">
-        <v>-40.8</v>
+        <v>-44.5</v>
       </c>
       <c r="H25" t="n">
-        <v>-9.199999999999999</v>
+        <v>-8.6</v>
       </c>
       <c r="I25" t="inlineStr">
         <is>
@@ -1621,13 +1621,13 @@
         <v>-14.2</v>
       </c>
       <c r="F26" t="n">
-        <v>-49.2</v>
+        <v>-51.5</v>
       </c>
       <c r="G26" t="n">
-        <v>-55.2</v>
+        <v>-57.3</v>
       </c>
       <c r="H26" t="n">
-        <v>-6</v>
+        <v>-5.7</v>
       </c>
       <c r="I26" t="inlineStr">
         <is>

--- a/outputs/transaction_anchor_comparison.xlsx
+++ b/outputs/transaction_anchor_comparison.xlsx
@@ -603,19 +603,19 @@
         <v>9.720000000000001</v>
       </c>
       <c r="D4" t="n">
-        <v>10.02</v>
+        <v>10.07</v>
       </c>
       <c r="E4" t="n">
-        <v>3.1</v>
+        <v>3.64</v>
       </c>
       <c r="F4" t="n">
         <v>18.9</v>
       </c>
       <c r="G4" t="n">
-        <v>22.9</v>
+        <v>23.5</v>
       </c>
       <c r="H4" t="n">
-        <v>3.9</v>
+        <v>4.6</v>
       </c>
       <c r="I4" t="inlineStr">
         <is>
@@ -631,7 +631,7 @@
         <v>9.119999999999999</v>
       </c>
       <c r="L4" t="n">
-        <v>9.42</v>
+        <v>9.470000000000001</v>
       </c>
     </row>
     <row r="5">
@@ -649,19 +649,19 @@
         <v>32.12</v>
       </c>
       <c r="D5" t="n">
-        <v>32.1</v>
+        <v>32.65</v>
       </c>
       <c r="E5" t="n">
-        <v>-0.04</v>
+        <v>1.66</v>
       </c>
       <c r="F5" t="n">
         <v>8.699999999999999</v>
       </c>
       <c r="G5" t="n">
-        <v>8.6</v>
+        <v>10.3</v>
       </c>
       <c r="H5" t="n">
-        <v>-0.1</v>
+        <v>1.6</v>
       </c>
       <c r="I5" t="inlineStr">
         <is>
@@ -677,7 +677,7 @@
         <v>20.49</v>
       </c>
       <c r="L5" t="n">
-        <v>20.47</v>
+        <v>20.79</v>
       </c>
     </row>
     <row r="6">
@@ -775,7 +775,7 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>ASC</t>
+          <t>SBLK</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -784,22 +784,22 @@
         </is>
       </c>
       <c r="C8" t="n">
-        <v>17.82</v>
+        <v>29.77</v>
       </c>
       <c r="D8" t="n">
-        <v>17.82</v>
+        <v>30.64</v>
       </c>
       <c r="E8" t="n">
-        <v>-0.02</v>
+        <v>2.93</v>
       </c>
       <c r="F8" t="n">
-        <v>1.5</v>
+        <v>-0.9</v>
       </c>
       <c r="G8" t="n">
-        <v>1.4</v>
+        <v>1.7</v>
       </c>
       <c r="H8" t="n">
-        <v>-0</v>
+        <v>2.6</v>
       </c>
       <c r="I8" t="inlineStr">
         <is>
@@ -812,16 +812,16 @@
         </is>
       </c>
       <c r="K8" t="n">
-        <v>16.85</v>
+        <v>27.89</v>
       </c>
       <c r="L8" t="n">
-        <v>16.85</v>
+        <v>28.62</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>CAPT</t>
+          <t>ASC</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -830,22 +830,22 @@
         </is>
       </c>
       <c r="C9" t="n">
-        <v>15.61</v>
+        <v>17.82</v>
       </c>
       <c r="D9" t="n">
-        <v>15.49</v>
+        <v>17.82</v>
       </c>
       <c r="E9" t="n">
-        <v>-0.77</v>
+        <v>-0.02</v>
       </c>
       <c r="F9" t="n">
-        <v>2.7</v>
+        <v>1.5</v>
       </c>
       <c r="G9" t="n">
-        <v>1</v>
+        <v>1.4</v>
       </c>
       <c r="H9" t="n">
-        <v>-1.7</v>
+        <v>-0</v>
       </c>
       <c r="I9" t="inlineStr">
         <is>
@@ -858,16 +858,16 @@
         </is>
       </c>
       <c r="K9" t="n">
-        <v>13.37</v>
+        <v>16.85</v>
       </c>
       <c r="L9" t="n">
-        <v>13.14</v>
+        <v>16.85</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>SBLK</t>
+          <t>CAPT</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -876,22 +876,22 @@
         </is>
       </c>
       <c r="C10" t="n">
-        <v>29.77</v>
+        <v>15.61</v>
       </c>
       <c r="D10" t="n">
-        <v>30.13</v>
+        <v>15.49</v>
       </c>
       <c r="E10" t="n">
-        <v>1.21</v>
+        <v>-0.77</v>
       </c>
       <c r="F10" t="n">
-        <v>-0.9</v>
+        <v>2.7</v>
       </c>
       <c r="G10" t="n">
-        <v>0.2</v>
+        <v>1</v>
       </c>
       <c r="H10" t="n">
-        <v>1.1</v>
+        <v>-1.7</v>
       </c>
       <c r="I10" t="inlineStr">
         <is>
@@ -904,10 +904,10 @@
         </is>
       </c>
       <c r="K10" t="n">
-        <v>27.89</v>
+        <v>13.37</v>
       </c>
       <c r="L10" t="n">
-        <v>28.19</v>
+        <v>13.14</v>
       </c>
     </row>
     <row r="11">
@@ -1109,19 +1109,19 @@
         <v>0.4</v>
       </c>
       <c r="D15" t="n">
-        <v>0.39</v>
+        <v>0.4</v>
       </c>
       <c r="E15" t="n">
-        <v>-2.67</v>
+        <v>-1.14</v>
       </c>
       <c r="F15" t="n">
         <v>-6.9</v>
       </c>
       <c r="G15" t="n">
-        <v>-9</v>
+        <v>-7.8</v>
       </c>
       <c r="H15" t="n">
-        <v>-2.1</v>
+        <v>-0.9</v>
       </c>
       <c r="I15" t="inlineStr">
         <is>
@@ -1137,37 +1137,37 @@
         <v>0.39</v>
       </c>
       <c r="L15" t="n">
-        <v>0.38</v>
+        <v>0.39</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>CMBT</t>
+          <t>GNK</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>WHOLE-COMPANY (hybrid aggregation)</t>
+          <t>whole-company</t>
         </is>
       </c>
       <c r="C16" t="n">
-        <v>15.84</v>
+        <v>25.53</v>
       </c>
       <c r="D16" t="n">
-        <v>16.12</v>
+        <v>25.98</v>
       </c>
       <c r="E16" t="n">
-        <v>1.76</v>
+        <v>1.78</v>
       </c>
       <c r="F16" t="n">
-        <v>-12.7</v>
+        <v>-11.4</v>
       </c>
       <c r="G16" t="n">
-        <v>-11.1</v>
+        <v>-10.1</v>
       </c>
       <c r="H16" t="n">
-        <v>1.6</v>
+        <v>1.4</v>
       </c>
       <c r="I16" t="inlineStr">
         <is>
@@ -1180,40 +1180,40 @@
         </is>
       </c>
       <c r="K16" t="n">
-        <v>13.74</v>
+        <v>23.71</v>
       </c>
       <c r="L16" t="n">
-        <v>13.99</v>
+        <v>24.08</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>GNK</t>
+          <t>CMBT</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>whole-company</t>
+          <t>WHOLE-COMPANY (hybrid aggregation)</t>
         </is>
       </c>
       <c r="C17" t="n">
-        <v>25.53</v>
+        <v>15.84</v>
       </c>
       <c r="D17" t="n">
-        <v>25.48</v>
+        <v>16.19</v>
       </c>
       <c r="E17" t="n">
-        <v>-0.17</v>
+        <v>2.2</v>
       </c>
       <c r="F17" t="n">
-        <v>-11.4</v>
+        <v>-12.7</v>
       </c>
       <c r="G17" t="n">
-        <v>-11.6</v>
+        <v>-10.7</v>
       </c>
       <c r="H17" t="n">
-        <v>-0.2</v>
+        <v>2</v>
       </c>
       <c r="I17" t="inlineStr">
         <is>
@@ -1226,10 +1226,10 @@
         </is>
       </c>
       <c r="K17" t="n">
-        <v>23.71</v>
+        <v>13.74</v>
       </c>
       <c r="L17" t="n">
-        <v>23.66</v>
+        <v>14.05</v>
       </c>
     </row>
     <row r="18">

--- a/outputs/transaction_anchor_comparison.xlsx
+++ b/outputs/transaction_anchor_comparison.xlsx
@@ -517,10 +517,10 @@
         <v>0</v>
       </c>
       <c r="F2" t="n">
-        <v>53.8</v>
+        <v>60.4</v>
       </c>
       <c r="G2" t="n">
-        <v>53.8</v>
+        <v>60.4</v>
       </c>
       <c r="H2" t="n">
         <v>0</v>
@@ -563,13 +563,13 @@
         <v>-7.42</v>
       </c>
       <c r="F3" t="n">
-        <v>54</v>
+        <v>51.5</v>
       </c>
       <c r="G3" t="n">
-        <v>43.6</v>
+        <v>41.3</v>
       </c>
       <c r="H3" t="n">
-        <v>-10.4</v>
+        <v>-10.3</v>
       </c>
       <c r="I3" t="inlineStr">
         <is>
@@ -582,10 +582,10 @@
         </is>
       </c>
       <c r="K3" t="n">
-        <v>60.66</v>
+        <v>60.96</v>
       </c>
       <c r="L3" t="n">
-        <v>56.56</v>
+        <v>56.83</v>
       </c>
     </row>
     <row r="4">
@@ -609,13 +609,13 @@
         <v>3.64</v>
       </c>
       <c r="F4" t="n">
-        <v>18.9</v>
+        <v>16.8</v>
       </c>
       <c r="G4" t="n">
-        <v>23.5</v>
+        <v>21.3</v>
       </c>
       <c r="H4" t="n">
-        <v>4.6</v>
+        <v>4.5</v>
       </c>
       <c r="I4" t="inlineStr">
         <is>
@@ -637,7 +637,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>CMDB</t>
+          <t>BRUT</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -646,22 +646,22 @@
         </is>
       </c>
       <c r="C5" t="n">
-        <v>32.12</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="D5" t="n">
-        <v>32.65</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="E5" t="n">
-        <v>1.66</v>
+        <v>0</v>
       </c>
       <c r="F5" t="n">
-        <v>8.699999999999999</v>
+        <v>10</v>
       </c>
       <c r="G5" t="n">
-        <v>10.3</v>
+        <v>8.1</v>
       </c>
       <c r="H5" t="n">
-        <v>1.6</v>
+        <v>-1.9</v>
       </c>
       <c r="I5" t="inlineStr">
         <is>
@@ -674,16 +674,16 @@
         </is>
       </c>
       <c r="K5" t="n">
-        <v>20.49</v>
+        <v>6.57</v>
       </c>
       <c r="L5" t="n">
-        <v>20.79</v>
+        <v>6.45</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>BRUT</t>
+          <t>CMDB</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -692,22 +692,22 @@
         </is>
       </c>
       <c r="C6" t="n">
-        <v>8.800000000000001</v>
+        <v>32.12</v>
       </c>
       <c r="D6" t="n">
-        <v>8.800000000000001</v>
+        <v>32.65</v>
       </c>
       <c r="E6" t="n">
-        <v>0</v>
+        <v>1.66</v>
       </c>
       <c r="F6" t="n">
-        <v>10.3</v>
+        <v>6.1</v>
       </c>
       <c r="G6" t="n">
-        <v>8.4</v>
+        <v>7.7</v>
       </c>
       <c r="H6" t="n">
-        <v>-1.9</v>
+        <v>1.5</v>
       </c>
       <c r="I6" t="inlineStr">
         <is>
@@ -720,10 +720,10 @@
         </is>
       </c>
       <c r="K6" t="n">
-        <v>6.32</v>
+        <v>20.49</v>
       </c>
       <c r="L6" t="n">
-        <v>6.21</v>
+        <v>20.79</v>
       </c>
     </row>
     <row r="7">
@@ -747,13 +747,13 @@
         <v>-4.25</v>
       </c>
       <c r="F7" t="n">
-        <v>9.1</v>
+        <v>9.4</v>
       </c>
       <c r="G7" t="n">
-        <v>5.2</v>
+        <v>5.6</v>
       </c>
       <c r="H7" t="n">
-        <v>-3.8</v>
+        <v>-3.9</v>
       </c>
       <c r="I7" t="inlineStr">
         <is>
@@ -793,10 +793,10 @@
         <v>2.93</v>
       </c>
       <c r="F8" t="n">
-        <v>-0.9</v>
+        <v>-3.1</v>
       </c>
       <c r="G8" t="n">
-        <v>1.7</v>
+        <v>-0.5</v>
       </c>
       <c r="H8" t="n">
         <v>2.6</v>
@@ -821,7 +821,7 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>ASC</t>
+          <t>STNG</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -830,22 +830,22 @@
         </is>
       </c>
       <c r="C9" t="n">
-        <v>17.82</v>
+        <v>80.97</v>
       </c>
       <c r="D9" t="n">
-        <v>17.82</v>
+        <v>77.13</v>
       </c>
       <c r="E9" t="n">
-        <v>-0.02</v>
+        <v>-4.74</v>
       </c>
       <c r="F9" t="n">
-        <v>1.5</v>
+        <v>3.8</v>
       </c>
       <c r="G9" t="n">
-        <v>1.4</v>
+        <v>-0.6</v>
       </c>
       <c r="H9" t="n">
-        <v>-0</v>
+        <v>-4.4</v>
       </c>
       <c r="I9" t="inlineStr">
         <is>
@@ -858,10 +858,10 @@
         </is>
       </c>
       <c r="K9" t="n">
-        <v>16.85</v>
+        <v>80.3</v>
       </c>
       <c r="L9" t="n">
-        <v>16.85</v>
+        <v>76.87</v>
       </c>
     </row>
     <row r="10">
@@ -885,10 +885,10 @@
         <v>-0.77</v>
       </c>
       <c r="F10" t="n">
-        <v>2.7</v>
+        <v>0.7</v>
       </c>
       <c r="G10" t="n">
-        <v>1</v>
+        <v>-1</v>
       </c>
       <c r="H10" t="n">
         <v>-1.7</v>
@@ -904,10 +904,10 @@
         </is>
       </c>
       <c r="K10" t="n">
-        <v>13.37</v>
+        <v>13.6</v>
       </c>
       <c r="L10" t="n">
-        <v>13.14</v>
+        <v>13.38</v>
       </c>
     </row>
     <row r="11">
@@ -931,10 +931,10 @@
         <v>0</v>
       </c>
       <c r="F11" t="n">
-        <v>-0.6</v>
+        <v>-1.5</v>
       </c>
       <c r="G11" t="n">
-        <v>-0.6</v>
+        <v>-1.5</v>
       </c>
       <c r="H11" t="n">
         <v>0</v>
@@ -959,7 +959,7 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>TNK</t>
+          <t>ASC</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -968,22 +968,22 @@
         </is>
       </c>
       <c r="C12" t="n">
-        <v>83.31999999999999</v>
+        <v>17.82</v>
       </c>
       <c r="D12" t="n">
-        <v>77.73</v>
+        <v>17.82</v>
       </c>
       <c r="E12" t="n">
-        <v>-6.71</v>
+        <v>-0.02</v>
       </c>
       <c r="F12" t="n">
-        <v>2.5</v>
+        <v>-3.1</v>
       </c>
       <c r="G12" t="n">
         <v>-3.2</v>
       </c>
       <c r="H12" t="n">
-        <v>-5.7</v>
+        <v>-0</v>
       </c>
       <c r="I12" t="inlineStr">
         <is>
@@ -996,16 +996,16 @@
         </is>
       </c>
       <c r="K12" t="n">
-        <v>77.67</v>
+        <v>16.85</v>
       </c>
       <c r="L12" t="n">
-        <v>73.34999999999999</v>
+        <v>16.85</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>STNG</t>
+          <t>GNK</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -1014,44 +1014,44 @@
         </is>
       </c>
       <c r="C13" t="n">
-        <v>80.97</v>
+        <v>25.53</v>
       </c>
       <c r="D13" t="n">
-        <v>77.13</v>
+        <v>25.98</v>
       </c>
       <c r="E13" t="n">
-        <v>-4.74</v>
+        <v>1.78</v>
       </c>
       <c r="F13" t="n">
-        <v>1</v>
+        <v>-8</v>
       </c>
       <c r="G13" t="n">
-        <v>-3.3</v>
+        <v>-6.5</v>
       </c>
       <c r="H13" t="n">
-        <v>-4.3</v>
+        <v>1.4</v>
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>HOLD (fairly valued)</t>
+          <t>TRIM/SHORT (overvalued)</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t>HOLD (fairly valued)</t>
+          <t>TRIM/SHORT (overvalued)</t>
         </is>
       </c>
       <c r="K13" t="n">
-        <v>80.3</v>
+        <v>23.71</v>
       </c>
       <c r="L13" t="n">
-        <v>76.87</v>
+        <v>24.08</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>GSL</t>
+          <t>2343</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1060,22 +1060,22 @@
         </is>
       </c>
       <c r="C14" t="n">
-        <v>38.59</v>
+        <v>0.4</v>
       </c>
       <c r="D14" t="n">
-        <v>38.59</v>
+        <v>0.4</v>
       </c>
       <c r="E14" t="n">
-        <v>0</v>
+        <v>-1.14</v>
       </c>
       <c r="F14" t="n">
-        <v>-7</v>
+        <v>-6.3</v>
       </c>
       <c r="G14" t="n">
-        <v>-7</v>
+        <v>-7.2</v>
       </c>
       <c r="H14" t="n">
-        <v>0</v>
+        <v>-0.9</v>
       </c>
       <c r="I14" t="inlineStr">
         <is>
@@ -1088,16 +1088,16 @@
         </is>
       </c>
       <c r="K14" t="n">
-        <v>40.54</v>
+        <v>0.39</v>
       </c>
       <c r="L14" t="n">
-        <v>40.54</v>
+        <v>0.39</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>2343</t>
+          <t>TNK</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1106,26 +1106,26 @@
         </is>
       </c>
       <c r="C15" t="n">
-        <v>0.4</v>
+        <v>83.31999999999999</v>
       </c>
       <c r="D15" t="n">
-        <v>0.4</v>
+        <v>77.73</v>
       </c>
       <c r="E15" t="n">
-        <v>-1.14</v>
+        <v>-6.71</v>
       </c>
       <c r="F15" t="n">
-        <v>-6.9</v>
+        <v>-2.4</v>
       </c>
       <c r="G15" t="n">
         <v>-7.8</v>
       </c>
       <c r="H15" t="n">
-        <v>-0.9</v>
+        <v>-5.5</v>
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>TRIM/SHORT (overvalued)</t>
+          <t>HOLD (fairly valued)</t>
         </is>
       </c>
       <c r="J15" t="inlineStr">
@@ -1134,16 +1134,16 @@
         </is>
       </c>
       <c r="K15" t="n">
-        <v>0.39</v>
+        <v>78.05</v>
       </c>
       <c r="L15" t="n">
-        <v>0.39</v>
+        <v>73.69</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>GNK</t>
+          <t>GSL</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1152,22 +1152,22 @@
         </is>
       </c>
       <c r="C16" t="n">
-        <v>25.53</v>
+        <v>38.59</v>
       </c>
       <c r="D16" t="n">
-        <v>25.98</v>
+        <v>38.59</v>
       </c>
       <c r="E16" t="n">
-        <v>1.78</v>
+        <v>0</v>
       </c>
       <c r="F16" t="n">
-        <v>-11.4</v>
+        <v>-8.5</v>
       </c>
       <c r="G16" t="n">
-        <v>-10.1</v>
+        <v>-8.5</v>
       </c>
       <c r="H16" t="n">
-        <v>1.4</v>
+        <v>0</v>
       </c>
       <c r="I16" t="inlineStr">
         <is>
@@ -1180,10 +1180,10 @@
         </is>
       </c>
       <c r="K16" t="n">
-        <v>23.71</v>
+        <v>40.54</v>
       </c>
       <c r="L16" t="n">
-        <v>24.08</v>
+        <v>40.54</v>
       </c>
     </row>
     <row r="17">
@@ -1207,13 +1207,13 @@
         <v>2.2</v>
       </c>
       <c r="F17" t="n">
+        <v>-14.6</v>
+      </c>
+      <c r="G17" t="n">
         <v>-12.7</v>
       </c>
-      <c r="G17" t="n">
-        <v>-10.7</v>
-      </c>
       <c r="H17" t="n">
-        <v>2</v>
+        <v>1.9</v>
       </c>
       <c r="I17" t="inlineStr">
         <is>
@@ -1226,10 +1226,10 @@
         </is>
       </c>
       <c r="K17" t="n">
-        <v>13.74</v>
+        <v>13.8</v>
       </c>
       <c r="L17" t="n">
-        <v>14.05</v>
+        <v>14.11</v>
       </c>
     </row>
     <row r="18">
@@ -1253,10 +1253,10 @@
         <v>-2.09</v>
       </c>
       <c r="F18" t="n">
-        <v>-17.3</v>
+        <v>-17.5</v>
       </c>
       <c r="G18" t="n">
-        <v>-18.6</v>
+        <v>-18.8</v>
       </c>
       <c r="H18" t="n">
         <v>-1.3</v>
@@ -1299,10 +1299,10 @@
         <v>0</v>
       </c>
       <c r="F19" t="n">
-        <v>-20.6</v>
+        <v>-19.8</v>
       </c>
       <c r="G19" t="n">
-        <v>-20.6</v>
+        <v>-19.8</v>
       </c>
       <c r="H19" t="n">
         <v>0</v>
@@ -1345,7 +1345,7 @@
         <v>-15.47</v>
       </c>
       <c r="F20" t="n">
-        <v>-18</v>
+        <v>-18.1</v>
       </c>
       <c r="G20" t="n">
         <v>-29</v>
@@ -1364,10 +1364,10 @@
         </is>
       </c>
       <c r="K20" t="n">
-        <v>15.13</v>
+        <v>15.29</v>
       </c>
       <c r="L20" t="n">
-        <v>13.1</v>
+        <v>13.24</v>
       </c>
     </row>
     <row r="21">
@@ -1391,10 +1391,10 @@
         <v>-0.05</v>
       </c>
       <c r="F21" t="n">
-        <v>-32.6</v>
+        <v>-34.3</v>
       </c>
       <c r="G21" t="n">
-        <v>-32.6</v>
+        <v>-34.4</v>
       </c>
       <c r="H21" t="n">
         <v>-0</v>
@@ -1437,10 +1437,10 @@
         <v>-0.07000000000000001</v>
       </c>
       <c r="F22" t="n">
-        <v>-34.2</v>
+        <v>-36.3</v>
       </c>
       <c r="G22" t="n">
-        <v>-34.2</v>
+        <v>-36.3</v>
       </c>
       <c r="H22" t="n">
         <v>-0</v>
@@ -1465,31 +1465,31 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>INSW</t>
+          <t>FRO</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>WHOLE-COMPANY (hybrid aggregation)</t>
+          <t>whole-company</t>
         </is>
       </c>
       <c r="C23" t="n">
-        <v>57.91</v>
+        <v>28.47</v>
       </c>
       <c r="D23" t="n">
-        <v>52.48</v>
+        <v>24.11</v>
       </c>
       <c r="E23" t="n">
-        <v>-9.380000000000001</v>
+        <v>-15.33</v>
       </c>
       <c r="F23" t="n">
-        <v>-36.7</v>
+        <v>-31.7</v>
       </c>
       <c r="G23" t="n">
-        <v>-41.4</v>
+        <v>-41.2</v>
       </c>
       <c r="H23" t="n">
-        <v>-4.7</v>
+        <v>-9.5</v>
       </c>
       <c r="I23" t="inlineStr">
         <is>
@@ -1502,40 +1502,40 @@
         </is>
       </c>
       <c r="K23" t="n">
-        <v>58.44</v>
+        <v>26.88</v>
       </c>
       <c r="L23" t="n">
-        <v>54.12</v>
+        <v>23.15</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>FRO</t>
+          <t>INSW</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>whole-company</t>
+          <t>WHOLE-COMPANY (hybrid aggregation)</t>
         </is>
       </c>
       <c r="C24" t="n">
-        <v>28.47</v>
+        <v>57.91</v>
       </c>
       <c r="D24" t="n">
-        <v>24.11</v>
+        <v>52.48</v>
       </c>
       <c r="E24" t="n">
-        <v>-15.33</v>
+        <v>-9.380000000000001</v>
       </c>
       <c r="F24" t="n">
-        <v>-32.5</v>
+        <v>-38.8</v>
       </c>
       <c r="G24" t="n">
-        <v>-42</v>
+        <v>-43.3</v>
       </c>
       <c r="H24" t="n">
-        <v>-9.4</v>
+        <v>-4.5</v>
       </c>
       <c r="I24" t="inlineStr">
         <is>
@@ -1548,10 +1548,10 @@
         </is>
       </c>
       <c r="K24" t="n">
-        <v>26.5</v>
+        <v>58.82</v>
       </c>
       <c r="L24" t="n">
-        <v>22.8</v>
+        <v>54.46</v>
       </c>
     </row>
     <row r="25">
@@ -1575,13 +1575,13 @@
         <v>-14.81</v>
       </c>
       <c r="F25" t="n">
-        <v>-35.9</v>
+        <v>-37.8</v>
       </c>
       <c r="G25" t="n">
-        <v>-44.5</v>
+        <v>-46.2</v>
       </c>
       <c r="H25" t="n">
-        <v>-8.6</v>
+        <v>-8.300000000000001</v>
       </c>
       <c r="I25" t="inlineStr">
         <is>
@@ -1594,10 +1594,10 @@
         </is>
       </c>
       <c r="K25" t="n">
-        <v>37.09</v>
+        <v>37.6</v>
       </c>
       <c r="L25" t="n">
-        <v>32.1</v>
+        <v>32.57</v>
       </c>
     </row>
     <row r="26">
@@ -1624,7 +1624,7 @@
         <v>-51.5</v>
       </c>
       <c r="G26" t="n">
-        <v>-57.3</v>
+        <v>-57.2</v>
       </c>
       <c r="H26" t="n">
         <v>-5.7</v>
@@ -1640,10 +1640,10 @@
         </is>
       </c>
       <c r="K26" t="n">
-        <v>3.13</v>
+        <v>3.16</v>
       </c>
       <c r="L26" t="n">
-        <v>2.76</v>
+        <v>2.79</v>
       </c>
     </row>
   </sheetData>

--- a/outputs/transaction_anchor_comparison.xlsx
+++ b/outputs/transaction_anchor_comparison.xlsx
@@ -600,22 +600,22 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>9.720000000000001</v>
+        <v>10.36</v>
       </c>
       <c r="D4" t="n">
-        <v>10.07</v>
+        <v>10.73</v>
       </c>
       <c r="E4" t="n">
-        <v>3.64</v>
+        <v>3.54</v>
       </c>
       <c r="F4" t="n">
-        <v>16.8</v>
+        <v>24.7</v>
       </c>
       <c r="G4" t="n">
-        <v>21.3</v>
+        <v>29.4</v>
       </c>
       <c r="H4" t="n">
-        <v>4.5</v>
+        <v>4.7</v>
       </c>
       <c r="I4" t="inlineStr">
         <is>
@@ -628,10 +628,10 @@
         </is>
       </c>
       <c r="K4" t="n">
-        <v>9.119999999999999</v>
+        <v>9.74</v>
       </c>
       <c r="L4" t="n">
-        <v>9.470000000000001</v>
+        <v>10.1</v>
       </c>
     </row>
     <row r="5">

--- a/outputs/transaction_anchor_comparison.xlsx
+++ b/outputs/transaction_anchor_comparison.xlsx
@@ -1005,7 +1005,7 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>GNK</t>
+          <t>TNK</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -1014,44 +1014,44 @@
         </is>
       </c>
       <c r="C13" t="n">
-        <v>25.53</v>
+        <v>86.53</v>
       </c>
       <c r="D13" t="n">
-        <v>25.98</v>
+        <v>81.48</v>
       </c>
       <c r="E13" t="n">
-        <v>1.78</v>
+        <v>-5.84</v>
       </c>
       <c r="F13" t="n">
-        <v>-8</v>
+        <v>1.2</v>
       </c>
       <c r="G13" t="n">
-        <v>-6.5</v>
+        <v>-3.8</v>
       </c>
       <c r="H13" t="n">
-        <v>1.4</v>
+        <v>-4.9</v>
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>TRIM/SHORT (overvalued)</t>
+          <t>HOLD (fairly valued)</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t>TRIM/SHORT (overvalued)</t>
+          <t>HOLD (fairly valued)</t>
         </is>
       </c>
       <c r="K13" t="n">
-        <v>23.71</v>
+        <v>80.90000000000001</v>
       </c>
       <c r="L13" t="n">
-        <v>24.08</v>
+        <v>76.95</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>2343</t>
+          <t>GNK</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1060,22 +1060,22 @@
         </is>
       </c>
       <c r="C14" t="n">
-        <v>0.4</v>
+        <v>25.53</v>
       </c>
       <c r="D14" t="n">
-        <v>0.4</v>
+        <v>25.98</v>
       </c>
       <c r="E14" t="n">
-        <v>-1.14</v>
+        <v>1.78</v>
       </c>
       <c r="F14" t="n">
-        <v>-6.3</v>
+        <v>-8</v>
       </c>
       <c r="G14" t="n">
-        <v>-7.2</v>
+        <v>-6.5</v>
       </c>
       <c r="H14" t="n">
-        <v>-0.9</v>
+        <v>1.4</v>
       </c>
       <c r="I14" t="inlineStr">
         <is>
@@ -1088,16 +1088,16 @@
         </is>
       </c>
       <c r="K14" t="n">
-        <v>0.39</v>
+        <v>23.71</v>
       </c>
       <c r="L14" t="n">
-        <v>0.39</v>
+        <v>24.08</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>TNK</t>
+          <t>2343</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1106,26 +1106,26 @@
         </is>
       </c>
       <c r="C15" t="n">
-        <v>83.31999999999999</v>
+        <v>0.4</v>
       </c>
       <c r="D15" t="n">
-        <v>77.73</v>
+        <v>0.4</v>
       </c>
       <c r="E15" t="n">
-        <v>-6.71</v>
+        <v>-1.14</v>
       </c>
       <c r="F15" t="n">
-        <v>-2.4</v>
+        <v>-6.3</v>
       </c>
       <c r="G15" t="n">
-        <v>-7.8</v>
+        <v>-7.2</v>
       </c>
       <c r="H15" t="n">
-        <v>-5.5</v>
+        <v>-0.9</v>
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>HOLD (fairly valued)</t>
+          <t>TRIM/SHORT (overvalued)</t>
         </is>
       </c>
       <c r="J15" t="inlineStr">
@@ -1134,10 +1134,10 @@
         </is>
       </c>
       <c r="K15" t="n">
-        <v>78.05</v>
+        <v>0.39</v>
       </c>
       <c r="L15" t="n">
-        <v>73.69</v>
+        <v>0.39</v>
       </c>
     </row>
     <row r="16">

--- a/outputs/transaction_anchor_comparison.xlsx
+++ b/outputs/transaction_anchor_comparison.xlsx
@@ -600,22 +600,22 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>10.36</v>
+        <v>9.720000000000001</v>
       </c>
       <c r="D4" t="n">
-        <v>10.73</v>
+        <v>10.07</v>
       </c>
       <c r="E4" t="n">
-        <v>3.54</v>
+        <v>3.64</v>
       </c>
       <c r="F4" t="n">
-        <v>24.7</v>
+        <v>16.8</v>
       </c>
       <c r="G4" t="n">
-        <v>29.4</v>
+        <v>21.3</v>
       </c>
       <c r="H4" t="n">
-        <v>4.7</v>
+        <v>4.5</v>
       </c>
       <c r="I4" t="inlineStr">
         <is>
@@ -628,10 +628,10 @@
         </is>
       </c>
       <c r="K4" t="n">
-        <v>9.74</v>
+        <v>9.119999999999999</v>
       </c>
       <c r="L4" t="n">
-        <v>10.1</v>
+        <v>9.470000000000001</v>
       </c>
     </row>
     <row r="5">
@@ -1005,7 +1005,7 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>TNK</t>
+          <t>GNK</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -1014,44 +1014,44 @@
         </is>
       </c>
       <c r="C13" t="n">
-        <v>86.53</v>
+        <v>25.53</v>
       </c>
       <c r="D13" t="n">
-        <v>81.48</v>
+        <v>25.98</v>
       </c>
       <c r="E13" t="n">
-        <v>-5.84</v>
+        <v>1.78</v>
       </c>
       <c r="F13" t="n">
-        <v>1.2</v>
+        <v>-8</v>
       </c>
       <c r="G13" t="n">
-        <v>-3.8</v>
+        <v>-6.5</v>
       </c>
       <c r="H13" t="n">
-        <v>-4.9</v>
+        <v>1.4</v>
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>HOLD (fairly valued)</t>
+          <t>TRIM/SHORT (overvalued)</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t>HOLD (fairly valued)</t>
+          <t>TRIM/SHORT (overvalued)</t>
         </is>
       </c>
       <c r="K13" t="n">
-        <v>80.90000000000001</v>
+        <v>23.71</v>
       </c>
       <c r="L13" t="n">
-        <v>76.95</v>
+        <v>24.08</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>GNK</t>
+          <t>2343</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1060,22 +1060,22 @@
         </is>
       </c>
       <c r="C14" t="n">
-        <v>25.53</v>
+        <v>0.4</v>
       </c>
       <c r="D14" t="n">
-        <v>25.98</v>
+        <v>0.4</v>
       </c>
       <c r="E14" t="n">
-        <v>1.78</v>
+        <v>-1.14</v>
       </c>
       <c r="F14" t="n">
-        <v>-8</v>
+        <v>-6.3</v>
       </c>
       <c r="G14" t="n">
-        <v>-6.5</v>
+        <v>-7.2</v>
       </c>
       <c r="H14" t="n">
-        <v>1.4</v>
+        <v>-0.9</v>
       </c>
       <c r="I14" t="inlineStr">
         <is>
@@ -1088,16 +1088,16 @@
         </is>
       </c>
       <c r="K14" t="n">
-        <v>23.71</v>
+        <v>0.39</v>
       </c>
       <c r="L14" t="n">
-        <v>24.08</v>
+        <v>0.39</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>2343</t>
+          <t>TNK</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1106,26 +1106,26 @@
         </is>
       </c>
       <c r="C15" t="n">
-        <v>0.4</v>
+        <v>83.31999999999999</v>
       </c>
       <c r="D15" t="n">
-        <v>0.4</v>
+        <v>77.73</v>
       </c>
       <c r="E15" t="n">
-        <v>-1.14</v>
+        <v>-6.71</v>
       </c>
       <c r="F15" t="n">
-        <v>-6.3</v>
+        <v>-2.4</v>
       </c>
       <c r="G15" t="n">
-        <v>-7.2</v>
+        <v>-7.8</v>
       </c>
       <c r="H15" t="n">
-        <v>-0.9</v>
+        <v>-5.5</v>
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>TRIM/SHORT (overvalued)</t>
+          <t>HOLD (fairly valued)</t>
         </is>
       </c>
       <c r="J15" t="inlineStr">
@@ -1134,10 +1134,10 @@
         </is>
       </c>
       <c r="K15" t="n">
-        <v>0.39</v>
+        <v>78.05</v>
       </c>
       <c r="L15" t="n">
-        <v>0.39</v>
+        <v>73.69</v>
       </c>
     </row>
     <row r="16">

--- a/outputs/transaction_anchor_comparison.xlsx
+++ b/outputs/transaction_anchor_comparison.xlsx
@@ -517,10 +517,10 @@
         <v>0</v>
       </c>
       <c r="F2" t="n">
-        <v>60.4</v>
+        <v>60.5</v>
       </c>
       <c r="G2" t="n">
-        <v>60.4</v>
+        <v>60.5</v>
       </c>
       <c r="H2" t="n">
         <v>0</v>
@@ -563,13 +563,13 @@
         <v>-7.42</v>
       </c>
       <c r="F3" t="n">
-        <v>51.5</v>
+        <v>55.7</v>
       </c>
       <c r="G3" t="n">
-        <v>41.3</v>
+        <v>45.2</v>
       </c>
       <c r="H3" t="n">
-        <v>-10.3</v>
+        <v>-10.5</v>
       </c>
       <c r="I3" t="inlineStr">
         <is>
@@ -609,13 +609,13 @@
         <v>3.64</v>
       </c>
       <c r="F4" t="n">
-        <v>16.8</v>
+        <v>20</v>
       </c>
       <c r="G4" t="n">
-        <v>21.3</v>
+        <v>24.6</v>
       </c>
       <c r="H4" t="n">
-        <v>4.5</v>
+        <v>4.6</v>
       </c>
       <c r="I4" t="inlineStr">
         <is>
@@ -637,7 +637,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>BRUT</t>
+          <t>CMDB</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -646,22 +646,22 @@
         </is>
       </c>
       <c r="C5" t="n">
-        <v>8.800000000000001</v>
+        <v>32.12</v>
       </c>
       <c r="D5" t="n">
-        <v>8.800000000000001</v>
+        <v>32.65</v>
       </c>
       <c r="E5" t="n">
-        <v>0</v>
+        <v>1.66</v>
       </c>
       <c r="F5" t="n">
-        <v>10</v>
+        <v>15.1</v>
       </c>
       <c r="G5" t="n">
-        <v>8.1</v>
+        <v>16.8</v>
       </c>
       <c r="H5" t="n">
-        <v>-1.9</v>
+        <v>1.7</v>
       </c>
       <c r="I5" t="inlineStr">
         <is>
@@ -674,16 +674,16 @@
         </is>
       </c>
       <c r="K5" t="n">
-        <v>6.57</v>
+        <v>20.49</v>
       </c>
       <c r="L5" t="n">
-        <v>6.45</v>
+        <v>20.79</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>CMDB</t>
+          <t>TRMD</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -692,22 +692,22 @@
         </is>
       </c>
       <c r="C6" t="n">
-        <v>32.12</v>
+        <v>31.65</v>
       </c>
       <c r="D6" t="n">
-        <v>32.65</v>
+        <v>30.3</v>
       </c>
       <c r="E6" t="n">
-        <v>1.66</v>
+        <v>-4.25</v>
       </c>
       <c r="F6" t="n">
-        <v>6.1</v>
+        <v>12</v>
       </c>
       <c r="G6" t="n">
-        <v>7.7</v>
+        <v>8.1</v>
       </c>
       <c r="H6" t="n">
-        <v>1.5</v>
+        <v>-3.9</v>
       </c>
       <c r="I6" t="inlineStr">
         <is>
@@ -720,16 +720,16 @@
         </is>
       </c>
       <c r="K6" t="n">
-        <v>20.49</v>
+        <v>33.03</v>
       </c>
       <c r="L6" t="n">
-        <v>20.79</v>
+        <v>31.87</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>TRMD</t>
+          <t>STNG</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -738,22 +738,22 @@
         </is>
       </c>
       <c r="C7" t="n">
-        <v>31.65</v>
+        <v>80.97</v>
       </c>
       <c r="D7" t="n">
-        <v>30.3</v>
+        <v>77.13</v>
       </c>
       <c r="E7" t="n">
-        <v>-4.25</v>
+        <v>-4.74</v>
       </c>
       <c r="F7" t="n">
-        <v>9.4</v>
+        <v>5.5</v>
       </c>
       <c r="G7" t="n">
-        <v>5.6</v>
+        <v>1</v>
       </c>
       <c r="H7" t="n">
-        <v>-3.9</v>
+        <v>-4.5</v>
       </c>
       <c r="I7" t="inlineStr">
         <is>
@@ -762,20 +762,20 @@
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>BUY (undervalued)</t>
+          <t>HOLD (fairly valued)</t>
         </is>
       </c>
       <c r="K7" t="n">
-        <v>33.03</v>
+        <v>80.3</v>
       </c>
       <c r="L7" t="n">
-        <v>31.87</v>
+        <v>76.87</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>SBLK</t>
+          <t>ASC</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -784,22 +784,22 @@
         </is>
       </c>
       <c r="C8" t="n">
-        <v>29.77</v>
+        <v>17.82</v>
       </c>
       <c r="D8" t="n">
-        <v>30.64</v>
+        <v>17.82</v>
       </c>
       <c r="E8" t="n">
-        <v>2.93</v>
+        <v>-0.02</v>
       </c>
       <c r="F8" t="n">
-        <v>-3.1</v>
+        <v>0.9</v>
       </c>
       <c r="G8" t="n">
-        <v>-0.5</v>
+        <v>0.8</v>
       </c>
       <c r="H8" t="n">
-        <v>2.6</v>
+        <v>-0</v>
       </c>
       <c r="I8" t="inlineStr">
         <is>
@@ -812,16 +812,16 @@
         </is>
       </c>
       <c r="K8" t="n">
-        <v>27.89</v>
+        <v>16.85</v>
       </c>
       <c r="L8" t="n">
-        <v>28.62</v>
+        <v>16.85</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>STNG</t>
+          <t>BRUT</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -830,22 +830,22 @@
         </is>
       </c>
       <c r="C9" t="n">
-        <v>80.97</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="D9" t="n">
-        <v>77.13</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="E9" t="n">
-        <v>-4.74</v>
+        <v>0</v>
       </c>
       <c r="F9" t="n">
-        <v>3.8</v>
+        <v>2.5</v>
       </c>
       <c r="G9" t="n">
-        <v>-0.6</v>
+        <v>0.7</v>
       </c>
       <c r="H9" t="n">
-        <v>-4.4</v>
+        <v>-1.7</v>
       </c>
       <c r="I9" t="inlineStr">
         <is>
@@ -858,16 +858,16 @@
         </is>
       </c>
       <c r="K9" t="n">
-        <v>80.3</v>
+        <v>6.57</v>
       </c>
       <c r="L9" t="n">
-        <v>76.87</v>
+        <v>6.45</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>CAPT</t>
+          <t>FLNG</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -876,22 +876,22 @@
         </is>
       </c>
       <c r="C10" t="n">
-        <v>15.61</v>
+        <v>28.45</v>
       </c>
       <c r="D10" t="n">
-        <v>15.49</v>
+        <v>28.45</v>
       </c>
       <c r="E10" t="n">
-        <v>-0.77</v>
+        <v>0</v>
       </c>
       <c r="F10" t="n">
-        <v>0.7</v>
+        <v>-0.5</v>
       </c>
       <c r="G10" t="n">
-        <v>-1</v>
+        <v>-0.5</v>
       </c>
       <c r="H10" t="n">
-        <v>-1.7</v>
+        <v>0</v>
       </c>
       <c r="I10" t="inlineStr">
         <is>
@@ -904,16 +904,16 @@
         </is>
       </c>
       <c r="K10" t="n">
-        <v>13.6</v>
+        <v>30.67</v>
       </c>
       <c r="L10" t="n">
-        <v>13.38</v>
+        <v>30.67</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>FLNG</t>
+          <t>SBLK</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -922,22 +922,22 @@
         </is>
       </c>
       <c r="C11" t="n">
-        <v>28.45</v>
+        <v>29.77</v>
       </c>
       <c r="D11" t="n">
-        <v>28.45</v>
+        <v>30.64</v>
       </c>
       <c r="E11" t="n">
-        <v>0</v>
+        <v>2.93</v>
       </c>
       <c r="F11" t="n">
-        <v>-1.5</v>
+        <v>-3.5</v>
       </c>
       <c r="G11" t="n">
-        <v>-1.5</v>
+        <v>-1</v>
       </c>
       <c r="H11" t="n">
-        <v>0</v>
+        <v>2.6</v>
       </c>
       <c r="I11" t="inlineStr">
         <is>
@@ -950,16 +950,16 @@
         </is>
       </c>
       <c r="K11" t="n">
-        <v>30.67</v>
+        <v>27.89</v>
       </c>
       <c r="L11" t="n">
-        <v>30.67</v>
+        <v>28.62</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>ASC</t>
+          <t>CAPT</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -968,22 +968,22 @@
         </is>
       </c>
       <c r="C12" t="n">
-        <v>17.82</v>
+        <v>15.61</v>
       </c>
       <c r="D12" t="n">
-        <v>17.82</v>
+        <v>15.49</v>
       </c>
       <c r="E12" t="n">
-        <v>-0.02</v>
+        <v>-0.77</v>
       </c>
       <c r="F12" t="n">
-        <v>-3.1</v>
+        <v>-2.4</v>
       </c>
       <c r="G12" t="n">
-        <v>-3.2</v>
+        <v>-4</v>
       </c>
       <c r="H12" t="n">
-        <v>-0</v>
+        <v>-1.6</v>
       </c>
       <c r="I12" t="inlineStr">
         <is>
@@ -996,16 +996,16 @@
         </is>
       </c>
       <c r="K12" t="n">
-        <v>16.85</v>
+        <v>13.6</v>
       </c>
       <c r="L12" t="n">
-        <v>16.85</v>
+        <v>13.38</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>GNK</t>
+          <t>GSL</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -1014,44 +1014,44 @@
         </is>
       </c>
       <c r="C13" t="n">
-        <v>25.53</v>
+        <v>38.59</v>
       </c>
       <c r="D13" t="n">
-        <v>25.98</v>
+        <v>38.59</v>
       </c>
       <c r="E13" t="n">
-        <v>1.78</v>
+        <v>0</v>
       </c>
       <c r="F13" t="n">
-        <v>-8</v>
+        <v>-4.5</v>
       </c>
       <c r="G13" t="n">
-        <v>-6.5</v>
+        <v>-4.5</v>
       </c>
       <c r="H13" t="n">
-        <v>1.4</v>
+        <v>0</v>
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>TRIM/SHORT (overvalued)</t>
+          <t>HOLD (fairly valued)</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t>TRIM/SHORT (overvalued)</t>
+          <t>HOLD (fairly valued)</t>
         </is>
       </c>
       <c r="K13" t="n">
-        <v>23.71</v>
+        <v>40.54</v>
       </c>
       <c r="L13" t="n">
-        <v>24.08</v>
+        <v>40.54</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>2343</t>
+          <t>TNK</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1060,44 +1060,44 @@
         </is>
       </c>
       <c r="C14" t="n">
-        <v>0.4</v>
+        <v>83.31999999999999</v>
       </c>
       <c r="D14" t="n">
-        <v>0.4</v>
+        <v>77.73</v>
       </c>
       <c r="E14" t="n">
-        <v>-1.14</v>
+        <v>-6.71</v>
       </c>
       <c r="F14" t="n">
-        <v>-6.3</v>
+        <v>1</v>
       </c>
       <c r="G14" t="n">
-        <v>-7.2</v>
+        <v>-4.6</v>
       </c>
       <c r="H14" t="n">
-        <v>-0.9</v>
+        <v>-5.6</v>
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>TRIM/SHORT (overvalued)</t>
+          <t>HOLD (fairly valued)</t>
         </is>
       </c>
       <c r="J14" t="inlineStr">
         <is>
-          <t>TRIM/SHORT (overvalued)</t>
+          <t>HOLD (fairly valued)</t>
         </is>
       </c>
       <c r="K14" t="n">
-        <v>0.39</v>
+        <v>78.05</v>
       </c>
       <c r="L14" t="n">
-        <v>0.39</v>
+        <v>73.69</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>TNK</t>
+          <t>GNK</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1106,68 +1106,68 @@
         </is>
       </c>
       <c r="C15" t="n">
-        <v>83.31999999999999</v>
+        <v>25.53</v>
       </c>
       <c r="D15" t="n">
-        <v>77.73</v>
+        <v>25.98</v>
       </c>
       <c r="E15" t="n">
-        <v>-6.71</v>
+        <v>1.78</v>
       </c>
       <c r="F15" t="n">
-        <v>-2.4</v>
+        <v>-6.4</v>
       </c>
       <c r="G15" t="n">
-        <v>-7.8</v>
+        <v>-4.9</v>
       </c>
       <c r="H15" t="n">
-        <v>-5.5</v>
+        <v>1.5</v>
       </c>
       <c r="I15" t="inlineStr">
         <is>
+          <t>TRIM/SHORT (overvalued)</t>
+        </is>
+      </c>
+      <c r="J15" t="inlineStr">
+        <is>
           <t>HOLD (fairly valued)</t>
         </is>
       </c>
-      <c r="J15" t="inlineStr">
-        <is>
-          <t>TRIM/SHORT (overvalued)</t>
-        </is>
-      </c>
       <c r="K15" t="n">
-        <v>78.05</v>
+        <v>23.71</v>
       </c>
       <c r="L15" t="n">
-        <v>73.69</v>
+        <v>24.08</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>GSL</t>
+          <t>CMBT</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>whole-company</t>
+          <t>WHOLE-COMPANY (hybrid aggregation)</t>
         </is>
       </c>
       <c r="C16" t="n">
-        <v>38.59</v>
+        <v>15.84</v>
       </c>
       <c r="D16" t="n">
-        <v>38.59</v>
+        <v>16.19</v>
       </c>
       <c r="E16" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="F16" t="n">
-        <v>-8.5</v>
+        <v>-15.3</v>
       </c>
       <c r="G16" t="n">
-        <v>-8.5</v>
+        <v>-13.4</v>
       </c>
       <c r="H16" t="n">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="I16" t="inlineStr">
         <is>
@@ -1180,40 +1180,40 @@
         </is>
       </c>
       <c r="K16" t="n">
-        <v>40.54</v>
+        <v>13.8</v>
       </c>
       <c r="L16" t="n">
-        <v>40.54</v>
+        <v>14.11</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>CMBT</t>
+          <t>HAFN</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>WHOLE-COMPANY (hybrid aggregation)</t>
+          <t>whole-company</t>
         </is>
       </c>
       <c r="C17" t="n">
-        <v>15.84</v>
+        <v>5.69</v>
       </c>
       <c r="D17" t="n">
-        <v>16.19</v>
+        <v>5.57</v>
       </c>
       <c r="E17" t="n">
-        <v>2.2</v>
+        <v>-2.09</v>
       </c>
       <c r="F17" t="n">
-        <v>-14.6</v>
+        <v>-15.7</v>
       </c>
       <c r="G17" t="n">
-        <v>-12.7</v>
+        <v>-17.1</v>
       </c>
       <c r="H17" t="n">
-        <v>1.9</v>
+        <v>-1.4</v>
       </c>
       <c r="I17" t="inlineStr">
         <is>
@@ -1226,16 +1226,16 @@
         </is>
       </c>
       <c r="K17" t="n">
-        <v>13.8</v>
+        <v>6.33</v>
       </c>
       <c r="L17" t="n">
-        <v>14.11</v>
+        <v>6.23</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>HAFN</t>
+          <t>MPCC</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1244,22 +1244,22 @@
         </is>
       </c>
       <c r="C18" t="n">
-        <v>5.69</v>
+        <v>2.04</v>
       </c>
       <c r="D18" t="n">
-        <v>5.57</v>
+        <v>2.04</v>
       </c>
       <c r="E18" t="n">
-        <v>-2.09</v>
+        <v>0</v>
       </c>
       <c r="F18" t="n">
-        <v>-17.5</v>
+        <v>-19.4</v>
       </c>
       <c r="G18" t="n">
-        <v>-18.8</v>
+        <v>-19.4</v>
       </c>
       <c r="H18" t="n">
-        <v>-1.3</v>
+        <v>0</v>
       </c>
       <c r="I18" t="inlineStr">
         <is>
@@ -1272,16 +1272,16 @@
         </is>
       </c>
       <c r="K18" t="n">
-        <v>6.33</v>
+        <v>2.06</v>
       </c>
       <c r="L18" t="n">
-        <v>6.23</v>
+        <v>2.06</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>MPCC</t>
+          <t>2343</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1290,22 +1290,22 @@
         </is>
       </c>
       <c r="C19" t="n">
-        <v>2.04</v>
+        <v>0.4</v>
       </c>
       <c r="D19" t="n">
-        <v>2.04</v>
+        <v>0.4</v>
       </c>
       <c r="E19" t="n">
-        <v>0</v>
+        <v>-1.14</v>
       </c>
       <c r="F19" t="n">
-        <v>-19.8</v>
+        <v>-19.1</v>
       </c>
       <c r="G19" t="n">
-        <v>-19.8</v>
+        <v>-19.9</v>
       </c>
       <c r="H19" t="n">
-        <v>0</v>
+        <v>-0.8</v>
       </c>
       <c r="I19" t="inlineStr">
         <is>
@@ -1318,10 +1318,10 @@
         </is>
       </c>
       <c r="K19" t="n">
-        <v>2.06</v>
+        <v>0.39</v>
       </c>
       <c r="L19" t="n">
-        <v>2.06</v>
+        <v>0.39</v>
       </c>
     </row>
     <row r="20">
@@ -1345,13 +1345,13 @@
         <v>-15.47</v>
       </c>
       <c r="F20" t="n">
-        <v>-18.1</v>
+        <v>-18.5</v>
       </c>
       <c r="G20" t="n">
-        <v>-29</v>
+        <v>-29.4</v>
       </c>
       <c r="H20" t="n">
-        <v>-11</v>
+        <v>-10.9</v>
       </c>
       <c r="I20" t="inlineStr">
         <is>
@@ -1373,7 +1373,7 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>LPG</t>
+          <t>BWLP</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -1382,19 +1382,19 @@
         </is>
       </c>
       <c r="C21" t="n">
-        <v>34.12</v>
+        <v>15.81</v>
       </c>
       <c r="D21" t="n">
-        <v>34.11</v>
+        <v>15.8</v>
       </c>
       <c r="E21" t="n">
-        <v>-0.05</v>
+        <v>-0.07000000000000001</v>
       </c>
       <c r="F21" t="n">
-        <v>-34.3</v>
+        <v>-33</v>
       </c>
       <c r="G21" t="n">
-        <v>-34.4</v>
+        <v>-33</v>
       </c>
       <c r="H21" t="n">
         <v>-0</v>
@@ -1410,16 +1410,16 @@
         </is>
       </c>
       <c r="K21" t="n">
-        <v>30.56</v>
+        <v>14.47</v>
       </c>
       <c r="L21" t="n">
-        <v>30.55</v>
+        <v>14.46</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>BWLP</t>
+          <t>LPG</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -1428,19 +1428,19 @@
         </is>
       </c>
       <c r="C22" t="n">
-        <v>15.81</v>
+        <v>34.12</v>
       </c>
       <c r="D22" t="n">
-        <v>15.8</v>
+        <v>34.11</v>
       </c>
       <c r="E22" t="n">
-        <v>-0.07000000000000001</v>
+        <v>-0.05</v>
       </c>
       <c r="F22" t="n">
-        <v>-36.3</v>
+        <v>-33.2</v>
       </c>
       <c r="G22" t="n">
-        <v>-36.3</v>
+        <v>-33.2</v>
       </c>
       <c r="H22" t="n">
         <v>-0</v>
@@ -1456,40 +1456,40 @@
         </is>
       </c>
       <c r="K22" t="n">
-        <v>14.47</v>
+        <v>30.56</v>
       </c>
       <c r="L22" t="n">
-        <v>14.46</v>
+        <v>30.55</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>FRO</t>
+          <t>INSW</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>whole-company</t>
+          <t>WHOLE-COMPANY (hybrid aggregation)</t>
         </is>
       </c>
       <c r="C23" t="n">
-        <v>28.47</v>
+        <v>57.91</v>
       </c>
       <c r="D23" t="n">
-        <v>24.11</v>
+        <v>52.48</v>
       </c>
       <c r="E23" t="n">
-        <v>-15.33</v>
+        <v>-9.380000000000001</v>
       </c>
       <c r="F23" t="n">
-        <v>-31.7</v>
+        <v>-36.4</v>
       </c>
       <c r="G23" t="n">
-        <v>-41.2</v>
+        <v>-41.1</v>
       </c>
       <c r="H23" t="n">
-        <v>-9.5</v>
+        <v>-4.7</v>
       </c>
       <c r="I23" t="inlineStr">
         <is>
@@ -1502,40 +1502,40 @@
         </is>
       </c>
       <c r="K23" t="n">
-        <v>26.88</v>
+        <v>58.82</v>
       </c>
       <c r="L23" t="n">
-        <v>23.15</v>
+        <v>54.46</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>INSW</t>
+          <t>FRO</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>WHOLE-COMPANY (hybrid aggregation)</t>
+          <t>whole-company</t>
         </is>
       </c>
       <c r="C24" t="n">
-        <v>57.91</v>
+        <v>28.47</v>
       </c>
       <c r="D24" t="n">
-        <v>52.48</v>
+        <v>24.11</v>
       </c>
       <c r="E24" t="n">
-        <v>-9.380000000000001</v>
+        <v>-15.33</v>
       </c>
       <c r="F24" t="n">
-        <v>-38.8</v>
+        <v>-32.4</v>
       </c>
       <c r="G24" t="n">
-        <v>-43.3</v>
+        <v>-41.8</v>
       </c>
       <c r="H24" t="n">
-        <v>-4.5</v>
+        <v>-9.4</v>
       </c>
       <c r="I24" t="inlineStr">
         <is>
@@ -1548,10 +1548,10 @@
         </is>
       </c>
       <c r="K24" t="n">
-        <v>58.82</v>
+        <v>26.88</v>
       </c>
       <c r="L24" t="n">
-        <v>54.46</v>
+        <v>23.15</v>
       </c>
     </row>
     <row r="25">
@@ -1575,13 +1575,13 @@
         <v>-14.81</v>
       </c>
       <c r="F25" t="n">
-        <v>-37.8</v>
+        <v>-39.2</v>
       </c>
       <c r="G25" t="n">
-        <v>-46.2</v>
+        <v>-47.4</v>
       </c>
       <c r="H25" t="n">
-        <v>-8.300000000000001</v>
+        <v>-8.1</v>
       </c>
       <c r="I25" t="inlineStr">
         <is>
@@ -1621,13 +1621,13 @@
         <v>-14.2</v>
       </c>
       <c r="F26" t="n">
-        <v>-51.5</v>
+        <v>-51</v>
       </c>
       <c r="G26" t="n">
-        <v>-57.2</v>
+        <v>-56.8</v>
       </c>
       <c r="H26" t="n">
-        <v>-5.7</v>
+        <v>-5.8</v>
       </c>
       <c r="I26" t="inlineStr">
         <is>

--- a/outputs/transaction_anchor_comparison.xlsx
+++ b/outputs/transaction_anchor_comparison.xlsx
@@ -600,22 +600,22 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>9.720000000000001</v>
+        <v>9.67</v>
       </c>
       <c r="D4" t="n">
-        <v>10.07</v>
+        <v>10.03</v>
       </c>
       <c r="E4" t="n">
-        <v>3.64</v>
+        <v>3.8</v>
       </c>
       <c r="F4" t="n">
-        <v>20</v>
+        <v>19.8</v>
       </c>
       <c r="G4" t="n">
         <v>24.6</v>
       </c>
       <c r="H4" t="n">
-        <v>4.6</v>
+        <v>4.8</v>
       </c>
       <c r="I4" t="inlineStr">
         <is>
@@ -628,7 +628,7 @@
         </is>
       </c>
       <c r="K4" t="n">
-        <v>9.119999999999999</v>
+        <v>9.1</v>
       </c>
       <c r="L4" t="n">
         <v>9.470000000000001</v>
@@ -729,7 +729,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>STNG</t>
+          <t>TNK</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -738,22 +738,22 @@
         </is>
       </c>
       <c r="C7" t="n">
-        <v>80.97</v>
+        <v>89.65000000000001</v>
       </c>
       <c r="D7" t="n">
-        <v>77.13</v>
+        <v>84.59999999999999</v>
       </c>
       <c r="E7" t="n">
-        <v>-4.74</v>
+        <v>-5.63</v>
       </c>
       <c r="F7" t="n">
-        <v>5.5</v>
+        <v>8.5</v>
       </c>
       <c r="G7" t="n">
-        <v>1</v>
+        <v>3.4</v>
       </c>
       <c r="H7" t="n">
-        <v>-4.5</v>
+        <v>-5.1</v>
       </c>
       <c r="I7" t="inlineStr">
         <is>
@@ -766,10 +766,10 @@
         </is>
       </c>
       <c r="K7" t="n">
-        <v>80.3</v>
+        <v>83.81</v>
       </c>
       <c r="L7" t="n">
-        <v>76.87</v>
+        <v>79.87</v>
       </c>
     </row>
     <row r="8">
@@ -784,19 +784,19 @@
         </is>
       </c>
       <c r="C8" t="n">
-        <v>17.82</v>
+        <v>17.38</v>
       </c>
       <c r="D8" t="n">
-        <v>17.82</v>
+        <v>17.37</v>
       </c>
       <c r="E8" t="n">
         <v>-0.02</v>
       </c>
       <c r="F8" t="n">
-        <v>0.9</v>
+        <v>2.4</v>
       </c>
       <c r="G8" t="n">
-        <v>0.8</v>
+        <v>2.4</v>
       </c>
       <c r="H8" t="n">
         <v>-0</v>
@@ -812,16 +812,16 @@
         </is>
       </c>
       <c r="K8" t="n">
-        <v>16.85</v>
+        <v>17.12</v>
       </c>
       <c r="L8" t="n">
-        <v>16.85</v>
+        <v>17.11</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>BRUT</t>
+          <t>STNG</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -830,44 +830,44 @@
         </is>
       </c>
       <c r="C9" t="n">
-        <v>8.800000000000001</v>
+        <v>80.97</v>
       </c>
       <c r="D9" t="n">
-        <v>8.800000000000001</v>
+        <v>77.13</v>
       </c>
       <c r="E9" t="n">
-        <v>0</v>
+        <v>-4.74</v>
       </c>
       <c r="F9" t="n">
-        <v>2.5</v>
+        <v>5.5</v>
       </c>
       <c r="G9" t="n">
-        <v>0.7</v>
+        <v>1</v>
       </c>
       <c r="H9" t="n">
-        <v>-1.7</v>
+        <v>-4.5</v>
       </c>
       <c r="I9" t="inlineStr">
         <is>
+          <t>BUY (undervalued)</t>
+        </is>
+      </c>
+      <c r="J9" t="inlineStr">
+        <is>
           <t>HOLD (fairly valued)</t>
         </is>
       </c>
-      <c r="J9" t="inlineStr">
-        <is>
-          <t>HOLD (fairly valued)</t>
-        </is>
-      </c>
       <c r="K9" t="n">
-        <v>6.57</v>
+        <v>80.3</v>
       </c>
       <c r="L9" t="n">
-        <v>6.45</v>
+        <v>76.87</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>FLNG</t>
+          <t>BRUT</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -876,22 +876,22 @@
         </is>
       </c>
       <c r="C10" t="n">
-        <v>28.45</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="D10" t="n">
-        <v>28.45</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="E10" t="n">
         <v>0</v>
       </c>
       <c r="F10" t="n">
-        <v>-0.5</v>
+        <v>2.5</v>
       </c>
       <c r="G10" t="n">
-        <v>-0.5</v>
+        <v>0.7</v>
       </c>
       <c r="H10" t="n">
-        <v>0</v>
+        <v>-1.7</v>
       </c>
       <c r="I10" t="inlineStr">
         <is>
@@ -904,16 +904,16 @@
         </is>
       </c>
       <c r="K10" t="n">
-        <v>30.67</v>
+        <v>6.57</v>
       </c>
       <c r="L10" t="n">
-        <v>30.67</v>
+        <v>6.45</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>SBLK</t>
+          <t>FLNG</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -922,22 +922,22 @@
         </is>
       </c>
       <c r="C11" t="n">
-        <v>29.77</v>
+        <v>28.45</v>
       </c>
       <c r="D11" t="n">
-        <v>30.64</v>
+        <v>28.45</v>
       </c>
       <c r="E11" t="n">
-        <v>2.93</v>
+        <v>0</v>
       </c>
       <c r="F11" t="n">
-        <v>-3.5</v>
+        <v>-0.5</v>
       </c>
       <c r="G11" t="n">
-        <v>-1</v>
+        <v>-0.5</v>
       </c>
       <c r="H11" t="n">
-        <v>2.6</v>
+        <v>0</v>
       </c>
       <c r="I11" t="inlineStr">
         <is>
@@ -950,16 +950,16 @@
         </is>
       </c>
       <c r="K11" t="n">
-        <v>27.89</v>
+        <v>30.67</v>
       </c>
       <c r="L11" t="n">
-        <v>28.62</v>
+        <v>30.67</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>CAPT</t>
+          <t>SBLK</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -968,22 +968,22 @@
         </is>
       </c>
       <c r="C12" t="n">
-        <v>15.61</v>
+        <v>29.77</v>
       </c>
       <c r="D12" t="n">
-        <v>15.49</v>
+        <v>30.64</v>
       </c>
       <c r="E12" t="n">
-        <v>-0.77</v>
+        <v>2.93</v>
       </c>
       <c r="F12" t="n">
-        <v>-2.4</v>
+        <v>-3.5</v>
       </c>
       <c r="G12" t="n">
-        <v>-4</v>
+        <v>-1</v>
       </c>
       <c r="H12" t="n">
-        <v>-1.6</v>
+        <v>2.6</v>
       </c>
       <c r="I12" t="inlineStr">
         <is>
@@ -996,16 +996,16 @@
         </is>
       </c>
       <c r="K12" t="n">
-        <v>13.6</v>
+        <v>27.89</v>
       </c>
       <c r="L12" t="n">
-        <v>13.38</v>
+        <v>28.62</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>GSL</t>
+          <t>CAPT</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -1014,22 +1014,22 @@
         </is>
       </c>
       <c r="C13" t="n">
-        <v>38.59</v>
+        <v>15.61</v>
       </c>
       <c r="D13" t="n">
-        <v>38.59</v>
+        <v>15.49</v>
       </c>
       <c r="E13" t="n">
-        <v>0</v>
+        <v>-0.77</v>
       </c>
       <c r="F13" t="n">
-        <v>-4.5</v>
+        <v>-2.4</v>
       </c>
       <c r="G13" t="n">
-        <v>-4.5</v>
+        <v>-4</v>
       </c>
       <c r="H13" t="n">
-        <v>0</v>
+        <v>-1.6</v>
       </c>
       <c r="I13" t="inlineStr">
         <is>
@@ -1042,16 +1042,16 @@
         </is>
       </c>
       <c r="K13" t="n">
-        <v>40.54</v>
+        <v>13.6</v>
       </c>
       <c r="L13" t="n">
-        <v>40.54</v>
+        <v>13.38</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>TNK</t>
+          <t>GSL</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1060,22 +1060,22 @@
         </is>
       </c>
       <c r="C14" t="n">
-        <v>83.31999999999999</v>
+        <v>38.59</v>
       </c>
       <c r="D14" t="n">
-        <v>77.73</v>
+        <v>38.59</v>
       </c>
       <c r="E14" t="n">
-        <v>-6.71</v>
+        <v>0</v>
       </c>
       <c r="F14" t="n">
-        <v>1</v>
+        <v>-4.5</v>
       </c>
       <c r="G14" t="n">
-        <v>-4.6</v>
+        <v>-4.5</v>
       </c>
       <c r="H14" t="n">
-        <v>-5.6</v>
+        <v>0</v>
       </c>
       <c r="I14" t="inlineStr">
         <is>
@@ -1088,10 +1088,10 @@
         </is>
       </c>
       <c r="K14" t="n">
-        <v>78.05</v>
+        <v>40.54</v>
       </c>
       <c r="L14" t="n">
-        <v>73.69</v>
+        <v>40.54</v>
       </c>
     </row>
     <row r="15">

--- a/outputs/transaction_anchor_comparison.xlsx
+++ b/outputs/transaction_anchor_comparison.xlsx
@@ -1566,22 +1566,22 @@
         </is>
       </c>
       <c r="C25" t="n">
-        <v>40.4</v>
+        <v>43.8</v>
       </c>
       <c r="D25" t="n">
-        <v>34.42</v>
+        <v>37.65</v>
       </c>
       <c r="E25" t="n">
-        <v>-14.81</v>
+        <v>-14.05</v>
       </c>
       <c r="F25" t="n">
-        <v>-39.2</v>
+        <v>-34</v>
       </c>
       <c r="G25" t="n">
-        <v>-47.4</v>
+        <v>-42.3</v>
       </c>
       <c r="H25" t="n">
-        <v>-8.1</v>
+        <v>-8.300000000000001</v>
       </c>
       <c r="I25" t="inlineStr">
         <is>
@@ -1594,10 +1594,10 @@
         </is>
       </c>
       <c r="K25" t="n">
-        <v>37.6</v>
+        <v>40.83</v>
       </c>
       <c r="L25" t="n">
-        <v>32.57</v>
+        <v>35.69</v>
       </c>
     </row>
     <row r="26">

--- a/outputs/transaction_anchor_comparison.xlsx
+++ b/outputs/transaction_anchor_comparison.xlsx
@@ -508,19 +508,19 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>28.1</v>
+        <v>25.7</v>
       </c>
       <c r="D2" t="n">
-        <v>28.1</v>
+        <v>25.7</v>
       </c>
       <c r="E2" t="n">
         <v>0</v>
       </c>
       <c r="F2" t="n">
-        <v>60.5</v>
+        <v>50.7</v>
       </c>
       <c r="G2" t="n">
-        <v>60.5</v>
+        <v>50.7</v>
       </c>
       <c r="H2" t="n">
         <v>0</v>
@@ -536,10 +536,10 @@
         </is>
       </c>
       <c r="K2" t="n">
-        <v>35.91</v>
+        <v>33.7</v>
       </c>
       <c r="L2" t="n">
-        <v>35.91</v>
+        <v>33.7</v>
       </c>
     </row>
     <row r="3">

--- a/outputs/transaction_anchor_comparison.xlsx
+++ b/outputs/transaction_anchor_comparison.xlsx
@@ -821,7 +821,7 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>STNG</t>
+          <t>BRUT</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -830,26 +830,26 @@
         </is>
       </c>
       <c r="C9" t="n">
-        <v>80.97</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="D9" t="n">
-        <v>77.13</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="E9" t="n">
-        <v>-4.74</v>
+        <v>0</v>
       </c>
       <c r="F9" t="n">
-        <v>5.5</v>
+        <v>2.5</v>
       </c>
       <c r="G9" t="n">
-        <v>1</v>
+        <v>0.7</v>
       </c>
       <c r="H9" t="n">
-        <v>-4.5</v>
+        <v>-1.7</v>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>BUY (undervalued)</t>
+          <t>HOLD (fairly valued)</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
@@ -858,16 +858,16 @@
         </is>
       </c>
       <c r="K9" t="n">
-        <v>80.3</v>
+        <v>6.57</v>
       </c>
       <c r="L9" t="n">
-        <v>76.87</v>
+        <v>6.45</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>BRUT</t>
+          <t>FLNG</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -876,22 +876,22 @@
         </is>
       </c>
       <c r="C10" t="n">
-        <v>8.800000000000001</v>
+        <v>28.45</v>
       </c>
       <c r="D10" t="n">
-        <v>8.800000000000001</v>
+        <v>28.45</v>
       </c>
       <c r="E10" t="n">
         <v>0</v>
       </c>
       <c r="F10" t="n">
-        <v>2.5</v>
+        <v>-0.5</v>
       </c>
       <c r="G10" t="n">
-        <v>0.7</v>
+        <v>-0.5</v>
       </c>
       <c r="H10" t="n">
-        <v>-1.7</v>
+        <v>0</v>
       </c>
       <c r="I10" t="inlineStr">
         <is>
@@ -904,16 +904,16 @@
         </is>
       </c>
       <c r="K10" t="n">
-        <v>6.57</v>
+        <v>30.67</v>
       </c>
       <c r="L10" t="n">
-        <v>6.45</v>
+        <v>30.67</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>FLNG</t>
+          <t>SBLK</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -922,22 +922,22 @@
         </is>
       </c>
       <c r="C11" t="n">
-        <v>28.45</v>
+        <v>29.77</v>
       </c>
       <c r="D11" t="n">
-        <v>28.45</v>
+        <v>30.64</v>
       </c>
       <c r="E11" t="n">
-        <v>0</v>
+        <v>2.93</v>
       </c>
       <c r="F11" t="n">
-        <v>-0.5</v>
+        <v>-3.5</v>
       </c>
       <c r="G11" t="n">
-        <v>-0.5</v>
+        <v>-1</v>
       </c>
       <c r="H11" t="n">
-        <v>0</v>
+        <v>2.6</v>
       </c>
       <c r="I11" t="inlineStr">
         <is>
@@ -950,16 +950,16 @@
         </is>
       </c>
       <c r="K11" t="n">
-        <v>30.67</v>
+        <v>27.89</v>
       </c>
       <c r="L11" t="n">
-        <v>30.67</v>
+        <v>28.62</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>SBLK</t>
+          <t>STNG</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -968,22 +968,22 @@
         </is>
       </c>
       <c r="C12" t="n">
-        <v>29.77</v>
+        <v>79.63</v>
       </c>
       <c r="D12" t="n">
-        <v>30.64</v>
+        <v>76.42</v>
       </c>
       <c r="E12" t="n">
-        <v>2.93</v>
+        <v>-4.03</v>
       </c>
       <c r="F12" t="n">
-        <v>-3.5</v>
+        <v>0.6</v>
       </c>
       <c r="G12" t="n">
-        <v>-1</v>
+        <v>-3.1</v>
       </c>
       <c r="H12" t="n">
-        <v>2.6</v>
+        <v>-3.7</v>
       </c>
       <c r="I12" t="inlineStr">
         <is>
@@ -996,10 +996,10 @@
         </is>
       </c>
       <c r="K12" t="n">
-        <v>27.89</v>
+        <v>76.52</v>
       </c>
       <c r="L12" t="n">
-        <v>28.62</v>
+        <v>73.73</v>
       </c>
     </row>
     <row r="13">

--- a/outputs/transaction_anchor_comparison.xlsx
+++ b/outputs/transaction_anchor_comparison.xlsx
@@ -1373,7 +1373,7 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>BWLP</t>
+          <t>LPG</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -1382,19 +1382,19 @@
         </is>
       </c>
       <c r="C21" t="n">
-        <v>15.81</v>
+        <v>35.7</v>
       </c>
       <c r="D21" t="n">
-        <v>15.8</v>
+        <v>35.69</v>
       </c>
       <c r="E21" t="n">
-        <v>-0.07000000000000001</v>
+        <v>-0.04</v>
       </c>
       <c r="F21" t="n">
-        <v>-33</v>
+        <v>-30.4</v>
       </c>
       <c r="G21" t="n">
-        <v>-33</v>
+        <v>-30.5</v>
       </c>
       <c r="H21" t="n">
         <v>-0</v>
@@ -1410,16 +1410,16 @@
         </is>
       </c>
       <c r="K21" t="n">
-        <v>14.47</v>
+        <v>31.84</v>
       </c>
       <c r="L21" t="n">
-        <v>14.46</v>
+        <v>31.82</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>LPG</t>
+          <t>BWLP</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -1428,19 +1428,19 @@
         </is>
       </c>
       <c r="C22" t="n">
-        <v>34.12</v>
+        <v>15.81</v>
       </c>
       <c r="D22" t="n">
-        <v>34.11</v>
+        <v>15.8</v>
       </c>
       <c r="E22" t="n">
-        <v>-0.05</v>
+        <v>-0.07000000000000001</v>
       </c>
       <c r="F22" t="n">
-        <v>-33.2</v>
+        <v>-33</v>
       </c>
       <c r="G22" t="n">
-        <v>-33.2</v>
+        <v>-33</v>
       </c>
       <c r="H22" t="n">
         <v>-0</v>
@@ -1456,10 +1456,10 @@
         </is>
       </c>
       <c r="K22" t="n">
-        <v>30.56</v>
+        <v>14.47</v>
       </c>
       <c r="L22" t="n">
-        <v>30.55</v>
+        <v>14.46</v>
       </c>
     </row>
     <row r="23">

--- a/outputs/transaction_anchor_comparison.xlsx
+++ b/outputs/transaction_anchor_comparison.xlsx
@@ -821,7 +821,7 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>BRUT</t>
+          <t>GSL</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -830,22 +830,22 @@
         </is>
       </c>
       <c r="C9" t="n">
-        <v>8.800000000000001</v>
+        <v>41.2</v>
       </c>
       <c r="D9" t="n">
-        <v>8.800000000000001</v>
+        <v>41.2</v>
       </c>
       <c r="E9" t="n">
         <v>0</v>
       </c>
       <c r="F9" t="n">
-        <v>2.5</v>
+        <v>1.4</v>
       </c>
       <c r="G9" t="n">
-        <v>0.7</v>
+        <v>1.4</v>
       </c>
       <c r="H9" t="n">
-        <v>-1.7</v>
+        <v>0</v>
       </c>
       <c r="I9" t="inlineStr">
         <is>
@@ -858,16 +858,16 @@
         </is>
       </c>
       <c r="K9" t="n">
-        <v>6.57</v>
+        <v>43.02</v>
       </c>
       <c r="L9" t="n">
-        <v>6.45</v>
+        <v>43.02</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>FLNG</t>
+          <t>BRUT</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -876,22 +876,22 @@
         </is>
       </c>
       <c r="C10" t="n">
-        <v>28.45</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="D10" t="n">
-        <v>28.45</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="E10" t="n">
         <v>0</v>
       </c>
       <c r="F10" t="n">
-        <v>-0.5</v>
+        <v>2.5</v>
       </c>
       <c r="G10" t="n">
-        <v>-0.5</v>
+        <v>0.7</v>
       </c>
       <c r="H10" t="n">
-        <v>0</v>
+        <v>-1.7</v>
       </c>
       <c r="I10" t="inlineStr">
         <is>
@@ -904,16 +904,16 @@
         </is>
       </c>
       <c r="K10" t="n">
-        <v>30.67</v>
+        <v>6.57</v>
       </c>
       <c r="L10" t="n">
-        <v>30.67</v>
+        <v>6.45</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>SBLK</t>
+          <t>FLNG</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -922,22 +922,22 @@
         </is>
       </c>
       <c r="C11" t="n">
-        <v>29.77</v>
+        <v>28.45</v>
       </c>
       <c r="D11" t="n">
-        <v>30.64</v>
+        <v>28.45</v>
       </c>
       <c r="E11" t="n">
-        <v>2.93</v>
+        <v>0</v>
       </c>
       <c r="F11" t="n">
-        <v>-3.5</v>
+        <v>-0.5</v>
       </c>
       <c r="G11" t="n">
-        <v>-1</v>
+        <v>-0.5</v>
       </c>
       <c r="H11" t="n">
-        <v>2.6</v>
+        <v>0</v>
       </c>
       <c r="I11" t="inlineStr">
         <is>
@@ -950,16 +950,16 @@
         </is>
       </c>
       <c r="K11" t="n">
-        <v>27.89</v>
+        <v>30.67</v>
       </c>
       <c r="L11" t="n">
-        <v>28.62</v>
+        <v>30.67</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>STNG</t>
+          <t>SBLK</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -968,22 +968,22 @@
         </is>
       </c>
       <c r="C12" t="n">
-        <v>79.63</v>
+        <v>29.77</v>
       </c>
       <c r="D12" t="n">
-        <v>76.42</v>
+        <v>30.64</v>
       </c>
       <c r="E12" t="n">
-        <v>-4.03</v>
+        <v>2.93</v>
       </c>
       <c r="F12" t="n">
-        <v>0.6</v>
+        <v>-3.5</v>
       </c>
       <c r="G12" t="n">
-        <v>-3.1</v>
+        <v>-1</v>
       </c>
       <c r="H12" t="n">
-        <v>-3.7</v>
+        <v>2.6</v>
       </c>
       <c r="I12" t="inlineStr">
         <is>
@@ -996,16 +996,16 @@
         </is>
       </c>
       <c r="K12" t="n">
-        <v>76.52</v>
+        <v>27.89</v>
       </c>
       <c r="L12" t="n">
-        <v>73.73</v>
+        <v>28.62</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>CAPT</t>
+          <t>STNG</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -1014,22 +1014,22 @@
         </is>
       </c>
       <c r="C13" t="n">
-        <v>15.61</v>
+        <v>79.63</v>
       </c>
       <c r="D13" t="n">
-        <v>15.49</v>
+        <v>76.42</v>
       </c>
       <c r="E13" t="n">
-        <v>-0.77</v>
+        <v>-4.03</v>
       </c>
       <c r="F13" t="n">
-        <v>-2.4</v>
+        <v>0.6</v>
       </c>
       <c r="G13" t="n">
-        <v>-4</v>
+        <v>-3.1</v>
       </c>
       <c r="H13" t="n">
-        <v>-1.6</v>
+        <v>-3.7</v>
       </c>
       <c r="I13" t="inlineStr">
         <is>
@@ -1042,16 +1042,16 @@
         </is>
       </c>
       <c r="K13" t="n">
-        <v>13.6</v>
+        <v>76.52</v>
       </c>
       <c r="L13" t="n">
-        <v>13.38</v>
+        <v>73.73</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>GSL</t>
+          <t>CAPT</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1060,22 +1060,22 @@
         </is>
       </c>
       <c r="C14" t="n">
-        <v>38.59</v>
+        <v>15.61</v>
       </c>
       <c r="D14" t="n">
-        <v>38.59</v>
+        <v>15.49</v>
       </c>
       <c r="E14" t="n">
-        <v>0</v>
+        <v>-0.77</v>
       </c>
       <c r="F14" t="n">
-        <v>-4.5</v>
+        <v>-2.4</v>
       </c>
       <c r="G14" t="n">
-        <v>-4.5</v>
+        <v>-4</v>
       </c>
       <c r="H14" t="n">
-        <v>0</v>
+        <v>-1.6</v>
       </c>
       <c r="I14" t="inlineStr">
         <is>
@@ -1088,10 +1088,10 @@
         </is>
       </c>
       <c r="K14" t="n">
-        <v>40.54</v>
+        <v>13.6</v>
       </c>
       <c r="L14" t="n">
-        <v>40.54</v>
+        <v>13.38</v>
       </c>
     </row>
     <row r="15">

--- a/outputs/transaction_anchor_comparison.xlsx
+++ b/outputs/transaction_anchor_comparison.xlsx
@@ -1336,19 +1336,19 @@
         </is>
       </c>
       <c r="C20" t="n">
-        <v>16.07</v>
+        <v>16.3</v>
       </c>
       <c r="D20" t="n">
-        <v>13.58</v>
+        <v>13.83</v>
       </c>
       <c r="E20" t="n">
-        <v>-15.47</v>
+        <v>-15.2</v>
       </c>
       <c r="F20" t="n">
-        <v>-18.5</v>
+        <v>-17.1</v>
       </c>
       <c r="G20" t="n">
-        <v>-29.4</v>
+        <v>-28</v>
       </c>
       <c r="H20" t="n">
         <v>-10.9</v>
@@ -1364,10 +1364,10 @@
         </is>
       </c>
       <c r="K20" t="n">
-        <v>15.29</v>
+        <v>15.55</v>
       </c>
       <c r="L20" t="n">
-        <v>13.24</v>
+        <v>13.51</v>
       </c>
     </row>
     <row r="21">

--- a/outputs/transaction_anchor_comparison.xlsx
+++ b/outputs/transaction_anchor_comparison.xlsx
@@ -1106,22 +1106,22 @@
         </is>
       </c>
       <c r="C15" t="n">
-        <v>25.53</v>
+        <v>24.77</v>
       </c>
       <c r="D15" t="n">
-        <v>25.98</v>
+        <v>25.26</v>
       </c>
       <c r="E15" t="n">
-        <v>1.78</v>
+        <v>1.97</v>
       </c>
       <c r="F15" t="n">
-        <v>-6.4</v>
+        <v>-9.1</v>
       </c>
       <c r="G15" t="n">
-        <v>-4.9</v>
+        <v>-7.5</v>
       </c>
       <c r="H15" t="n">
-        <v>1.5</v>
+        <v>1.6</v>
       </c>
       <c r="I15" t="inlineStr">
         <is>
@@ -1130,14 +1130,14 @@
       </c>
       <c r="J15" t="inlineStr">
         <is>
-          <t>HOLD (fairly valued)</t>
+          <t>TRIM/SHORT (overvalued)</t>
         </is>
       </c>
       <c r="K15" t="n">
-        <v>23.71</v>
+        <v>23.02</v>
       </c>
       <c r="L15" t="n">
-        <v>24.08</v>
+        <v>23.42</v>
       </c>
     </row>
     <row r="16">

--- a/outputs/transaction_anchor_comparison.xlsx
+++ b/outputs/transaction_anchor_comparison.xlsx
@@ -1235,7 +1235,7 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>MPCC</t>
+          <t>2343</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1244,22 +1244,22 @@
         </is>
       </c>
       <c r="C18" t="n">
-        <v>2.04</v>
+        <v>0.41</v>
       </c>
       <c r="D18" t="n">
-        <v>2.04</v>
+        <v>0.41</v>
       </c>
       <c r="E18" t="n">
-        <v>0</v>
+        <v>-1.03</v>
       </c>
       <c r="F18" t="n">
-        <v>-19.4</v>
+        <v>-16.7</v>
       </c>
       <c r="G18" t="n">
-        <v>-19.4</v>
+        <v>-17.5</v>
       </c>
       <c r="H18" t="n">
-        <v>0</v>
+        <v>-0.7</v>
       </c>
       <c r="I18" t="inlineStr">
         <is>
@@ -1272,16 +1272,16 @@
         </is>
       </c>
       <c r="K18" t="n">
-        <v>2.06</v>
+        <v>0.4</v>
       </c>
       <c r="L18" t="n">
-        <v>2.06</v>
+        <v>0.4</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>2343</t>
+          <t>MPCC</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1290,22 +1290,22 @@
         </is>
       </c>
       <c r="C19" t="n">
-        <v>0.4</v>
+        <v>2.04</v>
       </c>
       <c r="D19" t="n">
-        <v>0.4</v>
+        <v>2.04</v>
       </c>
       <c r="E19" t="n">
-        <v>-1.14</v>
+        <v>0</v>
       </c>
       <c r="F19" t="n">
-        <v>-19.1</v>
+        <v>-19.4</v>
       </c>
       <c r="G19" t="n">
-        <v>-19.9</v>
+        <v>-19.4</v>
       </c>
       <c r="H19" t="n">
-        <v>-0.8</v>
+        <v>0</v>
       </c>
       <c r="I19" t="inlineStr">
         <is>
@@ -1318,10 +1318,10 @@
         </is>
       </c>
       <c r="K19" t="n">
-        <v>0.39</v>
+        <v>2.06</v>
       </c>
       <c r="L19" t="n">
-        <v>0.39</v>
+        <v>2.06</v>
       </c>
     </row>
     <row r="20">

--- a/outputs/transaction_anchor_comparison.xlsx
+++ b/outputs/transaction_anchor_comparison.xlsx
@@ -729,7 +729,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>TNK</t>
+          <t>SBLK</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -738,26 +738,26 @@
         </is>
       </c>
       <c r="C7" t="n">
-        <v>89.65000000000001</v>
+        <v>31.53</v>
       </c>
       <c r="D7" t="n">
-        <v>84.59999999999999</v>
+        <v>32.39</v>
       </c>
       <c r="E7" t="n">
-        <v>-5.63</v>
+        <v>2.73</v>
       </c>
       <c r="F7" t="n">
-        <v>8.5</v>
+        <v>2</v>
       </c>
       <c r="G7" t="n">
-        <v>3.4</v>
+        <v>4.6</v>
       </c>
       <c r="H7" t="n">
-        <v>-5.1</v>
+        <v>2.5</v>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>BUY (undervalued)</t>
+          <t>HOLD (fairly valued)</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
@@ -766,16 +766,16 @@
         </is>
       </c>
       <c r="K7" t="n">
-        <v>83.81</v>
+        <v>29.48</v>
       </c>
       <c r="L7" t="n">
-        <v>79.87</v>
+        <v>30.22</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>ASC</t>
+          <t>TNK</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -784,44 +784,44 @@
         </is>
       </c>
       <c r="C8" t="n">
-        <v>17.38</v>
+        <v>89.65000000000001</v>
       </c>
       <c r="D8" t="n">
-        <v>17.37</v>
+        <v>84.59999999999999</v>
       </c>
       <c r="E8" t="n">
-        <v>-0.02</v>
+        <v>-5.63</v>
       </c>
       <c r="F8" t="n">
-        <v>2.4</v>
+        <v>8.5</v>
       </c>
       <c r="G8" t="n">
-        <v>2.4</v>
+        <v>3.4</v>
       </c>
       <c r="H8" t="n">
-        <v>-0</v>
+        <v>-5.1</v>
       </c>
       <c r="I8" t="inlineStr">
         <is>
+          <t>BUY (undervalued)</t>
+        </is>
+      </c>
+      <c r="J8" t="inlineStr">
+        <is>
           <t>HOLD (fairly valued)</t>
         </is>
       </c>
-      <c r="J8" t="inlineStr">
-        <is>
-          <t>HOLD (fairly valued)</t>
-        </is>
-      </c>
       <c r="K8" t="n">
-        <v>17.12</v>
+        <v>83.81</v>
       </c>
       <c r="L8" t="n">
-        <v>17.11</v>
+        <v>79.87</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>GSL</t>
+          <t>ASC</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -830,22 +830,22 @@
         </is>
       </c>
       <c r="C9" t="n">
-        <v>41.2</v>
+        <v>17.38</v>
       </c>
       <c r="D9" t="n">
-        <v>41.2</v>
+        <v>17.37</v>
       </c>
       <c r="E9" t="n">
-        <v>0</v>
+        <v>-0.02</v>
       </c>
       <c r="F9" t="n">
-        <v>1.4</v>
+        <v>2.4</v>
       </c>
       <c r="G9" t="n">
-        <v>1.4</v>
+        <v>2.4</v>
       </c>
       <c r="H9" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="I9" t="inlineStr">
         <is>
@@ -858,16 +858,16 @@
         </is>
       </c>
       <c r="K9" t="n">
-        <v>43.02</v>
+        <v>17.12</v>
       </c>
       <c r="L9" t="n">
-        <v>43.02</v>
+        <v>17.11</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>BRUT</t>
+          <t>GSL</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -876,22 +876,22 @@
         </is>
       </c>
       <c r="C10" t="n">
-        <v>8.800000000000001</v>
+        <v>41.2</v>
       </c>
       <c r="D10" t="n">
-        <v>8.800000000000001</v>
+        <v>41.2</v>
       </c>
       <c r="E10" t="n">
         <v>0</v>
       </c>
       <c r="F10" t="n">
-        <v>2.5</v>
+        <v>1.4</v>
       </c>
       <c r="G10" t="n">
-        <v>0.7</v>
+        <v>1.4</v>
       </c>
       <c r="H10" t="n">
-        <v>-1.7</v>
+        <v>0</v>
       </c>
       <c r="I10" t="inlineStr">
         <is>
@@ -904,16 +904,16 @@
         </is>
       </c>
       <c r="K10" t="n">
-        <v>6.57</v>
+        <v>43.02</v>
       </c>
       <c r="L10" t="n">
-        <v>6.45</v>
+        <v>43.02</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>FLNG</t>
+          <t>BRUT</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -922,22 +922,22 @@
         </is>
       </c>
       <c r="C11" t="n">
-        <v>28.45</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="D11" t="n">
-        <v>28.45</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="E11" t="n">
         <v>0</v>
       </c>
       <c r="F11" t="n">
-        <v>-0.5</v>
+        <v>2.5</v>
       </c>
       <c r="G11" t="n">
-        <v>-0.5</v>
+        <v>0.7</v>
       </c>
       <c r="H11" t="n">
-        <v>0</v>
+        <v>-1.7</v>
       </c>
       <c r="I11" t="inlineStr">
         <is>
@@ -950,16 +950,16 @@
         </is>
       </c>
       <c r="K11" t="n">
-        <v>30.67</v>
+        <v>6.57</v>
       </c>
       <c r="L11" t="n">
-        <v>30.67</v>
+        <v>6.45</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>SBLK</t>
+          <t>FLNG</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -968,22 +968,22 @@
         </is>
       </c>
       <c r="C12" t="n">
-        <v>29.77</v>
+        <v>28.45</v>
       </c>
       <c r="D12" t="n">
-        <v>30.64</v>
+        <v>28.45</v>
       </c>
       <c r="E12" t="n">
-        <v>2.93</v>
+        <v>0</v>
       </c>
       <c r="F12" t="n">
-        <v>-3.5</v>
+        <v>-0.5</v>
       </c>
       <c r="G12" t="n">
-        <v>-1</v>
+        <v>-0.5</v>
       </c>
       <c r="H12" t="n">
-        <v>2.6</v>
+        <v>0</v>
       </c>
       <c r="I12" t="inlineStr">
         <is>
@@ -996,10 +996,10 @@
         </is>
       </c>
       <c r="K12" t="n">
-        <v>27.89</v>
+        <v>30.67</v>
       </c>
       <c r="L12" t="n">
-        <v>28.62</v>
+        <v>30.67</v>
       </c>
     </row>
     <row r="13">

--- a/outputs/transaction_anchor_comparison.xlsx
+++ b/outputs/transaction_anchor_comparison.xlsx
@@ -646,22 +646,22 @@
         </is>
       </c>
       <c r="C5" t="n">
-        <v>32.12</v>
+        <v>31.44</v>
       </c>
       <c r="D5" t="n">
-        <v>32.65</v>
+        <v>31.92</v>
       </c>
       <c r="E5" t="n">
-        <v>1.66</v>
+        <v>1.52</v>
       </c>
       <c r="F5" t="n">
-        <v>15.1</v>
+        <v>12.7</v>
       </c>
       <c r="G5" t="n">
-        <v>16.8</v>
+        <v>14.2</v>
       </c>
       <c r="H5" t="n">
-        <v>1.7</v>
+        <v>1.5</v>
       </c>
       <c r="I5" t="inlineStr">
         <is>
@@ -674,10 +674,10 @@
         </is>
       </c>
       <c r="K5" t="n">
-        <v>20.49</v>
+        <v>20.06</v>
       </c>
       <c r="L5" t="n">
-        <v>20.79</v>
+        <v>20.33</v>
       </c>
     </row>
     <row r="6">

--- a/outputs/transaction_anchor_comparison.xlsx
+++ b/outputs/transaction_anchor_comparison.xlsx
@@ -557,19 +557,19 @@
         <v>94.58</v>
       </c>
       <c r="D3" t="n">
-        <v>87.56999999999999</v>
+        <v>88.16</v>
       </c>
       <c r="E3" t="n">
-        <v>-7.42</v>
+        <v>-6.79</v>
       </c>
       <c r="F3" t="n">
         <v>55.7</v>
       </c>
       <c r="G3" t="n">
-        <v>45.2</v>
+        <v>46</v>
       </c>
       <c r="H3" t="n">
-        <v>-10.5</v>
+        <v>-9.699999999999999</v>
       </c>
       <c r="I3" t="inlineStr">
         <is>
@@ -585,7 +585,7 @@
         <v>60.96</v>
       </c>
       <c r="L3" t="n">
-        <v>56.83</v>
+        <v>57.16</v>
       </c>
     </row>
     <row r="4">
@@ -603,19 +603,19 @@
         <v>9.67</v>
       </c>
       <c r="D4" t="n">
-        <v>10.03</v>
+        <v>10.58</v>
       </c>
       <c r="E4" t="n">
-        <v>3.8</v>
+        <v>9.43</v>
       </c>
       <c r="F4" t="n">
         <v>19.8</v>
       </c>
       <c r="G4" t="n">
-        <v>24.6</v>
+        <v>31.1</v>
       </c>
       <c r="H4" t="n">
-        <v>4.8</v>
+        <v>11.3</v>
       </c>
       <c r="I4" t="inlineStr">
         <is>
@@ -631,7 +631,7 @@
         <v>9.1</v>
       </c>
       <c r="L4" t="n">
-        <v>9.470000000000001</v>
+        <v>9.970000000000001</v>
       </c>
     </row>
     <row r="5">
@@ -649,19 +649,19 @@
         <v>31.44</v>
       </c>
       <c r="D5" t="n">
-        <v>31.92</v>
+        <v>32.43</v>
       </c>
       <c r="E5" t="n">
-        <v>1.52</v>
+        <v>3.12</v>
       </c>
       <c r="F5" t="n">
         <v>12.7</v>
       </c>
       <c r="G5" t="n">
-        <v>14.2</v>
+        <v>15.8</v>
       </c>
       <c r="H5" t="n">
-        <v>1.5</v>
+        <v>3.1</v>
       </c>
       <c r="I5" t="inlineStr">
         <is>
@@ -677,7 +677,7 @@
         <v>20.06</v>
       </c>
       <c r="L5" t="n">
-        <v>20.33</v>
+        <v>20.61</v>
       </c>
     </row>
     <row r="6">
@@ -695,19 +695,19 @@
         <v>31.65</v>
       </c>
       <c r="D6" t="n">
-        <v>30.3</v>
+        <v>30.22</v>
       </c>
       <c r="E6" t="n">
-        <v>-4.25</v>
+        <v>-4.51</v>
       </c>
       <c r="F6" t="n">
         <v>12</v>
       </c>
       <c r="G6" t="n">
-        <v>8.1</v>
+        <v>7.8</v>
       </c>
       <c r="H6" t="n">
-        <v>-3.9</v>
+        <v>-4.2</v>
       </c>
       <c r="I6" t="inlineStr">
         <is>
@@ -723,7 +723,7 @@
         <v>33.03</v>
       </c>
       <c r="L6" t="n">
-        <v>31.87</v>
+        <v>31.8</v>
       </c>
     </row>
     <row r="7">
@@ -741,19 +741,19 @@
         <v>31.53</v>
       </c>
       <c r="D7" t="n">
-        <v>32.39</v>
+        <v>33.04</v>
       </c>
       <c r="E7" t="n">
-        <v>2.73</v>
+        <v>4.78</v>
       </c>
       <c r="F7" t="n">
         <v>2</v>
       </c>
       <c r="G7" t="n">
-        <v>4.6</v>
+        <v>6.4</v>
       </c>
       <c r="H7" t="n">
-        <v>2.5</v>
+        <v>4.4</v>
       </c>
       <c r="I7" t="inlineStr">
         <is>
@@ -762,14 +762,14 @@
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>HOLD (fairly valued)</t>
+          <t>BUY (undervalued)</t>
         </is>
       </c>
       <c r="K7" t="n">
         <v>29.48</v>
       </c>
       <c r="L7" t="n">
-        <v>30.22</v>
+        <v>30.76</v>
       </c>
     </row>
     <row r="8">
@@ -934,10 +934,10 @@
         <v>2.5</v>
       </c>
       <c r="G11" t="n">
-        <v>0.7</v>
+        <v>1.3</v>
       </c>
       <c r="H11" t="n">
-        <v>-1.7</v>
+        <v>-1.2</v>
       </c>
       <c r="I11" t="inlineStr">
         <is>
@@ -953,7 +953,7 @@
         <v>6.57</v>
       </c>
       <c r="L11" t="n">
-        <v>6.45</v>
+        <v>6.49</v>
       </c>
     </row>
     <row r="12">
@@ -1017,19 +1017,19 @@
         <v>79.63</v>
       </c>
       <c r="D13" t="n">
-        <v>76.42</v>
+        <v>76.22</v>
       </c>
       <c r="E13" t="n">
-        <v>-4.03</v>
+        <v>-4.28</v>
       </c>
       <c r="F13" t="n">
         <v>0.6</v>
       </c>
       <c r="G13" t="n">
-        <v>-3.1</v>
+        <v>-3.3</v>
       </c>
       <c r="H13" t="n">
-        <v>-3.7</v>
+        <v>-3.9</v>
       </c>
       <c r="I13" t="inlineStr">
         <is>
@@ -1045,7 +1045,7 @@
         <v>76.52</v>
       </c>
       <c r="L13" t="n">
-        <v>73.73</v>
+        <v>73.56</v>
       </c>
     </row>
     <row r="14">
@@ -1063,19 +1063,19 @@
         <v>15.61</v>
       </c>
       <c r="D14" t="n">
-        <v>15.49</v>
+        <v>15.48</v>
       </c>
       <c r="E14" t="n">
-        <v>-0.77</v>
+        <v>-0.8100000000000001</v>
       </c>
       <c r="F14" t="n">
         <v>-2.4</v>
       </c>
       <c r="G14" t="n">
-        <v>-4</v>
+        <v>-3.9</v>
       </c>
       <c r="H14" t="n">
-        <v>-1.6</v>
+        <v>-1.5</v>
       </c>
       <c r="I14" t="inlineStr">
         <is>
@@ -1091,7 +1091,7 @@
         <v>13.6</v>
       </c>
       <c r="L14" t="n">
-        <v>13.38</v>
+        <v>13.39</v>
       </c>
     </row>
     <row r="15">
@@ -1109,19 +1109,19 @@
         <v>24.77</v>
       </c>
       <c r="D15" t="n">
-        <v>25.26</v>
+        <v>25.38</v>
       </c>
       <c r="E15" t="n">
-        <v>1.97</v>
+        <v>2.46</v>
       </c>
       <c r="F15" t="n">
         <v>-9.1</v>
       </c>
       <c r="G15" t="n">
-        <v>-7.5</v>
+        <v>-7.1</v>
       </c>
       <c r="H15" t="n">
-        <v>1.6</v>
+        <v>2</v>
       </c>
       <c r="I15" t="inlineStr">
         <is>
@@ -1137,7 +1137,7 @@
         <v>23.02</v>
       </c>
       <c r="L15" t="n">
-        <v>23.42</v>
+        <v>23.53</v>
       </c>
     </row>
     <row r="16">
@@ -1155,19 +1155,19 @@
         <v>15.84</v>
       </c>
       <c r="D16" t="n">
-        <v>16.19</v>
+        <v>16.46</v>
       </c>
       <c r="E16" t="n">
-        <v>2.2</v>
+        <v>3.89</v>
       </c>
       <c r="F16" t="n">
         <v>-15.3</v>
       </c>
       <c r="G16" t="n">
-        <v>-13.4</v>
+        <v>-11.9</v>
       </c>
       <c r="H16" t="n">
-        <v>1.9</v>
+        <v>3.4</v>
       </c>
       <c r="I16" t="inlineStr">
         <is>
@@ -1183,7 +1183,7 @@
         <v>13.8</v>
       </c>
       <c r="L16" t="n">
-        <v>14.11</v>
+        <v>14.35</v>
       </c>
     </row>
     <row r="17">
@@ -1201,10 +1201,10 @@
         <v>5.69</v>
       </c>
       <c r="D17" t="n">
-        <v>5.57</v>
+        <v>5.56</v>
       </c>
       <c r="E17" t="n">
-        <v>-2.09</v>
+        <v>-2.2</v>
       </c>
       <c r="F17" t="n">
         <v>-15.7</v>
@@ -1229,7 +1229,7 @@
         <v>6.33</v>
       </c>
       <c r="L17" t="n">
-        <v>6.23</v>
+        <v>6.22</v>
       </c>
     </row>
     <row r="18">
@@ -1250,13 +1250,13 @@
         <v>0.41</v>
       </c>
       <c r="E18" t="n">
-        <v>-1.03</v>
+        <v>-0.95</v>
       </c>
       <c r="F18" t="n">
         <v>-16.7</v>
       </c>
       <c r="G18" t="n">
-        <v>-17.5</v>
+        <v>-17.4</v>
       </c>
       <c r="H18" t="n">
         <v>-0.7</v>
@@ -1339,19 +1339,19 @@
         <v>16.3</v>
       </c>
       <c r="D20" t="n">
-        <v>13.83</v>
+        <v>15.01</v>
       </c>
       <c r="E20" t="n">
-        <v>-15.2</v>
+        <v>-7.97</v>
       </c>
       <c r="F20" t="n">
         <v>-17.1</v>
       </c>
       <c r="G20" t="n">
-        <v>-28</v>
+        <v>-22.8</v>
       </c>
       <c r="H20" t="n">
-        <v>-10.9</v>
+        <v>-5.7</v>
       </c>
       <c r="I20" t="inlineStr">
         <is>
@@ -1367,7 +1367,7 @@
         <v>15.55</v>
       </c>
       <c r="L20" t="n">
-        <v>13.51</v>
+        <v>14.48</v>
       </c>
     </row>
     <row r="21">
@@ -1465,31 +1465,31 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>INSW</t>
+          <t>FRO</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>WHOLE-COMPANY (hybrid aggregation)</t>
+          <t>whole-company</t>
         </is>
       </c>
       <c r="C23" t="n">
-        <v>57.91</v>
+        <v>28.47</v>
       </c>
       <c r="D23" t="n">
-        <v>52.48</v>
+        <v>25.34</v>
       </c>
       <c r="E23" t="n">
-        <v>-9.380000000000001</v>
+        <v>-11.01</v>
       </c>
       <c r="F23" t="n">
-        <v>-36.4</v>
+        <v>-32.4</v>
       </c>
       <c r="G23" t="n">
-        <v>-41.1</v>
+        <v>-39</v>
       </c>
       <c r="H23" t="n">
-        <v>-4.7</v>
+        <v>-6.7</v>
       </c>
       <c r="I23" t="inlineStr">
         <is>
@@ -1502,16 +1502,16 @@
         </is>
       </c>
       <c r="K23" t="n">
-        <v>58.82</v>
+        <v>26.88</v>
       </c>
       <c r="L23" t="n">
-        <v>54.46</v>
+        <v>24.22</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>FRO</t>
+          <t>ECO</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -1520,22 +1520,22 @@
         </is>
       </c>
       <c r="C24" t="n">
-        <v>28.47</v>
+        <v>43.8</v>
       </c>
       <c r="D24" t="n">
-        <v>24.11</v>
+        <v>39.54</v>
       </c>
       <c r="E24" t="n">
-        <v>-15.33</v>
+        <v>-9.73</v>
       </c>
       <c r="F24" t="n">
-        <v>-32.4</v>
+        <v>-34</v>
       </c>
       <c r="G24" t="n">
-        <v>-41.8</v>
+        <v>-39.7</v>
       </c>
       <c r="H24" t="n">
-        <v>-9.4</v>
+        <v>-5.7</v>
       </c>
       <c r="I24" t="inlineStr">
         <is>
@@ -1548,40 +1548,40 @@
         </is>
       </c>
       <c r="K24" t="n">
-        <v>26.88</v>
+        <v>40.83</v>
       </c>
       <c r="L24" t="n">
-        <v>23.15</v>
+        <v>37.31</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>ECO</t>
+          <t>INSW</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>whole-company</t>
+          <t>WHOLE-COMPANY (hybrid aggregation)</t>
         </is>
       </c>
       <c r="C25" t="n">
-        <v>43.8</v>
+        <v>57.91</v>
       </c>
       <c r="D25" t="n">
-        <v>37.65</v>
+        <v>53.88</v>
       </c>
       <c r="E25" t="n">
-        <v>-14.05</v>
+        <v>-6.95</v>
       </c>
       <c r="F25" t="n">
-        <v>-34</v>
+        <v>-36.4</v>
       </c>
       <c r="G25" t="n">
-        <v>-42.3</v>
+        <v>-39.8</v>
       </c>
       <c r="H25" t="n">
-        <v>-8.300000000000001</v>
+        <v>-3.5</v>
       </c>
       <c r="I25" t="inlineStr">
         <is>
@@ -1594,10 +1594,10 @@
         </is>
       </c>
       <c r="K25" t="n">
-        <v>40.83</v>
+        <v>58.82</v>
       </c>
       <c r="L25" t="n">
-        <v>35.69</v>
+        <v>55.59</v>
       </c>
     </row>
     <row r="26">

--- a/outputs/transaction_anchor_comparison.xlsx
+++ b/outputs/transaction_anchor_comparison.xlsx
@@ -609,13 +609,13 @@
         <v>9.43</v>
       </c>
       <c r="F4" t="n">
-        <v>19.8</v>
+        <v>14.4</v>
       </c>
       <c r="G4" t="n">
-        <v>31.1</v>
+        <v>25.4</v>
       </c>
       <c r="H4" t="n">
-        <v>11.3</v>
+        <v>11</v>
       </c>
       <c r="I4" t="inlineStr">
         <is>
@@ -628,10 +628,10 @@
         </is>
       </c>
       <c r="K4" t="n">
-        <v>9.1</v>
+        <v>8.699999999999999</v>
       </c>
       <c r="L4" t="n">
-        <v>9.970000000000001</v>
+        <v>9.529999999999999</v>
       </c>
     </row>
     <row r="5">
@@ -655,13 +655,13 @@
         <v>3.12</v>
       </c>
       <c r="F5" t="n">
-        <v>12.7</v>
+        <v>10.9</v>
       </c>
       <c r="G5" t="n">
-        <v>15.8</v>
+        <v>13.9</v>
       </c>
       <c r="H5" t="n">
-        <v>3.1</v>
+        <v>3</v>
       </c>
       <c r="I5" t="inlineStr">
         <is>
@@ -674,10 +674,10 @@
         </is>
       </c>
       <c r="K5" t="n">
-        <v>20.06</v>
+        <v>19.74</v>
       </c>
       <c r="L5" t="n">
-        <v>20.61</v>
+        <v>20.27</v>
       </c>
     </row>
     <row r="6">
@@ -747,13 +747,13 @@
         <v>4.78</v>
       </c>
       <c r="F7" t="n">
-        <v>2</v>
+        <v>-0.5</v>
       </c>
       <c r="G7" t="n">
-        <v>6.4</v>
+        <v>3.8</v>
       </c>
       <c r="H7" t="n">
-        <v>4.4</v>
+        <v>4.3</v>
       </c>
       <c r="I7" t="inlineStr">
         <is>
@@ -762,14 +762,14 @@
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>BUY (undervalued)</t>
+          <t>HOLD (fairly valued)</t>
         </is>
       </c>
       <c r="K7" t="n">
-        <v>29.48</v>
+        <v>28.76</v>
       </c>
       <c r="L7" t="n">
-        <v>30.76</v>
+        <v>30</v>
       </c>
     </row>
     <row r="8">
@@ -867,7 +867,7 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>GSL</t>
+          <t>BRUT</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -876,22 +876,22 @@
         </is>
       </c>
       <c r="C10" t="n">
-        <v>41.2</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="D10" t="n">
-        <v>41.2</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="E10" t="n">
         <v>0</v>
       </c>
       <c r="F10" t="n">
-        <v>1.4</v>
+        <v>2.5</v>
       </c>
       <c r="G10" t="n">
-        <v>1.4</v>
+        <v>1.3</v>
       </c>
       <c r="H10" t="n">
-        <v>0</v>
+        <v>-1.2</v>
       </c>
       <c r="I10" t="inlineStr">
         <is>
@@ -904,16 +904,16 @@
         </is>
       </c>
       <c r="K10" t="n">
-        <v>43.02</v>
+        <v>6.57</v>
       </c>
       <c r="L10" t="n">
-        <v>43.02</v>
+        <v>6.49</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>BRUT</t>
+          <t>GSL</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -922,22 +922,22 @@
         </is>
       </c>
       <c r="C11" t="n">
-        <v>8.800000000000001</v>
+        <v>41.2</v>
       </c>
       <c r="D11" t="n">
-        <v>8.800000000000001</v>
+        <v>41.2</v>
       </c>
       <c r="E11" t="n">
         <v>0</v>
       </c>
       <c r="F11" t="n">
-        <v>2.5</v>
+        <v>1</v>
       </c>
       <c r="G11" t="n">
-        <v>1.3</v>
+        <v>1</v>
       </c>
       <c r="H11" t="n">
-        <v>-1.2</v>
+        <v>0</v>
       </c>
       <c r="I11" t="inlineStr">
         <is>
@@ -950,10 +950,10 @@
         </is>
       </c>
       <c r="K11" t="n">
-        <v>6.57</v>
+        <v>42.88</v>
       </c>
       <c r="L11" t="n">
-        <v>6.49</v>
+        <v>42.88</v>
       </c>
     </row>
     <row r="12">
@@ -1115,13 +1115,13 @@
         <v>2.46</v>
       </c>
       <c r="F15" t="n">
-        <v>-9.1</v>
+        <v>-11.6</v>
       </c>
       <c r="G15" t="n">
-        <v>-7.1</v>
+        <v>-9.6</v>
       </c>
       <c r="H15" t="n">
-        <v>2</v>
+        <v>1.9</v>
       </c>
       <c r="I15" t="inlineStr">
         <is>
@@ -1134,10 +1134,10 @@
         </is>
       </c>
       <c r="K15" t="n">
-        <v>23.02</v>
+        <v>22.4</v>
       </c>
       <c r="L15" t="n">
-        <v>23.53</v>
+        <v>22.89</v>
       </c>
     </row>
     <row r="16">
@@ -1161,13 +1161,13 @@
         <v>3.89</v>
       </c>
       <c r="F16" t="n">
-        <v>-15.3</v>
+        <v>-18.1</v>
       </c>
       <c r="G16" t="n">
-        <v>-11.9</v>
+        <v>-14.9</v>
       </c>
       <c r="H16" t="n">
-        <v>3.4</v>
+        <v>3.2</v>
       </c>
       <c r="I16" t="inlineStr">
         <is>
@@ -1180,10 +1180,10 @@
         </is>
       </c>
       <c r="K16" t="n">
-        <v>13.8</v>
+        <v>13.33</v>
       </c>
       <c r="L16" t="n">
-        <v>14.35</v>
+        <v>13.86</v>
       </c>
     </row>
     <row r="17">
@@ -1253,10 +1253,10 @@
         <v>-0.95</v>
       </c>
       <c r="F18" t="n">
-        <v>-16.7</v>
+        <v>-17</v>
       </c>
       <c r="G18" t="n">
-        <v>-17.4</v>
+        <v>-17.7</v>
       </c>
       <c r="H18" t="n">
         <v>-0.7</v>
@@ -1290,19 +1290,19 @@
         </is>
       </c>
       <c r="C19" t="n">
-        <v>2.04</v>
+        <v>2.05</v>
       </c>
       <c r="D19" t="n">
-        <v>2.04</v>
+        <v>2.05</v>
       </c>
       <c r="E19" t="n">
         <v>0</v>
       </c>
       <c r="F19" t="n">
-        <v>-19.4</v>
+        <v>-19.1</v>
       </c>
       <c r="G19" t="n">
-        <v>-19.4</v>
+        <v>-19.1</v>
       </c>
       <c r="H19" t="n">
         <v>0</v>
@@ -1318,10 +1318,10 @@
         </is>
       </c>
       <c r="K19" t="n">
-        <v>2.06</v>
+        <v>2.07</v>
       </c>
       <c r="L19" t="n">
-        <v>2.06</v>
+        <v>2.07</v>
       </c>
     </row>
     <row r="20">

--- a/outputs/transaction_anchor_comparison.xlsx
+++ b/outputs/transaction_anchor_comparison.xlsx
@@ -649,19 +649,19 @@
         <v>31.44</v>
       </c>
       <c r="D5" t="n">
-        <v>32.43</v>
+        <v>32.13</v>
       </c>
       <c r="E5" t="n">
-        <v>3.12</v>
+        <v>2.19</v>
       </c>
       <c r="F5" t="n">
         <v>10.9</v>
       </c>
       <c r="G5" t="n">
-        <v>13.9</v>
+        <v>12.9</v>
       </c>
       <c r="H5" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="I5" t="inlineStr">
         <is>
@@ -677,7 +677,7 @@
         <v>19.74</v>
       </c>
       <c r="L5" t="n">
-        <v>20.27</v>
+        <v>20.11</v>
       </c>
     </row>
     <row r="6">
@@ -729,7 +729,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>SBLK</t>
+          <t>TNK</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -738,44 +738,44 @@
         </is>
       </c>
       <c r="C7" t="n">
-        <v>31.53</v>
+        <v>89.65000000000001</v>
       </c>
       <c r="D7" t="n">
-        <v>33.04</v>
+        <v>84.59999999999999</v>
       </c>
       <c r="E7" t="n">
-        <v>4.78</v>
+        <v>-5.63</v>
       </c>
       <c r="F7" t="n">
-        <v>-0.5</v>
+        <v>8.5</v>
       </c>
       <c r="G7" t="n">
-        <v>3.8</v>
+        <v>3.4</v>
       </c>
       <c r="H7" t="n">
-        <v>4.3</v>
+        <v>-5.1</v>
       </c>
       <c r="I7" t="inlineStr">
         <is>
+          <t>BUY (undervalued)</t>
+        </is>
+      </c>
+      <c r="J7" t="inlineStr">
+        <is>
           <t>HOLD (fairly valued)</t>
         </is>
       </c>
-      <c r="J7" t="inlineStr">
-        <is>
-          <t>HOLD (fairly valued)</t>
-        </is>
-      </c>
       <c r="K7" t="n">
-        <v>28.76</v>
+        <v>83.81</v>
       </c>
       <c r="L7" t="n">
-        <v>30</v>
+        <v>79.87</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>TNK</t>
+          <t>SBLK</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -784,26 +784,26 @@
         </is>
       </c>
       <c r="C8" t="n">
-        <v>89.65000000000001</v>
+        <v>31.53</v>
       </c>
       <c r="D8" t="n">
-        <v>84.59999999999999</v>
+        <v>32.78</v>
       </c>
       <c r="E8" t="n">
-        <v>-5.63</v>
+        <v>3.97</v>
       </c>
       <c r="F8" t="n">
-        <v>8.5</v>
+        <v>-0.5</v>
       </c>
       <c r="G8" t="n">
-        <v>3.4</v>
+        <v>3.1</v>
       </c>
       <c r="H8" t="n">
-        <v>-5.1</v>
+        <v>3.6</v>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>BUY (undervalued)</t>
+          <t>HOLD (fairly valued)</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
@@ -812,10 +812,10 @@
         </is>
       </c>
       <c r="K8" t="n">
-        <v>83.81</v>
+        <v>28.76</v>
       </c>
       <c r="L8" t="n">
-        <v>79.87</v>
+        <v>29.79</v>
       </c>
     </row>
     <row r="9">
@@ -1109,19 +1109,19 @@
         <v>24.77</v>
       </c>
       <c r="D15" t="n">
-        <v>25.38</v>
+        <v>25.12</v>
       </c>
       <c r="E15" t="n">
-        <v>2.46</v>
+        <v>1.42</v>
       </c>
       <c r="F15" t="n">
         <v>-11.6</v>
       </c>
       <c r="G15" t="n">
-        <v>-9.6</v>
+        <v>-10.5</v>
       </c>
       <c r="H15" t="n">
-        <v>1.9</v>
+        <v>1.1</v>
       </c>
       <c r="I15" t="inlineStr">
         <is>
@@ -1137,7 +1137,7 @@
         <v>22.4</v>
       </c>
       <c r="L15" t="n">
-        <v>22.89</v>
+        <v>22.67</v>
       </c>
     </row>
     <row r="16">
@@ -1250,16 +1250,16 @@
         <v>0.41</v>
       </c>
       <c r="E18" t="n">
-        <v>-0.95</v>
+        <v>-1.89</v>
       </c>
       <c r="F18" t="n">
         <v>-17</v>
       </c>
       <c r="G18" t="n">
-        <v>-17.7</v>
+        <v>-18.4</v>
       </c>
       <c r="H18" t="n">
-        <v>-0.7</v>
+        <v>-1.4</v>
       </c>
       <c r="I18" t="inlineStr">
         <is>

--- a/outputs/transaction_anchor_comparison.xlsx
+++ b/outputs/transaction_anchor_comparison.xlsx
@@ -499,7 +499,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>CCEC</t>
+          <t>TEN</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -508,22 +508,22 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>25.7</v>
+        <v>94.58</v>
       </c>
       <c r="D2" t="n">
-        <v>25.7</v>
+        <v>88.16</v>
       </c>
       <c r="E2" t="n">
-        <v>0</v>
+        <v>-6.79</v>
       </c>
       <c r="F2" t="n">
-        <v>50.7</v>
+        <v>70.3</v>
       </c>
       <c r="G2" t="n">
-        <v>50.7</v>
+        <v>59.6</v>
       </c>
       <c r="H2" t="n">
-        <v>0</v>
+        <v>-10.7</v>
       </c>
       <c r="I2" t="inlineStr">
         <is>
@@ -536,16 +536,16 @@
         </is>
       </c>
       <c r="K2" t="n">
-        <v>33.7</v>
+        <v>66.64</v>
       </c>
       <c r="L2" t="n">
-        <v>33.7</v>
+        <v>62.47</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>TEN</t>
+          <t>CCEC</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -554,22 +554,22 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>94.58</v>
+        <v>25.7</v>
       </c>
       <c r="D3" t="n">
-        <v>88.16</v>
+        <v>25.7</v>
       </c>
       <c r="E3" t="n">
-        <v>-6.79</v>
+        <v>0</v>
       </c>
       <c r="F3" t="n">
-        <v>55.7</v>
+        <v>50.7</v>
       </c>
       <c r="G3" t="n">
-        <v>46</v>
+        <v>50.7</v>
       </c>
       <c r="H3" t="n">
-        <v>-9.699999999999999</v>
+        <v>0</v>
       </c>
       <c r="I3" t="inlineStr">
         <is>
@@ -582,16 +582,16 @@
         </is>
       </c>
       <c r="K3" t="n">
-        <v>60.96</v>
+        <v>33.7</v>
       </c>
       <c r="L3" t="n">
-        <v>57.16</v>
+        <v>33.7</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>SB</t>
+          <t>BRUT</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -600,22 +600,22 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>9.67</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="D4" t="n">
-        <v>10.58</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="E4" t="n">
-        <v>9.43</v>
+        <v>0</v>
       </c>
       <c r="F4" t="n">
-        <v>14.4</v>
+        <v>46.9</v>
       </c>
       <c r="G4" t="n">
-        <v>25.4</v>
+        <v>45.6</v>
       </c>
       <c r="H4" t="n">
-        <v>11</v>
+        <v>-1.3</v>
       </c>
       <c r="I4" t="inlineStr">
         <is>
@@ -628,16 +628,16 @@
         </is>
       </c>
       <c r="K4" t="n">
-        <v>8.699999999999999</v>
+        <v>9.41</v>
       </c>
       <c r="L4" t="n">
-        <v>9.529999999999999</v>
+        <v>9.33</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>CMDB</t>
+          <t>SB</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -646,22 +646,22 @@
         </is>
       </c>
       <c r="C5" t="n">
-        <v>31.44</v>
+        <v>9.67</v>
       </c>
       <c r="D5" t="n">
-        <v>32.13</v>
+        <v>10.58</v>
       </c>
       <c r="E5" t="n">
-        <v>2.19</v>
+        <v>9.43</v>
       </c>
       <c r="F5" t="n">
-        <v>10.9</v>
+        <v>14.4</v>
       </c>
       <c r="G5" t="n">
-        <v>12.9</v>
+        <v>25.4</v>
       </c>
       <c r="H5" t="n">
-        <v>2</v>
+        <v>11</v>
       </c>
       <c r="I5" t="inlineStr">
         <is>
@@ -674,16 +674,16 @@
         </is>
       </c>
       <c r="K5" t="n">
-        <v>19.74</v>
+        <v>8.699999999999999</v>
       </c>
       <c r="L5" t="n">
-        <v>20.11</v>
+        <v>9.529999999999999</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>TRMD</t>
+          <t>CAPT</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -692,22 +692,22 @@
         </is>
       </c>
       <c r="C6" t="n">
-        <v>31.65</v>
+        <v>15.61</v>
       </c>
       <c r="D6" t="n">
-        <v>30.22</v>
+        <v>15.48</v>
       </c>
       <c r="E6" t="n">
-        <v>-4.51</v>
+        <v>-0.8100000000000001</v>
       </c>
       <c r="F6" t="n">
-        <v>12</v>
+        <v>15.6</v>
       </c>
       <c r="G6" t="n">
-        <v>7.8</v>
+        <v>13.9</v>
       </c>
       <c r="H6" t="n">
-        <v>-4.2</v>
+        <v>-1.7</v>
       </c>
       <c r="I6" t="inlineStr">
         <is>
@@ -720,16 +720,16 @@
         </is>
       </c>
       <c r="K6" t="n">
-        <v>33.03</v>
+        <v>16.11</v>
       </c>
       <c r="L6" t="n">
-        <v>31.8</v>
+        <v>15.88</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>TNK</t>
+          <t>TRMD</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -738,22 +738,22 @@
         </is>
       </c>
       <c r="C7" t="n">
-        <v>89.65000000000001</v>
+        <v>31.65</v>
       </c>
       <c r="D7" t="n">
-        <v>84.59999999999999</v>
+        <v>30.22</v>
       </c>
       <c r="E7" t="n">
-        <v>-5.63</v>
+        <v>-4.51</v>
       </c>
       <c r="F7" t="n">
-        <v>8.5</v>
+        <v>18.3</v>
       </c>
       <c r="G7" t="n">
-        <v>3.4</v>
+        <v>13.9</v>
       </c>
       <c r="H7" t="n">
-        <v>-5.1</v>
+        <v>-4.5</v>
       </c>
       <c r="I7" t="inlineStr">
         <is>
@@ -762,20 +762,20 @@
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>HOLD (fairly valued)</t>
+          <t>BUY (undervalued)</t>
         </is>
       </c>
       <c r="K7" t="n">
-        <v>83.81</v>
+        <v>34.89</v>
       </c>
       <c r="L7" t="n">
-        <v>79.87</v>
+        <v>33.58</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>SBLK</t>
+          <t>CMDB</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -784,44 +784,44 @@
         </is>
       </c>
       <c r="C8" t="n">
-        <v>31.53</v>
+        <v>31.44</v>
       </c>
       <c r="D8" t="n">
-        <v>32.78</v>
+        <v>32.13</v>
       </c>
       <c r="E8" t="n">
-        <v>3.97</v>
+        <v>2.19</v>
       </c>
       <c r="F8" t="n">
-        <v>-0.5</v>
+        <v>10.9</v>
       </c>
       <c r="G8" t="n">
-        <v>3.1</v>
+        <v>12.9</v>
       </c>
       <c r="H8" t="n">
-        <v>3.6</v>
+        <v>2</v>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>HOLD (fairly valued)</t>
+          <t>BUY (undervalued)</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>HOLD (fairly valued)</t>
+          <t>BUY (undervalued)</t>
         </is>
       </c>
       <c r="K8" t="n">
-        <v>28.76</v>
+        <v>19.74</v>
       </c>
       <c r="L8" t="n">
-        <v>29.79</v>
+        <v>20.11</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>ASC</t>
+          <t>TNK</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -830,44 +830,44 @@
         </is>
       </c>
       <c r="C9" t="n">
-        <v>17.38</v>
+        <v>89.65000000000001</v>
       </c>
       <c r="D9" t="n">
-        <v>17.37</v>
+        <v>84.59999999999999</v>
       </c>
       <c r="E9" t="n">
-        <v>-0.02</v>
+        <v>-5.63</v>
       </c>
       <c r="F9" t="n">
-        <v>2.4</v>
+        <v>14</v>
       </c>
       <c r="G9" t="n">
-        <v>2.4</v>
+        <v>8.4</v>
       </c>
       <c r="H9" t="n">
-        <v>-0</v>
+        <v>-5.6</v>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>HOLD (fairly valued)</t>
+          <t>BUY (undervalued)</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>HOLD (fairly valued)</t>
+          <t>BUY (undervalued)</t>
         </is>
       </c>
       <c r="K9" t="n">
-        <v>17.12</v>
+        <v>88.05</v>
       </c>
       <c r="L9" t="n">
-        <v>17.11</v>
+        <v>83.72</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>BRUT</t>
+          <t>SBLK</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -876,22 +876,22 @@
         </is>
       </c>
       <c r="C10" t="n">
-        <v>8.800000000000001</v>
+        <v>31.53</v>
       </c>
       <c r="D10" t="n">
-        <v>8.800000000000001</v>
+        <v>32.78</v>
       </c>
       <c r="E10" t="n">
-        <v>0</v>
+        <v>3.97</v>
       </c>
       <c r="F10" t="n">
-        <v>2.5</v>
+        <v>-0.5</v>
       </c>
       <c r="G10" t="n">
-        <v>1.3</v>
+        <v>3.1</v>
       </c>
       <c r="H10" t="n">
-        <v>-1.2</v>
+        <v>3.6</v>
       </c>
       <c r="I10" t="inlineStr">
         <is>
@@ -904,10 +904,10 @@
         </is>
       </c>
       <c r="K10" t="n">
-        <v>6.57</v>
+        <v>28.76</v>
       </c>
       <c r="L10" t="n">
-        <v>6.49</v>
+        <v>29.79</v>
       </c>
     </row>
     <row r="11">
@@ -959,7 +959,7 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>FLNG</t>
+          <t>STNG</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -968,22 +968,22 @@
         </is>
       </c>
       <c r="C12" t="n">
-        <v>28.45</v>
+        <v>79.63</v>
       </c>
       <c r="D12" t="n">
-        <v>28.45</v>
+        <v>76.22</v>
       </c>
       <c r="E12" t="n">
-        <v>0</v>
+        <v>-4.28</v>
       </c>
       <c r="F12" t="n">
-        <v>-0.5</v>
+        <v>5</v>
       </c>
       <c r="G12" t="n">
-        <v>-0.5</v>
+        <v>0.9</v>
       </c>
       <c r="H12" t="n">
-        <v>0</v>
+        <v>-4.1</v>
       </c>
       <c r="I12" t="inlineStr">
         <is>
@@ -996,16 +996,16 @@
         </is>
       </c>
       <c r="K12" t="n">
-        <v>30.67</v>
+        <v>79.88</v>
       </c>
       <c r="L12" t="n">
-        <v>30.67</v>
+        <v>76.73</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>STNG</t>
+          <t>FLNG</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -1014,22 +1014,22 @@
         </is>
       </c>
       <c r="C13" t="n">
-        <v>79.63</v>
+        <v>28.45</v>
       </c>
       <c r="D13" t="n">
-        <v>76.22</v>
+        <v>28.45</v>
       </c>
       <c r="E13" t="n">
-        <v>-4.28</v>
+        <v>0</v>
       </c>
       <c r="F13" t="n">
-        <v>0.6</v>
+        <v>-0.5</v>
       </c>
       <c r="G13" t="n">
-        <v>-3.3</v>
+        <v>-0.5</v>
       </c>
       <c r="H13" t="n">
-        <v>-3.9</v>
+        <v>0</v>
       </c>
       <c r="I13" t="inlineStr">
         <is>
@@ -1042,16 +1042,16 @@
         </is>
       </c>
       <c r="K13" t="n">
-        <v>76.52</v>
+        <v>30.67</v>
       </c>
       <c r="L13" t="n">
-        <v>73.56</v>
+        <v>30.67</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>CAPT</t>
+          <t>ASC</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1060,22 +1060,22 @@
         </is>
       </c>
       <c r="C14" t="n">
-        <v>15.61</v>
+        <v>17.38</v>
       </c>
       <c r="D14" t="n">
-        <v>15.48</v>
+        <v>17.37</v>
       </c>
       <c r="E14" t="n">
-        <v>-0.8100000000000001</v>
+        <v>-0.02</v>
       </c>
       <c r="F14" t="n">
-        <v>-2.4</v>
+        <v>-2</v>
       </c>
       <c r="G14" t="n">
-        <v>-3.9</v>
+        <v>-2</v>
       </c>
       <c r="H14" t="n">
-        <v>-1.5</v>
+        <v>-0</v>
       </c>
       <c r="I14" t="inlineStr">
         <is>
@@ -1088,10 +1088,10 @@
         </is>
       </c>
       <c r="K14" t="n">
-        <v>13.6</v>
+        <v>16.38</v>
       </c>
       <c r="L14" t="n">
-        <v>13.39</v>
+        <v>16.38</v>
       </c>
     </row>
     <row r="15">
@@ -1161,13 +1161,13 @@
         <v>3.89</v>
       </c>
       <c r="F16" t="n">
-        <v>-18.1</v>
+        <v>-14.8</v>
       </c>
       <c r="G16" t="n">
-        <v>-14.9</v>
+        <v>-11.7</v>
       </c>
       <c r="H16" t="n">
-        <v>3.2</v>
+        <v>3.1</v>
       </c>
       <c r="I16" t="inlineStr">
         <is>
@@ -1180,10 +1180,10 @@
         </is>
       </c>
       <c r="K16" t="n">
-        <v>13.33</v>
+        <v>13.88</v>
       </c>
       <c r="L16" t="n">
-        <v>13.86</v>
+        <v>14.38</v>
       </c>
     </row>
     <row r="17">
@@ -1207,13 +1207,13 @@
         <v>-2.2</v>
       </c>
       <c r="F17" t="n">
-        <v>-15.7</v>
+        <v>-11.2</v>
       </c>
       <c r="G17" t="n">
-        <v>-17.1</v>
+        <v>-12.7</v>
       </c>
       <c r="H17" t="n">
-        <v>-1.4</v>
+        <v>-1.5</v>
       </c>
       <c r="I17" t="inlineStr">
         <is>
@@ -1226,16 +1226,16 @@
         </is>
       </c>
       <c r="K17" t="n">
-        <v>6.33</v>
+        <v>6.67</v>
       </c>
       <c r="L17" t="n">
-        <v>6.22</v>
+        <v>6.56</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>2343</t>
+          <t>DHT</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1244,22 +1244,22 @@
         </is>
       </c>
       <c r="C18" t="n">
-        <v>0.41</v>
+        <v>16.3</v>
       </c>
       <c r="D18" t="n">
-        <v>0.41</v>
+        <v>15.01</v>
       </c>
       <c r="E18" t="n">
-        <v>-1.89</v>
+        <v>-7.97</v>
       </c>
       <c r="F18" t="n">
-        <v>-17</v>
+        <v>-9.1</v>
       </c>
       <c r="G18" t="n">
-        <v>-18.4</v>
+        <v>-15.4</v>
       </c>
       <c r="H18" t="n">
-        <v>-1.4</v>
+        <v>-6.3</v>
       </c>
       <c r="I18" t="inlineStr">
         <is>
@@ -1272,16 +1272,16 @@
         </is>
       </c>
       <c r="K18" t="n">
-        <v>0.4</v>
+        <v>17.06</v>
       </c>
       <c r="L18" t="n">
-        <v>0.4</v>
+        <v>15.88</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>MPCC</t>
+          <t>2343</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1290,22 +1290,22 @@
         </is>
       </c>
       <c r="C19" t="n">
-        <v>2.05</v>
+        <v>0.41</v>
       </c>
       <c r="D19" t="n">
-        <v>2.05</v>
+        <v>0.41</v>
       </c>
       <c r="E19" t="n">
-        <v>0</v>
+        <v>-1.89</v>
       </c>
       <c r="F19" t="n">
-        <v>-19.1</v>
+        <v>-17</v>
       </c>
       <c r="G19" t="n">
-        <v>-19.1</v>
+        <v>-18.4</v>
       </c>
       <c r="H19" t="n">
-        <v>0</v>
+        <v>-1.4</v>
       </c>
       <c r="I19" t="inlineStr">
         <is>
@@ -1318,16 +1318,16 @@
         </is>
       </c>
       <c r="K19" t="n">
-        <v>2.07</v>
+        <v>0.4</v>
       </c>
       <c r="L19" t="n">
-        <v>2.07</v>
+        <v>0.4</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>DHT</t>
+          <t>MPCC</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -1336,22 +1336,22 @@
         </is>
       </c>
       <c r="C20" t="n">
-        <v>16.3</v>
+        <v>2.05</v>
       </c>
       <c r="D20" t="n">
-        <v>15.01</v>
+        <v>2.05</v>
       </c>
       <c r="E20" t="n">
-        <v>-7.97</v>
+        <v>0</v>
       </c>
       <c r="F20" t="n">
-        <v>-17.1</v>
+        <v>-19.1</v>
       </c>
       <c r="G20" t="n">
-        <v>-22.8</v>
+        <v>-19.1</v>
       </c>
       <c r="H20" t="n">
-        <v>-5.7</v>
+        <v>0</v>
       </c>
       <c r="I20" t="inlineStr">
         <is>
@@ -1364,10 +1364,10 @@
         </is>
       </c>
       <c r="K20" t="n">
-        <v>15.55</v>
+        <v>2.07</v>
       </c>
       <c r="L20" t="n">
-        <v>14.48</v>
+        <v>2.07</v>
       </c>
     </row>
     <row r="21">
@@ -1419,7 +1419,7 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>BWLP</t>
+          <t>FRO</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -1428,22 +1428,22 @@
         </is>
       </c>
       <c r="C22" t="n">
-        <v>15.81</v>
+        <v>28.47</v>
       </c>
       <c r="D22" t="n">
-        <v>15.8</v>
+        <v>25.34</v>
       </c>
       <c r="E22" t="n">
-        <v>-0.07000000000000001</v>
+        <v>-11.01</v>
       </c>
       <c r="F22" t="n">
-        <v>-33</v>
+        <v>-23.2</v>
       </c>
       <c r="G22" t="n">
-        <v>-33</v>
+        <v>-30.6</v>
       </c>
       <c r="H22" t="n">
-        <v>-0</v>
+        <v>-7.4</v>
       </c>
       <c r="I22" t="inlineStr">
         <is>
@@ -1456,16 +1456,16 @@
         </is>
       </c>
       <c r="K22" t="n">
-        <v>14.47</v>
+        <v>30.53</v>
       </c>
       <c r="L22" t="n">
-        <v>14.46</v>
+        <v>27.57</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>FRO</t>
+          <t>ECO</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -1474,22 +1474,22 @@
         </is>
       </c>
       <c r="C23" t="n">
-        <v>28.47</v>
+        <v>43.8</v>
       </c>
       <c r="D23" t="n">
-        <v>25.34</v>
+        <v>39.54</v>
       </c>
       <c r="E23" t="n">
-        <v>-11.01</v>
+        <v>-9.73</v>
       </c>
       <c r="F23" t="n">
-        <v>-32.4</v>
+        <v>-26.7</v>
       </c>
       <c r="G23" t="n">
-        <v>-39</v>
+        <v>-33</v>
       </c>
       <c r="H23" t="n">
-        <v>-6.7</v>
+        <v>-6.3</v>
       </c>
       <c r="I23" t="inlineStr">
         <is>
@@ -1502,16 +1502,16 @@
         </is>
       </c>
       <c r="K23" t="n">
-        <v>26.88</v>
+        <v>45.33</v>
       </c>
       <c r="L23" t="n">
-        <v>24.22</v>
+        <v>41.44</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>ECO</t>
+          <t>BWLP</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -1520,22 +1520,22 @@
         </is>
       </c>
       <c r="C24" t="n">
-        <v>43.8</v>
+        <v>15.81</v>
       </c>
       <c r="D24" t="n">
-        <v>39.54</v>
+        <v>15.8</v>
       </c>
       <c r="E24" t="n">
-        <v>-9.73</v>
+        <v>-0.07000000000000001</v>
       </c>
       <c r="F24" t="n">
-        <v>-34</v>
+        <v>-33</v>
       </c>
       <c r="G24" t="n">
-        <v>-39.7</v>
+        <v>-33</v>
       </c>
       <c r="H24" t="n">
-        <v>-5.7</v>
+        <v>-0</v>
       </c>
       <c r="I24" t="inlineStr">
         <is>
@@ -1548,10 +1548,10 @@
         </is>
       </c>
       <c r="K24" t="n">
-        <v>40.83</v>
+        <v>14.47</v>
       </c>
       <c r="L24" t="n">
-        <v>37.31</v>
+        <v>14.46</v>
       </c>
     </row>
     <row r="25">
@@ -1566,22 +1566,22 @@
         </is>
       </c>
       <c r="C25" t="n">
-        <v>57.91</v>
+        <v>58.55</v>
       </c>
       <c r="D25" t="n">
-        <v>53.88</v>
+        <v>54.64</v>
       </c>
       <c r="E25" t="n">
-        <v>-6.95</v>
+        <v>-6.68</v>
       </c>
       <c r="F25" t="n">
-        <v>-36.4</v>
+        <v>-32</v>
       </c>
       <c r="G25" t="n">
-        <v>-39.8</v>
+        <v>-35.7</v>
       </c>
       <c r="H25" t="n">
-        <v>-3.5</v>
+        <v>-3.7</v>
       </c>
       <c r="I25" t="inlineStr">
         <is>
@@ -1594,10 +1594,10 @@
         </is>
       </c>
       <c r="K25" t="n">
-        <v>58.82</v>
+        <v>62.82</v>
       </c>
       <c r="L25" t="n">
-        <v>55.59</v>
+        <v>59.39</v>
       </c>
     </row>
     <row r="26">
@@ -1621,13 +1621,13 @@
         <v>-14.2</v>
       </c>
       <c r="F26" t="n">
-        <v>-51</v>
+        <v>-46.5</v>
       </c>
       <c r="G26" t="n">
-        <v>-56.8</v>
+        <v>-52.8</v>
       </c>
       <c r="H26" t="n">
-        <v>-5.8</v>
+        <v>-6.3</v>
       </c>
       <c r="I26" t="inlineStr">
         <is>
@@ -1640,10 +1640,10 @@
         </is>
       </c>
       <c r="K26" t="n">
-        <v>3.16</v>
+        <v>3.46</v>
       </c>
       <c r="L26" t="n">
-        <v>2.79</v>
+        <v>3.05</v>
       </c>
     </row>
   </sheetData>

--- a/outputs/transaction_anchor_comparison.xlsx
+++ b/outputs/transaction_anchor_comparison.xlsx
@@ -499,7 +499,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>TEN</t>
+          <t>BRUT</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -508,22 +508,22 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>94.58</v>
+        <v>9.619999999999999</v>
       </c>
       <c r="D2" t="n">
-        <v>88.16</v>
+        <v>9.619999999999999</v>
       </c>
       <c r="E2" t="n">
-        <v>-6.79</v>
+        <v>0</v>
       </c>
       <c r="F2" t="n">
-        <v>70.3</v>
+        <v>63.2</v>
       </c>
       <c r="G2" t="n">
-        <v>59.6</v>
+        <v>61.8</v>
       </c>
       <c r="H2" t="n">
-        <v>-10.7</v>
+        <v>-1.4</v>
       </c>
       <c r="I2" t="inlineStr">
         <is>
@@ -536,16 +536,16 @@
         </is>
       </c>
       <c r="K2" t="n">
-        <v>66.64</v>
+        <v>10.21</v>
       </c>
       <c r="L2" t="n">
-        <v>62.47</v>
+        <v>10.13</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>CCEC</t>
+          <t>TEN</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -554,22 +554,22 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>25.7</v>
+        <v>94.58</v>
       </c>
       <c r="D3" t="n">
-        <v>25.7</v>
+        <v>88.16</v>
       </c>
       <c r="E3" t="n">
-        <v>0</v>
+        <v>-6.79</v>
       </c>
       <c r="F3" t="n">
-        <v>50.7</v>
+        <v>69.5</v>
       </c>
       <c r="G3" t="n">
-        <v>50.7</v>
+        <v>58.9</v>
       </c>
       <c r="H3" t="n">
-        <v>0</v>
+        <v>-10.6</v>
       </c>
       <c r="I3" t="inlineStr">
         <is>
@@ -582,16 +582,16 @@
         </is>
       </c>
       <c r="K3" t="n">
-        <v>33.7</v>
+        <v>66.64</v>
       </c>
       <c r="L3" t="n">
-        <v>33.7</v>
+        <v>62.47</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>BRUT</t>
+          <t>CCEC</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -600,22 +600,22 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>8.800000000000001</v>
+        <v>25.7</v>
       </c>
       <c r="D4" t="n">
-        <v>8.800000000000001</v>
+        <v>25.7</v>
       </c>
       <c r="E4" t="n">
         <v>0</v>
       </c>
       <c r="F4" t="n">
-        <v>46.9</v>
+        <v>49.2</v>
       </c>
       <c r="G4" t="n">
-        <v>45.6</v>
+        <v>49.2</v>
       </c>
       <c r="H4" t="n">
-        <v>-1.3</v>
+        <v>0</v>
       </c>
       <c r="I4" t="inlineStr">
         <is>
@@ -628,10 +628,10 @@
         </is>
       </c>
       <c r="K4" t="n">
-        <v>9.41</v>
+        <v>33.7</v>
       </c>
       <c r="L4" t="n">
-        <v>9.33</v>
+        <v>33.7</v>
       </c>
     </row>
     <row r="5">
@@ -655,13 +655,13 @@
         <v>9.43</v>
       </c>
       <c r="F5" t="n">
-        <v>14.4</v>
+        <v>16.6</v>
       </c>
       <c r="G5" t="n">
-        <v>25.4</v>
+        <v>27.8</v>
       </c>
       <c r="H5" t="n">
-        <v>11</v>
+        <v>11.2</v>
       </c>
       <c r="I5" t="inlineStr">
         <is>
@@ -683,7 +683,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>CAPT</t>
+          <t>TRMD</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -692,22 +692,22 @@
         </is>
       </c>
       <c r="C6" t="n">
-        <v>15.61</v>
+        <v>31.65</v>
       </c>
       <c r="D6" t="n">
-        <v>15.48</v>
+        <v>30.22</v>
       </c>
       <c r="E6" t="n">
-        <v>-0.8100000000000001</v>
+        <v>-4.51</v>
       </c>
       <c r="F6" t="n">
-        <v>15.6</v>
+        <v>20.4</v>
       </c>
       <c r="G6" t="n">
-        <v>13.9</v>
+        <v>15.9</v>
       </c>
       <c r="H6" t="n">
-        <v>-1.7</v>
+        <v>-4.5</v>
       </c>
       <c r="I6" t="inlineStr">
         <is>
@@ -720,16 +720,16 @@
         </is>
       </c>
       <c r="K6" t="n">
-        <v>16.11</v>
+        <v>34.89</v>
       </c>
       <c r="L6" t="n">
-        <v>15.88</v>
+        <v>33.58</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>TRMD</t>
+          <t>CMDB</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -738,22 +738,22 @@
         </is>
       </c>
       <c r="C7" t="n">
-        <v>31.65</v>
+        <v>31.44</v>
       </c>
       <c r="D7" t="n">
-        <v>30.22</v>
+        <v>32.13</v>
       </c>
       <c r="E7" t="n">
-        <v>-4.51</v>
+        <v>2.19</v>
       </c>
       <c r="F7" t="n">
-        <v>18.3</v>
+        <v>11.7</v>
       </c>
       <c r="G7" t="n">
-        <v>13.9</v>
+        <v>13.7</v>
       </c>
       <c r="H7" t="n">
-        <v>-4.5</v>
+        <v>2.1</v>
       </c>
       <c r="I7" t="inlineStr">
         <is>
@@ -766,16 +766,16 @@
         </is>
       </c>
       <c r="K7" t="n">
-        <v>34.89</v>
+        <v>19.74</v>
       </c>
       <c r="L7" t="n">
-        <v>33.58</v>
+        <v>20.11</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>CMDB</t>
+          <t>CAPT</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -784,22 +784,22 @@
         </is>
       </c>
       <c r="C8" t="n">
-        <v>31.44</v>
+        <v>15.61</v>
       </c>
       <c r="D8" t="n">
-        <v>32.13</v>
+        <v>15.48</v>
       </c>
       <c r="E8" t="n">
-        <v>2.19</v>
+        <v>-0.8100000000000001</v>
       </c>
       <c r="F8" t="n">
-        <v>10.9</v>
+        <v>12.6</v>
       </c>
       <c r="G8" t="n">
-        <v>12.9</v>
+        <v>11</v>
       </c>
       <c r="H8" t="n">
-        <v>2</v>
+        <v>-1.6</v>
       </c>
       <c r="I8" t="inlineStr">
         <is>
@@ -812,16 +812,16 @@
         </is>
       </c>
       <c r="K8" t="n">
-        <v>19.74</v>
+        <v>16.11</v>
       </c>
       <c r="L8" t="n">
-        <v>20.11</v>
+        <v>15.88</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>TNK</t>
+          <t>SBLK</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -830,44 +830,44 @@
         </is>
       </c>
       <c r="C9" t="n">
-        <v>89.65000000000001</v>
+        <v>31.53</v>
       </c>
       <c r="D9" t="n">
-        <v>84.59999999999999</v>
+        <v>32.78</v>
       </c>
       <c r="E9" t="n">
-        <v>-5.63</v>
+        <v>3.97</v>
       </c>
       <c r="F9" t="n">
-        <v>14</v>
+        <v>3.1</v>
       </c>
       <c r="G9" t="n">
-        <v>8.4</v>
+        <v>6.8</v>
       </c>
       <c r="H9" t="n">
-        <v>-5.6</v>
+        <v>3.7</v>
       </c>
       <c r="I9" t="inlineStr">
         <is>
+          <t>HOLD (fairly valued)</t>
+        </is>
+      </c>
+      <c r="J9" t="inlineStr">
+        <is>
           <t>BUY (undervalued)</t>
         </is>
       </c>
-      <c r="J9" t="inlineStr">
-        <is>
-          <t>BUY (undervalued)</t>
-        </is>
-      </c>
       <c r="K9" t="n">
-        <v>88.05</v>
+        <v>28.76</v>
       </c>
       <c r="L9" t="n">
-        <v>83.72</v>
+        <v>29.79</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>SBLK</t>
+          <t>FLNG</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -876,22 +876,22 @@
         </is>
       </c>
       <c r="C10" t="n">
-        <v>31.53</v>
+        <v>28.45</v>
       </c>
       <c r="D10" t="n">
-        <v>32.78</v>
+        <v>28.45</v>
       </c>
       <c r="E10" t="n">
-        <v>3.97</v>
+        <v>0</v>
       </c>
       <c r="F10" t="n">
-        <v>-0.5</v>
+        <v>4</v>
       </c>
       <c r="G10" t="n">
-        <v>3.1</v>
+        <v>4</v>
       </c>
       <c r="H10" t="n">
-        <v>3.6</v>
+        <v>0</v>
       </c>
       <c r="I10" t="inlineStr">
         <is>
@@ -904,10 +904,10 @@
         </is>
       </c>
       <c r="K10" t="n">
-        <v>28.76</v>
+        <v>30.67</v>
       </c>
       <c r="L10" t="n">
-        <v>29.79</v>
+        <v>30.67</v>
       </c>
     </row>
     <row r="11">
@@ -931,10 +931,10 @@
         <v>0</v>
       </c>
       <c r="F11" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="G11" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="H11" t="n">
         <v>0</v>
@@ -959,7 +959,7 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>STNG</t>
+          <t>TNK</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -968,44 +968,44 @@
         </is>
       </c>
       <c r="C12" t="n">
-        <v>79.63</v>
+        <v>89.65000000000001</v>
       </c>
       <c r="D12" t="n">
-        <v>76.22</v>
+        <v>84.59999999999999</v>
       </c>
       <c r="E12" t="n">
-        <v>-4.28</v>
+        <v>-5.63</v>
       </c>
       <c r="F12" t="n">
-        <v>5</v>
+        <v>8.9</v>
       </c>
       <c r="G12" t="n">
-        <v>0.9</v>
+        <v>3.5</v>
       </c>
       <c r="H12" t="n">
-        <v>-4.1</v>
+        <v>-5.3</v>
       </c>
       <c r="I12" t="inlineStr">
         <is>
+          <t>BUY (undervalued)</t>
+        </is>
+      </c>
+      <c r="J12" t="inlineStr">
+        <is>
           <t>HOLD (fairly valued)</t>
         </is>
       </c>
-      <c r="J12" t="inlineStr">
-        <is>
-          <t>HOLD (fairly valued)</t>
-        </is>
-      </c>
       <c r="K12" t="n">
-        <v>79.88</v>
+        <v>88.05</v>
       </c>
       <c r="L12" t="n">
-        <v>76.73</v>
+        <v>83.72</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>FLNG</t>
+          <t>2343</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -1014,22 +1014,22 @@
         </is>
       </c>
       <c r="C13" t="n">
-        <v>28.45</v>
+        <v>0.41</v>
       </c>
       <c r="D13" t="n">
-        <v>28.45</v>
+        <v>0.41</v>
       </c>
       <c r="E13" t="n">
-        <v>0</v>
+        <v>-1.89</v>
       </c>
       <c r="F13" t="n">
-        <v>-0.5</v>
+        <v>3.1</v>
       </c>
       <c r="G13" t="n">
-        <v>-0.5</v>
+        <v>1.4</v>
       </c>
       <c r="H13" t="n">
-        <v>0</v>
+        <v>-1.7</v>
       </c>
       <c r="I13" t="inlineStr">
         <is>
@@ -1042,16 +1042,16 @@
         </is>
       </c>
       <c r="K13" t="n">
-        <v>30.67</v>
+        <v>0.4</v>
       </c>
       <c r="L13" t="n">
-        <v>30.67</v>
+        <v>0.4</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>ASC</t>
+          <t>STNG</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1060,22 +1060,22 @@
         </is>
       </c>
       <c r="C14" t="n">
-        <v>17.38</v>
+        <v>79.63</v>
       </c>
       <c r="D14" t="n">
-        <v>17.37</v>
+        <v>76.22</v>
       </c>
       <c r="E14" t="n">
-        <v>-0.02</v>
+        <v>-4.28</v>
       </c>
       <c r="F14" t="n">
-        <v>-2</v>
+        <v>4.9</v>
       </c>
       <c r="G14" t="n">
-        <v>-2</v>
+        <v>0.8</v>
       </c>
       <c r="H14" t="n">
-        <v>-0</v>
+        <v>-4.1</v>
       </c>
       <c r="I14" t="inlineStr">
         <is>
@@ -1088,16 +1088,16 @@
         </is>
       </c>
       <c r="K14" t="n">
-        <v>16.38</v>
+        <v>79.88</v>
       </c>
       <c r="L14" t="n">
-        <v>16.38</v>
+        <v>76.73</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>GNK</t>
+          <t>ASC</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1106,68 +1106,68 @@
         </is>
       </c>
       <c r="C15" t="n">
-        <v>24.77</v>
+        <v>17.38</v>
       </c>
       <c r="D15" t="n">
-        <v>25.12</v>
+        <v>17.37</v>
       </c>
       <c r="E15" t="n">
-        <v>1.42</v>
+        <v>-0.02</v>
       </c>
       <c r="F15" t="n">
-        <v>-11.6</v>
+        <v>-1.7</v>
       </c>
       <c r="G15" t="n">
-        <v>-10.5</v>
+        <v>-1.8</v>
       </c>
       <c r="H15" t="n">
-        <v>1.1</v>
+        <v>-0</v>
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>TRIM/SHORT (overvalued)</t>
+          <t>HOLD (fairly valued)</t>
         </is>
       </c>
       <c r="J15" t="inlineStr">
         <is>
-          <t>TRIM/SHORT (overvalued)</t>
+          <t>HOLD (fairly valued)</t>
         </is>
       </c>
       <c r="K15" t="n">
-        <v>22.4</v>
+        <v>16.38</v>
       </c>
       <c r="L15" t="n">
-        <v>22.67</v>
+        <v>16.38</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>CMBT</t>
+          <t>GNK</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>WHOLE-COMPANY (hybrid aggregation)</t>
+          <t>whole-company</t>
         </is>
       </c>
       <c r="C16" t="n">
-        <v>15.84</v>
+        <v>24.77</v>
       </c>
       <c r="D16" t="n">
-        <v>16.46</v>
+        <v>25.12</v>
       </c>
       <c r="E16" t="n">
-        <v>3.89</v>
+        <v>1.42</v>
       </c>
       <c r="F16" t="n">
-        <v>-14.8</v>
+        <v>-11.3</v>
       </c>
       <c r="G16" t="n">
-        <v>-11.7</v>
+        <v>-10.2</v>
       </c>
       <c r="H16" t="n">
-        <v>3.1</v>
+        <v>1.1</v>
       </c>
       <c r="I16" t="inlineStr">
         <is>
@@ -1180,10 +1180,10 @@
         </is>
       </c>
       <c r="K16" t="n">
-        <v>13.88</v>
+        <v>22.4</v>
       </c>
       <c r="L16" t="n">
-        <v>14.38</v>
+        <v>22.67</v>
       </c>
     </row>
     <row r="17">
@@ -1207,10 +1207,10 @@
         <v>-2.2</v>
       </c>
       <c r="F17" t="n">
-        <v>-11.2</v>
+        <v>-10.9</v>
       </c>
       <c r="G17" t="n">
-        <v>-12.7</v>
+        <v>-12.5</v>
       </c>
       <c r="H17" t="n">
         <v>-1.5</v>
@@ -1235,31 +1235,31 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>DHT</t>
+          <t>CMBT</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>whole-company</t>
+          <t>WHOLE-COMPANY (hybrid aggregation)</t>
         </is>
       </c>
       <c r="C18" t="n">
-        <v>16.3</v>
+        <v>15.84</v>
       </c>
       <c r="D18" t="n">
-        <v>15.01</v>
+        <v>16.46</v>
       </c>
       <c r="E18" t="n">
-        <v>-7.97</v>
+        <v>3.89</v>
       </c>
       <c r="F18" t="n">
-        <v>-9.1</v>
+        <v>-17.2</v>
       </c>
       <c r="G18" t="n">
-        <v>-15.4</v>
+        <v>-14.2</v>
       </c>
       <c r="H18" t="n">
-        <v>-6.3</v>
+        <v>3</v>
       </c>
       <c r="I18" t="inlineStr">
         <is>
@@ -1272,16 +1272,16 @@
         </is>
       </c>
       <c r="K18" t="n">
-        <v>17.06</v>
+        <v>13.88</v>
       </c>
       <c r="L18" t="n">
-        <v>15.88</v>
+        <v>14.38</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>2343</t>
+          <t>DHT</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1290,22 +1290,22 @@
         </is>
       </c>
       <c r="C19" t="n">
-        <v>0.41</v>
+        <v>16.3</v>
       </c>
       <c r="D19" t="n">
-        <v>0.41</v>
+        <v>15.01</v>
       </c>
       <c r="E19" t="n">
-        <v>-1.89</v>
+        <v>-7.97</v>
       </c>
       <c r="F19" t="n">
-        <v>-17</v>
+        <v>-8.9</v>
       </c>
       <c r="G19" t="n">
-        <v>-18.4</v>
+        <v>-15.2</v>
       </c>
       <c r="H19" t="n">
-        <v>-1.4</v>
+        <v>-6.3</v>
       </c>
       <c r="I19" t="inlineStr">
         <is>
@@ -1318,10 +1318,10 @@
         </is>
       </c>
       <c r="K19" t="n">
-        <v>0.4</v>
+        <v>17.06</v>
       </c>
       <c r="L19" t="n">
-        <v>0.4</v>
+        <v>15.88</v>
       </c>
     </row>
     <row r="20">
@@ -1345,10 +1345,10 @@
         <v>0</v>
       </c>
       <c r="F20" t="n">
-        <v>-19.1</v>
+        <v>-18.8</v>
       </c>
       <c r="G20" t="n">
-        <v>-19.1</v>
+        <v>-18.8</v>
       </c>
       <c r="H20" t="n">
         <v>0</v>
@@ -1391,10 +1391,10 @@
         <v>-0.04</v>
       </c>
       <c r="F21" t="n">
-        <v>-30.4</v>
+        <v>-28.8</v>
       </c>
       <c r="G21" t="n">
-        <v>-30.5</v>
+        <v>-28.9</v>
       </c>
       <c r="H21" t="n">
         <v>-0</v>
@@ -1437,13 +1437,13 @@
         <v>-11.01</v>
       </c>
       <c r="F22" t="n">
-        <v>-23.2</v>
+        <v>-22.9</v>
       </c>
       <c r="G22" t="n">
-        <v>-30.6</v>
+        <v>-30.3</v>
       </c>
       <c r="H22" t="n">
-        <v>-7.4</v>
+        <v>-7.5</v>
       </c>
       <c r="I22" t="inlineStr">
         <is>
@@ -1483,13 +1483,13 @@
         <v>-9.73</v>
       </c>
       <c r="F23" t="n">
-        <v>-26.7</v>
+        <v>-27.9</v>
       </c>
       <c r="G23" t="n">
-        <v>-33</v>
+        <v>-34.1</v>
       </c>
       <c r="H23" t="n">
-        <v>-6.3</v>
+        <v>-6.2</v>
       </c>
       <c r="I23" t="inlineStr">
         <is>
@@ -1529,10 +1529,10 @@
         <v>-0.07000000000000001</v>
       </c>
       <c r="F24" t="n">
-        <v>-33</v>
+        <v>-34.5</v>
       </c>
       <c r="G24" t="n">
-        <v>-33</v>
+        <v>-34.5</v>
       </c>
       <c r="H24" t="n">
         <v>-0</v>
@@ -1621,10 +1621,10 @@
         <v>-14.2</v>
       </c>
       <c r="F26" t="n">
-        <v>-46.5</v>
+        <v>-46.3</v>
       </c>
       <c r="G26" t="n">
-        <v>-52.8</v>
+        <v>-52.6</v>
       </c>
       <c r="H26" t="n">
         <v>-6.3</v>

--- a/outputs/transaction_anchor_comparison.xlsx
+++ b/outputs/transaction_anchor_comparison.xlsx
@@ -517,13 +517,13 @@
         <v>0</v>
       </c>
       <c r="F2" t="n">
-        <v>63.2</v>
+        <v>53.8</v>
       </c>
       <c r="G2" t="n">
-        <v>61.8</v>
+        <v>52.5</v>
       </c>
       <c r="H2" t="n">
-        <v>-1.4</v>
+        <v>-1.3</v>
       </c>
       <c r="I2" t="inlineStr">
         <is>
@@ -536,10 +536,10 @@
         </is>
       </c>
       <c r="K2" t="n">
-        <v>10.21</v>
+        <v>10.37</v>
       </c>
       <c r="L2" t="n">
-        <v>10.13</v>
+        <v>10.28</v>
       </c>
     </row>
     <row r="3">
@@ -563,13 +563,13 @@
         <v>-6.79</v>
       </c>
       <c r="F3" t="n">
-        <v>69.5</v>
+        <v>61.3</v>
       </c>
       <c r="G3" t="n">
-        <v>58.9</v>
+        <v>51.2</v>
       </c>
       <c r="H3" t="n">
-        <v>-10.6</v>
+        <v>-10.1</v>
       </c>
       <c r="I3" t="inlineStr">
         <is>
@@ -582,10 +582,10 @@
         </is>
       </c>
       <c r="K3" t="n">
-        <v>66.64</v>
+        <v>66.84</v>
       </c>
       <c r="L3" t="n">
-        <v>62.47</v>
+        <v>62.66</v>
       </c>
     </row>
     <row r="4">
@@ -609,10 +609,10 @@
         <v>0</v>
       </c>
       <c r="F4" t="n">
-        <v>49.2</v>
+        <v>49.1</v>
       </c>
       <c r="G4" t="n">
-        <v>49.2</v>
+        <v>49.1</v>
       </c>
       <c r="H4" t="n">
         <v>0</v>
@@ -655,13 +655,13 @@
         <v>9.43</v>
       </c>
       <c r="F5" t="n">
-        <v>16.6</v>
+        <v>12.2</v>
       </c>
       <c r="G5" t="n">
-        <v>27.8</v>
+        <v>23</v>
       </c>
       <c r="H5" t="n">
-        <v>11.2</v>
+        <v>10.8</v>
       </c>
       <c r="I5" t="inlineStr">
         <is>
@@ -701,13 +701,13 @@
         <v>-4.51</v>
       </c>
       <c r="F6" t="n">
-        <v>20.4</v>
+        <v>16</v>
       </c>
       <c r="G6" t="n">
-        <v>15.9</v>
+        <v>11.6</v>
       </c>
       <c r="H6" t="n">
-        <v>-4.5</v>
+        <v>-4.4</v>
       </c>
       <c r="I6" t="inlineStr">
         <is>
@@ -747,13 +747,13 @@
         <v>2.19</v>
       </c>
       <c r="F7" t="n">
-        <v>11.7</v>
+        <v>8.300000000000001</v>
       </c>
       <c r="G7" t="n">
-        <v>13.7</v>
+        <v>10.3</v>
       </c>
       <c r="H7" t="n">
-        <v>2.1</v>
+        <v>2</v>
       </c>
       <c r="I7" t="inlineStr">
         <is>
@@ -793,10 +793,10 @@
         <v>-0.8100000000000001</v>
       </c>
       <c r="F8" t="n">
-        <v>12.6</v>
+        <v>10.7</v>
       </c>
       <c r="G8" t="n">
-        <v>11</v>
+        <v>9.1</v>
       </c>
       <c r="H8" t="n">
         <v>-1.6</v>
@@ -812,10 +812,10 @@
         </is>
       </c>
       <c r="K8" t="n">
-        <v>16.11</v>
+        <v>16.26</v>
       </c>
       <c r="L8" t="n">
-        <v>15.88</v>
+        <v>16.02</v>
       </c>
     </row>
     <row r="9">
@@ -839,13 +839,13 @@
         <v>3.97</v>
       </c>
       <c r="F9" t="n">
-        <v>3.1</v>
+        <v>-1</v>
       </c>
       <c r="G9" t="n">
-        <v>6.8</v>
+        <v>2.5</v>
       </c>
       <c r="H9" t="n">
-        <v>3.7</v>
+        <v>3.5</v>
       </c>
       <c r="I9" t="inlineStr">
         <is>
@@ -854,7 +854,7 @@
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>BUY (undervalued)</t>
+          <t>HOLD (fairly valued)</t>
         </is>
       </c>
       <c r="K9" t="n">
@@ -867,7 +867,7 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>FLNG</t>
+          <t>GSL</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -876,19 +876,19 @@
         </is>
       </c>
       <c r="C10" t="n">
-        <v>28.45</v>
+        <v>41.2</v>
       </c>
       <c r="D10" t="n">
-        <v>28.45</v>
+        <v>41.2</v>
       </c>
       <c r="E10" t="n">
         <v>0</v>
       </c>
       <c r="F10" t="n">
-        <v>4</v>
+        <v>1.7</v>
       </c>
       <c r="G10" t="n">
-        <v>4</v>
+        <v>1.7</v>
       </c>
       <c r="H10" t="n">
         <v>0</v>
@@ -904,16 +904,16 @@
         </is>
       </c>
       <c r="K10" t="n">
-        <v>30.67</v>
+        <v>42.88</v>
       </c>
       <c r="L10" t="n">
-        <v>30.67</v>
+        <v>42.88</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>GSL</t>
+          <t>FLNG</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -922,19 +922,19 @@
         </is>
       </c>
       <c r="C11" t="n">
-        <v>41.2</v>
+        <v>28.45</v>
       </c>
       <c r="D11" t="n">
-        <v>41.2</v>
+        <v>28.45</v>
       </c>
       <c r="E11" t="n">
         <v>0</v>
       </c>
       <c r="F11" t="n">
-        <v>4</v>
+        <v>-0.4</v>
       </c>
       <c r="G11" t="n">
-        <v>4</v>
+        <v>-0.4</v>
       </c>
       <c r="H11" t="n">
         <v>0</v>
@@ -950,10 +950,10 @@
         </is>
       </c>
       <c r="K11" t="n">
-        <v>42.88</v>
+        <v>30.67</v>
       </c>
       <c r="L11" t="n">
-        <v>42.88</v>
+        <v>30.67</v>
       </c>
     </row>
     <row r="12">
@@ -977,17 +977,17 @@
         <v>-5.63</v>
       </c>
       <c r="F12" t="n">
-        <v>8.9</v>
+        <v>3.7</v>
       </c>
       <c r="G12" t="n">
-        <v>3.5</v>
+        <v>-1.4</v>
       </c>
       <c r="H12" t="n">
-        <v>-5.3</v>
+        <v>-5.1</v>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>BUY (undervalued)</t>
+          <t>HOLD (fairly valued)</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
@@ -996,16 +996,16 @@
         </is>
       </c>
       <c r="K12" t="n">
-        <v>88.05</v>
+        <v>88.28</v>
       </c>
       <c r="L12" t="n">
-        <v>83.72</v>
+        <v>83.93000000000001</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>2343</t>
+          <t>STNG</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -1014,22 +1014,22 @@
         </is>
       </c>
       <c r="C13" t="n">
-        <v>0.41</v>
+        <v>79.63</v>
       </c>
       <c r="D13" t="n">
-        <v>0.41</v>
+        <v>76.22</v>
       </c>
       <c r="E13" t="n">
-        <v>-1.89</v>
+        <v>-4.28</v>
       </c>
       <c r="F13" t="n">
-        <v>3.1</v>
+        <v>0.6</v>
       </c>
       <c r="G13" t="n">
-        <v>1.4</v>
+        <v>-3.4</v>
       </c>
       <c r="H13" t="n">
-        <v>-1.7</v>
+        <v>-4</v>
       </c>
       <c r="I13" t="inlineStr">
         <is>
@@ -1042,16 +1042,16 @@
         </is>
       </c>
       <c r="K13" t="n">
-        <v>0.4</v>
+        <v>79.88</v>
       </c>
       <c r="L13" t="n">
-        <v>0.4</v>
+        <v>76.73</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>STNG</t>
+          <t>ASC</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1060,44 +1060,44 @@
         </is>
       </c>
       <c r="C14" t="n">
-        <v>79.63</v>
+        <v>17.38</v>
       </c>
       <c r="D14" t="n">
-        <v>76.22</v>
+        <v>17.37</v>
       </c>
       <c r="E14" t="n">
-        <v>-4.28</v>
+        <v>-0.02</v>
       </c>
       <c r="F14" t="n">
-        <v>4.9</v>
+        <v>-7</v>
       </c>
       <c r="G14" t="n">
-        <v>0.8</v>
+        <v>-7</v>
       </c>
       <c r="H14" t="n">
-        <v>-4.1</v>
+        <v>-0</v>
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>HOLD (fairly valued)</t>
+          <t>TRIM/SHORT (overvalued)</t>
         </is>
       </c>
       <c r="J14" t="inlineStr">
         <is>
-          <t>HOLD (fairly valued)</t>
+          <t>TRIM/SHORT (overvalued)</t>
         </is>
       </c>
       <c r="K14" t="n">
-        <v>79.88</v>
+        <v>16.38</v>
       </c>
       <c r="L14" t="n">
-        <v>76.73</v>
+        <v>16.38</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>ASC</t>
+          <t>GNK</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1106,44 +1106,44 @@
         </is>
       </c>
       <c r="C15" t="n">
-        <v>17.38</v>
+        <v>24.77</v>
       </c>
       <c r="D15" t="n">
-        <v>17.37</v>
+        <v>25.12</v>
       </c>
       <c r="E15" t="n">
-        <v>-0.02</v>
+        <v>1.42</v>
       </c>
       <c r="F15" t="n">
-        <v>-1.7</v>
+        <v>-15</v>
       </c>
       <c r="G15" t="n">
-        <v>-1.8</v>
+        <v>-13.9</v>
       </c>
       <c r="H15" t="n">
-        <v>-0</v>
+        <v>1</v>
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>HOLD (fairly valued)</t>
+          <t>TRIM/SHORT (overvalued)</t>
         </is>
       </c>
       <c r="J15" t="inlineStr">
         <is>
-          <t>HOLD (fairly valued)</t>
+          <t>TRIM/SHORT (overvalued)</t>
         </is>
       </c>
       <c r="K15" t="n">
-        <v>16.38</v>
+        <v>22.4</v>
       </c>
       <c r="L15" t="n">
-        <v>16.38</v>
+        <v>22.67</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>GNK</t>
+          <t>HAFN</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1152,22 +1152,22 @@
         </is>
       </c>
       <c r="C16" t="n">
-        <v>24.77</v>
+        <v>5.69</v>
       </c>
       <c r="D16" t="n">
-        <v>25.12</v>
+        <v>5.56</v>
       </c>
       <c r="E16" t="n">
-        <v>1.42</v>
+        <v>-2.2</v>
       </c>
       <c r="F16" t="n">
-        <v>-11.3</v>
+        <v>-13.8</v>
       </c>
       <c r="G16" t="n">
-        <v>-10.2</v>
+        <v>-15.3</v>
       </c>
       <c r="H16" t="n">
-        <v>1.1</v>
+        <v>-1.5</v>
       </c>
       <c r="I16" t="inlineStr">
         <is>
@@ -1180,40 +1180,40 @@
         </is>
       </c>
       <c r="K16" t="n">
-        <v>22.4</v>
+        <v>6.67</v>
       </c>
       <c r="L16" t="n">
-        <v>22.67</v>
+        <v>6.56</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>HAFN</t>
+          <t>CMBT</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>whole-company</t>
+          <t>WHOLE-COMPANY (hybrid aggregation)</t>
         </is>
       </c>
       <c r="C17" t="n">
-        <v>5.69</v>
+        <v>15.84</v>
       </c>
       <c r="D17" t="n">
-        <v>5.56</v>
+        <v>16.46</v>
       </c>
       <c r="E17" t="n">
-        <v>-2.2</v>
+        <v>3.89</v>
       </c>
       <c r="F17" t="n">
-        <v>-10.9</v>
+        <v>-19.3</v>
       </c>
       <c r="G17" t="n">
-        <v>-12.5</v>
+        <v>-16.4</v>
       </c>
       <c r="H17" t="n">
-        <v>-1.5</v>
+        <v>2.9</v>
       </c>
       <c r="I17" t="inlineStr">
         <is>
@@ -1226,40 +1226,40 @@
         </is>
       </c>
       <c r="K17" t="n">
-        <v>6.67</v>
+        <v>13.91</v>
       </c>
       <c r="L17" t="n">
-        <v>6.56</v>
+        <v>14.41</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>CMBT</t>
+          <t>DHT</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>WHOLE-COMPANY (hybrid aggregation)</t>
+          <t>whole-company</t>
         </is>
       </c>
       <c r="C18" t="n">
-        <v>15.84</v>
+        <v>16.3</v>
       </c>
       <c r="D18" t="n">
-        <v>16.46</v>
+        <v>15.01</v>
       </c>
       <c r="E18" t="n">
-        <v>3.89</v>
+        <v>-7.97</v>
       </c>
       <c r="F18" t="n">
-        <v>-17.2</v>
+        <v>-12.1</v>
       </c>
       <c r="G18" t="n">
-        <v>-14.2</v>
+        <v>-18.2</v>
       </c>
       <c r="H18" t="n">
-        <v>3</v>
+        <v>-6.1</v>
       </c>
       <c r="I18" t="inlineStr">
         <is>
@@ -1272,16 +1272,16 @@
         </is>
       </c>
       <c r="K18" t="n">
-        <v>13.88</v>
+        <v>17.16</v>
       </c>
       <c r="L18" t="n">
-        <v>14.38</v>
+        <v>15.97</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>DHT</t>
+          <t>2343</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1290,22 +1290,22 @@
         </is>
       </c>
       <c r="C19" t="n">
-        <v>16.3</v>
+        <v>0.41</v>
       </c>
       <c r="D19" t="n">
-        <v>15.01</v>
+        <v>0.41</v>
       </c>
       <c r="E19" t="n">
-        <v>-7.97</v>
+        <v>-1.89</v>
       </c>
       <c r="F19" t="n">
-        <v>-8.9</v>
+        <v>-18.8</v>
       </c>
       <c r="G19" t="n">
-        <v>-15.2</v>
+        <v>-20.2</v>
       </c>
       <c r="H19" t="n">
-        <v>-6.3</v>
+        <v>-1.3</v>
       </c>
       <c r="I19" t="inlineStr">
         <is>
@@ -1318,10 +1318,10 @@
         </is>
       </c>
       <c r="K19" t="n">
-        <v>17.06</v>
+        <v>0.4</v>
       </c>
       <c r="L19" t="n">
-        <v>15.88</v>
+        <v>0.4</v>
       </c>
     </row>
     <row r="20">
@@ -1345,10 +1345,10 @@
         <v>0</v>
       </c>
       <c r="F20" t="n">
-        <v>-18.8</v>
+        <v>-23.9</v>
       </c>
       <c r="G20" t="n">
-        <v>-18.8</v>
+        <v>-23.9</v>
       </c>
       <c r="H20" t="n">
         <v>0</v>
@@ -1373,7 +1373,7 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>LPG</t>
+          <t>ECO</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -1382,22 +1382,22 @@
         </is>
       </c>
       <c r="C21" t="n">
-        <v>35.7</v>
+        <v>43.8</v>
       </c>
       <c r="D21" t="n">
-        <v>35.69</v>
+        <v>39.54</v>
       </c>
       <c r="E21" t="n">
-        <v>-0.04</v>
+        <v>-9.73</v>
       </c>
       <c r="F21" t="n">
-        <v>-28.8</v>
+        <v>-24.3</v>
       </c>
       <c r="G21" t="n">
-        <v>-28.9</v>
+        <v>-30.8</v>
       </c>
       <c r="H21" t="n">
-        <v>-0</v>
+        <v>-6.5</v>
       </c>
       <c r="I21" t="inlineStr">
         <is>
@@ -1410,10 +1410,10 @@
         </is>
       </c>
       <c r="K21" t="n">
-        <v>31.84</v>
+        <v>45.62</v>
       </c>
       <c r="L21" t="n">
-        <v>31.82</v>
+        <v>41.71</v>
       </c>
     </row>
     <row r="22">
@@ -1437,13 +1437,13 @@
         <v>-11.01</v>
       </c>
       <c r="F22" t="n">
-        <v>-22.9</v>
+        <v>-25.4</v>
       </c>
       <c r="G22" t="n">
-        <v>-30.3</v>
+        <v>-32.6</v>
       </c>
       <c r="H22" t="n">
-        <v>-7.5</v>
+        <v>-7.2</v>
       </c>
       <c r="I22" t="inlineStr">
         <is>
@@ -1456,16 +1456,16 @@
         </is>
       </c>
       <c r="K22" t="n">
-        <v>30.53</v>
+        <v>30.75</v>
       </c>
       <c r="L22" t="n">
-        <v>27.57</v>
+        <v>27.79</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>ECO</t>
+          <t>LPG</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -1474,22 +1474,22 @@
         </is>
       </c>
       <c r="C23" t="n">
-        <v>43.8</v>
+        <v>35.7</v>
       </c>
       <c r="D23" t="n">
-        <v>39.54</v>
+        <v>35.69</v>
       </c>
       <c r="E23" t="n">
-        <v>-9.73</v>
+        <v>-0.04</v>
       </c>
       <c r="F23" t="n">
-        <v>-27.9</v>
+        <v>-32.8</v>
       </c>
       <c r="G23" t="n">
-        <v>-34.1</v>
+        <v>-32.8</v>
       </c>
       <c r="H23" t="n">
-        <v>-6.2</v>
+        <v>-0</v>
       </c>
       <c r="I23" t="inlineStr">
         <is>
@@ -1502,10 +1502,10 @@
         </is>
       </c>
       <c r="K23" t="n">
-        <v>45.33</v>
+        <v>31.84</v>
       </c>
       <c r="L23" t="n">
-        <v>41.44</v>
+        <v>31.82</v>
       </c>
     </row>
     <row r="24">
@@ -1529,10 +1529,10 @@
         <v>-0.07000000000000001</v>
       </c>
       <c r="F24" t="n">
-        <v>-34.5</v>
+        <v>-36.4</v>
       </c>
       <c r="G24" t="n">
-        <v>-34.5</v>
+        <v>-36.4</v>
       </c>
       <c r="H24" t="n">
         <v>-0</v>
@@ -1575,13 +1575,13 @@
         <v>-6.68</v>
       </c>
       <c r="F25" t="n">
-        <v>-32</v>
+        <v>-35.1</v>
       </c>
       <c r="G25" t="n">
-        <v>-35.7</v>
+        <v>-38.6</v>
       </c>
       <c r="H25" t="n">
-        <v>-3.7</v>
+        <v>-3.5</v>
       </c>
       <c r="I25" t="inlineStr">
         <is>
@@ -1594,10 +1594,10 @@
         </is>
       </c>
       <c r="K25" t="n">
-        <v>62.82</v>
+        <v>63.03</v>
       </c>
       <c r="L25" t="n">
-        <v>59.39</v>
+        <v>59.59</v>
       </c>
     </row>
     <row r="26">
@@ -1621,13 +1621,13 @@
         <v>-14.2</v>
       </c>
       <c r="F26" t="n">
-        <v>-46.3</v>
+        <v>-48.2</v>
       </c>
       <c r="G26" t="n">
-        <v>-52.6</v>
+        <v>-54.3</v>
       </c>
       <c r="H26" t="n">
-        <v>-6.3</v>
+        <v>-6</v>
       </c>
       <c r="I26" t="inlineStr">
         <is>
@@ -1640,10 +1640,10 @@
         </is>
       </c>
       <c r="K26" t="n">
-        <v>3.46</v>
+        <v>3.47</v>
       </c>
       <c r="L26" t="n">
-        <v>3.05</v>
+        <v>3.07</v>
       </c>
     </row>
   </sheetData>

--- a/outputs/transaction_anchor_comparison.xlsx
+++ b/outputs/transaction_anchor_comparison.xlsx
@@ -517,13 +517,13 @@
         <v>0</v>
       </c>
       <c r="F2" t="n">
-        <v>53.8</v>
+        <v>64.09999999999999</v>
       </c>
       <c r="G2" t="n">
-        <v>52.5</v>
+        <v>62.7</v>
       </c>
       <c r="H2" t="n">
-        <v>-1.3</v>
+        <v>-1.4</v>
       </c>
       <c r="I2" t="inlineStr">
         <is>
@@ -545,7 +545,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>TEN</t>
+          <t>SB</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -554,22 +554,22 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>94.58</v>
+        <v>9.67</v>
       </c>
       <c r="D3" t="n">
-        <v>88.16</v>
+        <v>10.58</v>
       </c>
       <c r="E3" t="n">
-        <v>-6.79</v>
+        <v>9.43</v>
       </c>
       <c r="F3" t="n">
-        <v>61.3</v>
+        <v>36.1</v>
       </c>
       <c r="G3" t="n">
-        <v>51.2</v>
+        <v>49.2</v>
       </c>
       <c r="H3" t="n">
-        <v>-10.1</v>
+        <v>13.1</v>
       </c>
       <c r="I3" t="inlineStr">
         <is>
@@ -582,10 +582,10 @@
         </is>
       </c>
       <c r="K3" t="n">
-        <v>66.84</v>
+        <v>8.699999999999999</v>
       </c>
       <c r="L3" t="n">
-        <v>62.66</v>
+        <v>9.529999999999999</v>
       </c>
     </row>
     <row r="4">
@@ -609,10 +609,10 @@
         <v>0</v>
       </c>
       <c r="F4" t="n">
-        <v>49.1</v>
+        <v>49</v>
       </c>
       <c r="G4" t="n">
-        <v>49.1</v>
+        <v>49</v>
       </c>
       <c r="H4" t="n">
         <v>0</v>
@@ -637,7 +637,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>SB</t>
+          <t>TEN</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -646,22 +646,22 @@
         </is>
       </c>
       <c r="C5" t="n">
-        <v>9.67</v>
+        <v>94.58</v>
       </c>
       <c r="D5" t="n">
-        <v>10.58</v>
+        <v>88.16</v>
       </c>
       <c r="E5" t="n">
-        <v>9.43</v>
+        <v>-6.79</v>
       </c>
       <c r="F5" t="n">
-        <v>12.2</v>
+        <v>58.1</v>
       </c>
       <c r="G5" t="n">
-        <v>23</v>
+        <v>48.2</v>
       </c>
       <c r="H5" t="n">
-        <v>10.8</v>
+        <v>-9.9</v>
       </c>
       <c r="I5" t="inlineStr">
         <is>
@@ -674,10 +674,10 @@
         </is>
       </c>
       <c r="K5" t="n">
-        <v>8.699999999999999</v>
+        <v>66.84</v>
       </c>
       <c r="L5" t="n">
-        <v>9.529999999999999</v>
+        <v>62.66</v>
       </c>
     </row>
     <row r="6">
@@ -701,13 +701,13 @@
         <v>-4.51</v>
       </c>
       <c r="F6" t="n">
-        <v>16</v>
+        <v>10.9</v>
       </c>
       <c r="G6" t="n">
-        <v>11.6</v>
+        <v>6.7</v>
       </c>
       <c r="H6" t="n">
-        <v>-4.4</v>
+        <v>-4.2</v>
       </c>
       <c r="I6" t="inlineStr">
         <is>
@@ -729,7 +729,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>CMDB</t>
+          <t>2343</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -738,44 +738,44 @@
         </is>
       </c>
       <c r="C7" t="n">
-        <v>31.44</v>
+        <v>0.41</v>
       </c>
       <c r="D7" t="n">
-        <v>32.13</v>
+        <v>0.41</v>
       </c>
       <c r="E7" t="n">
-        <v>2.19</v>
+        <v>-1.89</v>
       </c>
       <c r="F7" t="n">
-        <v>8.300000000000001</v>
+        <v>3.1</v>
       </c>
       <c r="G7" t="n">
-        <v>10.3</v>
+        <v>1.4</v>
       </c>
       <c r="H7" t="n">
-        <v>2</v>
+        <v>-1.7</v>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>BUY (undervalued)</t>
+          <t>HOLD (fairly valued)</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>BUY (undervalued)</t>
+          <t>HOLD (fairly valued)</t>
         </is>
       </c>
       <c r="K7" t="n">
-        <v>19.74</v>
+        <v>0.4</v>
       </c>
       <c r="L7" t="n">
-        <v>20.11</v>
+        <v>0.4</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>CAPT</t>
+          <t>STNG</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -784,44 +784,44 @@
         </is>
       </c>
       <c r="C8" t="n">
-        <v>15.61</v>
+        <v>79.63</v>
       </c>
       <c r="D8" t="n">
-        <v>15.48</v>
+        <v>76.22</v>
       </c>
       <c r="E8" t="n">
-        <v>-0.8100000000000001</v>
+        <v>-4.28</v>
       </c>
       <c r="F8" t="n">
-        <v>10.7</v>
+        <v>3.5</v>
       </c>
       <c r="G8" t="n">
-        <v>9.1</v>
+        <v>-0.6</v>
       </c>
       <c r="H8" t="n">
-        <v>-1.6</v>
+        <v>-4.1</v>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>BUY (undervalued)</t>
+          <t>HOLD (fairly valued)</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>BUY (undervalued)</t>
+          <t>HOLD (fairly valued)</t>
         </is>
       </c>
       <c r="K8" t="n">
-        <v>16.26</v>
+        <v>79.88</v>
       </c>
       <c r="L8" t="n">
-        <v>16.02</v>
+        <v>76.73</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>SBLK</t>
+          <t>CMDB</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -830,22 +830,22 @@
         </is>
       </c>
       <c r="C9" t="n">
-        <v>31.53</v>
+        <v>31.44</v>
       </c>
       <c r="D9" t="n">
-        <v>32.78</v>
+        <v>32.13</v>
       </c>
       <c r="E9" t="n">
-        <v>3.97</v>
+        <v>2.19</v>
       </c>
       <c r="F9" t="n">
-        <v>-1</v>
+        <v>-4.2</v>
       </c>
       <c r="G9" t="n">
-        <v>2.5</v>
+        <v>-2.4</v>
       </c>
       <c r="H9" t="n">
-        <v>3.5</v>
+        <v>1.8</v>
       </c>
       <c r="I9" t="inlineStr">
         <is>
@@ -858,16 +858,16 @@
         </is>
       </c>
       <c r="K9" t="n">
-        <v>28.76</v>
+        <v>19.74</v>
       </c>
       <c r="L9" t="n">
-        <v>29.79</v>
+        <v>20.11</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>GSL</t>
+          <t>CAPT</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -876,22 +876,22 @@
         </is>
       </c>
       <c r="C10" t="n">
-        <v>41.2</v>
+        <v>15.61</v>
       </c>
       <c r="D10" t="n">
-        <v>41.2</v>
+        <v>15.48</v>
       </c>
       <c r="E10" t="n">
-        <v>0</v>
+        <v>-0.8100000000000001</v>
       </c>
       <c r="F10" t="n">
-        <v>1.7</v>
+        <v>-1.7</v>
       </c>
       <c r="G10" t="n">
-        <v>1.7</v>
+        <v>-3.1</v>
       </c>
       <c r="H10" t="n">
-        <v>0</v>
+        <v>-1.4</v>
       </c>
       <c r="I10" t="inlineStr">
         <is>
@@ -904,16 +904,16 @@
         </is>
       </c>
       <c r="K10" t="n">
-        <v>42.88</v>
+        <v>16.26</v>
       </c>
       <c r="L10" t="n">
-        <v>42.88</v>
+        <v>16.02</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>FLNG</t>
+          <t>SBLK</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -922,44 +922,44 @@
         </is>
       </c>
       <c r="C11" t="n">
-        <v>28.45</v>
+        <v>31.53</v>
       </c>
       <c r="D11" t="n">
-        <v>28.45</v>
+        <v>32.78</v>
       </c>
       <c r="E11" t="n">
-        <v>0</v>
+        <v>3.97</v>
       </c>
       <c r="F11" t="n">
-        <v>-0.4</v>
+        <v>-7.6</v>
       </c>
       <c r="G11" t="n">
-        <v>-0.4</v>
+        <v>-4.2</v>
       </c>
       <c r="H11" t="n">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="I11" t="inlineStr">
         <is>
+          <t>TRIM/SHORT (overvalued)</t>
+        </is>
+      </c>
+      <c r="J11" t="inlineStr">
+        <is>
           <t>HOLD (fairly valued)</t>
         </is>
       </c>
-      <c r="J11" t="inlineStr">
-        <is>
-          <t>HOLD (fairly valued)</t>
-        </is>
-      </c>
       <c r="K11" t="n">
-        <v>30.67</v>
+        <v>28.76</v>
       </c>
       <c r="L11" t="n">
-        <v>30.67</v>
+        <v>29.79</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>TNK</t>
+          <t>GSL</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -968,44 +968,44 @@
         </is>
       </c>
       <c r="C12" t="n">
-        <v>89.65000000000001</v>
+        <v>41.2</v>
       </c>
       <c r="D12" t="n">
-        <v>84.59999999999999</v>
+        <v>41.2</v>
       </c>
       <c r="E12" t="n">
-        <v>-5.63</v>
+        <v>0</v>
       </c>
       <c r="F12" t="n">
-        <v>3.7</v>
+        <v>-5.3</v>
       </c>
       <c r="G12" t="n">
-        <v>-1.4</v>
+        <v>-5.3</v>
       </c>
       <c r="H12" t="n">
-        <v>-5.1</v>
+        <v>0</v>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>HOLD (fairly valued)</t>
+          <t>TRIM/SHORT (overvalued)</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>HOLD (fairly valued)</t>
+          <t>TRIM/SHORT (overvalued)</t>
         </is>
       </c>
       <c r="K12" t="n">
-        <v>88.28</v>
+        <v>42.88</v>
       </c>
       <c r="L12" t="n">
-        <v>83.93000000000001</v>
+        <v>42.88</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>STNG</t>
+          <t>TNK</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -1014,22 +1014,22 @@
         </is>
       </c>
       <c r="C13" t="n">
-        <v>79.63</v>
+        <v>89.65000000000001</v>
       </c>
       <c r="D13" t="n">
-        <v>76.22</v>
+        <v>84.59999999999999</v>
       </c>
       <c r="E13" t="n">
-        <v>-4.28</v>
+        <v>-5.63</v>
       </c>
       <c r="F13" t="n">
-        <v>0.6</v>
+        <v>-1.9</v>
       </c>
       <c r="G13" t="n">
-        <v>-3.4</v>
+        <v>-6.8</v>
       </c>
       <c r="H13" t="n">
-        <v>-4</v>
+        <v>-4.8</v>
       </c>
       <c r="I13" t="inlineStr">
         <is>
@@ -1038,20 +1038,20 @@
       </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t>HOLD (fairly valued)</t>
+          <t>TRIM/SHORT (overvalued)</t>
         </is>
       </c>
       <c r="K13" t="n">
-        <v>79.88</v>
+        <v>88.28</v>
       </c>
       <c r="L13" t="n">
-        <v>76.73</v>
+        <v>83.93000000000001</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>ASC</t>
+          <t>FLNG</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1060,22 +1060,22 @@
         </is>
       </c>
       <c r="C14" t="n">
-        <v>17.38</v>
+        <v>27.22</v>
       </c>
       <c r="D14" t="n">
-        <v>17.37</v>
+        <v>27.22</v>
       </c>
       <c r="E14" t="n">
-        <v>-0.02</v>
+        <v>0</v>
       </c>
       <c r="F14" t="n">
-        <v>-7</v>
+        <v>-7.7</v>
       </c>
       <c r="G14" t="n">
-        <v>-7</v>
+        <v>-7.7</v>
       </c>
       <c r="H14" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="I14" t="inlineStr">
         <is>
@@ -1088,16 +1088,16 @@
         </is>
       </c>
       <c r="K14" t="n">
-        <v>16.38</v>
+        <v>29.47</v>
       </c>
       <c r="L14" t="n">
-        <v>16.38</v>
+        <v>29.47</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>GNK</t>
+          <t>ASC</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1106,22 +1106,22 @@
         </is>
       </c>
       <c r="C15" t="n">
-        <v>24.77</v>
+        <v>17.38</v>
       </c>
       <c r="D15" t="n">
-        <v>25.12</v>
+        <v>17.37</v>
       </c>
       <c r="E15" t="n">
-        <v>1.42</v>
+        <v>-0.02</v>
       </c>
       <c r="F15" t="n">
-        <v>-15</v>
+        <v>-9</v>
       </c>
       <c r="G15" t="n">
-        <v>-13.9</v>
+        <v>-9</v>
       </c>
       <c r="H15" t="n">
-        <v>1</v>
+        <v>-0</v>
       </c>
       <c r="I15" t="inlineStr">
         <is>
@@ -1134,16 +1134,16 @@
         </is>
       </c>
       <c r="K15" t="n">
-        <v>22.4</v>
+        <v>16.38</v>
       </c>
       <c r="L15" t="n">
-        <v>22.67</v>
+        <v>16.38</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>HAFN</t>
+          <t>DHT</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1152,22 +1152,22 @@
         </is>
       </c>
       <c r="C16" t="n">
-        <v>5.69</v>
+        <v>16.3</v>
       </c>
       <c r="D16" t="n">
-        <v>5.56</v>
+        <v>15.01</v>
       </c>
       <c r="E16" t="n">
-        <v>-2.2</v>
+        <v>-7.97</v>
       </c>
       <c r="F16" t="n">
-        <v>-13.8</v>
+        <v>-10.5</v>
       </c>
       <c r="G16" t="n">
-        <v>-15.3</v>
+        <v>-16.7</v>
       </c>
       <c r="H16" t="n">
-        <v>-1.5</v>
+        <v>-6.2</v>
       </c>
       <c r="I16" t="inlineStr">
         <is>
@@ -1180,40 +1180,40 @@
         </is>
       </c>
       <c r="K16" t="n">
-        <v>6.67</v>
+        <v>17.16</v>
       </c>
       <c r="L16" t="n">
-        <v>6.56</v>
+        <v>15.97</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>CMBT</t>
+          <t>GNK</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>WHOLE-COMPANY (hybrid aggregation)</t>
+          <t>whole-company</t>
         </is>
       </c>
       <c r="C17" t="n">
-        <v>15.84</v>
+        <v>24.77</v>
       </c>
       <c r="D17" t="n">
-        <v>16.46</v>
+        <v>25.12</v>
       </c>
       <c r="E17" t="n">
-        <v>3.89</v>
+        <v>1.42</v>
       </c>
       <c r="F17" t="n">
-        <v>-19.3</v>
+        <v>-18</v>
       </c>
       <c r="G17" t="n">
-        <v>-16.4</v>
+        <v>-17</v>
       </c>
       <c r="H17" t="n">
-        <v>2.9</v>
+        <v>1</v>
       </c>
       <c r="I17" t="inlineStr">
         <is>
@@ -1226,16 +1226,16 @@
         </is>
       </c>
       <c r="K17" t="n">
-        <v>13.91</v>
+        <v>22.4</v>
       </c>
       <c r="L17" t="n">
-        <v>14.41</v>
+        <v>22.67</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>DHT</t>
+          <t>HAFN</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1244,22 +1244,22 @@
         </is>
       </c>
       <c r="C18" t="n">
-        <v>16.3</v>
+        <v>5.69</v>
       </c>
       <c r="D18" t="n">
-        <v>15.01</v>
+        <v>5.56</v>
       </c>
       <c r="E18" t="n">
-        <v>-7.97</v>
+        <v>-2.2</v>
       </c>
       <c r="F18" t="n">
-        <v>-12.1</v>
+        <v>-18.6</v>
       </c>
       <c r="G18" t="n">
-        <v>-18.2</v>
+        <v>-19.9</v>
       </c>
       <c r="H18" t="n">
-        <v>-6.1</v>
+        <v>-1.4</v>
       </c>
       <c r="I18" t="inlineStr">
         <is>
@@ -1272,40 +1272,40 @@
         </is>
       </c>
       <c r="K18" t="n">
-        <v>17.16</v>
+        <v>6.67</v>
       </c>
       <c r="L18" t="n">
-        <v>15.97</v>
+        <v>6.56</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>2343</t>
+          <t>CMBT</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>whole-company</t>
+          <t>WHOLE-COMPANY (hybrid aggregation)</t>
         </is>
       </c>
       <c r="C19" t="n">
-        <v>0.41</v>
+        <v>15.84</v>
       </c>
       <c r="D19" t="n">
-        <v>0.41</v>
+        <v>16.46</v>
       </c>
       <c r="E19" t="n">
-        <v>-1.89</v>
+        <v>3.89</v>
       </c>
       <c r="F19" t="n">
-        <v>-18.8</v>
+        <v>-23.4</v>
       </c>
       <c r="G19" t="n">
-        <v>-20.2</v>
+        <v>-20.7</v>
       </c>
       <c r="H19" t="n">
-        <v>-1.3</v>
+        <v>2.7</v>
       </c>
       <c r="I19" t="inlineStr">
         <is>
@@ -1318,10 +1318,10 @@
         </is>
       </c>
       <c r="K19" t="n">
-        <v>0.4</v>
+        <v>13.91</v>
       </c>
       <c r="L19" t="n">
-        <v>0.4</v>
+        <v>14.41</v>
       </c>
     </row>
     <row r="20">
@@ -1345,10 +1345,10 @@
         <v>0</v>
       </c>
       <c r="F20" t="n">
-        <v>-23.9</v>
+        <v>-31.4</v>
       </c>
       <c r="G20" t="n">
-        <v>-23.9</v>
+        <v>-31.4</v>
       </c>
       <c r="H20" t="n">
         <v>0</v>
@@ -1391,13 +1391,13 @@
         <v>-9.73</v>
       </c>
       <c r="F21" t="n">
-        <v>-24.3</v>
+        <v>-29.9</v>
       </c>
       <c r="G21" t="n">
-        <v>-30.8</v>
+        <v>-35.9</v>
       </c>
       <c r="H21" t="n">
-        <v>-6.5</v>
+        <v>-6</v>
       </c>
       <c r="I21" t="inlineStr">
         <is>
@@ -1437,13 +1437,13 @@
         <v>-11.01</v>
       </c>
       <c r="F22" t="n">
-        <v>-25.4</v>
+        <v>-29.2</v>
       </c>
       <c r="G22" t="n">
-        <v>-32.6</v>
+        <v>-36.1</v>
       </c>
       <c r="H22" t="n">
-        <v>-7.2</v>
+        <v>-6.8</v>
       </c>
       <c r="I22" t="inlineStr">
         <is>
@@ -1483,10 +1483,10 @@
         <v>-0.04</v>
       </c>
       <c r="F23" t="n">
-        <v>-32.8</v>
+        <v>-37.3</v>
       </c>
       <c r="G23" t="n">
-        <v>-32.8</v>
+        <v>-37.3</v>
       </c>
       <c r="H23" t="n">
         <v>-0</v>
@@ -1511,31 +1511,31 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>BWLP</t>
+          <t>INSW</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>whole-company</t>
+          <t>WHOLE-COMPANY (hybrid aggregation)</t>
         </is>
       </c>
       <c r="C24" t="n">
-        <v>15.81</v>
+        <v>58.55</v>
       </c>
       <c r="D24" t="n">
-        <v>15.8</v>
+        <v>54.64</v>
       </c>
       <c r="E24" t="n">
-        <v>-0.07000000000000001</v>
+        <v>-6.68</v>
       </c>
       <c r="F24" t="n">
         <v>-36.4</v>
       </c>
       <c r="G24" t="n">
-        <v>-36.4</v>
+        <v>-39.8</v>
       </c>
       <c r="H24" t="n">
-        <v>-0</v>
+        <v>-3.5</v>
       </c>
       <c r="I24" t="inlineStr">
         <is>
@@ -1548,40 +1548,40 @@
         </is>
       </c>
       <c r="K24" t="n">
-        <v>14.47</v>
+        <v>63.03</v>
       </c>
       <c r="L24" t="n">
-        <v>14.46</v>
+        <v>59.59</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>INSW</t>
+          <t>BWLP</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>WHOLE-COMPANY (hybrid aggregation)</t>
+          <t>whole-company</t>
         </is>
       </c>
       <c r="C25" t="n">
-        <v>58.55</v>
+        <v>15.81</v>
       </c>
       <c r="D25" t="n">
-        <v>54.64</v>
+        <v>15.8</v>
       </c>
       <c r="E25" t="n">
-        <v>-6.68</v>
+        <v>-0.07000000000000001</v>
       </c>
       <c r="F25" t="n">
-        <v>-35.1</v>
+        <v>-42.3</v>
       </c>
       <c r="G25" t="n">
-        <v>-38.6</v>
+        <v>-42.3</v>
       </c>
       <c r="H25" t="n">
-        <v>-3.5</v>
+        <v>-0</v>
       </c>
       <c r="I25" t="inlineStr">
         <is>
@@ -1594,10 +1594,10 @@
         </is>
       </c>
       <c r="K25" t="n">
-        <v>63.03</v>
+        <v>14.47</v>
       </c>
       <c r="L25" t="n">
-        <v>59.59</v>
+        <v>14.46</v>
       </c>
     </row>
     <row r="26">
@@ -1621,13 +1621,13 @@
         <v>-14.2</v>
       </c>
       <c r="F26" t="n">
-        <v>-48.2</v>
+        <v>-49.6</v>
       </c>
       <c r="G26" t="n">
-        <v>-54.3</v>
+        <v>-55.5</v>
       </c>
       <c r="H26" t="n">
-        <v>-6</v>
+        <v>-5.9</v>
       </c>
       <c r="I26" t="inlineStr">
         <is>

--- a/outputs/transaction_anchor_comparison.xlsx
+++ b/outputs/transaction_anchor_comparison.xlsx
@@ -517,13 +517,13 @@
         <v>0</v>
       </c>
       <c r="F2" t="n">
-        <v>64.09999999999999</v>
+        <v>109.7</v>
       </c>
       <c r="G2" t="n">
-        <v>62.7</v>
+        <v>108</v>
       </c>
       <c r="H2" t="n">
-        <v>-1.4</v>
+        <v>-1.8</v>
       </c>
       <c r="I2" t="inlineStr">
         <is>
@@ -609,10 +609,10 @@
         <v>0</v>
       </c>
       <c r="F4" t="n">
-        <v>49</v>
+        <v>48.3</v>
       </c>
       <c r="G4" t="n">
-        <v>49</v>
+        <v>48.3</v>
       </c>
       <c r="H4" t="n">
         <v>0</v>
@@ -655,13 +655,13 @@
         <v>-6.79</v>
       </c>
       <c r="F5" t="n">
-        <v>58.1</v>
+        <v>57.2</v>
       </c>
       <c r="G5" t="n">
-        <v>48.2</v>
+        <v>47.4</v>
       </c>
       <c r="H5" t="n">
-        <v>-9.9</v>
+        <v>-9.800000000000001</v>
       </c>
       <c r="I5" t="inlineStr">
         <is>
@@ -692,22 +692,22 @@
         </is>
       </c>
       <c r="C6" t="n">
-        <v>31.65</v>
+        <v>33.69</v>
       </c>
       <c r="D6" t="n">
-        <v>30.22</v>
+        <v>32.3</v>
       </c>
       <c r="E6" t="n">
-        <v>-4.51</v>
+        <v>-4.11</v>
       </c>
       <c r="F6" t="n">
-        <v>10.9</v>
+        <v>13.6</v>
       </c>
       <c r="G6" t="n">
-        <v>6.7</v>
+        <v>9.699999999999999</v>
       </c>
       <c r="H6" t="n">
-        <v>-4.2</v>
+        <v>-3.9</v>
       </c>
       <c r="I6" t="inlineStr">
         <is>
@@ -720,10 +720,10 @@
         </is>
       </c>
       <c r="K6" t="n">
-        <v>34.89</v>
+        <v>37.06</v>
       </c>
       <c r="L6" t="n">
-        <v>33.58</v>
+        <v>35.79</v>
       </c>
     </row>
     <row r="7">
@@ -793,13 +793,13 @@
         <v>-4.28</v>
       </c>
       <c r="F8" t="n">
-        <v>3.5</v>
+        <v>2.4</v>
       </c>
       <c r="G8" t="n">
-        <v>-0.6</v>
+        <v>-1.7</v>
       </c>
       <c r="H8" t="n">
-        <v>-4.1</v>
+        <v>-4</v>
       </c>
       <c r="I8" t="inlineStr">
         <is>
@@ -839,10 +839,10 @@
         <v>2.19</v>
       </c>
       <c r="F9" t="n">
-        <v>-4.2</v>
+        <v>-3.8</v>
       </c>
       <c r="G9" t="n">
-        <v>-2.4</v>
+        <v>-2</v>
       </c>
       <c r="H9" t="n">
         <v>1.8</v>
@@ -867,7 +867,7 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>CAPT</t>
+          <t>SBLK</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -876,44 +876,44 @@
         </is>
       </c>
       <c r="C10" t="n">
-        <v>15.61</v>
+        <v>31.53</v>
       </c>
       <c r="D10" t="n">
-        <v>15.48</v>
+        <v>32.78</v>
       </c>
       <c r="E10" t="n">
-        <v>-0.8100000000000001</v>
+        <v>3.97</v>
       </c>
       <c r="F10" t="n">
-        <v>-1.7</v>
+        <v>-5.6</v>
       </c>
       <c r="G10" t="n">
-        <v>-3.1</v>
+        <v>-2.3</v>
       </c>
       <c r="H10" t="n">
-        <v>-1.4</v>
+        <v>3.4</v>
       </c>
       <c r="I10" t="inlineStr">
         <is>
+          <t>TRIM/SHORT (overvalued)</t>
+        </is>
+      </c>
+      <c r="J10" t="inlineStr">
+        <is>
           <t>HOLD (fairly valued)</t>
         </is>
       </c>
-      <c r="J10" t="inlineStr">
-        <is>
-          <t>HOLD (fairly valued)</t>
-        </is>
-      </c>
       <c r="K10" t="n">
-        <v>16.26</v>
+        <v>28.76</v>
       </c>
       <c r="L10" t="n">
-        <v>16.02</v>
+        <v>29.79</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>SBLK</t>
+          <t>CAPT</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -922,26 +922,26 @@
         </is>
       </c>
       <c r="C11" t="n">
-        <v>31.53</v>
+        <v>15.61</v>
       </c>
       <c r="D11" t="n">
-        <v>32.78</v>
+        <v>15.48</v>
       </c>
       <c r="E11" t="n">
-        <v>3.97</v>
+        <v>-0.8100000000000001</v>
       </c>
       <c r="F11" t="n">
-        <v>-7.6</v>
+        <v>-1.3</v>
       </c>
       <c r="G11" t="n">
-        <v>-4.2</v>
+        <v>-2.7</v>
       </c>
       <c r="H11" t="n">
-        <v>3.3</v>
+        <v>-1.4</v>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>TRIM/SHORT (overvalued)</t>
+          <t>HOLD (fairly valued)</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
@@ -950,10 +950,10 @@
         </is>
       </c>
       <c r="K11" t="n">
-        <v>28.76</v>
+        <v>16.26</v>
       </c>
       <c r="L11" t="n">
-        <v>29.79</v>
+        <v>16.02</v>
       </c>
     </row>
     <row r="12">
@@ -977,22 +977,22 @@
         <v>0</v>
       </c>
       <c r="F12" t="n">
-        <v>-5.3</v>
+        <v>-3.7</v>
       </c>
       <c r="G12" t="n">
-        <v>-5.3</v>
+        <v>-3.7</v>
       </c>
       <c r="H12" t="n">
         <v>0</v>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>TRIM/SHORT (overvalued)</t>
+          <t>HOLD (fairly valued)</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>TRIM/SHORT (overvalued)</t>
+          <t>HOLD (fairly valued)</t>
         </is>
       </c>
       <c r="K12" t="n">
@@ -1023,13 +1023,13 @@
         <v>-5.63</v>
       </c>
       <c r="F13" t="n">
-        <v>-1.9</v>
+        <v>-0.5</v>
       </c>
       <c r="G13" t="n">
-        <v>-6.8</v>
+        <v>-5.4</v>
       </c>
       <c r="H13" t="n">
-        <v>-4.8</v>
+        <v>-4.9</v>
       </c>
       <c r="I13" t="inlineStr">
         <is>
@@ -1051,7 +1051,7 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>FLNG</t>
+          <t>ASC</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1060,22 +1060,22 @@
         </is>
       </c>
       <c r="C14" t="n">
-        <v>27.22</v>
+        <v>17.38</v>
       </c>
       <c r="D14" t="n">
-        <v>27.22</v>
+        <v>17.37</v>
       </c>
       <c r="E14" t="n">
-        <v>0</v>
+        <v>-0.02</v>
       </c>
       <c r="F14" t="n">
-        <v>-7.7</v>
+        <v>-5.7</v>
       </c>
       <c r="G14" t="n">
-        <v>-7.7</v>
+        <v>-5.7</v>
       </c>
       <c r="H14" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="I14" t="inlineStr">
         <is>
@@ -1088,16 +1088,16 @@
         </is>
       </c>
       <c r="K14" t="n">
-        <v>29.47</v>
+        <v>16.38</v>
       </c>
       <c r="L14" t="n">
-        <v>29.47</v>
+        <v>16.38</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>ASC</t>
+          <t>FLNG</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1106,22 +1106,22 @@
         </is>
       </c>
       <c r="C15" t="n">
-        <v>17.38</v>
+        <v>27.22</v>
       </c>
       <c r="D15" t="n">
-        <v>17.37</v>
+        <v>27.22</v>
       </c>
       <c r="E15" t="n">
-        <v>-0.02</v>
+        <v>0</v>
       </c>
       <c r="F15" t="n">
-        <v>-9</v>
+        <v>-6.4</v>
       </c>
       <c r="G15" t="n">
-        <v>-9</v>
+        <v>-6.4</v>
       </c>
       <c r="H15" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="I15" t="inlineStr">
         <is>
@@ -1134,16 +1134,16 @@
         </is>
       </c>
       <c r="K15" t="n">
-        <v>16.38</v>
+        <v>29.47</v>
       </c>
       <c r="L15" t="n">
-        <v>16.38</v>
+        <v>29.47</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>DHT</t>
+          <t>GNK</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1152,22 +1152,22 @@
         </is>
       </c>
       <c r="C16" t="n">
-        <v>16.3</v>
+        <v>24.77</v>
       </c>
       <c r="D16" t="n">
-        <v>15.01</v>
+        <v>25.12</v>
       </c>
       <c r="E16" t="n">
-        <v>-7.97</v>
+        <v>1.42</v>
       </c>
       <c r="F16" t="n">
-        <v>-10.5</v>
+        <v>-13.4</v>
       </c>
       <c r="G16" t="n">
-        <v>-16.7</v>
+        <v>-12.4</v>
       </c>
       <c r="H16" t="n">
-        <v>-6.2</v>
+        <v>1.1</v>
       </c>
       <c r="I16" t="inlineStr">
         <is>
@@ -1180,16 +1180,16 @@
         </is>
       </c>
       <c r="K16" t="n">
-        <v>17.16</v>
+        <v>22.4</v>
       </c>
       <c r="L16" t="n">
-        <v>15.97</v>
+        <v>22.67</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>GNK</t>
+          <t>DHT</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1198,22 +1198,22 @@
         </is>
       </c>
       <c r="C17" t="n">
-        <v>24.77</v>
+        <v>16.3</v>
       </c>
       <c r="D17" t="n">
-        <v>25.12</v>
+        <v>15.01</v>
       </c>
       <c r="E17" t="n">
-        <v>1.42</v>
+        <v>-7.97</v>
       </c>
       <c r="F17" t="n">
-        <v>-18</v>
+        <v>-12.7</v>
       </c>
       <c r="G17" t="n">
-        <v>-17</v>
+        <v>-18.8</v>
       </c>
       <c r="H17" t="n">
-        <v>1</v>
+        <v>-6.1</v>
       </c>
       <c r="I17" t="inlineStr">
         <is>
@@ -1226,40 +1226,40 @@
         </is>
       </c>
       <c r="K17" t="n">
-        <v>22.4</v>
+        <v>17.16</v>
       </c>
       <c r="L17" t="n">
-        <v>22.67</v>
+        <v>15.97</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>HAFN</t>
+          <t>CMBT</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>whole-company</t>
+          <t>WHOLE-COMPANY (hybrid aggregation)</t>
         </is>
       </c>
       <c r="C18" t="n">
-        <v>5.69</v>
+        <v>15.84</v>
       </c>
       <c r="D18" t="n">
-        <v>5.56</v>
+        <v>16.46</v>
       </c>
       <c r="E18" t="n">
-        <v>-2.2</v>
+        <v>3.89</v>
       </c>
       <c r="F18" t="n">
-        <v>-18.6</v>
+        <v>-24.2</v>
       </c>
       <c r="G18" t="n">
-        <v>-19.9</v>
+        <v>-21.5</v>
       </c>
       <c r="H18" t="n">
-        <v>-1.4</v>
+        <v>2.7</v>
       </c>
       <c r="I18" t="inlineStr">
         <is>
@@ -1272,40 +1272,40 @@
         </is>
       </c>
       <c r="K18" t="n">
-        <v>6.67</v>
+        <v>13.91</v>
       </c>
       <c r="L18" t="n">
-        <v>6.56</v>
+        <v>14.41</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>CMBT</t>
+          <t>HAFN</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>WHOLE-COMPANY (hybrid aggregation)</t>
+          <t>whole-company</t>
         </is>
       </c>
       <c r="C19" t="n">
-        <v>15.84</v>
+        <v>5.69</v>
       </c>
       <c r="D19" t="n">
-        <v>16.46</v>
+        <v>5.56</v>
       </c>
       <c r="E19" t="n">
-        <v>3.89</v>
+        <v>-2.2</v>
       </c>
       <c r="F19" t="n">
-        <v>-23.4</v>
+        <v>-21.2</v>
       </c>
       <c r="G19" t="n">
-        <v>-20.7</v>
+        <v>-22.6</v>
       </c>
       <c r="H19" t="n">
-        <v>2.7</v>
+        <v>-1.3</v>
       </c>
       <c r="I19" t="inlineStr">
         <is>
@@ -1318,10 +1318,10 @@
         </is>
       </c>
       <c r="K19" t="n">
-        <v>13.91</v>
+        <v>6.67</v>
       </c>
       <c r="L19" t="n">
-        <v>14.41</v>
+        <v>6.56</v>
       </c>
     </row>
     <row r="20">
@@ -1345,10 +1345,10 @@
         <v>0</v>
       </c>
       <c r="F20" t="n">
-        <v>-31.4</v>
+        <v>-27.5</v>
       </c>
       <c r="G20" t="n">
-        <v>-31.4</v>
+        <v>-27.5</v>
       </c>
       <c r="H20" t="n">
         <v>0</v>
@@ -1373,7 +1373,7 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>ECO</t>
+          <t>LPG</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -1382,22 +1382,22 @@
         </is>
       </c>
       <c r="C21" t="n">
-        <v>43.8</v>
+        <v>35.7</v>
       </c>
       <c r="D21" t="n">
-        <v>39.54</v>
+        <v>35.69</v>
       </c>
       <c r="E21" t="n">
-        <v>-9.73</v>
+        <v>-0.04</v>
       </c>
       <c r="F21" t="n">
-        <v>-29.9</v>
+        <v>-36</v>
       </c>
       <c r="G21" t="n">
-        <v>-35.9</v>
+        <v>-36.1</v>
       </c>
       <c r="H21" t="n">
-        <v>-6</v>
+        <v>-0</v>
       </c>
       <c r="I21" t="inlineStr">
         <is>
@@ -1410,10 +1410,10 @@
         </is>
       </c>
       <c r="K21" t="n">
-        <v>45.62</v>
+        <v>31.84</v>
       </c>
       <c r="L21" t="n">
-        <v>41.71</v>
+        <v>31.82</v>
       </c>
     </row>
     <row r="22">
@@ -1437,13 +1437,13 @@
         <v>-11.01</v>
       </c>
       <c r="F22" t="n">
-        <v>-29.2</v>
+        <v>-30.4</v>
       </c>
       <c r="G22" t="n">
-        <v>-36.1</v>
+        <v>-37.1</v>
       </c>
       <c r="H22" t="n">
-        <v>-6.8</v>
+        <v>-6.7</v>
       </c>
       <c r="I22" t="inlineStr">
         <is>
@@ -1465,7 +1465,7 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>LPG</t>
+          <t>ECO</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -1474,22 +1474,22 @@
         </is>
       </c>
       <c r="C23" t="n">
-        <v>35.7</v>
+        <v>43.8</v>
       </c>
       <c r="D23" t="n">
-        <v>35.69</v>
+        <v>39.54</v>
       </c>
       <c r="E23" t="n">
-        <v>-0.04</v>
+        <v>-9.73</v>
       </c>
       <c r="F23" t="n">
-        <v>-37.3</v>
+        <v>-31.8</v>
       </c>
       <c r="G23" t="n">
-        <v>-37.3</v>
+        <v>-37.6</v>
       </c>
       <c r="H23" t="n">
-        <v>-0</v>
+        <v>-5.8</v>
       </c>
       <c r="I23" t="inlineStr">
         <is>
@@ -1502,10 +1502,10 @@
         </is>
       </c>
       <c r="K23" t="n">
-        <v>31.84</v>
+        <v>45.62</v>
       </c>
       <c r="L23" t="n">
-        <v>31.82</v>
+        <v>41.71</v>
       </c>
     </row>
     <row r="24">
@@ -1529,10 +1529,10 @@
         <v>-6.68</v>
       </c>
       <c r="F24" t="n">
-        <v>-36.4</v>
+        <v>-36.2</v>
       </c>
       <c r="G24" t="n">
-        <v>-39.8</v>
+        <v>-39.7</v>
       </c>
       <c r="H24" t="n">
         <v>-3.5</v>
@@ -1575,10 +1575,10 @@
         <v>-0.07000000000000001</v>
       </c>
       <c r="F25" t="n">
-        <v>-42.3</v>
+        <v>-39.8</v>
       </c>
       <c r="G25" t="n">
-        <v>-42.3</v>
+        <v>-39.9</v>
       </c>
       <c r="H25" t="n">
         <v>-0</v>
@@ -1621,13 +1621,13 @@
         <v>-14.2</v>
       </c>
       <c r="F26" t="n">
-        <v>-49.6</v>
+        <v>-48.7</v>
       </c>
       <c r="G26" t="n">
-        <v>-55.5</v>
+        <v>-54.7</v>
       </c>
       <c r="H26" t="n">
-        <v>-5.9</v>
+        <v>-6</v>
       </c>
       <c r="I26" t="inlineStr">
         <is>

--- a/outputs/transaction_anchor_comparison.xlsx
+++ b/outputs/transaction_anchor_comparison.xlsx
@@ -499,7 +499,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>BRUT</t>
+          <t>SB</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -508,22 +508,22 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>9.619999999999999</v>
+        <v>9.67</v>
       </c>
       <c r="D2" t="n">
-        <v>9.619999999999999</v>
+        <v>10.58</v>
       </c>
       <c r="E2" t="n">
-        <v>0</v>
+        <v>9.43</v>
       </c>
       <c r="F2" t="n">
-        <v>109.7</v>
+        <v>36.1</v>
       </c>
       <c r="G2" t="n">
-        <v>108</v>
+        <v>49.2</v>
       </c>
       <c r="H2" t="n">
-        <v>-1.8</v>
+        <v>13.1</v>
       </c>
       <c r="I2" t="inlineStr">
         <is>
@@ -536,16 +536,16 @@
         </is>
       </c>
       <c r="K2" t="n">
-        <v>10.37</v>
+        <v>8.699999999999999</v>
       </c>
       <c r="L2" t="n">
-        <v>10.28</v>
+        <v>9.529999999999999</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>SB</t>
+          <t>CCEC</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -554,22 +554,22 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>9.67</v>
+        <v>25.7</v>
       </c>
       <c r="D3" t="n">
-        <v>10.58</v>
+        <v>25.7</v>
       </c>
       <c r="E3" t="n">
-        <v>9.43</v>
+        <v>0</v>
       </c>
       <c r="F3" t="n">
-        <v>36.1</v>
+        <v>48.3</v>
       </c>
       <c r="G3" t="n">
-        <v>49.2</v>
+        <v>48.3</v>
       </c>
       <c r="H3" t="n">
-        <v>13.1</v>
+        <v>0</v>
       </c>
       <c r="I3" t="inlineStr">
         <is>
@@ -582,16 +582,16 @@
         </is>
       </c>
       <c r="K3" t="n">
-        <v>8.699999999999999</v>
+        <v>33.7</v>
       </c>
       <c r="L3" t="n">
-        <v>9.529999999999999</v>
+        <v>33.7</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>CCEC</t>
+          <t>TEN</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -600,22 +600,22 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>25.7</v>
+        <v>94.58</v>
       </c>
       <c r="D4" t="n">
-        <v>25.7</v>
+        <v>88.16</v>
       </c>
       <c r="E4" t="n">
-        <v>0</v>
+        <v>-6.79</v>
       </c>
       <c r="F4" t="n">
-        <v>48.3</v>
+        <v>57.2</v>
       </c>
       <c r="G4" t="n">
-        <v>48.3</v>
+        <v>47.4</v>
       </c>
       <c r="H4" t="n">
-        <v>0</v>
+        <v>-9.800000000000001</v>
       </c>
       <c r="I4" t="inlineStr">
         <is>
@@ -628,16 +628,16 @@
         </is>
       </c>
       <c r="K4" t="n">
-        <v>33.7</v>
+        <v>66.84</v>
       </c>
       <c r="L4" t="n">
-        <v>33.7</v>
+        <v>62.66</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>TEN</t>
+          <t>TRMD</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -646,22 +646,22 @@
         </is>
       </c>
       <c r="C5" t="n">
-        <v>94.58</v>
+        <v>33.69</v>
       </c>
       <c r="D5" t="n">
-        <v>88.16</v>
+        <v>32.3</v>
       </c>
       <c r="E5" t="n">
-        <v>-6.79</v>
+        <v>-4.11</v>
       </c>
       <c r="F5" t="n">
-        <v>57.2</v>
+        <v>13.6</v>
       </c>
       <c r="G5" t="n">
-        <v>47.4</v>
+        <v>9.699999999999999</v>
       </c>
       <c r="H5" t="n">
-        <v>-9.800000000000001</v>
+        <v>-3.9</v>
       </c>
       <c r="I5" t="inlineStr">
         <is>
@@ -674,16 +674,16 @@
         </is>
       </c>
       <c r="K5" t="n">
-        <v>66.84</v>
+        <v>37.06</v>
       </c>
       <c r="L5" t="n">
-        <v>62.66</v>
+        <v>35.79</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>TRMD</t>
+          <t>BRUT</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -692,22 +692,22 @@
         </is>
       </c>
       <c r="C6" t="n">
-        <v>33.69</v>
+        <v>4.92</v>
       </c>
       <c r="D6" t="n">
-        <v>32.3</v>
+        <v>4.92</v>
       </c>
       <c r="E6" t="n">
-        <v>-4.11</v>
+        <v>0</v>
       </c>
       <c r="F6" t="n">
-        <v>13.6</v>
+        <v>5.1</v>
       </c>
       <c r="G6" t="n">
-        <v>9.699999999999999</v>
+        <v>3.6</v>
       </c>
       <c r="H6" t="n">
-        <v>-3.9</v>
+        <v>-1.5</v>
       </c>
       <c r="I6" t="inlineStr">
         <is>
@@ -716,14 +716,14 @@
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>BUY (undervalued)</t>
+          <t>HOLD (fairly valued)</t>
         </is>
       </c>
       <c r="K6" t="n">
-        <v>37.06</v>
+        <v>5.19</v>
       </c>
       <c r="L6" t="n">
-        <v>35.79</v>
+        <v>5.12</v>
       </c>
     </row>
     <row r="7">

--- a/outputs/transaction_anchor_comparison.xlsx
+++ b/outputs/transaction_anchor_comparison.xlsx
@@ -499,7 +499,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>SB</t>
+          <t>CCEC</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -508,22 +508,22 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>9.67</v>
+        <v>25.7</v>
       </c>
       <c r="D2" t="n">
-        <v>10.58</v>
+        <v>25.7</v>
       </c>
       <c r="E2" t="n">
-        <v>9.43</v>
+        <v>0</v>
       </c>
       <c r="F2" t="n">
-        <v>36.1</v>
+        <v>48.3</v>
       </c>
       <c r="G2" t="n">
-        <v>49.2</v>
+        <v>48.3</v>
       </c>
       <c r="H2" t="n">
-        <v>13.1</v>
+        <v>0</v>
       </c>
       <c r="I2" t="inlineStr">
         <is>
@@ -536,16 +536,16 @@
         </is>
       </c>
       <c r="K2" t="n">
-        <v>8.699999999999999</v>
+        <v>33.7</v>
       </c>
       <c r="L2" t="n">
-        <v>9.529999999999999</v>
+        <v>33.7</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>CCEC</t>
+          <t>TEN</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -554,22 +554,22 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>25.7</v>
+        <v>94.58</v>
       </c>
       <c r="D3" t="n">
-        <v>25.7</v>
+        <v>88.16</v>
       </c>
       <c r="E3" t="n">
-        <v>0</v>
+        <v>-6.79</v>
       </c>
       <c r="F3" t="n">
-        <v>48.3</v>
+        <v>57.2</v>
       </c>
       <c r="G3" t="n">
-        <v>48.3</v>
+        <v>47.4</v>
       </c>
       <c r="H3" t="n">
-        <v>0</v>
+        <v>-9.800000000000001</v>
       </c>
       <c r="I3" t="inlineStr">
         <is>
@@ -582,16 +582,16 @@
         </is>
       </c>
       <c r="K3" t="n">
-        <v>33.7</v>
+        <v>66.84</v>
       </c>
       <c r="L3" t="n">
-        <v>33.7</v>
+        <v>62.66</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>TEN</t>
+          <t>SB</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -600,38 +600,38 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>94.58</v>
+        <v>9.67</v>
       </c>
       <c r="D4" t="n">
-        <v>88.16</v>
+        <v>10.58</v>
       </c>
       <c r="E4" t="n">
-        <v>-6.79</v>
+        <v>9.43</v>
       </c>
       <c r="F4" t="n">
-        <v>57.2</v>
+        <v>2.1</v>
       </c>
       <c r="G4" t="n">
-        <v>47.4</v>
+        <v>11.9</v>
       </c>
       <c r="H4" t="n">
-        <v>-9.800000000000001</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="I4" t="inlineStr">
         <is>
+          <t>HOLD (fairly valued)</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
           <t>BUY (undervalued)</t>
         </is>
       </c>
-      <c r="J4" t="inlineStr">
-        <is>
-          <t>BUY (undervalued)</t>
-        </is>
-      </c>
       <c r="K4" t="n">
-        <v>66.84</v>
+        <v>8.699999999999999</v>
       </c>
       <c r="L4" t="n">
-        <v>62.66</v>
+        <v>9.529999999999999</v>
       </c>
     </row>
     <row r="5">
@@ -729,7 +729,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>2343</t>
+          <t>STNG</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -738,22 +738,22 @@
         </is>
       </c>
       <c r="C7" t="n">
-        <v>0.41</v>
+        <v>79.63</v>
       </c>
       <c r="D7" t="n">
-        <v>0.41</v>
+        <v>76.22</v>
       </c>
       <c r="E7" t="n">
-        <v>-1.89</v>
+        <v>-4.28</v>
       </c>
       <c r="F7" t="n">
-        <v>3.1</v>
+        <v>2.4</v>
       </c>
       <c r="G7" t="n">
-        <v>1.4</v>
+        <v>-1.7</v>
       </c>
       <c r="H7" t="n">
-        <v>-1.7</v>
+        <v>-4</v>
       </c>
       <c r="I7" t="inlineStr">
         <is>
@@ -766,16 +766,16 @@
         </is>
       </c>
       <c r="K7" t="n">
-        <v>0.4</v>
+        <v>79.88</v>
       </c>
       <c r="L7" t="n">
-        <v>0.4</v>
+        <v>76.73</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>STNG</t>
+          <t>CMDB</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -784,22 +784,22 @@
         </is>
       </c>
       <c r="C8" t="n">
-        <v>79.63</v>
+        <v>31.44</v>
       </c>
       <c r="D8" t="n">
-        <v>76.22</v>
+        <v>32.13</v>
       </c>
       <c r="E8" t="n">
-        <v>-4.28</v>
+        <v>2.19</v>
       </c>
       <c r="F8" t="n">
-        <v>2.4</v>
+        <v>-3.8</v>
       </c>
       <c r="G8" t="n">
-        <v>-1.7</v>
+        <v>-2</v>
       </c>
       <c r="H8" t="n">
-        <v>-4</v>
+        <v>1.8</v>
       </c>
       <c r="I8" t="inlineStr">
         <is>
@@ -812,16 +812,16 @@
         </is>
       </c>
       <c r="K8" t="n">
-        <v>79.88</v>
+        <v>19.74</v>
       </c>
       <c r="L8" t="n">
-        <v>76.73</v>
+        <v>20.11</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>CMDB</t>
+          <t>SBLK</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -830,44 +830,44 @@
         </is>
       </c>
       <c r="C9" t="n">
-        <v>31.44</v>
+        <v>31.53</v>
       </c>
       <c r="D9" t="n">
-        <v>32.13</v>
+        <v>32.78</v>
       </c>
       <c r="E9" t="n">
-        <v>2.19</v>
+        <v>3.97</v>
       </c>
       <c r="F9" t="n">
-        <v>-3.8</v>
+        <v>-5.6</v>
       </c>
       <c r="G9" t="n">
-        <v>-2</v>
+        <v>-2.3</v>
       </c>
       <c r="H9" t="n">
-        <v>1.8</v>
+        <v>3.4</v>
       </c>
       <c r="I9" t="inlineStr">
         <is>
+          <t>TRIM/SHORT (overvalued)</t>
+        </is>
+      </c>
+      <c r="J9" t="inlineStr">
+        <is>
           <t>HOLD (fairly valued)</t>
         </is>
       </c>
-      <c r="J9" t="inlineStr">
-        <is>
-          <t>HOLD (fairly valued)</t>
-        </is>
-      </c>
       <c r="K9" t="n">
-        <v>19.74</v>
+        <v>28.76</v>
       </c>
       <c r="L9" t="n">
-        <v>20.11</v>
+        <v>29.79</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>SBLK</t>
+          <t>CAPT</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -876,26 +876,26 @@
         </is>
       </c>
       <c r="C10" t="n">
-        <v>31.53</v>
+        <v>15.61</v>
       </c>
       <c r="D10" t="n">
-        <v>32.78</v>
+        <v>15.48</v>
       </c>
       <c r="E10" t="n">
-        <v>3.97</v>
+        <v>-0.8100000000000001</v>
       </c>
       <c r="F10" t="n">
-        <v>-5.6</v>
+        <v>-1.3</v>
       </c>
       <c r="G10" t="n">
-        <v>-2.3</v>
+        <v>-2.7</v>
       </c>
       <c r="H10" t="n">
-        <v>3.4</v>
+        <v>-1.4</v>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>TRIM/SHORT (overvalued)</t>
+          <t>HOLD (fairly valued)</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
@@ -904,16 +904,16 @@
         </is>
       </c>
       <c r="K10" t="n">
-        <v>28.76</v>
+        <v>16.26</v>
       </c>
       <c r="L10" t="n">
-        <v>29.79</v>
+        <v>16.02</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>CAPT</t>
+          <t>GSL</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -922,22 +922,22 @@
         </is>
       </c>
       <c r="C11" t="n">
-        <v>15.61</v>
+        <v>41.2</v>
       </c>
       <c r="D11" t="n">
-        <v>15.48</v>
+        <v>41.2</v>
       </c>
       <c r="E11" t="n">
-        <v>-0.8100000000000001</v>
+        <v>0</v>
       </c>
       <c r="F11" t="n">
-        <v>-1.3</v>
+        <v>-3.7</v>
       </c>
       <c r="G11" t="n">
-        <v>-2.7</v>
+        <v>-3.7</v>
       </c>
       <c r="H11" t="n">
-        <v>-1.4</v>
+        <v>0</v>
       </c>
       <c r="I11" t="inlineStr">
         <is>
@@ -950,16 +950,16 @@
         </is>
       </c>
       <c r="K11" t="n">
-        <v>16.26</v>
+        <v>42.88</v>
       </c>
       <c r="L11" t="n">
-        <v>16.02</v>
+        <v>42.88</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>GSL</t>
+          <t>TNK</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -968,22 +968,22 @@
         </is>
       </c>
       <c r="C12" t="n">
-        <v>41.2</v>
+        <v>89.65000000000001</v>
       </c>
       <c r="D12" t="n">
-        <v>41.2</v>
+        <v>84.59999999999999</v>
       </c>
       <c r="E12" t="n">
-        <v>0</v>
+        <v>-5.63</v>
       </c>
       <c r="F12" t="n">
-        <v>-3.7</v>
+        <v>-0.5</v>
       </c>
       <c r="G12" t="n">
-        <v>-3.7</v>
+        <v>-5.4</v>
       </c>
       <c r="H12" t="n">
-        <v>0</v>
+        <v>-4.9</v>
       </c>
       <c r="I12" t="inlineStr">
         <is>
@@ -992,20 +992,20 @@
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>HOLD (fairly valued)</t>
+          <t>TRIM/SHORT (overvalued)</t>
         </is>
       </c>
       <c r="K12" t="n">
-        <v>42.88</v>
+        <v>88.28</v>
       </c>
       <c r="L12" t="n">
-        <v>42.88</v>
+        <v>83.93000000000001</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>TNK</t>
+          <t>ASC</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -1014,26 +1014,26 @@
         </is>
       </c>
       <c r="C13" t="n">
-        <v>89.65000000000001</v>
+        <v>17.38</v>
       </c>
       <c r="D13" t="n">
-        <v>84.59999999999999</v>
+        <v>17.37</v>
       </c>
       <c r="E13" t="n">
-        <v>-5.63</v>
+        <v>-0.02</v>
       </c>
       <c r="F13" t="n">
-        <v>-0.5</v>
+        <v>-5.7</v>
       </c>
       <c r="G13" t="n">
-        <v>-5.4</v>
+        <v>-5.7</v>
       </c>
       <c r="H13" t="n">
-        <v>-4.9</v>
+        <v>-0</v>
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>HOLD (fairly valued)</t>
+          <t>TRIM/SHORT (overvalued)</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
@@ -1042,16 +1042,16 @@
         </is>
       </c>
       <c r="K13" t="n">
-        <v>88.28</v>
+        <v>16.38</v>
       </c>
       <c r="L13" t="n">
-        <v>83.93000000000001</v>
+        <v>16.38</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>ASC</t>
+          <t>FLNG</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1060,22 +1060,22 @@
         </is>
       </c>
       <c r="C14" t="n">
-        <v>17.38</v>
+        <v>27.22</v>
       </c>
       <c r="D14" t="n">
-        <v>17.37</v>
+        <v>27.22</v>
       </c>
       <c r="E14" t="n">
-        <v>-0.02</v>
+        <v>0</v>
       </c>
       <c r="F14" t="n">
-        <v>-5.7</v>
+        <v>-6.4</v>
       </c>
       <c r="G14" t="n">
-        <v>-5.7</v>
+        <v>-6.4</v>
       </c>
       <c r="H14" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="I14" t="inlineStr">
         <is>
@@ -1088,16 +1088,16 @@
         </is>
       </c>
       <c r="K14" t="n">
-        <v>16.38</v>
+        <v>29.47</v>
       </c>
       <c r="L14" t="n">
-        <v>16.38</v>
+        <v>29.47</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>FLNG</t>
+          <t>GNK</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1106,22 +1106,22 @@
         </is>
       </c>
       <c r="C15" t="n">
-        <v>27.22</v>
+        <v>24.77</v>
       </c>
       <c r="D15" t="n">
-        <v>27.22</v>
+        <v>25.12</v>
       </c>
       <c r="E15" t="n">
-        <v>0</v>
+        <v>1.42</v>
       </c>
       <c r="F15" t="n">
-        <v>-6.4</v>
+        <v>-13.4</v>
       </c>
       <c r="G15" t="n">
-        <v>-6.4</v>
+        <v>-12.4</v>
       </c>
       <c r="H15" t="n">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="I15" t="inlineStr">
         <is>
@@ -1134,16 +1134,16 @@
         </is>
       </c>
       <c r="K15" t="n">
-        <v>29.47</v>
+        <v>22.4</v>
       </c>
       <c r="L15" t="n">
-        <v>29.47</v>
+        <v>22.67</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>GNK</t>
+          <t>DHT</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1152,22 +1152,22 @@
         </is>
       </c>
       <c r="C16" t="n">
-        <v>24.77</v>
+        <v>16.3</v>
       </c>
       <c r="D16" t="n">
-        <v>25.12</v>
+        <v>15.01</v>
       </c>
       <c r="E16" t="n">
-        <v>1.42</v>
+        <v>-7.97</v>
       </c>
       <c r="F16" t="n">
-        <v>-13.4</v>
+        <v>-12.7</v>
       </c>
       <c r="G16" t="n">
-        <v>-12.4</v>
+        <v>-18.8</v>
       </c>
       <c r="H16" t="n">
-        <v>1.1</v>
+        <v>-6.1</v>
       </c>
       <c r="I16" t="inlineStr">
         <is>
@@ -1180,40 +1180,40 @@
         </is>
       </c>
       <c r="K16" t="n">
-        <v>22.4</v>
+        <v>17.16</v>
       </c>
       <c r="L16" t="n">
-        <v>22.67</v>
+        <v>15.97</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>DHT</t>
+          <t>CMBT</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>whole-company</t>
+          <t>WHOLE-COMPANY (hybrid aggregation)</t>
         </is>
       </c>
       <c r="C17" t="n">
-        <v>16.3</v>
+        <v>15.84</v>
       </c>
       <c r="D17" t="n">
-        <v>15.01</v>
+        <v>16.46</v>
       </c>
       <c r="E17" t="n">
-        <v>-7.97</v>
+        <v>3.89</v>
       </c>
       <c r="F17" t="n">
-        <v>-12.7</v>
+        <v>-24.2</v>
       </c>
       <c r="G17" t="n">
-        <v>-18.8</v>
+        <v>-21.5</v>
       </c>
       <c r="H17" t="n">
-        <v>-6.1</v>
+        <v>2.7</v>
       </c>
       <c r="I17" t="inlineStr">
         <is>
@@ -1226,40 +1226,40 @@
         </is>
       </c>
       <c r="K17" t="n">
-        <v>17.16</v>
+        <v>13.91</v>
       </c>
       <c r="L17" t="n">
-        <v>15.97</v>
+        <v>14.41</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>CMBT</t>
+          <t>HAFN</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>WHOLE-COMPANY (hybrid aggregation)</t>
+          <t>whole-company</t>
         </is>
       </c>
       <c r="C18" t="n">
-        <v>15.84</v>
+        <v>5.69</v>
       </c>
       <c r="D18" t="n">
-        <v>16.46</v>
+        <v>5.56</v>
       </c>
       <c r="E18" t="n">
-        <v>3.89</v>
+        <v>-2.2</v>
       </c>
       <c r="F18" t="n">
-        <v>-24.2</v>
+        <v>-21.2</v>
       </c>
       <c r="G18" t="n">
-        <v>-21.5</v>
+        <v>-22.6</v>
       </c>
       <c r="H18" t="n">
-        <v>2.7</v>
+        <v>-1.3</v>
       </c>
       <c r="I18" t="inlineStr">
         <is>
@@ -1272,16 +1272,16 @@
         </is>
       </c>
       <c r="K18" t="n">
-        <v>13.91</v>
+        <v>6.67</v>
       </c>
       <c r="L18" t="n">
-        <v>14.41</v>
+        <v>6.56</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>HAFN</t>
+          <t>2343</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1290,22 +1290,22 @@
         </is>
       </c>
       <c r="C19" t="n">
-        <v>5.69</v>
+        <v>0.41</v>
       </c>
       <c r="D19" t="n">
-        <v>5.56</v>
+        <v>0.41</v>
       </c>
       <c r="E19" t="n">
-        <v>-2.2</v>
+        <v>-1.89</v>
       </c>
       <c r="F19" t="n">
-        <v>-21.2</v>
+        <v>-24.5</v>
       </c>
       <c r="G19" t="n">
-        <v>-22.6</v>
+        <v>-25.8</v>
       </c>
       <c r="H19" t="n">
-        <v>-1.3</v>
+        <v>-1.2</v>
       </c>
       <c r="I19" t="inlineStr">
         <is>
@@ -1318,10 +1318,10 @@
         </is>
       </c>
       <c r="K19" t="n">
-        <v>6.67</v>
+        <v>0.4</v>
       </c>
       <c r="L19" t="n">
-        <v>6.56</v>
+        <v>0.4</v>
       </c>
     </row>
     <row r="20">

--- a/outputs/transaction_anchor_comparison.xlsx
+++ b/outputs/transaction_anchor_comparison.xlsx
@@ -591,7 +591,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>SB</t>
+          <t>TRMD</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -600,26 +600,26 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>9.67</v>
+        <v>33.69</v>
       </c>
       <c r="D4" t="n">
-        <v>10.58</v>
+        <v>32.3</v>
       </c>
       <c r="E4" t="n">
-        <v>9.43</v>
+        <v>-4.11</v>
       </c>
       <c r="F4" t="n">
-        <v>2.1</v>
+        <v>13.6</v>
       </c>
       <c r="G4" t="n">
-        <v>11.9</v>
+        <v>9.699999999999999</v>
       </c>
       <c r="H4" t="n">
-        <v>9.800000000000001</v>
+        <v>-3.9</v>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>HOLD (fairly valued)</t>
+          <t>BUY (undervalued)</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
@@ -628,16 +628,16 @@
         </is>
       </c>
       <c r="K4" t="n">
-        <v>8.699999999999999</v>
+        <v>37.06</v>
       </c>
       <c r="L4" t="n">
-        <v>9.529999999999999</v>
+        <v>35.79</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>TRMD</t>
+          <t>SB</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -646,38 +646,38 @@
         </is>
       </c>
       <c r="C5" t="n">
-        <v>33.69</v>
+        <v>9.67</v>
       </c>
       <c r="D5" t="n">
-        <v>32.3</v>
+        <v>10.65</v>
       </c>
       <c r="E5" t="n">
-        <v>-4.11</v>
+        <v>10.21</v>
       </c>
       <c r="F5" t="n">
-        <v>13.6</v>
+        <v>-2.1</v>
       </c>
       <c r="G5" t="n">
-        <v>9.699999999999999</v>
+        <v>8.4</v>
       </c>
       <c r="H5" t="n">
-        <v>-3.9</v>
+        <v>10.4</v>
       </c>
       <c r="I5" t="inlineStr">
         <is>
+          <t>HOLD (fairly valued)</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
           <t>BUY (undervalued)</t>
         </is>
       </c>
-      <c r="J5" t="inlineStr">
-        <is>
-          <t>BUY (undervalued)</t>
-        </is>
-      </c>
       <c r="K5" t="n">
-        <v>37.06</v>
+        <v>8.34</v>
       </c>
       <c r="L5" t="n">
-        <v>35.79</v>
+        <v>9.23</v>
       </c>
     </row>
     <row r="6">
@@ -775,7 +775,7 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>CMDB</t>
+          <t>CAPT</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -784,22 +784,22 @@
         </is>
       </c>
       <c r="C8" t="n">
-        <v>31.44</v>
+        <v>15.61</v>
       </c>
       <c r="D8" t="n">
-        <v>32.13</v>
+        <v>15.48</v>
       </c>
       <c r="E8" t="n">
-        <v>2.19</v>
+        <v>-0.8100000000000001</v>
       </c>
       <c r="F8" t="n">
-        <v>-3.8</v>
+        <v>-1.3</v>
       </c>
       <c r="G8" t="n">
-        <v>-2</v>
+        <v>-2.7</v>
       </c>
       <c r="H8" t="n">
-        <v>1.8</v>
+        <v>-1.4</v>
       </c>
       <c r="I8" t="inlineStr">
         <is>
@@ -812,16 +812,16 @@
         </is>
       </c>
       <c r="K8" t="n">
-        <v>19.74</v>
+        <v>16.26</v>
       </c>
       <c r="L8" t="n">
-        <v>20.11</v>
+        <v>16.02</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>SBLK</t>
+          <t>GSL</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -830,26 +830,26 @@
         </is>
       </c>
       <c r="C9" t="n">
-        <v>31.53</v>
+        <v>41.2</v>
       </c>
       <c r="D9" t="n">
-        <v>32.78</v>
+        <v>41.2</v>
       </c>
       <c r="E9" t="n">
-        <v>3.97</v>
+        <v>0</v>
       </c>
       <c r="F9" t="n">
-        <v>-5.6</v>
+        <v>-3.7</v>
       </c>
       <c r="G9" t="n">
-        <v>-2.3</v>
+        <v>-3.7</v>
       </c>
       <c r="H9" t="n">
-        <v>3.4</v>
+        <v>0</v>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>TRIM/SHORT (overvalued)</t>
+          <t>HOLD (fairly valued)</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
@@ -858,16 +858,16 @@
         </is>
       </c>
       <c r="K9" t="n">
-        <v>28.76</v>
+        <v>42.88</v>
       </c>
       <c r="L9" t="n">
-        <v>29.79</v>
+        <v>42.88</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>CAPT</t>
+          <t>CMDB</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -876,44 +876,44 @@
         </is>
       </c>
       <c r="C10" t="n">
-        <v>15.61</v>
+        <v>31.44</v>
       </c>
       <c r="D10" t="n">
-        <v>15.48</v>
+        <v>32.2</v>
       </c>
       <c r="E10" t="n">
-        <v>-0.8100000000000001</v>
+        <v>2.41</v>
       </c>
       <c r="F10" t="n">
-        <v>-1.3</v>
+        <v>-6.8</v>
       </c>
       <c r="G10" t="n">
-        <v>-2.7</v>
+        <v>-4.8</v>
       </c>
       <c r="H10" t="n">
-        <v>-1.4</v>
+        <v>1.9</v>
       </c>
       <c r="I10" t="inlineStr">
         <is>
+          <t>TRIM/SHORT (overvalued)</t>
+        </is>
+      </c>
+      <c r="J10" t="inlineStr">
+        <is>
           <t>HOLD (fairly valued)</t>
         </is>
       </c>
-      <c r="J10" t="inlineStr">
-        <is>
-          <t>HOLD (fairly valued)</t>
-        </is>
-      </c>
       <c r="K10" t="n">
-        <v>16.26</v>
+        <v>19.13</v>
       </c>
       <c r="L10" t="n">
-        <v>16.02</v>
+        <v>19.53</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>GSL</t>
+          <t>TNK</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -922,22 +922,22 @@
         </is>
       </c>
       <c r="C11" t="n">
-        <v>41.2</v>
+        <v>89.65000000000001</v>
       </c>
       <c r="D11" t="n">
-        <v>41.2</v>
+        <v>84.59999999999999</v>
       </c>
       <c r="E11" t="n">
-        <v>0</v>
+        <v>-5.63</v>
       </c>
       <c r="F11" t="n">
-        <v>-3.7</v>
+        <v>-0.5</v>
       </c>
       <c r="G11" t="n">
-        <v>-3.7</v>
+        <v>-5.4</v>
       </c>
       <c r="H11" t="n">
-        <v>0</v>
+        <v>-4.9</v>
       </c>
       <c r="I11" t="inlineStr">
         <is>
@@ -946,20 +946,20 @@
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>HOLD (fairly valued)</t>
+          <t>TRIM/SHORT (overvalued)</t>
         </is>
       </c>
       <c r="K11" t="n">
-        <v>42.88</v>
+        <v>88.28</v>
       </c>
       <c r="L11" t="n">
-        <v>42.88</v>
+        <v>83.93000000000001</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>TNK</t>
+          <t>ASC</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -968,26 +968,26 @@
         </is>
       </c>
       <c r="C12" t="n">
-        <v>89.65000000000001</v>
+        <v>17.38</v>
       </c>
       <c r="D12" t="n">
-        <v>84.59999999999999</v>
+        <v>17.37</v>
       </c>
       <c r="E12" t="n">
-        <v>-5.63</v>
+        <v>-0.02</v>
       </c>
       <c r="F12" t="n">
-        <v>-0.5</v>
+        <v>-5.7</v>
       </c>
       <c r="G12" t="n">
-        <v>-5.4</v>
+        <v>-5.7</v>
       </c>
       <c r="H12" t="n">
-        <v>-4.9</v>
+        <v>-0</v>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>HOLD (fairly valued)</t>
+          <t>TRIM/SHORT (overvalued)</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
@@ -996,16 +996,16 @@
         </is>
       </c>
       <c r="K12" t="n">
-        <v>88.28</v>
+        <v>16.38</v>
       </c>
       <c r="L12" t="n">
-        <v>83.93000000000001</v>
+        <v>16.38</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>ASC</t>
+          <t>SBLK</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -1014,22 +1014,22 @@
         </is>
       </c>
       <c r="C13" t="n">
-        <v>17.38</v>
+        <v>31.53</v>
       </c>
       <c r="D13" t="n">
-        <v>17.37</v>
+        <v>32.88</v>
       </c>
       <c r="E13" t="n">
-        <v>-0.02</v>
+        <v>4.26</v>
       </c>
       <c r="F13" t="n">
-        <v>-5.7</v>
+        <v>-9.199999999999999</v>
       </c>
       <c r="G13" t="n">
         <v>-5.7</v>
       </c>
       <c r="H13" t="n">
-        <v>-0</v>
+        <v>3.5</v>
       </c>
       <c r="I13" t="inlineStr">
         <is>
@@ -1042,10 +1042,10 @@
         </is>
       </c>
       <c r="K13" t="n">
-        <v>16.38</v>
+        <v>27.66</v>
       </c>
       <c r="L13" t="n">
-        <v>16.38</v>
+        <v>28.74</v>
       </c>
     </row>
     <row r="14">
@@ -1115,13 +1115,13 @@
         <v>1.42</v>
       </c>
       <c r="F15" t="n">
-        <v>-13.4</v>
+        <v>-17.4</v>
       </c>
       <c r="G15" t="n">
-        <v>-12.4</v>
+        <v>-16.3</v>
       </c>
       <c r="H15" t="n">
-        <v>1.1</v>
+        <v>1</v>
       </c>
       <c r="I15" t="inlineStr">
         <is>
@@ -1134,10 +1134,10 @@
         </is>
       </c>
       <c r="K15" t="n">
-        <v>22.4</v>
+        <v>21.39</v>
       </c>
       <c r="L15" t="n">
-        <v>22.67</v>
+        <v>21.66</v>
       </c>
     </row>
     <row r="16">
@@ -1189,31 +1189,31 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>CMBT</t>
+          <t>HAFN</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>WHOLE-COMPANY (hybrid aggregation)</t>
+          <t>whole-company</t>
         </is>
       </c>
       <c r="C17" t="n">
-        <v>15.84</v>
+        <v>5.69</v>
       </c>
       <c r="D17" t="n">
-        <v>16.46</v>
+        <v>5.56</v>
       </c>
       <c r="E17" t="n">
-        <v>3.89</v>
+        <v>-2.2</v>
       </c>
       <c r="F17" t="n">
-        <v>-24.2</v>
+        <v>-21.2</v>
       </c>
       <c r="G17" t="n">
-        <v>-21.5</v>
+        <v>-22.6</v>
       </c>
       <c r="H17" t="n">
-        <v>2.7</v>
+        <v>-1.3</v>
       </c>
       <c r="I17" t="inlineStr">
         <is>
@@ -1226,40 +1226,40 @@
         </is>
       </c>
       <c r="K17" t="n">
-        <v>13.91</v>
+        <v>6.67</v>
       </c>
       <c r="L17" t="n">
-        <v>14.41</v>
+        <v>6.56</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>HAFN</t>
+          <t>CMBT</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>whole-company</t>
+          <t>WHOLE-COMPANY (hybrid aggregation)</t>
         </is>
       </c>
       <c r="C18" t="n">
-        <v>5.69</v>
+        <v>15.84</v>
       </c>
       <c r="D18" t="n">
-        <v>5.56</v>
+        <v>16.5</v>
       </c>
       <c r="E18" t="n">
-        <v>-2.2</v>
+        <v>4.19</v>
       </c>
       <c r="F18" t="n">
-        <v>-21.2</v>
+        <v>-27.2</v>
       </c>
       <c r="G18" t="n">
-        <v>-22.6</v>
+        <v>-24.4</v>
       </c>
       <c r="H18" t="n">
-        <v>-1.3</v>
+        <v>2.8</v>
       </c>
       <c r="I18" t="inlineStr">
         <is>
@@ -1272,16 +1272,16 @@
         </is>
       </c>
       <c r="K18" t="n">
-        <v>6.67</v>
+        <v>13.36</v>
       </c>
       <c r="L18" t="n">
-        <v>6.56</v>
+        <v>13.87</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>2343</t>
+          <t>MPCC</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1290,22 +1290,22 @@
         </is>
       </c>
       <c r="C19" t="n">
-        <v>0.41</v>
+        <v>2.05</v>
       </c>
       <c r="D19" t="n">
-        <v>0.41</v>
+        <v>2.05</v>
       </c>
       <c r="E19" t="n">
-        <v>-1.89</v>
+        <v>0</v>
       </c>
       <c r="F19" t="n">
-        <v>-24.5</v>
+        <v>-27.5</v>
       </c>
       <c r="G19" t="n">
-        <v>-25.8</v>
+        <v>-27.5</v>
       </c>
       <c r="H19" t="n">
-        <v>-1.2</v>
+        <v>0</v>
       </c>
       <c r="I19" t="inlineStr">
         <is>
@@ -1318,16 +1318,16 @@
         </is>
       </c>
       <c r="K19" t="n">
-        <v>0.4</v>
+        <v>2.07</v>
       </c>
       <c r="L19" t="n">
-        <v>0.4</v>
+        <v>2.07</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>MPCC</t>
+          <t>2343</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -1336,22 +1336,22 @@
         </is>
       </c>
       <c r="C20" t="n">
-        <v>2.05</v>
+        <v>0.41</v>
       </c>
       <c r="D20" t="n">
-        <v>2.05</v>
+        <v>0.41</v>
       </c>
       <c r="E20" t="n">
-        <v>0</v>
+        <v>-1.89</v>
       </c>
       <c r="F20" t="n">
-        <v>-27.5</v>
+        <v>-28</v>
       </c>
       <c r="G20" t="n">
-        <v>-27.5</v>
+        <v>-29.2</v>
       </c>
       <c r="H20" t="n">
-        <v>0</v>
+        <v>-1.2</v>
       </c>
       <c r="I20" t="inlineStr">
         <is>
@@ -1364,10 +1364,10 @@
         </is>
       </c>
       <c r="K20" t="n">
-        <v>2.07</v>
+        <v>0.38</v>
       </c>
       <c r="L20" t="n">
-        <v>2.07</v>
+        <v>0.38</v>
       </c>
     </row>
     <row r="21">

--- a/outputs/transaction_anchor_comparison.xlsx
+++ b/outputs/transaction_anchor_comparison.xlsx
@@ -1290,19 +1290,19 @@
         </is>
       </c>
       <c r="C19" t="n">
-        <v>2.05</v>
+        <v>2.1</v>
       </c>
       <c r="D19" t="n">
-        <v>2.05</v>
+        <v>2.1</v>
       </c>
       <c r="E19" t="n">
         <v>0</v>
       </c>
       <c r="F19" t="n">
-        <v>-27.5</v>
+        <v>-24.8</v>
       </c>
       <c r="G19" t="n">
-        <v>-27.5</v>
+        <v>-24.8</v>
       </c>
       <c r="H19" t="n">
         <v>0</v>
@@ -1318,10 +1318,10 @@
         </is>
       </c>
       <c r="K19" t="n">
-        <v>2.07</v>
+        <v>2.15</v>
       </c>
       <c r="L19" t="n">
-        <v>2.07</v>
+        <v>2.15</v>
       </c>
     </row>
     <row r="20">

--- a/outputs/transaction_anchor_comparison.xlsx
+++ b/outputs/transaction_anchor_comparison.xlsx
@@ -1189,31 +1189,31 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>HAFN</t>
+          <t>CMBT</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>whole-company</t>
+          <t>WHOLE-COMPANY (hybrid aggregation)</t>
         </is>
       </c>
       <c r="C17" t="n">
-        <v>5.69</v>
+        <v>15.84</v>
       </c>
       <c r="D17" t="n">
-        <v>5.56</v>
+        <v>16.5</v>
       </c>
       <c r="E17" t="n">
-        <v>-2.2</v>
+        <v>4.19</v>
       </c>
       <c r="F17" t="n">
-        <v>-21.2</v>
+        <v>-27.2</v>
       </c>
       <c r="G17" t="n">
-        <v>-22.6</v>
+        <v>-24.4</v>
       </c>
       <c r="H17" t="n">
-        <v>-1.3</v>
+        <v>2.8</v>
       </c>
       <c r="I17" t="inlineStr">
         <is>
@@ -1226,40 +1226,40 @@
         </is>
       </c>
       <c r="K17" t="n">
-        <v>6.67</v>
+        <v>13.36</v>
       </c>
       <c r="L17" t="n">
-        <v>6.56</v>
+        <v>13.87</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>CMBT</t>
+          <t>MPCC</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>WHOLE-COMPANY (hybrid aggregation)</t>
+          <t>whole-company</t>
         </is>
       </c>
       <c r="C18" t="n">
-        <v>15.84</v>
+        <v>2.1</v>
       </c>
       <c r="D18" t="n">
-        <v>16.5</v>
+        <v>2.1</v>
       </c>
       <c r="E18" t="n">
-        <v>4.19</v>
+        <v>0</v>
       </c>
       <c r="F18" t="n">
-        <v>-27.2</v>
+        <v>-24.8</v>
       </c>
       <c r="G18" t="n">
-        <v>-24.4</v>
+        <v>-24.8</v>
       </c>
       <c r="H18" t="n">
-        <v>2.8</v>
+        <v>0</v>
       </c>
       <c r="I18" t="inlineStr">
         <is>
@@ -1272,16 +1272,16 @@
         </is>
       </c>
       <c r="K18" t="n">
-        <v>13.36</v>
+        <v>2.15</v>
       </c>
       <c r="L18" t="n">
-        <v>13.87</v>
+        <v>2.15</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>MPCC</t>
+          <t>2343</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1290,22 +1290,22 @@
         </is>
       </c>
       <c r="C19" t="n">
-        <v>2.1</v>
+        <v>0.41</v>
       </c>
       <c r="D19" t="n">
-        <v>2.1</v>
+        <v>0.41</v>
       </c>
       <c r="E19" t="n">
-        <v>0</v>
+        <v>-1.89</v>
       </c>
       <c r="F19" t="n">
-        <v>-24.8</v>
+        <v>-28</v>
       </c>
       <c r="G19" t="n">
-        <v>-24.8</v>
+        <v>-29.2</v>
       </c>
       <c r="H19" t="n">
-        <v>0</v>
+        <v>-1.2</v>
       </c>
       <c r="I19" t="inlineStr">
         <is>
@@ -1318,16 +1318,16 @@
         </is>
       </c>
       <c r="K19" t="n">
-        <v>2.15</v>
+        <v>0.38</v>
       </c>
       <c r="L19" t="n">
-        <v>2.15</v>
+        <v>0.38</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>2343</t>
+          <t>HAFN</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -1336,22 +1336,22 @@
         </is>
       </c>
       <c r="C20" t="n">
-        <v>0.41</v>
+        <v>4.73</v>
       </c>
       <c r="D20" t="n">
-        <v>0.41</v>
+        <v>4.64</v>
       </c>
       <c r="E20" t="n">
-        <v>-1.89</v>
+        <v>-2.02</v>
       </c>
       <c r="F20" t="n">
-        <v>-28</v>
+        <v>-33</v>
       </c>
       <c r="G20" t="n">
-        <v>-29.2</v>
+        <v>-34</v>
       </c>
       <c r="H20" t="n">
-        <v>-1.2</v>
+        <v>-1.1</v>
       </c>
       <c r="I20" t="inlineStr">
         <is>
@@ -1364,16 +1364,16 @@
         </is>
       </c>
       <c r="K20" t="n">
-        <v>0.38</v>
+        <v>5.68</v>
       </c>
       <c r="L20" t="n">
-        <v>0.38</v>
+        <v>5.59</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>LPG</t>
+          <t>FRO</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -1382,22 +1382,22 @@
         </is>
       </c>
       <c r="C21" t="n">
-        <v>35.7</v>
+        <v>29.18</v>
       </c>
       <c r="D21" t="n">
-        <v>35.69</v>
+        <v>26.04</v>
       </c>
       <c r="E21" t="n">
-        <v>-0.04</v>
+        <v>-10.75</v>
       </c>
       <c r="F21" t="n">
+        <v>-29.3</v>
+      </c>
+      <c r="G21" t="n">
         <v>-36</v>
       </c>
-      <c r="G21" t="n">
-        <v>-36.1</v>
-      </c>
       <c r="H21" t="n">
-        <v>-0</v>
+        <v>-6.7</v>
       </c>
       <c r="I21" t="inlineStr">
         <is>
@@ -1410,16 +1410,16 @@
         </is>
       </c>
       <c r="K21" t="n">
-        <v>31.84</v>
+        <v>31.24</v>
       </c>
       <c r="L21" t="n">
-        <v>31.82</v>
+        <v>28.29</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>FRO</t>
+          <t>LPG</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -1428,22 +1428,22 @@
         </is>
       </c>
       <c r="C22" t="n">
-        <v>28.47</v>
+        <v>35.7</v>
       </c>
       <c r="D22" t="n">
-        <v>25.34</v>
+        <v>35.69</v>
       </c>
       <c r="E22" t="n">
-        <v>-11.01</v>
+        <v>-0.04</v>
       </c>
       <c r="F22" t="n">
-        <v>-30.4</v>
+        <v>-36</v>
       </c>
       <c r="G22" t="n">
-        <v>-37.1</v>
+        <v>-36.1</v>
       </c>
       <c r="H22" t="n">
-        <v>-6.7</v>
+        <v>-0</v>
       </c>
       <c r="I22" t="inlineStr">
         <is>
@@ -1456,10 +1456,10 @@
         </is>
       </c>
       <c r="K22" t="n">
-        <v>30.75</v>
+        <v>31.84</v>
       </c>
       <c r="L22" t="n">
-        <v>27.79</v>
+        <v>31.82</v>
       </c>
     </row>
     <row r="23">
@@ -1511,31 +1511,31 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>INSW</t>
+          <t>BWLP</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>WHOLE-COMPANY (hybrid aggregation)</t>
+          <t>whole-company</t>
         </is>
       </c>
       <c r="C24" t="n">
-        <v>58.55</v>
+        <v>15.84</v>
       </c>
       <c r="D24" t="n">
-        <v>54.64</v>
+        <v>15.83</v>
       </c>
       <c r="E24" t="n">
-        <v>-6.68</v>
+        <v>-0.06</v>
       </c>
       <c r="F24" t="n">
-        <v>-36.2</v>
+        <v>-39.6</v>
       </c>
       <c r="G24" t="n">
-        <v>-39.7</v>
+        <v>-39.6</v>
       </c>
       <c r="H24" t="n">
-        <v>-3.5</v>
+        <v>-0</v>
       </c>
       <c r="I24" t="inlineStr">
         <is>
@@ -1548,40 +1548,40 @@
         </is>
       </c>
       <c r="K24" t="n">
-        <v>63.03</v>
+        <v>14.53</v>
       </c>
       <c r="L24" t="n">
-        <v>59.59</v>
+        <v>14.52</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>BWLP</t>
+          <t>INSW</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>whole-company</t>
+          <t>WHOLE-COMPANY (hybrid aggregation)</t>
         </is>
       </c>
       <c r="C25" t="n">
-        <v>15.81</v>
+        <v>58.55</v>
       </c>
       <c r="D25" t="n">
-        <v>15.8</v>
+        <v>54.64</v>
       </c>
       <c r="E25" t="n">
-        <v>-0.07000000000000001</v>
+        <v>-6.68</v>
       </c>
       <c r="F25" t="n">
-        <v>-39.8</v>
+        <v>-36.2</v>
       </c>
       <c r="G25" t="n">
-        <v>-39.9</v>
+        <v>-39.7</v>
       </c>
       <c r="H25" t="n">
-        <v>-0</v>
+        <v>-3.5</v>
       </c>
       <c r="I25" t="inlineStr">
         <is>
@@ -1594,10 +1594,10 @@
         </is>
       </c>
       <c r="K25" t="n">
-        <v>14.47</v>
+        <v>63.03</v>
       </c>
       <c r="L25" t="n">
-        <v>14.46</v>
+        <v>59.59</v>
       </c>
     </row>
     <row r="26">
@@ -1612,22 +1612,22 @@
         </is>
       </c>
       <c r="C26" t="n">
-        <v>3.32</v>
+        <v>3.21</v>
       </c>
       <c r="D26" t="n">
-        <v>2.85</v>
+        <v>2.76</v>
       </c>
       <c r="E26" t="n">
-        <v>-14.2</v>
+        <v>-13.93</v>
       </c>
       <c r="F26" t="n">
-        <v>-48.7</v>
+        <v>-50.1</v>
       </c>
       <c r="G26" t="n">
-        <v>-54.7</v>
+        <v>-55.8</v>
       </c>
       <c r="H26" t="n">
-        <v>-6</v>
+        <v>-5.7</v>
       </c>
       <c r="I26" t="inlineStr">
         <is>
@@ -1640,10 +1640,10 @@
         </is>
       </c>
       <c r="K26" t="n">
-        <v>3.47</v>
+        <v>3.38</v>
       </c>
       <c r="L26" t="n">
-        <v>3.07</v>
+        <v>3</v>
       </c>
     </row>
   </sheetData>

--- a/outputs/transaction_anchor_comparison.xlsx
+++ b/outputs/transaction_anchor_comparison.xlsx
@@ -683,7 +683,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>BRUT</t>
+          <t>CAPT</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -692,22 +692,22 @@
         </is>
       </c>
       <c r="C6" t="n">
-        <v>4.92</v>
+        <v>17.51</v>
       </c>
       <c r="D6" t="n">
-        <v>4.92</v>
+        <v>17.32</v>
       </c>
       <c r="E6" t="n">
-        <v>0</v>
+        <v>-1.09</v>
       </c>
       <c r="F6" t="n">
-        <v>5.1</v>
+        <v>8.6</v>
       </c>
       <c r="G6" t="n">
-        <v>3.6</v>
+        <v>6.7</v>
       </c>
       <c r="H6" t="n">
-        <v>-1.5</v>
+        <v>-1.9</v>
       </c>
       <c r="I6" t="inlineStr">
         <is>
@@ -716,20 +716,20 @@
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>HOLD (fairly valued)</t>
+          <t>BUY (undervalued)</t>
         </is>
       </c>
       <c r="K6" t="n">
-        <v>5.19</v>
+        <v>17.88</v>
       </c>
       <c r="L6" t="n">
-        <v>5.12</v>
+        <v>17.56</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>STNG</t>
+          <t>BRUT</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -738,44 +738,44 @@
         </is>
       </c>
       <c r="C7" t="n">
-        <v>79.63</v>
+        <v>4.92</v>
       </c>
       <c r="D7" t="n">
-        <v>76.22</v>
+        <v>4.92</v>
       </c>
       <c r="E7" t="n">
-        <v>-4.28</v>
+        <v>0</v>
       </c>
       <c r="F7" t="n">
-        <v>2.4</v>
+        <v>5.1</v>
       </c>
       <c r="G7" t="n">
-        <v>-1.7</v>
+        <v>3.6</v>
       </c>
       <c r="H7" t="n">
-        <v>-4</v>
+        <v>-1.5</v>
       </c>
       <c r="I7" t="inlineStr">
         <is>
+          <t>BUY (undervalued)</t>
+        </is>
+      </c>
+      <c r="J7" t="inlineStr">
+        <is>
           <t>HOLD (fairly valued)</t>
         </is>
       </c>
-      <c r="J7" t="inlineStr">
-        <is>
-          <t>HOLD (fairly valued)</t>
-        </is>
-      </c>
       <c r="K7" t="n">
-        <v>79.88</v>
+        <v>5.19</v>
       </c>
       <c r="L7" t="n">
-        <v>76.73</v>
+        <v>5.12</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>CAPT</t>
+          <t>STNG</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -784,22 +784,22 @@
         </is>
       </c>
       <c r="C8" t="n">
-        <v>15.61</v>
+        <v>79.63</v>
       </c>
       <c r="D8" t="n">
-        <v>15.48</v>
+        <v>76.22</v>
       </c>
       <c r="E8" t="n">
-        <v>-0.8100000000000001</v>
+        <v>-4.28</v>
       </c>
       <c r="F8" t="n">
-        <v>-1.3</v>
+        <v>2.4</v>
       </c>
       <c r="G8" t="n">
-        <v>-2.7</v>
+        <v>-1.7</v>
       </c>
       <c r="H8" t="n">
-        <v>-1.4</v>
+        <v>-4</v>
       </c>
       <c r="I8" t="inlineStr">
         <is>
@@ -812,10 +812,10 @@
         </is>
       </c>
       <c r="K8" t="n">
-        <v>16.26</v>
+        <v>79.88</v>
       </c>
       <c r="L8" t="n">
-        <v>16.02</v>
+        <v>76.73</v>
       </c>
     </row>
     <row r="9">

--- a/outputs/transaction_anchor_comparison.xlsx
+++ b/outputs/transaction_anchor_comparison.xlsx
@@ -649,19 +649,19 @@
         <v>9.67</v>
       </c>
       <c r="D5" t="n">
-        <v>10.65</v>
+        <v>10.72</v>
       </c>
       <c r="E5" t="n">
-        <v>10.21</v>
+        <v>10.87</v>
       </c>
       <c r="F5" t="n">
-        <v>-2.1</v>
+        <v>-4.2</v>
       </c>
       <c r="G5" t="n">
-        <v>8.4</v>
+        <v>6.7</v>
       </c>
       <c r="H5" t="n">
-        <v>10.4</v>
+        <v>11</v>
       </c>
       <c r="I5" t="inlineStr">
         <is>
@@ -674,10 +674,10 @@
         </is>
       </c>
       <c r="K5" t="n">
-        <v>8.34</v>
+        <v>8.16</v>
       </c>
       <c r="L5" t="n">
-        <v>9.23</v>
+        <v>9.09</v>
       </c>
     </row>
     <row r="6">
@@ -879,19 +879,19 @@
         <v>31.44</v>
       </c>
       <c r="D10" t="n">
-        <v>32.2</v>
+        <v>32.6</v>
       </c>
       <c r="E10" t="n">
-        <v>2.41</v>
+        <v>3.68</v>
       </c>
       <c r="F10" t="n">
-        <v>-6.8</v>
+        <v>-7.9</v>
       </c>
       <c r="G10" t="n">
-        <v>-4.8</v>
+        <v>-4.9</v>
       </c>
       <c r="H10" t="n">
-        <v>1.9</v>
+        <v>3</v>
       </c>
       <c r="I10" t="inlineStr">
         <is>
@@ -904,10 +904,10 @@
         </is>
       </c>
       <c r="K10" t="n">
-        <v>19.13</v>
+        <v>18.9</v>
       </c>
       <c r="L10" t="n">
-        <v>19.53</v>
+        <v>19.51</v>
       </c>
     </row>
     <row r="11">
@@ -1017,19 +1017,19 @@
         <v>31.53</v>
       </c>
       <c r="D13" t="n">
-        <v>32.88</v>
+        <v>33.27</v>
       </c>
       <c r="E13" t="n">
-        <v>4.26</v>
+        <v>5.5</v>
       </c>
       <c r="F13" t="n">
-        <v>-9.199999999999999</v>
+        <v>-10.7</v>
       </c>
       <c r="G13" t="n">
-        <v>-5.7</v>
+        <v>-6.2</v>
       </c>
       <c r="H13" t="n">
-        <v>3.5</v>
+        <v>4.5</v>
       </c>
       <c r="I13" t="inlineStr">
         <is>
@@ -1042,10 +1042,10 @@
         </is>
       </c>
       <c r="K13" t="n">
-        <v>27.66</v>
+        <v>27.22</v>
       </c>
       <c r="L13" t="n">
-        <v>28.74</v>
+        <v>28.59</v>
       </c>
     </row>
     <row r="14">
@@ -1109,19 +1109,19 @@
         <v>24.77</v>
       </c>
       <c r="D15" t="n">
-        <v>25.12</v>
+        <v>25.37</v>
       </c>
       <c r="E15" t="n">
-        <v>1.42</v>
+        <v>2.45</v>
       </c>
       <c r="F15" t="n">
-        <v>-17.4</v>
+        <v>-18.9</v>
       </c>
       <c r="G15" t="n">
-        <v>-16.3</v>
+        <v>-17.1</v>
       </c>
       <c r="H15" t="n">
-        <v>1</v>
+        <v>1.8</v>
       </c>
       <c r="I15" t="inlineStr">
         <is>
@@ -1134,10 +1134,10 @@
         </is>
       </c>
       <c r="K15" t="n">
-        <v>21.39</v>
+        <v>20.99</v>
       </c>
       <c r="L15" t="n">
-        <v>21.66</v>
+        <v>21.45</v>
       </c>
     </row>
     <row r="16">
@@ -1189,31 +1189,31 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>CMBT</t>
+          <t>MPCC</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>WHOLE-COMPANY (hybrid aggregation)</t>
+          <t>whole-company</t>
         </is>
       </c>
       <c r="C17" t="n">
-        <v>15.84</v>
+        <v>2.1</v>
       </c>
       <c r="D17" t="n">
-        <v>16.5</v>
+        <v>2.1</v>
       </c>
       <c r="E17" t="n">
-        <v>4.19</v>
+        <v>0</v>
       </c>
       <c r="F17" t="n">
-        <v>-27.2</v>
+        <v>-24.8</v>
       </c>
       <c r="G17" t="n">
-        <v>-24.4</v>
+        <v>-24.8</v>
       </c>
       <c r="H17" t="n">
-        <v>2.8</v>
+        <v>0</v>
       </c>
       <c r="I17" t="inlineStr">
         <is>
@@ -1226,40 +1226,40 @@
         </is>
       </c>
       <c r="K17" t="n">
-        <v>13.36</v>
+        <v>2.15</v>
       </c>
       <c r="L17" t="n">
-        <v>13.87</v>
+        <v>2.15</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>MPCC</t>
+          <t>CMBT</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>whole-company</t>
+          <t>WHOLE-COMPANY (hybrid aggregation)</t>
         </is>
       </c>
       <c r="C18" t="n">
-        <v>2.1</v>
+        <v>15.84</v>
       </c>
       <c r="D18" t="n">
-        <v>2.1</v>
+        <v>16.54</v>
       </c>
       <c r="E18" t="n">
-        <v>0</v>
+        <v>4.4</v>
       </c>
       <c r="F18" t="n">
-        <v>-24.8</v>
+        <v>-28.6</v>
       </c>
       <c r="G18" t="n">
-        <v>-24.8</v>
+        <v>-25.7</v>
       </c>
       <c r="H18" t="n">
-        <v>0</v>
+        <v>2.9</v>
       </c>
       <c r="I18" t="inlineStr">
         <is>
@@ -1272,10 +1272,10 @@
         </is>
       </c>
       <c r="K18" t="n">
-        <v>2.15</v>
+        <v>13.1</v>
       </c>
       <c r="L18" t="n">
-        <v>2.15</v>
+        <v>13.63</v>
       </c>
     </row>
     <row r="19">
@@ -1296,16 +1296,16 @@
         <v>0.41</v>
       </c>
       <c r="E19" t="n">
-        <v>-1.89</v>
+        <v>-0.9399999999999999</v>
       </c>
       <c r="F19" t="n">
-        <v>-28</v>
+        <v>-28.9</v>
       </c>
       <c r="G19" t="n">
-        <v>-29.2</v>
+        <v>-29.4</v>
       </c>
       <c r="H19" t="n">
-        <v>-1.2</v>
+        <v>-0.6</v>
       </c>
       <c r="I19" t="inlineStr">
         <is>
